--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G201</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G201"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -5013,10 +5013,33 @@
         <v/>
       </c>
     </row>
+    <row r="201">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D201" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E201" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F201" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G201" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G200"/>
+  <autoFilter ref="A1:G201"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G201"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G207</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G207"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -490,19 +490,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C4" t="str">
-        <v>Security hardening</v>
+        <v>Organization profile</v>
       </c>
       <c r="D4" t="str">
-        <v>Image uploads accept real images only; query injection closed; secure cookies; allowed-origin list; statuses cannot be changed through generic saves. Two review passes (Jul and Sep 2026).</v>
+        <v>Settings ▸ Organization: upload the company logo and enter the company name (both required), legal name, GSTIN / PAN / IEC, address, phone, email, website and bank details. Used on the sidebar, login, browser tab, every PDF / print (quotes, dispatch and load copies, packing report, pallet and batch slips, invoices) and the shared pages. Change it any time.</v>
       </c>
       <c r="E4" t="str">
         <v>Completed</v>
       </c>
       <c r="F4" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G4" t="str">
-        <v>CR-205…207</v>
+        <v>CR-445</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C5" t="str">
-        <v>App shell</v>
+        <v>Security hardening</v>
       </c>
       <c r="D5" t="str">
-        <v>Sidebar grouped Dashboard · Inventory · Sales · Reports, filtered by role; global search; user menu; settings gear for admins.</v>
+        <v>Image uploads accept real images only; query injection closed; secure cookies; allowed-origin list; statuses cannot be changed through generic saves. Two review passes (Jul and Sep 2026).</v>
       </c>
       <c r="E5" t="str">
         <v>Completed</v>
@@ -525,7 +525,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>CR-205…207</v>
       </c>
     </row>
     <row r="6">
@@ -536,10 +536,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C6" t="str">
-        <v>Settings workspace</v>
+        <v>App shell</v>
       </c>
       <c r="D6" t="str">
-        <v>Two-pane page: Preferences, Masters, Users, Roles, Currencies, Data operations (admin repair tools).</v>
+        <v>Sidebar grouped Dashboard · Inventory · Sales · Reports, filtered by role; global search; user menu; settings gear for admins.</v>
       </c>
       <c r="E6" t="str">
         <v>Completed</v>
@@ -559,10 +559,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C7" t="str">
-        <v>House grid standard</v>
+        <v>Settings workspace</v>
       </c>
       <c r="D7" t="str">
-        <v>Every list: one-line rows, page footer, show / hide and reorder columns (applied on Apply), advanced search, newest first, click anywhere on a row to open it.</v>
+        <v>Two-pane page: Preferences, Masters, Users, Roles, Currencies, Data operations (admin repair tools).</v>
       </c>
       <c r="E7" t="str">
         <v>Completed</v>
@@ -582,10 +582,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C8" t="str">
-        <v>House form standard</v>
+        <v>House grid standard</v>
       </c>
       <c r="D8" t="str">
-        <v>Required fields marked; grey = calculated, white = you type; every pick list comes from the live masters; dates default to today; Sales Person defaults to the signed-in user; no negative numbers.</v>
+        <v>Every list: one-line rows, page footer, show / hide and reorder columns (applied on Apply), advanced search, newest first, click anywhere on a row to open it.</v>
       </c>
       <c r="E8" t="str">
         <v>Completed</v>
@@ -605,10 +605,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C9" t="str">
-        <v>Detail page standard + Clone</v>
+        <v>House form standard</v>
       </c>
       <c r="D9" t="str">
-        <v>One detail design everywhere; Edit and More top-right; every record can be cloned; after create / clone you land on the new record.</v>
+        <v>Required fields marked; grey = calculated, white = you type; every pick list comes from the live masters; dates default to today; Sales Person defaults to the signed-in user; no negative numbers.</v>
       </c>
       <c r="E9" t="str">
         <v>Completed</v>
@@ -628,10 +628,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C10" t="str">
-        <v>Create / edit forms are full pages</v>
+        <v>Detail page standard + Clone</v>
       </c>
       <c r="D10" t="str">
-        <v>Quote, Sales Order, Item, Pallet, Customer, Production, Palletization, Loading — pages, not pop-ups.</v>
+        <v>One detail design everywhere; Edit and More top-right; every record can be cloned; after create / clone you land on the new record.</v>
       </c>
       <c r="E10" t="str">
         <v>Completed</v>
@@ -640,7 +640,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G10" t="str">
-        <v>CR-219…222</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -651,10 +651,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C11" t="str">
-        <v>One visual language</v>
+        <v>Create / edit forms are full pages</v>
       </c>
       <c r="D11" t="str">
-        <v>Indigo / slate theme, one input skin, one button family, one font scale on every screen.</v>
+        <v>Quote, Sales Order, Item, Pallet, Customer, Production, Palletization, Loading — pages, not pop-ups.</v>
       </c>
       <c r="E11" t="str">
         <v>Completed</v>
@@ -663,7 +663,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>CR-219…222</v>
       </c>
     </row>
     <row r="12">
@@ -674,10 +674,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C12" t="str">
-        <v>Onboarding tours</v>
+        <v>One visual language</v>
       </c>
       <c r="D12" t="str">
-        <v>Welcome tour on first sign-in walks the business flow; Palletization and Loading have page guides; replayable from the user menu.</v>
+        <v>Indigo / slate theme, one input skin, one button family, one font scale on every screen.</v>
       </c>
       <c r="E12" t="str">
         <v>Completed</v>
@@ -686,7 +686,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G12" t="str">
-        <v>CR-158/159</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -697,10 +697,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C13" t="str">
-        <v>Public pages</v>
+        <v>Onboarding tours</v>
       </c>
       <c r="D13" t="str">
-        <v>Pallet QR scan page, batch QR slip page and item images open without sign-in via unguessable links.</v>
+        <v>Welcome tour on first sign-in walks the business flow; Palletization and Loading have page guides; replayable from the user menu.</v>
       </c>
       <c r="E13" t="str">
         <v>Completed</v>
@@ -709,7 +709,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>CR-158/159</v>
       </c>
     </row>
     <row r="14">
@@ -720,19 +720,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C14" t="str">
-        <v>Grids lead with Customer → Design</v>
+        <v>Public pages</v>
       </c>
       <c r="D14" t="str">
-        <v>Every list opens with Customer and Design (or item / name) first; system numbers (SO, Quote, PNL, PRD, TRF, CUS, SKU) hidden until ticked; customer PO stays visible; whole-row click everywhere.</v>
+        <v>Pallet QR scan page, batch QR slip page and item images open without sign-in via unguessable links.</v>
       </c>
       <c r="E14" t="str">
         <v>Completed</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-10-19</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G14" t="str">
-        <v>CR-355</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -743,19 +743,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C15" t="str">
-        <v>Staff default role</v>
+        <v>Grids lead with Customer → Design</v>
       </c>
       <c r="D15" t="str">
-        <v>New role Staff: view + create everything, never edit, delete or approve. Default for every new user. Server now enforces no-edit / no-delete on every route; maintenance routes Admin-only.</v>
+        <v>Every list opens with Customer and Design (or item / name) first; system numbers (SO, Quote, PNL, PRD, TRF, CUS, SKU) hidden until ticked; customer PO stays visible; whole-row click everywhere.</v>
       </c>
       <c r="E15" t="str">
         <v>Completed</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G15" t="str">
-        <v>CR-336</v>
+        <v>CR-355</v>
       </c>
     </row>
     <row r="16">
@@ -766,10 +766,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C16" t="str">
-        <v>Zoho-linked accounts</v>
+        <v>Staff default role</v>
       </c>
       <c r="D16" t="str">
-        <v>Settings ▸ Users shows how each account signs in (Zoho / Password / Both / None); password-less Zoho-only users; company email domains self-provision a Staff account on first Zoho sign-in.</v>
+        <v>New role Staff: view + create everything, never edit, delete or approve. Default for every new user. Server now enforces no-edit / no-delete on every route; maintenance routes Admin-only.</v>
       </c>
       <c r="E16" t="str">
         <v>Completed</v>
@@ -778,7 +778,7 @@
         <v>2026-10-13</v>
       </c>
       <c r="G16" t="str">
-        <v>CR-337</v>
+        <v>CR-336</v>
       </c>
     </row>
     <row r="17">
@@ -789,19 +789,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C17" t="str">
-        <v>Discard changes? Yes / No</v>
+        <v>Zoho-linked accounts</v>
       </c>
       <c r="D17" t="str">
-        <v>Leaving a form or edit mode with unsaved changes asks a plain Yes / No question on every screen (no more 'Delete' wording).</v>
+        <v>Settings ▸ Users shows how each account signs in (Zoho / Password / Both / None); password-less Zoho-only users; company email domains self-provision a Staff account on first Zoho sign-in.</v>
       </c>
       <c r="E17" t="str">
         <v>Completed</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G17" t="str">
-        <v>CR-268</v>
+        <v>CR-337</v>
       </c>
     </row>
     <row r="18">
@@ -812,10 +812,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C18" t="str">
-        <v>Delete asks why</v>
+        <v>Discard changes? Yes / No</v>
       </c>
       <c r="D18" t="str">
-        <v>Every delete asks for a reason first (Admin exempt); the reason is kept on the record's activity log and the server refuses a reason-less delete.</v>
+        <v>Leaving a form or edit mode with unsaved changes asks a plain Yes / No question on every screen (no more 'Delete' wording).</v>
       </c>
       <c r="E18" t="str">
         <v>Completed</v>
@@ -824,7 +824,7 @@
         <v>2026-10-03</v>
       </c>
       <c r="G18" t="str">
-        <v>CR-270</v>
+        <v>CR-268</v>
       </c>
     </row>
     <row r="19">
@@ -835,19 +835,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C19" t="str">
-        <v>Zoho Books-style form layout</v>
+        <v>Delete asks why</v>
       </c>
       <c r="D19" t="str">
-        <v>Every create / edit form page puts the label on the left and the control on the right, two fields per row; Customer on its own row with Billing | Shipping under it; tightened label gap, one-control-wide rows, three-line notes boxes.</v>
+        <v>Every delete asks for a reason first (Admin exempt); the reason is kept on the record's activity log and the server refuses a reason-less delete.</v>
       </c>
       <c r="E19" t="str">
         <v>Completed</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-10-06</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G19" t="str">
-        <v>CR-275, CR-277</v>
+        <v>CR-270</v>
       </c>
     </row>
     <row r="20">
@@ -858,19 +858,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C20" t="str">
-        <v>Clear / None option on every pick list</v>
+        <v>Zoho Books-style form layout</v>
       </c>
       <c r="D20" t="str">
-        <v>A way to clear a chosen value on every dropdown in the app.</v>
+        <v>Every create / edit form page puts the label on the left and the control on the right, two fields per row; Customer on its own row with Billing | Shipping under it; tightened label gap, one-control-wide rows, three-line notes boxes.</v>
       </c>
       <c r="E20" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>2026-10-06</v>
       </c>
       <c r="G20" t="str">
-        <v>CR-069</v>
+        <v>CR-275, CR-277</v>
       </c>
     </row>
     <row r="21">
@@ -881,10 +881,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C21" t="str">
-        <v>Pick-list keyboard navigation</v>
+        <v>Clear / None option on every pick list</v>
       </c>
       <c r="D21" t="str">
-        <v>Arrow keys move, Enter / Space selects, on every dropdown — to be verified and completed across all screens.</v>
+        <v>A way to clear a chosen value on every dropdown in the app.</v>
       </c>
       <c r="E21" t="str">
         <v>Future</v>
@@ -893,7 +893,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>CR-009</v>
+        <v>CR-069</v>
       </c>
     </row>
     <row r="22">
@@ -904,10 +904,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C22" t="str">
-        <v>Hosting platform upgrade</v>
+        <v>Pick-list keyboard navigation</v>
       </c>
       <c r="D22" t="str">
-        <v>Move the app to the newer hosting platform (same app, same data; faster page loads). Planned, not started.</v>
+        <v>Arrow keys move, Enter / Space selects, on every dropdown — to be verified and completed across all screens.</v>
       </c>
       <c r="E22" t="str">
         <v>Future</v>
@@ -916,7 +916,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>CR-009</v>
       </c>
     </row>
     <row r="23">
@@ -924,19 +924,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C23" t="str">
-        <v>Items (Design Master)</v>
+        <v>Hosting platform upgrade</v>
       </c>
       <c r="D23" t="str">
-        <v>One record per sellable tile: name, SKU, size, finish, category, glaze, grade, brand, images (gallery + lightbox), per-box weight with per-piece / per-m² helpers, batch-tracked flag, Active / Inactive. Item detail shows stock, production and orders.</v>
+        <v>Move the app to the newer hosting platform (same app, same data; faster page loads). Planned, not started.</v>
       </c>
       <c r="E23" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F23" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -950,19 +950,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C24" t="str">
-        <v>Design Master to the new spec</v>
+        <v>Items (Design Master)</v>
       </c>
       <c r="D24" t="str">
-        <v>Item form in five sections (Main Information · Calculations · Design Data · Working Data · Marketing Data) with the image on the form; Pcs Per Packing typed per item and coverage from the item's own numbers (a Size edit no longer rewrites them); Design Owner and Custom Design Buyer as customers (default owner in Settings); the buyer's brands offered as Customer Brand; Base Design picked from existing items; new lookups Surface Application, Punch Type (with image), Series, Catalogue.</v>
+        <v>One record per sellable tile: name, SKU, size, finish, category, glaze, grade, brand, images (gallery + lightbox), per-box weight with per-piece / per-m² helpers, batch-tracked flag, Active / Inactive. Item detail shows stock, production and orders.</v>
       </c>
       <c r="E24" t="str">
         <v>Completed</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-10-23</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G24" t="str">
-        <v>CR-391…396</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -973,19 +973,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C25" t="str">
-        <v>Opening stock with lock</v>
+        <v>Design Master to the new spec</v>
       </c>
       <c r="D25" t="str">
-        <v>Entered once per item (per batch for batch-tracked items); locks after first save; Admin can re-open with a reason written to the audit log.</v>
+        <v>Item form in five sections (Main Information · Calculations · Design Data · Working Data · Marketing Data) with the image on the form; Pcs Per Packing typed per item and coverage from the item's own numbers (a Size edit no longer rewrites them); Design Owner and Custom Design Buyer as customers (default owner in Settings); the buyer's brands offered as Customer Brand; Base Design picked from existing items; new lookups Surface Application, Punch Type (with image), Series, Catalogue.</v>
       </c>
       <c r="E25" t="str">
         <v>Completed</v>
       </c>
       <c r="F25" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-23</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>CR-391…396</v>
       </c>
     </row>
     <row r="26">
@@ -996,10 +996,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C26" t="str">
-        <v>Size Master with packing defaults</v>
+        <v>Opening stock with lock</v>
       </c>
       <c r="D26" t="str">
-        <v>Dimensions, pieces per box, coverage m² / ft², box weight. Pallet formats snapshot the size; items take the dimensions and start their own pieces per box and box weight from it. Editing a size fans the defaults out (typed item values are kept).</v>
+        <v>Entered once per item (per batch for batch-tracked items); locks after first save; Admin can re-open with a reason written to the audit log.</v>
       </c>
       <c r="E26" t="str">
         <v>Completed</v>
@@ -1008,7 +1008,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G26" t="str">
-        <v>CR-391</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1019,10 +1019,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C27" t="str">
-        <v>Pallet Master</v>
+        <v>Size Master with packing defaults</v>
       </c>
       <c r="D27" t="str">
-        <v>Pallet formats: boxes per pallet, empty and loaded pallet weight, which size they fit. Pick lists offer the formats matching the item's size. Boxes-only since Phase 2 (container capacity moved to Container Master).</v>
+        <v>Dimensions, pieces per box, coverage m² / ft², box weight. Pallet formats snapshot the size; items take the dimensions and start their own pieces per box and box weight from it. Editing a size fans the defaults out (typed item values are kept).</v>
       </c>
       <c r="E27" t="str">
         <v>Completed</v>
@@ -1031,7 +1031,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G27" t="str">
-        <v>CR-261</v>
+        <v>CR-391</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1042,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C28" t="str">
-        <v>Stock Details</v>
+        <v>Pallet Master</v>
       </c>
       <c r="D28" t="str">
-        <v>Batch-wise on-hand per item.</v>
+        <v>Pallet formats: boxes per pallet, empty and loaded pallet weight, which size they fit. Pick lists offer the formats matching the item's size. Boxes-only since Phase 2 (container capacity moved to Container Master).</v>
       </c>
       <c r="E28" t="str">
         <v>Completed</v>
@@ -1054,7 +1054,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>CR-261</v>
       </c>
     </row>
     <row r="29">
@@ -1065,10 +1065,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C29" t="str">
-        <v>Lookups</v>
+        <v>Stock Details</v>
       </c>
       <c r="D29" t="str">
-        <v>Brand (with logo on forms), Grade, Finish, Category, Glaze, Payment terms, Currency with exchange rate, Vehicle (kept in sync from typed numbers), Container sizes, Organization, document number series.</v>
+        <v>Batch-wise on-hand per item.</v>
       </c>
       <c r="E29" t="str">
         <v>Completed</v>
@@ -1088,19 +1088,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C30" t="str">
-        <v>Container Master</v>
+        <v>Lookups</v>
       </c>
       <c r="D30" t="str">
-        <v>New master: what one container of a size holds — pallet formats as lines (format × how many), totals follow; several containers per size; auto-name shows the pallet maths, e.g. 800x1600 - GVT - 2 · [(48*10) + (10*6)] = 540 boxes. Grid, form page, detail with Clone / Delete, activity.</v>
+        <v>Brand (with logo on forms), Grade, Finish, Category, Glaze, Payment terms, Currency with exchange rate, Vehicle (kept in sync from typed numbers), Container sizes, Organization, document number series.</v>
       </c>
       <c r="E30" t="str">
         <v>Completed</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G30" t="str">
-        <v>CR-261, 269, 273, 292</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1111,19 +1111,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C31" t="str">
-        <v>Capacity comes from the Container Master</v>
+        <v>Container Master</v>
       </c>
       <c r="D31" t="str">
-        <v>Fill % on loading and palletization and the planner's box fitting use the size's container; a size with no container shows no fill % and says so.</v>
+        <v>New master: what one container of a size holds — pallet formats as lines (format × how many), totals follow; several containers per size; auto-name shows the pallet maths, e.g. 800x1600 - GVT - 2 · [(48*10) + (10*6)] = 540 boxes. Grid, form page, detail with Clone / Delete, activity.</v>
       </c>
       <c r="E31" t="str">
         <v>Completed</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G31" t="str">
-        <v>CR-261</v>
+        <v>CR-261, 269, 273, 292</v>
       </c>
     </row>
     <row r="32">
@@ -1134,19 +1134,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C32" t="str">
-        <v>Warehouse master</v>
+        <v>Capacity comes from the Container Master</v>
       </c>
       <c r="D32" t="str">
-        <v>Settings ▸ Warehouses: name, Primary ★, purposes (Production · Palletization · Loading Bay · Raw Material · Sample Cut Panels), note. Primary and any warehouse with history cannot be deleted.</v>
+        <v>Fill % on loading and palletization and the planner's box fitting use the size's container; a size with no container shows no fill % and says so.</v>
       </c>
       <c r="E32" t="str">
         <v>Completed</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G32" t="str">
-        <v>CR-329</v>
+        <v>CR-261</v>
       </c>
     </row>
     <row r="33">
@@ -1157,19 +1157,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C33" t="str">
-        <v>Add a new container from where it is needed</v>
+        <v>Warehouse master</v>
       </c>
       <c r="D33" t="str">
-        <v>Create a Container Master record without leaving the loading / planning screen. Scope to be confirmed.</v>
+        <v>Settings ▸ Warehouses: name, Primary ★, purposes (Production · Palletization · Loading Bay · Raw Material · Sample Cut Panels), note. Primary and any warehouse with history cannot be deleted.</v>
       </c>
       <c r="E33" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>2026-10-12</v>
       </c>
       <c r="G33" t="str">
-        <v>Panel Craft list #10</v>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="34">
@@ -1180,10 +1180,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C34" t="str">
-        <v>Container master naming</v>
+        <v>Add a new container from where it is needed</v>
       </c>
       <c r="D34" t="str">
-        <v>Naming / login rule for container records. Requirement to be clarified.</v>
+        <v>Create a Container Master record without leaving the loading / planning screen. Scope to be confirmed.</v>
       </c>
       <c r="E34" t="str">
         <v>Future</v>
@@ -1192,7 +1192,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>Panel Craft list #11</v>
+        <v>Panel Craft list #10</v>
       </c>
     </row>
     <row r="35">
@@ -1203,10 +1203,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C35" t="str">
-        <v>Pallet size as length × width</v>
+        <v>Container master naming</v>
       </c>
       <c r="D35" t="str">
-        <v>New Pallet form takes length and width instead of one size field.</v>
+        <v>Naming / login rule for container records. Requirement to be clarified.</v>
       </c>
       <c r="E35" t="str">
         <v>Future</v>
@@ -1215,7 +1215,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>CR-101</v>
+        <v>Panel Craft list #11</v>
       </c>
     </row>
     <row r="36">
@@ -1226,10 +1226,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C36" t="str">
-        <v>Readable SKU</v>
+        <v>Pallet size as length × width</v>
       </c>
       <c r="D36" t="str">
-        <v>Acronym-based SKU built from each master's short code (decisions agreed, not built).</v>
+        <v>New Pallet form takes length and width instead of one size field.</v>
       </c>
       <c r="E36" t="str">
         <v>Future</v>
@@ -1238,7 +1238,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>CR-015</v>
+        <v>CR-101</v>
       </c>
     </row>
     <row r="37">
@@ -1246,22 +1246,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Customers</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C37" t="str">
-        <v>Customer master (full page)</v>
+        <v>Readable SKU</v>
       </c>
       <c r="D37" t="str">
-        <v>Code, name, contacts, billing and shipping addresses side by side, country, currency, payment terms, default Box Brand, sales person, brand.</v>
+        <v>Acronym-based SKU built from each master's short code (decisions agreed, not built).</v>
       </c>
       <c r="E37" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F37" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>CR-015</v>
       </c>
     </row>
     <row r="38">
@@ -1272,19 +1272,19 @@
         <v>Customers</v>
       </c>
       <c r="C38" t="str">
-        <v>Customer Brands</v>
+        <v>Customer master (full page)</v>
       </c>
       <c r="D38" t="str">
-        <v>Several brand names per customer on the Customer detail (add / delete); the Item form offers them as the buyer's Customer Brand.</v>
+        <v>Code, name, contacts, billing and shipping addresses side by side, country, currency, payment terms, default Box Brand, sales person, brand.</v>
       </c>
       <c r="E38" t="str">
         <v>Completed</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-10-23</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G38" t="str">
-        <v>CR-393</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1295,19 +1295,19 @@
         <v>Customers</v>
       </c>
       <c r="C39" t="str">
-        <v>Customer detail</v>
+        <v>Customer Brands</v>
       </c>
       <c r="D39" t="str">
-        <v>Quotes, sales orders and dispatches for that customer in one place; Showcase Panels and Customer Samples sections.</v>
+        <v>Several brand names per customer on the Customer detail (add / delete); the Item form offers them as the buyer's Customer Brand.</v>
       </c>
       <c r="E39" t="str">
         <v>Completed</v>
       </c>
       <c r="F39" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-23</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>CR-393</v>
       </c>
     </row>
     <row r="40">
@@ -1318,10 +1318,10 @@
         <v>Customers</v>
       </c>
       <c r="C40" t="str">
-        <v>Transactions inherit customer fields</v>
+        <v>Customer detail</v>
       </c>
       <c r="D40" t="str">
-        <v>Every quote and order fills currency, terms, addresses, brand and box brand from the customer on pick — nothing retyped.</v>
+        <v>Quotes, sales orders and dispatches for that customer in one place; Showcase Panels and Customer Samples sections.</v>
       </c>
       <c r="E40" t="str">
         <v>Completed</v>
@@ -1341,19 +1341,19 @@
         <v>Customers</v>
       </c>
       <c r="C41" t="str">
-        <v>Sign in with Zoho</v>
+        <v>Transactions inherit customer fields</v>
       </c>
       <c r="D41" t="str">
-        <v>Login page leads with a Zoho button; password form stays as fallback; only existing active app users get in; roles stay Admin-controlled.</v>
+        <v>Every quote and order fills currency, terms, addresses, brand and box brand from the customer on pick — nothing retyped.</v>
       </c>
       <c r="E41" t="str">
         <v>Completed</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G41" t="str">
-        <v>CR-324</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1364,19 +1364,19 @@
         <v>Customers</v>
       </c>
       <c r="C42" t="str">
-        <v>Zoho CRM Accounts as the customer source</v>
+        <v>Sign in with Zoho</v>
       </c>
       <c r="D42" t="str">
-        <v>Changes arrive via webhook / scheduled pull; Import all once; Create in / Push to Zoho CRM from the customer; From Zoho CRM on the Customers page; Map / Re-pull / Unmap by hand. Contact persons from CRM Contacts; GSTIN, PAN, GST treatment, Place of Supply, Credit Limit, Payment Term picked up automatically.</v>
+        <v>Login page leads with a Zoho button; password form stays as fallback; only existing active app users get in; roles stay Admin-controlled.</v>
       </c>
       <c r="E42" t="str">
         <v>Completed</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G42" t="str">
-        <v>CR-359</v>
+        <v>CR-324</v>
       </c>
     </row>
     <row r="43">
@@ -1387,10 +1387,10 @@
         <v>Customers</v>
       </c>
       <c r="C43" t="str">
-        <v>Zoho Books customer sync (built, switched off)</v>
+        <v>Zoho CRM Accounts as the customer source</v>
       </c>
       <c r="D43" t="str">
-        <v>Two-way customer sync with Zoho Books (event-driven pull, Import all, Push) and the Books tax / credit / notes fields on the customer. Hidden since the switch to CRM at the customer's request; data kept.</v>
+        <v>Changes arrive via webhook / scheduled pull; Import all once; Create in / Push to Zoho CRM from the customer; From Zoho CRM on the Customers page; Map / Re-pull / Unmap by hand. Contact persons from CRM Contacts; GSTIN, PAN, GST treatment, Place of Supply, Credit Limit, Payment Term picked up automatically.</v>
       </c>
       <c r="E43" t="str">
         <v>Completed</v>
@@ -1399,7 +1399,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G43" t="str">
-        <v>CR-325, 356, 358</v>
+        <v>CR-359</v>
       </c>
     </row>
     <row r="44">
@@ -1410,10 +1410,10 @@
         <v>Customers</v>
       </c>
       <c r="C44" t="str">
-        <v>Zoho link status per customer</v>
+        <v>Zoho Books customer sync (built, switched off)</v>
       </c>
       <c r="D44" t="str">
-        <v>Customers grid column Zoho: CRM &amp; Books / CRM only / Books only; customer page spells it out with both ids; advanced filter takes the states; token handling fixed so the status fills for every synced customer.</v>
+        <v>Two-way customer sync with Zoho Books (event-driven pull, Import all, Push) and the Books tax / credit / notes fields on the customer. Hidden since the switch to CRM at the customer's request; data kept.</v>
       </c>
       <c r="E44" t="str">
         <v>Completed</v>
@@ -1422,7 +1422,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G44" t="str">
-        <v>CR-362, 363</v>
+        <v>CR-325, 356, 358</v>
       </c>
     </row>
     <row r="45">
@@ -1433,19 +1433,19 @@
         <v>Customers</v>
       </c>
       <c r="C45" t="str">
-        <v>Sync never creates a twin; duplicate names are an error</v>
+        <v>Zoho link status per customer</v>
       </c>
       <c r="D45" t="str">
-        <v>The existing-customer lookup reads every customer; a CRM account whose name already belongs to another linked customer is reported as a duplicate and not created; CRM comes first.</v>
+        <v>Customers grid column Zoho: CRM &amp; Books / CRM only / Books only; customer page spells it out with both ids; advanced filter takes the states; token handling fixed so the status fills for every synced customer.</v>
       </c>
       <c r="E45" t="str">
         <v>Completed</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G45" t="str">
-        <v>CR-372</v>
+        <v>CR-362, 363</v>
       </c>
     </row>
     <row r="46">
@@ -1456,10 +1456,10 @@
         <v>Customers</v>
       </c>
       <c r="C46" t="str">
-        <v>Duplicate customers card</v>
+        <v>Sync never creates a twin; duplicate names are an error</v>
       </c>
       <c r="D46" t="str">
-        <v>Settings ▸ Zoho CRM ▸ Duplicate customers: Find duplicates → Merge N duplicates (quotes, orders, panel and sample orders move to the surviving customer; reused codes renewed). Import all refuses to run while duplicates exist.</v>
+        <v>The existing-customer lookup reads every customer; a CRM account whose name already belongs to another linked customer is reported as a duplicate and not created; CRM comes first.</v>
       </c>
       <c r="E46" t="str">
         <v>Completed</v>
@@ -1468,7 +1468,7 @@
         <v>2026-10-22</v>
       </c>
       <c r="G46" t="str">
-        <v>CR-373</v>
+        <v>CR-372</v>
       </c>
     </row>
     <row r="47">
@@ -1479,19 +1479,19 @@
         <v>Customers</v>
       </c>
       <c r="C47" t="str">
-        <v>Zoho item reference</v>
+        <v>Duplicate customers card</v>
       </c>
       <c r="D47" t="str">
-        <v>Link items to the Zoho item master. Blocked — reference layout never supplied.</v>
+        <v>Settings ▸ Zoho CRM ▸ Duplicate customers: Find duplicates → Merge N duplicates (quotes, orders, panel and sample orders move to the surviving customer; reused codes renewed). Import all refuses to run while duplicates exist.</v>
       </c>
       <c r="E47" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>2026-10-22</v>
       </c>
       <c r="G47" t="str">
-        <v>CR-013.2</v>
+        <v>CR-373</v>
       </c>
     </row>
     <row r="48">
@@ -1499,22 +1499,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Quotes &amp; Approvals</v>
+        <v>Customers</v>
       </c>
       <c r="C48" t="str">
-        <v>Quote form (create / edit / clone)</v>
+        <v>Zoho item reference</v>
       </c>
       <c r="D48" t="str">
-        <v>Customer, currency (INR default, any currency with the day's rate), payment terms, box brand, lines item · size · boxes · rate; totals in document currency and INR.</v>
+        <v>Link items to the Zoho item master. Blocked — reference layout never supplied.</v>
       </c>
       <c r="E48" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F48" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>CR-013.2</v>
       </c>
     </row>
     <row r="49">
@@ -1525,10 +1525,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C49" t="str">
-        <v>Grouped by design</v>
+        <v>Quote form (create / edit / clone)</v>
       </c>
       <c r="D49" t="str">
-        <v>On screen, in print and in the PDF, with per-design subtotals.</v>
+        <v>Customer, currency (INR default, any currency with the day's rate), payment terms, box brand, lines item · size · boxes · rate; totals in document currency and INR.</v>
       </c>
       <c r="E49" t="str">
         <v>Completed</v>
@@ -1548,10 +1548,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C50" t="str">
-        <v>PDF and public share link</v>
+        <v>Grouped by design</v>
       </c>
       <c r="D50" t="str">
-        <v>Customer-facing PDF and an unguessable share link.</v>
+        <v>On screen, in print and in the PDF, with per-design subtotals.</v>
       </c>
       <c r="E50" t="str">
         <v>Completed</v>
@@ -1571,10 +1571,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C51" t="str">
-        <v>Container planning on the quote</v>
+        <v>PDF and public share link</v>
       </c>
       <c r="D51" t="str">
-        <v>Plan quoted boxes into containers in Box Fitting or Weight Fitting mode; move boxes between containers; fractional fill for mixed containers; optimiser respects pallet slots, area, weight and box caps.</v>
+        <v>Customer-facing PDF and an unguessable share link.</v>
       </c>
       <c r="E51" t="str">
         <v>Completed</v>
@@ -1594,10 +1594,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C52" t="str">
-        <v>Approvals page</v>
+        <v>Container planning on the quote</v>
       </c>
       <c r="D52" t="str">
-        <v>Approve or reject with a reason; sales person notified; an approver's own quotes are born Approved. Lifecycle Draft → Pending approval → Approved → Sent → Accepted → Converted.</v>
+        <v>Plan quoted boxes into containers in Box Fitting or Weight Fitting mode; move boxes between containers; fractional fill for mixed containers; optimiser respects pallet slots, area, weight and box caps.</v>
       </c>
       <c r="E52" t="str">
         <v>Completed</v>
@@ -1617,10 +1617,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C53" t="str">
-        <v>Quote aging report</v>
+        <v>Approvals page</v>
       </c>
       <c r="D53" t="str">
-        <v>Shows where quotes are stuck.</v>
+        <v>Approve or reject with a reason; sales person notified; an approver's own quotes are born Approved. Lifecycle Draft → Pending approval → Approved → Sent → Accepted → Converted.</v>
       </c>
       <c r="E53" t="str">
         <v>Completed</v>
@@ -1640,19 +1640,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C54" t="str">
-        <v>Suitable Containers panel</v>
+        <v>Quote aging report</v>
       </c>
       <c r="D54" t="str">
-        <v>Per size on the quote: the container it fits, boxes quoted, containers needed and how full the last one is (on screen).</v>
+        <v>Shows where quotes are stuck.</v>
       </c>
       <c r="E54" t="str">
         <v>Completed</v>
       </c>
       <c r="F54" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G54" t="str">
-        <v>CR-262</v>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -1663,19 +1663,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C55" t="str">
-        <v>Planner picks the container per item row</v>
+        <v>Suitable Containers panel</v>
       </c>
       <c r="D55" t="str">
-        <v>A Container column on every planner row lists the containers of that size built from the chosen pallet; default the largest; saved with the plan; a loading made from the plan starts on it.</v>
+        <v>Per size on the quote: the container it fits, boxes quoted, containers needed and how full the last one is (on screen).</v>
       </c>
       <c r="E55" t="str">
         <v>Completed</v>
       </c>
       <c r="F55" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G55" t="str">
-        <v>CR-274, 300</v>
+        <v>CR-262</v>
       </c>
     </row>
     <row r="56">
@@ -1686,19 +1686,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C56" t="str">
-        <v>Customer search modal</v>
+        <v>Planner picks the container per item row</v>
       </c>
       <c r="D56" t="str">
-        <v>Magnifier beside the Customer field on Quote, Sales Order and New Palletization opens a searchable customer table; dropdown shows code · country.</v>
+        <v>A Container column on every planner row lists the containers of that size built from the chosen pallet; default the largest; saved with the plan; a loading made from the plan starts on it.</v>
       </c>
       <c r="E56" t="str">
         <v>Completed</v>
       </c>
       <c r="F56" t="str">
-        <v>2026-10-06</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G56" t="str">
-        <v>CR-276</v>
+        <v>CR-274, 300</v>
       </c>
     </row>
     <row r="57">
@@ -1709,19 +1709,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C57" t="str">
-        <v>Suitable Containers on print / PDF / share link</v>
+        <v>Customer search modal</v>
       </c>
       <c r="D57" t="str">
-        <v>Carry the on-screen Suitable Containers panel onto the printed quote, PDF and share link.</v>
+        <v>Magnifier beside the Customer field on Quote, Sales Order and New Palletization opens a searchable customer table; dropdown shows code · country.</v>
       </c>
       <c r="E57" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>2026-10-06</v>
       </c>
       <c r="G57" t="str">
-        <v>CR-262 follow-up</v>
+        <v>CR-276</v>
       </c>
     </row>
     <row r="58">
@@ -1732,10 +1732,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C58" t="str">
-        <v>Weight fitting from the container's max weight</v>
+        <v>Suitable Containers on print / PDF / share link</v>
       </c>
       <c r="D58" t="str">
-        <v>Planner uses the container's own weight limit instead of a typed tonnage.</v>
+        <v>Carry the on-screen Suitable Containers panel onto the printed quote, PDF and share link.</v>
       </c>
       <c r="E58" t="str">
         <v>Future</v>
@@ -1744,7 +1744,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v/>
+        <v>CR-262 follow-up</v>
       </c>
     </row>
     <row r="59">
@@ -1755,10 +1755,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C59" t="str">
-        <v>Qty total on screen and on the printed quote</v>
+        <v>Weight fitting from the container's max weight</v>
       </c>
       <c r="D59" t="str">
-        <v>Box total shown on the quote and in print / PDF.</v>
+        <v>Planner uses the container's own weight limit instead of a typed tonnage.</v>
       </c>
       <c r="E59" t="str">
         <v>Future</v>
@@ -1767,7 +1767,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>CR-079</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -1778,10 +1778,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C60" t="str">
-        <v>Collapse long remarks / terms</v>
+        <v>Qty total on screen and on the printed quote</v>
       </c>
       <c r="D60" t="str">
-        <v>Long remarks and terms fold behind 'view more' so the page does not stretch.</v>
+        <v>Box total shown on the quote and in print / PDF.</v>
       </c>
       <c r="E60" t="str">
         <v>Future</v>
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>CR-088</v>
+        <v>CR-079</v>
       </c>
     </row>
     <row r="61">
@@ -1798,22 +1798,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Sales Orders</v>
+        <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C61" t="str">
-        <v>Convert to Sales Order</v>
+        <v>Collapse long remarks / terms</v>
       </c>
       <c r="D61" t="str">
-        <v>From an Accepted quote, full or partial (quote becomes Partially converted and can be converted again); the quote's container plan is copied and the order owns its editable copy.</v>
+        <v>Long remarks and terms fold behind 'view more' so the page does not stretch.</v>
       </c>
       <c r="E61" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F61" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>CR-088</v>
       </c>
     </row>
     <row r="62">
@@ -1824,10 +1824,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C62" t="str">
-        <v>Sales Order form (page)</v>
+        <v>Convert to Sales Order</v>
       </c>
       <c r="D62" t="str">
-        <v>Same layout family as the quote; PO number; editable after work has started (a line with pallets or loads keeps its item and cannot drop below what was done).</v>
+        <v>From an Accepted quote, full or partial (quote becomes Partially converted and can be converted again); the quote's container plan is copied and the order owns its editable copy.</v>
       </c>
       <c r="E62" t="str">
         <v>Completed</v>
@@ -1847,10 +1847,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C63" t="str">
-        <v>Allocate Stock</v>
+        <v>Sales Order form (page)</v>
       </c>
       <c r="D63" t="str">
-        <v>Hand free boxes of chosen batches to an order line (one flat table item → batch rows, with search). Allocation is a claim, not a movement.</v>
+        <v>Same layout family as the quote; PO number; editable after work has started (a line with pallets or loads keeps its item and cannot drop below what was done).</v>
       </c>
       <c r="E63" t="str">
         <v>Completed</v>
@@ -1859,7 +1859,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G63" t="str">
-        <v>CR-194…200</v>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -1870,10 +1870,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C64" t="str">
-        <v>Status = order lifecycle; Palletization / Loading progress separate</v>
+        <v>Allocate Stock</v>
       </c>
       <c r="D64" t="str">
-        <v>Draft → Pending approval → Confirmed → In progress → Partially completed → Completed, rolled up from dispatched vs ordered. Palletization and Loading progress are their own columns / fields. Admin override with reason.</v>
+        <v>Hand free boxes of chosen batches to an order line (one flat table item → batch rows, with search). Allocation is a claim, not a movement.</v>
       </c>
       <c r="E64" t="str">
         <v>Completed</v>
@@ -1882,7 +1882,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G64" t="str">
-        <v>CR-230…233</v>
+        <v>CR-194…200</v>
       </c>
     </row>
     <row r="65">
@@ -1893,10 +1893,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C65" t="str">
-        <v>Order detail tabs and actions</v>
+        <v>Status = order lifecycle; Palletization / Loading progress separate</v>
       </c>
       <c r="D65" t="str">
-        <v>Items (ordered · allocated · palletized · loaded · dispatched per line), Palletization, Dispatch, Activity; Send to Palletization, New Loading, Allocate Stock, Containerise, Clone.</v>
+        <v>Draft → Pending approval → Confirmed → In progress → Partially completed → Completed, rolled up from dispatched vs ordered. Palletization and Loading progress are their own columns / fields. Admin override with reason.</v>
       </c>
       <c r="E65" t="str">
         <v>Completed</v>
@@ -1905,7 +1905,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>CR-230…233</v>
       </c>
     </row>
     <row r="66">
@@ -1916,10 +1916,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C66" t="str">
-        <v>Orders grid, By-order view, Kanban pipeline</v>
+        <v>Order detail tabs and actions</v>
       </c>
       <c r="D66" t="str">
-        <v>Three views over the same data.</v>
+        <v>Items (ordered · allocated · palletized · loaded · dispatched per line), Palletization, Dispatch, Activity; Send to Palletization, New Loading, Allocate Stock, Containerise, Clone.</v>
       </c>
       <c r="E66" t="str">
         <v>Completed</v>
@@ -1939,19 +1939,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C67" t="str">
-        <v>Remaining, totals and Deallocate Stock</v>
+        <v>Orders grid, By-order view, Kanban pipeline</v>
       </c>
       <c r="D67" t="str">
-        <v>Items table shows Remaining = Ordered − Allocated and a totals row; ✕ per allocated line returns boxes to free stock unless already palletized; partial deallocate ('5 of 520'); Allocate / Deallocate buttons always visible with the reason when greyed.</v>
+        <v>Three views over the same data.</v>
       </c>
       <c r="E67" t="str">
         <v>Completed</v>
       </c>
       <c r="F67" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G67" t="str">
-        <v>CR-263, 297</v>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -1962,10 +1962,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C68" t="str">
-        <v>Item STOCK card itemises on-hand</v>
+        <v>Remaining, totals and Deallocate Stock</v>
       </c>
       <c r="D68" t="str">
-        <v>Awaiting palletization row between In production and In loading, each with per-order drill-down, so Available adds up on screen.</v>
+        <v>Items table shows Remaining = Ordered − Allocated and a totals row; ✕ per allocated line returns boxes to free stock unless already palletized; partial deallocate ('5 of 520'); Allocate / Deallocate buttons always visible with the reason when greyed.</v>
       </c>
       <c r="E68" t="str">
         <v>Completed</v>
@@ -1974,7 +1974,7 @@
         <v>2026-10-07</v>
       </c>
       <c r="G68" t="str">
-        <v>CR-298</v>
+        <v>CR-263, 297</v>
       </c>
     </row>
     <row r="69">
@@ -1985,19 +1985,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C69" t="str">
-        <v>A worked order cannot be deleted</v>
+        <v>Item STOCK card itemises on-hand</v>
       </c>
       <c r="D69" t="str">
-        <v>Once any line is allocated, palletized, loaded, dispatched or on a plan, Delete is greyed and refused ('Cancel it instead').</v>
+        <v>Awaiting palletization row between In production and In loading, each with per-order drill-down, so Available adds up on screen.</v>
       </c>
       <c r="E69" t="str">
         <v>Completed</v>
       </c>
       <c r="F69" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G69" t="str">
-        <v>CR-271</v>
+        <v>CR-298</v>
       </c>
     </row>
     <row r="70">
@@ -2008,19 +2008,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C70" t="str">
-        <v>Customer PO first, SO number small</v>
+        <v>A worked order cannot be deleted</v>
       </c>
       <c r="D70" t="str">
-        <v>Sales Order page titled by the customer's PO with SO/FY/NNN small beneath; Orders grid first column PO Number; drawer and By-Order cards follow.</v>
+        <v>Once any line is allocated, palletized, loaded, dispatched or on a plan, Delete is greyed and refused ('Cancel it instead').</v>
       </c>
       <c r="E70" t="str">
         <v>Completed</v>
       </c>
       <c r="F70" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G70" t="str">
-        <v>CR-353</v>
+        <v>CR-271</v>
       </c>
     </row>
     <row r="71">
@@ -2031,19 +2031,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C71" t="str">
-        <v>Cancel Order clears the palletization board</v>
+        <v>Customer PO first, SO number small</v>
       </c>
       <c r="D71" t="str">
-        <v>Cancelling a sales order (reason required) removes its boxes from open containers, every palletization line and every allocation; a dispatched container blocks the cancel.</v>
+        <v>Sales Order page titled by the customer's PO with SO/FY/NNN small beneath; Orders grid first column PO Number; drawer and By-Order cards follow.</v>
       </c>
       <c r="E71" t="str">
         <v>Completed</v>
       </c>
       <c r="F71" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G71" t="str">
-        <v>CR-371</v>
+        <v>CR-353</v>
       </c>
     </row>
     <row r="72">
@@ -2054,19 +2054,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C72" t="str">
-        <v>'Mark in progress' → 'Mark as sent'</v>
+        <v>Cancel Order clears the palletization board</v>
       </c>
       <c r="D72" t="str">
-        <v>Rename the status action to what it means: the sales person acknowledged the customer.</v>
+        <v>Cancelling a sales order (reason required) removes its boxes from open containers, every palletization line and every allocation; a dispatched container blocks the cancel.</v>
       </c>
       <c r="E72" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G72" t="str">
-        <v>CR-041</v>
+        <v>CR-371</v>
       </c>
     </row>
     <row r="73">
@@ -2077,10 +2077,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C73" t="str">
-        <v>'Send to Palletization' in the More menu</v>
+        <v>'Mark in progress' → 'Mark as sent'</v>
       </c>
       <c r="D73" t="str">
-        <v>Move the action into More and name it 'Palletization'.</v>
+        <v>Rename the status action to what it means: the sales person acknowledged the customer.</v>
       </c>
       <c r="E73" t="str">
         <v>Future</v>
@@ -2089,7 +2089,7 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>CR-042</v>
+        <v>CR-041</v>
       </c>
     </row>
     <row r="74">
@@ -2097,22 +2097,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>Production</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C74" t="str">
-        <v>Production page — Sheet / Kanban / Grid</v>
+        <v>'Send to Palletization' in the More menu</v>
       </c>
       <c r="D74" t="str">
-        <v>Three views of the same rows (Sheet default); one row per logged batch; Group by Item / Customer / Order / Size; status filter with All.</v>
+        <v>Move the action into More and name it 'Palletization'.</v>
       </c>
       <c r="E74" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F74" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>CR-042</v>
       </c>
     </row>
     <row r="75">
@@ -2123,10 +2123,10 @@
         <v>Production</v>
       </c>
       <c r="C75" t="str">
-        <v>To Produce view</v>
+        <v>Production page — Sheet / Kanban / Grid</v>
       </c>
       <c r="D75" t="str">
-        <v>Per item: open demand, free stock, in production and what still needs producing, with the Box Brand wanted; tick rows to start a job.</v>
+        <v>Three views of the same rows (Sheet default); one row per logged batch; Group by Item / Customer / Order / Size; status filter with All.</v>
       </c>
       <c r="E75" t="str">
         <v>Completed</v>
@@ -2146,10 +2146,10 @@
         <v>Production</v>
       </c>
       <c r="C76" t="str">
-        <v>Start / Log / Complete Production</v>
+        <v>To Produce view</v>
       </c>
       <c r="D76" t="str">
-        <v>Start creates the job (Item · Quantity); Log adds batch rows from the row's + menu (first log → In Production, full coverage → Completed automatically); Complete closes the job.</v>
+        <v>Per item: open demand, free stock, in production and what still needs producing, with the Box Brand wanted; tick rows to start a job.</v>
       </c>
       <c r="E76" t="str">
         <v>Completed</v>
@@ -2158,7 +2158,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G76" t="str">
-        <v>CR-234…237</v>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -2169,10 +2169,10 @@
         <v>Production</v>
       </c>
       <c r="C77" t="str">
-        <v>Record Production sheet (bulk, make-to-stock)</v>
+        <v>Start / Log / Complete Production</v>
       </c>
       <c r="D77" t="str">
-        <v>One ruled sheet, one row per item: Size · Design · Batch (blank = automatic) · Box Brand · Qty · Remark; paste from Excel; one Save records every row into stock; retry-safe.</v>
+        <v>Start creates the job (Item · Quantity); Log adds batch rows from the row's + menu (first log → In Production, full coverage → Completed automatically); Complete closes the job.</v>
       </c>
       <c r="E77" t="str">
         <v>Completed</v>
@@ -2181,7 +2181,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G77" t="str">
-        <v>CR-244, 264</v>
+        <v>CR-234…237</v>
       </c>
     </row>
     <row r="78">
@@ -2192,10 +2192,10 @@
         <v>Production</v>
       </c>
       <c r="C78" t="str">
-        <v>Sheet edit mode</v>
+        <v>Record Production sheet (bulk, make-to-stock)</v>
       </c>
       <c r="D78" t="str">
-        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
+        <v>One ruled sheet, one row per item: Size · Design · Batch (blank = automatic) · Box Brand · Qty · Remark; paste from Excel; one Save records every row into stock; retry-safe.</v>
       </c>
       <c r="E78" t="str">
         <v>Completed</v>
@@ -2204,7 +2204,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G78" t="str">
-        <v>CR-111</v>
+        <v>CR-244, 264</v>
       </c>
     </row>
     <row r="79">
@@ -2215,10 +2215,10 @@
         <v>Production</v>
       </c>
       <c r="C79" t="str">
-        <v>Excel import of the factory file</v>
+        <v>Sheet edit mode</v>
       </c>
       <c r="D79" t="str">
-        <v>Import production from the factory's spreadsheet.</v>
+        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
       </c>
       <c r="E79" t="str">
         <v>Completed</v>
@@ -2227,7 +2227,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G79" t="str">
-        <v/>
+        <v>CR-111</v>
       </c>
     </row>
     <row r="80">
@@ -2238,10 +2238,10 @@
         <v>Production</v>
       </c>
       <c r="C80" t="str">
-        <v>Batch numbering and rules</v>
+        <v>Excel import of the factory file</v>
       </c>
       <c r="D80" t="str">
-        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
+        <v>Import production from the factory's spreadsheet.</v>
       </c>
       <c r="E80" t="str">
         <v>Completed</v>
@@ -2261,10 +2261,10 @@
         <v>Production</v>
       </c>
       <c r="C81" t="str">
-        <v>Production detail page</v>
+        <v>Batch numbering and rules</v>
       </c>
       <c r="D81" t="str">
-        <v>Lines, batches logged, activity.</v>
+        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
       </c>
       <c r="E81" t="str">
         <v>Completed</v>
@@ -2284,19 +2284,19 @@
         <v>Production</v>
       </c>
       <c r="C82" t="str">
-        <v>Date-first production</v>
+        <v>Production detail page</v>
       </c>
       <c r="D82" t="str">
-        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
+        <v>Lines, batches logged, activity.</v>
       </c>
       <c r="E82" t="str">
         <v>Completed</v>
       </c>
       <c r="F82" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G82" t="str">
-        <v>CR-265, 267</v>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -2307,19 +2307,19 @@
         <v>Production</v>
       </c>
       <c r="C83" t="str">
-        <v>Quality Control stage on the board</v>
+        <v>Date-first production</v>
       </c>
       <c r="D83" t="str">
-        <v>QC exists in the data model; putting it on the board is parked.</v>
+        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
       </c>
       <c r="E83" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F83" t="str">
-        <v/>
+        <v>2026-10-03</v>
       </c>
       <c r="G83" t="str">
-        <v>CR-051</v>
+        <v>CR-265, 267</v>
       </c>
     </row>
     <row r="84">
@@ -2330,10 +2330,10 @@
         <v>Production</v>
       </c>
       <c r="C84" t="str">
-        <v>Duplicate detection on Excel re-import</v>
+        <v>Quality Control stage on the board</v>
       </c>
       <c r="D84" t="str">
-        <v>Warn / skip when the same production file is imported twice.</v>
+        <v>QC exists in the data model; putting it on the board is parked.</v>
       </c>
       <c r="E84" t="str">
         <v>Future</v>
@@ -2342,7 +2342,7 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v/>
+        <v>CR-051</v>
       </c>
     </row>
     <row r="85">
@@ -2350,19 +2350,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>Palletization</v>
+        <v>Production</v>
       </c>
       <c r="C85" t="str">
-        <v>Palletization board and plan numbers</v>
+        <v>Duplicate detection on Excel re-import</v>
       </c>
       <c r="D85" t="str">
-        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
+        <v>Warn / skip when the same production file is imported twice.</v>
       </c>
       <c r="E85" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F85" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -2376,10 +2376,10 @@
         <v>Palletization</v>
       </c>
       <c r="C86" t="str">
-        <v>Columns, totals footer and selection bar</v>
+        <v>Palletization board and plan numbers</v>
       </c>
       <c r="D86" t="str">
-        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
+        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
       </c>
       <c r="E86" t="str">
         <v>Completed</v>
@@ -2388,7 +2388,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G86" t="str">
-        <v>CR-279</v>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -2399,10 +2399,10 @@
         <v>Palletization</v>
       </c>
       <c r="C87" t="str">
-        <v>Plan detail page</v>
+        <v>Columns, totals footer and selection bar</v>
       </c>
       <c r="D87" t="str">
-        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
+        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
       </c>
       <c r="E87" t="str">
         <v>Completed</v>
@@ -2411,7 +2411,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G87" t="str">
-        <v/>
+        <v>CR-279</v>
       </c>
     </row>
     <row r="88">
@@ -2422,10 +2422,10 @@
         <v>Palletization</v>
       </c>
       <c r="C88" t="str">
-        <v>Prints on demand</v>
+        <v>Plan detail page</v>
       </c>
       <c r="D88" t="str">
-        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
+        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
       </c>
       <c r="E88" t="str">
         <v>Completed</v>
@@ -2445,10 +2445,10 @@
         <v>Palletization</v>
       </c>
       <c r="C89" t="str">
-        <v>Board rules</v>
+        <v>Prints on demand</v>
       </c>
       <c r="D89" t="str">
-        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
+        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
       </c>
       <c r="E89" t="str">
         <v>Completed</v>
@@ -2457,7 +2457,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G89" t="str">
-        <v>CR-129, 248</v>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -2468,10 +2468,10 @@
         <v>Palletization</v>
       </c>
       <c r="C90" t="str">
-        <v>Three ways onto the queue</v>
+        <v>Board rules</v>
       </c>
       <c r="D90" t="str">
-        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
+        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
       </c>
       <c r="E90" t="str">
         <v>Completed</v>
@@ -2480,7 +2480,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G90" t="str">
-        <v>CR-223/224</v>
+        <v>CR-129, 248</v>
       </c>
     </row>
     <row r="91">
@@ -2491,10 +2491,10 @@
         <v>Palletization</v>
       </c>
       <c r="C91" t="str">
-        <v>'+' menu: Start / Top Up Batch / Complete</v>
+        <v>Three ways onto the queue</v>
       </c>
       <c r="D91" t="str">
-        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
+        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
       </c>
       <c r="E91" t="str">
         <v>Completed</v>
@@ -2503,7 +2503,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G91" t="str">
-        <v>CR-148…150, 281</v>
+        <v>CR-223/224</v>
       </c>
     </row>
     <row r="92">
@@ -2514,10 +2514,10 @@
         <v>Palletization</v>
       </c>
       <c r="C92" t="str">
-        <v>Sheet edit mode and multi-select</v>
+        <v>'+' menu: Start / Top Up Batch / Complete</v>
       </c>
       <c r="D92" t="str">
-        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
+        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
       </c>
       <c r="E92" t="str">
         <v>Completed</v>
@@ -2526,7 +2526,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G92" t="str">
-        <v>CR-153</v>
+        <v>CR-148…150, 281</v>
       </c>
     </row>
     <row r="93">
@@ -2537,19 +2537,19 @@
         <v>Palletization</v>
       </c>
       <c r="C93" t="str">
-        <v>Date column, PAL code hidden</v>
+        <v>Sheet edit mode and multi-select</v>
       </c>
       <c r="D93" t="str">
-        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
+        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
       </c>
       <c r="E93" t="str">
         <v>Completed</v>
       </c>
       <c r="F93" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G93" t="str">
-        <v>CR-266</v>
+        <v>CR-153</v>
       </c>
     </row>
     <row r="94">
@@ -2560,19 +2560,19 @@
         <v>Palletization</v>
       </c>
       <c r="C94" t="str">
-        <v>Complete dialog shows progress</v>
+        <v>Date column, PAL code hidden</v>
       </c>
       <c r="D94" t="str">
-        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
+        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
       </c>
       <c r="E94" t="str">
         <v>Completed</v>
       </c>
       <c r="F94" t="str">
-        <v>2026-10-06</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G94" t="str">
-        <v>CR-280</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="95">
@@ -2583,19 +2583,19 @@
         <v>Palletization</v>
       </c>
       <c r="C95" t="str">
-        <v>Plan edit keeps Box Brand and batches</v>
+        <v>Complete dialog shows progress</v>
       </c>
       <c r="D95" t="str">
-        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
+        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
       </c>
       <c r="E95" t="str">
         <v>Completed</v>
       </c>
       <c r="F95" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-06</v>
       </c>
       <c r="G95" t="str">
-        <v>CR-340</v>
+        <v>CR-280</v>
       </c>
     </row>
     <row r="96">
@@ -2606,19 +2606,19 @@
         <v>Palletization</v>
       </c>
       <c r="C96" t="str">
-        <v>Three pages, one stage each</v>
+        <v>Plan edit keeps Box Brand and batches</v>
       </c>
       <c r="D96" t="str">
-        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
+        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
       </c>
       <c r="E96" t="str">
         <v>Completed</v>
       </c>
       <c r="F96" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G96" t="str">
-        <v>CR-360, 364</v>
+        <v>CR-340</v>
       </c>
     </row>
     <row r="97">
@@ -2629,10 +2629,10 @@
         <v>Palletization</v>
       </c>
       <c r="C97" t="str">
-        <v>Release palletized boxes</v>
+        <v>Three pages, one stage each</v>
       </c>
       <c r="D97" t="str">
-        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
+        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
       </c>
       <c r="E97" t="str">
         <v>Completed</v>
@@ -2641,7 +2641,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G97" t="str">
-        <v>CR-361</v>
+        <v>CR-360, 364</v>
       </c>
     </row>
     <row r="98">
@@ -2652,19 +2652,19 @@
         <v>Palletization</v>
       </c>
       <c r="C98" t="str">
-        <v>Discard the current palletization task</v>
+        <v>Release palletized boxes</v>
       </c>
       <c r="D98" t="str">
-        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
+        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
       </c>
       <c r="E98" t="str">
         <v>Completed</v>
       </c>
       <c r="F98" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G98" t="str">
-        <v>CR-369</v>
+        <v>CR-361</v>
       </c>
     </row>
     <row r="99">
@@ -2675,19 +2675,19 @@
         <v>Palletization</v>
       </c>
       <c r="C99" t="str">
-        <v>Delete a plan returns its boxes</v>
+        <v>Discard the current palletization task</v>
       </c>
       <c r="D99" t="str">
-        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
+        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
       </c>
       <c r="E99" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F99" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G99" t="str">
-        <v>CR-370</v>
+        <v>CR-369</v>
       </c>
     </row>
     <row r="100">
@@ -2698,19 +2698,19 @@
         <v>Palletization</v>
       </c>
       <c r="C100" t="str">
-        <v>Partial Start Palletization</v>
+        <v>Delete a plan returns its boxes</v>
       </c>
       <c r="D100" t="str">
-        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
+        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
       </c>
       <c r="E100" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F100" t="str">
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>Panel Craft list #9</v>
+        <v>CR-370</v>
       </c>
     </row>
     <row r="101">
@@ -2721,10 +2721,10 @@
         <v>Palletization</v>
       </c>
       <c r="C101" t="str">
-        <v>Ready pallets — type and pallet count</v>
+        <v>Partial Start Palletization</v>
       </c>
       <c r="D101" t="str">
-        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
+        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
       </c>
       <c r="E101" t="str">
         <v>Future</v>
@@ -2733,7 +2733,7 @@
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>Panel Craft list #7</v>
+        <v>Panel Craft list #9</v>
       </c>
     </row>
     <row r="102">
@@ -2744,10 +2744,10 @@
         <v>Palletization</v>
       </c>
       <c r="C102" t="str">
-        <v>Remove 'Ordered / Completed' where not needed</v>
+        <v>Ready pallets — type and pallet count</v>
       </c>
       <c r="D102" t="str">
-        <v>Screen to be confirmed.</v>
+        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
       </c>
       <c r="E102" t="str">
         <v>Future</v>
@@ -2756,7 +2756,7 @@
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>Panel Craft list #8</v>
+        <v>Panel Craft list #7</v>
       </c>
     </row>
     <row r="103">
@@ -2764,22 +2764,22 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C103" t="str">
-        <v>A loading = one container</v>
+        <v>Remove 'Ordered / Completed' where not needed</v>
       </c>
       <c r="D103" t="str">
-        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
+        <v>Screen to be confirmed.</v>
       </c>
       <c r="E103" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F103" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G103" t="str">
-        <v>CR-120…124</v>
+        <v>Panel Craft list #8</v>
       </c>
     </row>
     <row r="104">
@@ -2790,10 +2790,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C104" t="str">
-        <v>Loading and Dispatch page</v>
+        <v>A loading = one container</v>
       </c>
       <c r="D104" t="str">
-        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
+        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
       </c>
       <c r="E104" t="str">
         <v>Completed</v>
@@ -2802,7 +2802,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G104" t="str">
-        <v>CR-140, 141</v>
+        <v>CR-120…124</v>
       </c>
     </row>
     <row r="105">
@@ -2813,10 +2813,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C105" t="str">
-        <v>Loading detail</v>
+        <v>Loading and Dispatch page</v>
       </c>
       <c r="D105" t="str">
-        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
+        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
       </c>
       <c r="E105" t="str">
         <v>Completed</v>
@@ -2825,7 +2825,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>CR-140, 141</v>
       </c>
     </row>
     <row r="106">
@@ -2836,10 +2836,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C106" t="str">
-        <v>Vehicle and shipment details</v>
+        <v>Loading detail</v>
       </c>
       <c r="D106" t="str">
-        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
+        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
       </c>
       <c r="E106" t="str">
         <v>Completed</v>
@@ -2859,10 +2859,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C107" t="str">
-        <v>Dispatch with gates and warnings</v>
+        <v>Vehicle and shipment details</v>
       </c>
       <c r="D107" t="str">
-        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
+        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
       </c>
       <c r="E107" t="str">
         <v>Completed</v>
@@ -2882,10 +2882,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C108" t="str">
-        <v>Invoice and dispatch prints</v>
+        <v>Dispatch with gates and warnings</v>
       </c>
       <c r="D108" t="str">
-        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
+        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
       </c>
       <c r="E108" t="str">
         <v>Completed</v>
@@ -2905,10 +2905,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C109" t="str">
-        <v>Four ways to fill a container</v>
+        <v>Invoice and dispatch prints</v>
       </c>
       <c r="D109" t="str">
-        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
+        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
       </c>
       <c r="E109" t="str">
         <v>Completed</v>
@@ -2917,7 +2917,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G109" t="str">
-        <v>CR-126…128, 201/202</v>
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -2928,10 +2928,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C110" t="str">
-        <v>Editing a loading</v>
+        <v>Four ways to fill a container</v>
       </c>
       <c r="D110" t="str">
-        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
+        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
       </c>
       <c r="E110" t="str">
         <v>Completed</v>
@@ -2940,7 +2940,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>CR-126…128, 201/202</v>
       </c>
     </row>
     <row r="111">
@@ -2951,19 +2951,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C111" t="str">
-        <v>Date column, LOAD code hidden</v>
+        <v>Editing a loading</v>
       </c>
       <c r="D111" t="str">
-        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
+        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
       </c>
       <c r="E111" t="str">
         <v>Completed</v>
       </c>
       <c r="F111" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G111" t="str">
-        <v>CR-266</v>
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -2974,19 +2974,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C112" t="str">
-        <v>Several containers in one New Loading</v>
+        <v>Date column, LOAD code hidden</v>
       </c>
       <c r="D112" t="str">
-        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
+        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
       </c>
       <c r="E112" t="str">
         <v>Completed</v>
       </c>
       <c r="F112" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G112" t="str">
-        <v>CR-301</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="113">
@@ -2997,19 +2997,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C113" t="str">
-        <v>Loading Workspace — a tab per container</v>
+        <v>Several containers in one New Loading</v>
       </c>
       <c r="D113" t="str">
-        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
+        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
       </c>
       <c r="E113" t="str">
         <v>Completed</v>
       </c>
       <c r="F113" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G113" t="str">
-        <v>CR-326, 334, 335</v>
+        <v>CR-301</v>
       </c>
     </row>
     <row r="114">
@@ -3020,10 +3020,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C114" t="str">
-        <v>Every customer listed, with search</v>
+        <v>Loading Workspace — a tab per container</v>
       </c>
       <c r="D114" t="str">
-        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
+        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
       </c>
       <c r="E114" t="str">
         <v>Completed</v>
@@ -3032,7 +3032,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G114" t="str">
-        <v>CR-327</v>
+        <v>CR-326, 334, 335</v>
       </c>
     </row>
     <row r="115">
@@ -3043,10 +3043,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C115" t="str">
-        <v>'What to do first' reasons</v>
+        <v>Every customer listed, with search</v>
       </c>
       <c r="D115" t="str">
-        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
+        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
       </c>
       <c r="E115" t="str">
         <v>Completed</v>
@@ -3055,7 +3055,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G115" t="str">
-        <v>CR-328</v>
+        <v>CR-327</v>
       </c>
     </row>
     <row r="116">
@@ -3066,19 +3066,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C116" t="str">
-        <v>Pick the planned container at loading</v>
+        <v>'What to do first' reasons</v>
       </c>
       <c r="D116" t="str">
-        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
+        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
       </c>
       <c r="E116" t="str">
         <v>Completed</v>
       </c>
       <c r="F116" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G116" t="str">
-        <v>CR-338</v>
+        <v>CR-328</v>
       </c>
     </row>
     <row r="117">
@@ -3089,19 +3089,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C117" t="str">
-        <v>Two steps per container; C1 / C2 naming</v>
+        <v>Pick the planned container at loading</v>
       </c>
       <c r="D117" t="str">
-        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
+        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
       </c>
       <c r="E117" t="str">
         <v>Completed</v>
       </c>
       <c r="F117" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G117" t="str">
-        <v>CR-350, 354</v>
+        <v>CR-338</v>
       </c>
     </row>
     <row r="118">
@@ -3112,19 +3112,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C118" t="str">
-        <v>Mix Batch at loading</v>
+        <v>Two steps per container; C1 / C2 naming</v>
       </c>
       <c r="D118" t="str">
-        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
+        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
       </c>
       <c r="E118" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F118" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G118" t="str">
-        <v>CR-260 follow-up</v>
+        <v>CR-350, 354</v>
       </c>
     </row>
     <row r="119">
@@ -3132,22 +3132,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C119" t="str">
-        <v>One stock rule everywhere</v>
+        <v>Mix Batch at loading</v>
       </c>
       <c r="D119" t="str">
-        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
+        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
       </c>
       <c r="E119" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F119" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G119" t="str">
-        <v/>
+        <v>CR-260 follow-up</v>
       </c>
     </row>
     <row r="120">
@@ -3158,10 +3158,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C120" t="str">
-        <v>Counters recomputed, never incremented</v>
+        <v>One stock rule everywhere</v>
       </c>
       <c r="D120" t="str">
-        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
+        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
       </c>
       <c r="E120" t="str">
         <v>Completed</v>
@@ -3181,10 +3181,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C121" t="str">
-        <v>Allocation and batch ledger</v>
+        <v>Counters recomputed, never incremented</v>
       </c>
       <c r="D121" t="str">
-        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
+        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
       </c>
       <c r="E121" t="str">
         <v>Completed</v>
@@ -3204,10 +3204,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C122" t="str">
-        <v>Admin repair operations</v>
+        <v>Allocation and batch ledger</v>
       </c>
       <c r="D122" t="str">
-        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
+        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
       </c>
       <c r="E122" t="str">
         <v>Completed</v>
@@ -3227,19 +3227,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C123" t="str">
-        <v>Inventory adjustments</v>
+        <v>Admin repair operations</v>
       </c>
       <c r="D123" t="str">
-        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
+        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
       </c>
       <c r="E123" t="str">
         <v>Completed</v>
       </c>
       <c r="F123" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G123" t="str">
-        <v>CR-308</v>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -3250,19 +3250,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C124" t="str">
-        <v>Stock per warehouse</v>
+        <v>Inventory adjustments</v>
       </c>
       <c r="D124" t="str">
-        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
+        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
       </c>
       <c r="E124" t="str">
         <v>Completed</v>
       </c>
       <c r="F124" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G124" t="str">
-        <v>CR-329</v>
+        <v>CR-308</v>
       </c>
     </row>
     <row r="125">
@@ -3273,10 +3273,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C125" t="str">
-        <v>Transfer Orders</v>
+        <v>Stock per warehouse</v>
       </c>
       <c r="D125" t="str">
-        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
+        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
       </c>
       <c r="E125" t="str">
         <v>Completed</v>
@@ -3285,7 +3285,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G125" t="str">
-        <v>CR-330</v>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="126">
@@ -3296,10 +3296,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C126" t="str">
-        <v>Locations on items</v>
+        <v>Transfer Orders</v>
       </c>
       <c r="D126" t="str">
-        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
+        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
       </c>
       <c r="E126" t="str">
         <v>Completed</v>
@@ -3308,7 +3308,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G126" t="str">
-        <v>CR-332</v>
+        <v>CR-330</v>
       </c>
     </row>
     <row r="127">
@@ -3319,19 +3319,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C127" t="str">
-        <v>Stock keyed by the item</v>
+        <v>Locations on items</v>
       </c>
       <c r="D127" t="str">
-        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
+        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
       </c>
       <c r="E127" t="str">
         <v>Completed</v>
       </c>
       <c r="F127" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G127" t="str">
-        <v>CR-341</v>
+        <v>CR-332</v>
       </c>
     </row>
     <row r="128">
@@ -3339,22 +3339,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C128" t="str">
-        <v>Sales reports</v>
+        <v>Stock keyed by the item</v>
       </c>
       <c r="D128" t="str">
-        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
+        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
       </c>
       <c r="E128" t="str">
         <v>Completed</v>
       </c>
       <c r="F128" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G128" t="str">
-        <v/>
+        <v>CR-341</v>
       </c>
     </row>
     <row r="129">
@@ -3365,10 +3365,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C129" t="str">
-        <v>Inventory reports</v>
+        <v>Sales reports</v>
       </c>
       <c r="D129" t="str">
-        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
+        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
       </c>
       <c r="E129" t="str">
         <v>Completed</v>
@@ -3377,7 +3377,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G129" t="str">
-        <v>CR-104</v>
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -3388,10 +3388,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C130" t="str">
-        <v>Dispatch reports</v>
+        <v>Inventory reports</v>
       </c>
       <c r="D130" t="str">
-        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
+        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
       </c>
       <c r="E130" t="str">
         <v>Completed</v>
@@ -3411,10 +3411,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C131" t="str">
-        <v>Audit log and activity</v>
+        <v>Dispatch reports</v>
       </c>
       <c r="D131" t="str">
-        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
+        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
       </c>
       <c r="E131" t="str">
         <v>Completed</v>
@@ -3423,7 +3423,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G131" t="str">
-        <v/>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="132">
@@ -3434,10 +3434,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C132" t="str">
-        <v>Dashboard</v>
+        <v>Audit log and activity</v>
       </c>
       <c r="D132" t="str">
-        <v>Headline numbers.</v>
+        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
       </c>
       <c r="E132" t="str">
         <v>Completed</v>
@@ -3457,19 +3457,19 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C133" t="str">
-        <v>Warehouse Stock report</v>
+        <v>Dashboard</v>
       </c>
       <c r="D133" t="str">
-        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
+        <v>Headline numbers.</v>
       </c>
       <c r="E133" t="str">
         <v>Completed</v>
       </c>
       <c r="F133" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G133" t="str">
-        <v>CR-331</v>
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -3477,22 +3477,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C134" t="str">
-        <v>Panel Master</v>
+        <v>Warehouse Stock report</v>
       </c>
       <c r="D134" t="str">
-        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
+        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
       </c>
       <c r="E134" t="str">
         <v>Completed</v>
       </c>
       <c r="F134" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G134" t="str">
-        <v>CR-283…285, 291, 319</v>
+        <v>CR-331</v>
       </c>
     </row>
     <row r="135">
@@ -3503,19 +3503,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C135" t="str">
-        <v>Remarks on a panel</v>
+        <v>Panel Master</v>
       </c>
       <c r="D135" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
       </c>
       <c r="E135" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F135" t="str">
-        <v/>
+        <v>2026-10-08</v>
       </c>
       <c r="G135" t="str">
-        <v>CR-425</v>
+        <v>CR-283…285, 291, 319</v>
       </c>
     </row>
     <row r="136">
@@ -3526,10 +3526,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C136" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D136" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E136" t="str">
         <v>In progress</v>
@@ -3538,7 +3538,7 @@
         <v/>
       </c>
       <c r="G136" t="str">
-        <v>CR-426</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="137">
@@ -3546,13 +3546,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C137" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D137" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E137" t="str">
         <v>In progress</v>
@@ -3561,7 +3561,7 @@
         <v/>
       </c>
       <c r="G137" t="str">
-        <v>CR-427</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="138">
@@ -3569,22 +3569,22 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C138" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D138" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E138" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F138" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G138" t="str">
-        <v>CR-428</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="139">
@@ -3595,10 +3595,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C139" t="str">
-        <v>One Masters page</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D139" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E139" t="str">
         <v>Completed</v>
@@ -3607,7 +3607,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G139" t="str">
-        <v>CR-436</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="140">
@@ -3618,10 +3618,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C140" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>One Masters page</v>
       </c>
       <c r="D140" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E140" t="str">
         <v>Completed</v>
@@ -3630,7 +3630,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G140" t="str">
-        <v>CR-439</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="141">
@@ -3641,10 +3641,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C141" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D141" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E141" t="str">
         <v>Completed</v>
@@ -3653,7 +3653,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G141" t="str">
-        <v>CR-440</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="142">
@@ -3661,13 +3661,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>Items</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C142" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D142" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E142" t="str">
         <v>Completed</v>
@@ -3676,7 +3676,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G142" t="str">
-        <v>CR-437</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="143">
@@ -3684,22 +3684,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Items</v>
       </c>
       <c r="C143" t="str">
-        <v>Names save as Title Case</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D143" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E143" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F143" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G143" t="str">
-        <v>CR-429</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="144">
@@ -3707,13 +3707,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C144" t="str">
-        <v>Brand off the Item form</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D144" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E144" t="str">
         <v>In progress</v>
@@ -3722,7 +3722,7 @@
         <v/>
       </c>
       <c r="G144" t="str">
-        <v>CR-430</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="145">
@@ -3730,22 +3730,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C145" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D145" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E145" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F145" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G145" t="str">
-        <v>CR-306</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="146">
@@ -3756,19 +3756,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C146" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D146" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E146" t="str">
         <v>Completed</v>
       </c>
       <c r="F146" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G146" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="147">
@@ -3779,10 +3779,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C147" t="str">
-        <v>MDF master</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D147" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E147" t="str">
         <v>Completed</v>
@@ -3791,7 +3791,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G147" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="148">
@@ -3802,19 +3802,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C148" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>MDF master</v>
       </c>
       <c r="D148" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E148" t="str">
         <v>Completed</v>
       </c>
       <c r="F148" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G148" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="149">
@@ -3825,19 +3825,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C149" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D149" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E149" t="str">
         <v>Completed</v>
       </c>
       <c r="F149" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G149" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="150">
@@ -3848,19 +3848,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C150" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D150" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E150" t="str">
         <v>Completed</v>
       </c>
       <c r="F150" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G150" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="151">
@@ -3871,19 +3871,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C151" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D151" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E151" t="str">
         <v>Completed</v>
       </c>
       <c r="F151" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G151" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="152">
@@ -3894,19 +3894,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C152" t="str">
-        <v>Production checkpoints</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D152" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
       </c>
       <c r="F152" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="153">
@@ -3917,10 +3917,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C153" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D153" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
@@ -3929,7 +3929,7 @@
         <v>2026-10-09</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="154">
@@ -3940,19 +3940,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C154" t="str">
-        <v>Sample Orders</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D154" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
       </c>
       <c r="F154" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-315…317</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="155">
@@ -3963,19 +3963,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C155" t="str">
-        <v>One Orders register</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D155" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E155" t="str">
         <v>Completed</v>
       </c>
       <c r="F155" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G155" t="str">
-        <v>CR-345</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="156">
@@ -3986,10 +3986,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C156" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>One Orders register</v>
       </c>
       <c r="D156" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E156" t="str">
         <v>Completed</v>
@@ -3998,7 +3998,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G156" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="157">
@@ -4009,10 +4009,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C157" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D157" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E157" t="str">
         <v>Completed</v>
@@ -4021,7 +4021,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G157" t="str">
-        <v>CR-349</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="158">
@@ -4032,19 +4032,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C158" t="str">
-        <v>Load Copy print</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D158" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E158" t="str">
         <v>Completed</v>
       </c>
       <c r="F158" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G158" t="str">
-        <v>CR-351</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="159">
@@ -4055,19 +4055,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C159" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D159" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E159" t="str">
         <v>Completed</v>
       </c>
       <c r="F159" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G159" t="str">
-        <v>CR-433</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="160">
@@ -4078,19 +4078,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C160" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D160" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E160" t="str">
         <v>Completed</v>
       </c>
       <c r="F160" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G160" t="str">
-        <v>CR-311</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="161">
@@ -4101,19 +4101,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C161" t="str">
-        <v>Small UX items</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D161" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
       </c>
       <c r="F161" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="162">
@@ -4124,19 +4124,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C162" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>Small UX items</v>
       </c>
       <c r="D162" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E162" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F162" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-365</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="163">
@@ -4147,10 +4147,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C163" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D163" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E163" t="str">
         <v>In progress</v>
@@ -4159,7 +4159,7 @@
         <v/>
       </c>
       <c r="G163" t="str">
-        <v>CR-366</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="164">
@@ -4170,10 +4170,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C164" t="str">
-        <v>One Status column</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D164" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E164" t="str">
         <v>In progress</v>
@@ -4182,7 +4182,7 @@
         <v/>
       </c>
       <c r="G164" t="str">
-        <v>CR-367</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="165">
@@ -4193,10 +4193,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C165" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>One Status column</v>
       </c>
       <c r="D165" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E165" t="str">
         <v>In progress</v>
@@ -4205,7 +4205,7 @@
         <v/>
       </c>
       <c r="G165" t="str">
-        <v>CR-368</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="166">
@@ -4216,10 +4216,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C166" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D166" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E166" t="str">
         <v>In progress</v>
@@ -4228,7 +4228,7 @@
         <v/>
       </c>
       <c r="G166" t="str">
-        <v>CR-399</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="167">
@@ -4239,10 +4239,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C167" t="str">
-        <v>One four-state order status</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D167" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E167" t="str">
         <v>In progress</v>
@@ -4251,7 +4251,7 @@
         <v/>
       </c>
       <c r="G167" t="str">
-        <v>CR-400</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="168">
@@ -4262,10 +4262,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D168" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E168" t="str">
         <v>In progress</v>
@@ -4274,7 +4274,7 @@
         <v/>
       </c>
       <c r="G168" t="str">
-        <v>CR-401</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="169">
@@ -4285,10 +4285,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D169" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E169" t="str">
         <v>In progress</v>
@@ -4297,7 +4297,7 @@
         <v/>
       </c>
       <c r="G169" t="str">
-        <v>CR-402</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="170">
@@ -4308,10 +4308,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D170" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E170" t="str">
         <v>In progress</v>
@@ -4320,7 +4320,7 @@
         <v/>
       </c>
       <c r="G170" t="str">
-        <v>CR-403</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="171">
@@ -4331,10 +4331,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Load part of a panel</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D171" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E171" t="str">
         <v>In progress</v>
@@ -4343,7 +4343,7 @@
         <v/>
       </c>
       <c r="G171" t="str">
-        <v>CR-405</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="172">
@@ -4354,10 +4354,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>MDF row on every panel</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D172" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E172" t="str">
         <v>In progress</v>
@@ -4366,7 +4366,7 @@
         <v/>
       </c>
       <c r="G172" t="str">
-        <v>CR-406</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="173">
@@ -4377,10 +4377,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>Load whole panel in one click</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D173" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E173" t="str">
         <v>In progress</v>
@@ -4389,7 +4389,7 @@
         <v/>
       </c>
       <c r="G173" t="str">
-        <v>CR-407</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="174">
@@ -4397,22 +4397,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Settings search everywhere</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D174" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E174" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F174" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G174" t="str">
-        <v>CR-408</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="175">
@@ -4420,13 +4420,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C175" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D175" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E175" t="str">
         <v>Completed</v>
@@ -4435,7 +4435,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G175" t="str">
-        <v>CR-409</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="176">
@@ -4446,10 +4446,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C176" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D176" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E176" t="str">
         <v>Completed</v>
@@ -4458,7 +4458,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G176" t="str">
-        <v>CR-438</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="177">
@@ -4469,10 +4469,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C177" t="str">
-        <v>Location at every stage</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D177" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E177" t="str">
         <v>Completed</v>
@@ -4481,7 +4481,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G177" t="str">
-        <v>CR-411…413</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="178">
@@ -4489,22 +4489,22 @@
         <v>177</v>
       </c>
       <c r="B178" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C178" t="str">
-        <v>Panel location</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D178" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E178" t="str">
         <v>Completed</v>
       </c>
       <c r="F178" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G178" t="str">
-        <v>CR-410</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="179">
@@ -4512,22 +4512,22 @@
         <v>178</v>
       </c>
       <c r="B179" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C179" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D179" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E179" t="str">
         <v>Completed</v>
       </c>
       <c r="F179" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G179" t="str">
-        <v>CR-419</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="180">
@@ -4538,19 +4538,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C180" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D180" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E180" t="str">
         <v>Completed</v>
       </c>
       <c r="F180" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G180" t="str">
-        <v>CR-415</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="181">
@@ -4558,22 +4558,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C181" t="str">
-        <v>No long helper notes</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D181" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E181" t="str">
         <v>Completed</v>
       </c>
       <c r="F181" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G181" t="str">
-        <v>CR-416</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="182">
@@ -4581,22 +4581,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="str">
-        <v>Production</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C182" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D182" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E182" t="str">
         <v>Completed</v>
       </c>
       <c r="F182" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-417</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="183">
@@ -4604,13 +4604,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C183" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D183" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E183" t="str">
         <v>Completed</v>
@@ -4619,7 +4619,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-418</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="184">
@@ -4627,13 +4627,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Notifications read / unread</v>
+        <v>Panel location</v>
       </c>
       <c r="D184" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E184" t="str">
         <v>Completed</v>
@@ -4642,7 +4642,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G184" t="str">
-        <v>CR-419…421</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="185">
@@ -4650,13 +4650,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D185" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E185" t="str">
         <v>Completed</v>
@@ -4665,7 +4665,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G185" t="str">
-        <v>CR-422</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="186">
@@ -4676,19 +4676,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D186" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E186" t="str">
         <v>Completed</v>
       </c>
       <c r="F186" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G186" t="str">
-        <v>CR-404</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="187">
@@ -4696,22 +4696,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C187" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D187" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E187" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F187" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="188">
@@ -4719,22 +4719,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Panel Craft</v>
+        <v>Production</v>
       </c>
       <c r="C188" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D188" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E188" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F188" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G188" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="189">
@@ -4742,22 +4742,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C189" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D189" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E189" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F189" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G189" t="str">
-        <v>Panel Craft list #2</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="190">
@@ -4765,22 +4765,22 @@
         <v>189</v>
       </c>
       <c r="B190" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C190" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D190" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E190" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F190" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G190" t="str">
-        <v>Panel Craft list #4</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="191">
@@ -4788,22 +4788,22 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C191" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D191" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E191" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F191" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G191" t="str">
-        <v>Panel Craft list #5</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="192">
@@ -4814,19 +4814,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C192" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D192" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E192" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F192" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G192" t="str">
-        <v>Panel Craft list #6</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="193">
@@ -4837,19 +4837,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C193" t="str">
-        <v>Bill / expense</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D193" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E193" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F193" t="str">
         <v/>
       </c>
       <c r="G193" t="str">
-        <v>Panel Craft list #12</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="194">
@@ -4857,22 +4857,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C194" t="str">
-        <v>System reference and change-request register</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D194" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E194" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F194" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G194" t="str">
-        <v/>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="195">
@@ -4880,22 +4880,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C195" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D195" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E195" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F195" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G195" t="str">
-        <v/>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="196">
@@ -4903,22 +4903,22 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C196" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D196" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E196" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F196" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G196" t="str">
-        <v/>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="197">
@@ -4926,22 +4926,22 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C197" t="str">
-        <v>Data Flow reference</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D197" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E197" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F197" t="str">
-        <v>2026-10-03</v>
+        <v/>
       </c>
       <c r="G197" t="str">
-        <v>CR-272</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="198">
@@ -4949,22 +4949,22 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C198" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D198" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E198" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F198" t="str">
-        <v>2026-10-03</v>
+        <v/>
       </c>
       <c r="G198" t="str">
-        <v/>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="199">
@@ -4972,22 +4972,22 @@
         <v>198</v>
       </c>
       <c r="B199" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C199" t="str">
-        <v>Locations guide</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D199" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E199" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F199" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G199" t="str">
-        <v>CR-411…413</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="200">
@@ -4998,16 +4998,16 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C200" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D200" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
       </c>
       <c r="F200" t="str">
-        <v>2026-10-22</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G200" t="str">
         <v/>
@@ -5021,25 +5021,163 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C201" t="str">
+        <v>Change log, user flow, user manual</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+      </c>
+      <c r="E201" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Seed and teardown scripts</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+      </c>
+      <c r="E202" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Data Flow reference</v>
+      </c>
+      <c r="D203" t="str">
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+      </c>
+      <c r="E203" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F203" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G203" t="str">
+        <v>CR-272</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Phase 2 inventory</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+      </c>
+      <c r="E204" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F204" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Locations guide</v>
+      </c>
+      <c r="D205" t="str">
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+      </c>
+      <c r="E205" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F205" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="G205" t="str">
+        <v>CR-411…413</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Deliverables list (this workbook)</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+      </c>
+      <c r="E206" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F206" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C207" t="str">
         <v>Demo / test environment</v>
       </c>
-      <c r="D201" t="str">
+      <c r="D207" t="str">
         <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
       </c>
-      <c r="E201" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F201" t="str">
+      <c r="E207" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F207" t="str">
         <v>2026-10-25</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G207" t="str">
         <v>CR-441</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G201"/>
+  <autoFilter ref="A1:G207"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G207"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G208</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G208"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -5174,10 +5174,33 @@
         <v>CR-441</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Demo carries no BOFFO branding</v>
+      </c>
+      <c r="D208" t="str">
+        <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
+      </c>
+      <c r="E208" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F208" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="G208" t="str">
+        <v>CR-454</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G207"/>
+  <autoFilter ref="A1:G208"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G208"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G212</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G212"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -4512,22 +4512,22 @@
         <v>178</v>
       </c>
       <c r="B179" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C179" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D179" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E179" t="str">
         <v>Completed</v>
       </c>
       <c r="F179" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G179" t="str">
-        <v>CR-447</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="180">
@@ -4535,22 +4535,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C180" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D180" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E180" t="str">
         <v>Completed</v>
       </c>
       <c r="F180" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G180" t="str">
-        <v>CR-448</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="181">
@@ -4558,22 +4558,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C181" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D181" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E181" t="str">
         <v>Completed</v>
       </c>
       <c r="F181" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G181" t="str">
-        <v>CR-449</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="182">
@@ -4581,13 +4581,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C182" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D182" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E182" t="str">
         <v>Completed</v>
@@ -4596,7 +4596,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-450</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="183">
@@ -4604,22 +4604,22 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C183" t="str">
-        <v>Location at every stage</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D183" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E183" t="str">
         <v>Completed</v>
       </c>
       <c r="F183" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-411…413</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="184">
@@ -4630,19 +4630,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Panel location</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D184" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E184" t="str">
         <v>Completed</v>
       </c>
       <c r="F184" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G184" t="str">
-        <v>CR-410</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="185">
@@ -4653,19 +4653,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D185" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E185" t="str">
         <v>Completed</v>
       </c>
       <c r="F185" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G185" t="str">
-        <v>CR-419</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="186">
@@ -4676,19 +4676,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D186" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E186" t="str">
         <v>Completed</v>
       </c>
       <c r="F186" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G186" t="str">
-        <v>CR-415</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="187">
@@ -4696,13 +4696,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C187" t="str">
-        <v>No long helper notes</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D187" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E187" t="str">
         <v>Completed</v>
@@ -4711,7 +4711,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-416</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="188">
@@ -4719,13 +4719,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Production</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C188" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>Panel location</v>
       </c>
       <c r="D188" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
@@ -4734,7 +4734,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-417</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="189">
@@ -4742,13 +4742,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C189" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D189" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
@@ -4757,7 +4757,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-418</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="190">
@@ -4765,13 +4765,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C190" t="str">
-        <v>Notifications read / unread</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D190" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
@@ -4780,7 +4780,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-419…421</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="191">
@@ -4788,13 +4788,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C191" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D191" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
@@ -4803,7 +4803,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-422</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="192">
@@ -4811,22 +4811,22 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>Panel Craft</v>
+        <v>Production</v>
       </c>
       <c r="C192" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D192" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
       </c>
       <c r="F192" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-404</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="193">
@@ -4834,22 +4834,22 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C193" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D193" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E193" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F193" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="194">
@@ -4857,22 +4857,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C194" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D194" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E194" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F194" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G194" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="195">
@@ -4880,22 +4880,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C195" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D195" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E195" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F195" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G195" t="str">
-        <v>Panel Craft list #2</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="196">
@@ -4906,19 +4906,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C196" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D196" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E196" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F196" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G196" t="str">
-        <v>Panel Craft list #4</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="197">
@@ -4929,19 +4929,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C197" t="str">
-        <v>Godown print — issue / request</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D197" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E197" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F197" t="str">
         <v/>
       </c>
       <c r="G197" t="str">
-        <v>Panel Craft list #5</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="198">
@@ -4952,10 +4952,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C198" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D198" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E198" t="str">
         <v>Future</v>
@@ -4964,7 +4964,7 @@
         <v/>
       </c>
       <c r="G198" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="199">
@@ -4975,10 +4975,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C199" t="str">
-        <v>Bill / expense</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D199" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E199" t="str">
         <v>Future</v>
@@ -4987,7 +4987,7 @@
         <v/>
       </c>
       <c r="G199" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="200">
@@ -4995,22 +4995,22 @@
         <v>199</v>
       </c>
       <c r="B200" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C200" t="str">
-        <v>System reference and change-request register</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D200" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E200" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F200" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G200" t="str">
-        <v/>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="201">
@@ -5018,22 +5018,22 @@
         <v>200</v>
       </c>
       <c r="B201" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C201" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D201" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E201" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F201" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G201" t="str">
-        <v/>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="202">
@@ -5041,22 +5041,22 @@
         <v>201</v>
       </c>
       <c r="B202" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C202" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D202" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E202" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F202" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G202" t="str">
-        <v/>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="203">
@@ -5064,22 +5064,22 @@
         <v>202</v>
       </c>
       <c r="B203" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C203" t="str">
-        <v>Data Flow reference</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D203" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E203" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F203" t="str">
-        <v>2026-10-03</v>
+        <v/>
       </c>
       <c r="G203" t="str">
-        <v>CR-272</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="204">
@@ -5090,16 +5090,16 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C204" t="str">
-        <v>Phase 2 inventory</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D204" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E204" t="str">
         <v>Completed</v>
       </c>
       <c r="F204" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G204" t="str">
         <v/>
@@ -5113,19 +5113,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C205" t="str">
-        <v>Locations guide</v>
+        <v>Change log, user flow, user manual</v>
       </c>
       <c r="D205" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
       </c>
       <c r="E205" t="str">
         <v>Completed</v>
       </c>
       <c r="F205" t="str">
-        <v>2026-10-24</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G205" t="str">
-        <v>CR-411…413</v>
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -5136,16 +5136,16 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C206" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Seed and teardown scripts</v>
       </c>
       <c r="D206" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
       </c>
       <c r="F206" t="str">
-        <v>2026-10-22</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G206" t="str">
         <v/>
@@ -5159,19 +5159,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C207" t="str">
-        <v>Demo / test environment</v>
+        <v>Data Flow reference</v>
       </c>
       <c r="D207" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
       </c>
       <c r="F207" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G207" t="str">
-        <v>CR-441</v>
+        <v>CR-272</v>
       </c>
     </row>
     <row r="208">
@@ -5182,25 +5182,117 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C208" t="str">
+        <v>Phase 2 inventory</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+      </c>
+      <c r="E208" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F208" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Locations guide</v>
+      </c>
+      <c r="D209" t="str">
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+      </c>
+      <c r="E209" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F209" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="G209" t="str">
+        <v>CR-411…413</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Deliverables list (this workbook)</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+      </c>
+      <c r="E210" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F210" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D211" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E211" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F211" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G211" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C212" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D208" t="str">
+      <c r="D212" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E208" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F208" t="str">
+      <c r="E212" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F212" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G208" t="str">
+      <c r="G212" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G208"/>
+  <autoFilter ref="A1:G212"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G212"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G213</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G213"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -4561,10 +4561,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C181" t="str">
-        <v>Stock history in date order</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D181" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E181" t="str">
         <v>Completed</v>
@@ -4573,7 +4573,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G181" t="str">
-        <v>CR-455</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="182">
@@ -4581,22 +4581,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C182" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D182" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E182" t="str">
         <v>Completed</v>
       </c>
       <c r="F182" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-447</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="183">
@@ -4604,13 +4604,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C183" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D183" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E183" t="str">
         <v>Completed</v>
@@ -4619,7 +4619,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-448</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="184">
@@ -4630,19 +4630,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D184" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E184" t="str">
         <v>Completed</v>
       </c>
       <c r="F184" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G184" t="str">
-        <v>CR-456</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="185">
@@ -4653,19 +4653,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D185" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E185" t="str">
         <v>Completed</v>
       </c>
       <c r="F185" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G185" t="str">
-        <v>CR-449</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="186">
@@ -4676,10 +4676,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D186" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E186" t="str">
         <v>Completed</v>
@@ -4688,7 +4688,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G186" t="str">
-        <v>CR-450</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="187">
@@ -4696,22 +4696,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C187" t="str">
-        <v>Location at every stage</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D187" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E187" t="str">
         <v>Completed</v>
       </c>
       <c r="F187" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-411…413</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="188">
@@ -4719,13 +4719,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C188" t="str">
-        <v>Panel location</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D188" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
@@ -4734,7 +4734,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-410</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="189">
@@ -4745,10 +4745,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C189" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel location</v>
       </c>
       <c r="D189" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
@@ -4757,7 +4757,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-419</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="190">
@@ -4768,10 +4768,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C190" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D190" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
@@ -4780,7 +4780,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-415</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="191">
@@ -4788,13 +4788,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C191" t="str">
-        <v>No long helper notes</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D191" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
@@ -4803,7 +4803,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-416</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="192">
@@ -4811,13 +4811,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>Production</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C192" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D192" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
@@ -4826,7 +4826,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-417</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="193">
@@ -4834,13 +4834,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Production</v>
       </c>
       <c r="C193" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D193" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E193" t="str">
         <v>Completed</v>
@@ -4849,7 +4849,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-418</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="194">
@@ -4860,10 +4860,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C194" t="str">
-        <v>Notifications read / unread</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D194" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E194" t="str">
         <v>Completed</v>
@@ -4872,7 +4872,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G194" t="str">
-        <v>CR-419…421</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="195">
@@ -4880,13 +4880,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C195" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D195" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
@@ -4895,7 +4895,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-422</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="196">
@@ -4903,22 +4903,22 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C196" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D196" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
       </c>
       <c r="F196" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-404</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="197">
@@ -4929,19 +4929,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C197" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D197" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E197" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F197" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="198">
@@ -4952,19 +4952,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C198" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D198" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E198" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F198" t="str">
         <v/>
       </c>
       <c r="G198" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="199">
@@ -4975,10 +4975,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C199" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D199" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E199" t="str">
         <v>Future</v>
@@ -4987,7 +4987,7 @@
         <v/>
       </c>
       <c r="G199" t="str">
-        <v>Panel Craft list #2</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="200">
@@ -4998,10 +4998,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C200" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D200" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E200" t="str">
         <v>Future</v>
@@ -5010,7 +5010,7 @@
         <v/>
       </c>
       <c r="G200" t="str">
-        <v>Panel Craft list #4</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="201">
@@ -5021,10 +5021,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C201" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D201" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E201" t="str">
         <v>Future</v>
@@ -5033,7 +5033,7 @@
         <v/>
       </c>
       <c r="G201" t="str">
-        <v>Panel Craft list #5</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="202">
@@ -5044,10 +5044,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C202" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D202" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E202" t="str">
         <v>Future</v>
@@ -5056,7 +5056,7 @@
         <v/>
       </c>
       <c r="G202" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="203">
@@ -5067,10 +5067,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C203" t="str">
-        <v>Bill / expense</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D203" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E203" t="str">
         <v>Future</v>
@@ -5079,7 +5079,7 @@
         <v/>
       </c>
       <c r="G203" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="204">
@@ -5087,22 +5087,22 @@
         <v>203</v>
       </c>
       <c r="B204" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C204" t="str">
-        <v>System reference and change-request register</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D204" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E204" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F204" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G204" t="str">
-        <v/>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="205">
@@ -5113,10 +5113,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C205" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D205" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E205" t="str">
         <v>Completed</v>
@@ -5136,10 +5136,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C206" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Change log, user flow, user manual</v>
       </c>
       <c r="D206" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
@@ -5159,19 +5159,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C207" t="str">
-        <v>Data Flow reference</v>
+        <v>Seed and teardown scripts</v>
       </c>
       <c r="D207" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
       </c>
       <c r="F207" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G207" t="str">
-        <v>CR-272</v>
+        <v/>
       </c>
     </row>
     <row r="208">
@@ -5182,10 +5182,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C208" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Data Flow reference</v>
       </c>
       <c r="D208" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
       </c>
       <c r="E208" t="str">
         <v>Completed</v>
@@ -5194,7 +5194,7 @@
         <v>2026-10-03</v>
       </c>
       <c r="G208" t="str">
-        <v/>
+        <v>CR-272</v>
       </c>
     </row>
     <row r="209">
@@ -5205,19 +5205,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C209" t="str">
-        <v>Locations guide</v>
+        <v>Phase 2 inventory</v>
       </c>
       <c r="D209" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
       </c>
       <c r="E209" t="str">
         <v>Completed</v>
       </c>
       <c r="F209" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G209" t="str">
-        <v>CR-411…413</v>
+        <v/>
       </c>
     </row>
     <row r="210">
@@ -5228,19 +5228,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C210" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Locations guide</v>
       </c>
       <c r="D210" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
       </c>
       <c r="F210" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G210" t="str">
-        <v/>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="211">
@@ -5251,19 +5251,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C211" t="str">
-        <v>Demo / test environment</v>
+        <v>Deliverables list (this workbook)</v>
       </c>
       <c r="D211" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
       </c>
       <c r="F211" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G211" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="212">
@@ -5274,25 +5274,48 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C212" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D212" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E212" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F212" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G212" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C213" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D212" t="str">
+      <c r="D213" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E212" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F212" t="str">
+      <c r="E213" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F213" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G212" t="str">
+      <c r="G213" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G212"/>
+  <autoFilter ref="A1:G213"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G212"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G213"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G214</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G213"/>
+  <dimension ref="A1:G214"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -4584,10 +4584,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C182" t="str">
-        <v>Stock history in date order</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D182" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E182" t="str">
         <v>Completed</v>
@@ -4596,7 +4596,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-455</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="183">
@@ -4604,22 +4604,22 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C183" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D183" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E183" t="str">
         <v>Completed</v>
       </c>
       <c r="F183" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-447</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="184">
@@ -4627,13 +4627,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C184" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D184" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E184" t="str">
         <v>Completed</v>
@@ -4642,7 +4642,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G184" t="str">
-        <v>CR-448</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="185">
@@ -4653,19 +4653,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D185" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E185" t="str">
         <v>Completed</v>
       </c>
       <c r="F185" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G185" t="str">
-        <v>CR-456</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="186">
@@ -4676,19 +4676,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D186" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E186" t="str">
         <v>Completed</v>
       </c>
       <c r="F186" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G186" t="str">
-        <v>CR-449</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="187">
@@ -4699,10 +4699,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C187" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D187" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E187" t="str">
         <v>Completed</v>
@@ -4711,7 +4711,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-450</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="188">
@@ -4719,22 +4719,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C188" t="str">
-        <v>Location at every stage</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D188" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
       </c>
       <c r="F188" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-411…413</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="189">
@@ -4742,13 +4742,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C189" t="str">
-        <v>Panel location</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D189" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
@@ -4757,7 +4757,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-410</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="190">
@@ -4768,10 +4768,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C190" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel location</v>
       </c>
       <c r="D190" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
@@ -4780,7 +4780,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-419</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="191">
@@ -4791,10 +4791,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C191" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D191" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
@@ -4803,7 +4803,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-415</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="192">
@@ -4811,13 +4811,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C192" t="str">
-        <v>No long helper notes</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D192" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
@@ -4826,7 +4826,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-416</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="193">
@@ -4834,13 +4834,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Production</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C193" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D193" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E193" t="str">
         <v>Completed</v>
@@ -4849,7 +4849,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-417</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="194">
@@ -4857,13 +4857,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Production</v>
       </c>
       <c r="C194" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D194" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E194" t="str">
         <v>Completed</v>
@@ -4872,7 +4872,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G194" t="str">
-        <v>CR-418</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="195">
@@ -4883,10 +4883,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C195" t="str">
-        <v>Notifications read / unread</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D195" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
@@ -4895,7 +4895,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-419…421</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="196">
@@ -4903,13 +4903,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C196" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D196" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
@@ -4918,7 +4918,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-422</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="197">
@@ -4926,22 +4926,22 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C197" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D197" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
       </c>
       <c r="F197" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-404</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="198">
@@ -4952,19 +4952,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C198" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D198" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E198" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F198" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="199">
@@ -4975,19 +4975,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C199" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D199" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E199" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F199" t="str">
         <v/>
       </c>
       <c r="G199" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="200">
@@ -4998,10 +4998,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C200" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D200" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E200" t="str">
         <v>Future</v>
@@ -5010,7 +5010,7 @@
         <v/>
       </c>
       <c r="G200" t="str">
-        <v>Panel Craft list #2</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="201">
@@ -5021,10 +5021,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C201" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D201" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E201" t="str">
         <v>Future</v>
@@ -5033,7 +5033,7 @@
         <v/>
       </c>
       <c r="G201" t="str">
-        <v>Panel Craft list #4</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="202">
@@ -5044,10 +5044,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C202" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D202" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E202" t="str">
         <v>Future</v>
@@ -5056,7 +5056,7 @@
         <v/>
       </c>
       <c r="G202" t="str">
-        <v>Panel Craft list #5</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="203">
@@ -5067,10 +5067,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C203" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D203" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E203" t="str">
         <v>Future</v>
@@ -5079,7 +5079,7 @@
         <v/>
       </c>
       <c r="G203" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="204">
@@ -5090,10 +5090,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C204" t="str">
-        <v>Bill / expense</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D204" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E204" t="str">
         <v>Future</v>
@@ -5102,7 +5102,7 @@
         <v/>
       </c>
       <c r="G204" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="205">
@@ -5110,22 +5110,22 @@
         <v>204</v>
       </c>
       <c r="B205" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C205" t="str">
-        <v>System reference and change-request register</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D205" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E205" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F205" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G205" t="str">
-        <v/>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="206">
@@ -5136,10 +5136,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C206" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D206" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
@@ -5159,10 +5159,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C207" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Change log, user flow, user manual</v>
       </c>
       <c r="D207" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
@@ -5182,19 +5182,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C208" t="str">
-        <v>Data Flow reference</v>
+        <v>Seed and teardown scripts</v>
       </c>
       <c r="D208" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
       </c>
       <c r="E208" t="str">
         <v>Completed</v>
       </c>
       <c r="F208" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G208" t="str">
-        <v>CR-272</v>
+        <v/>
       </c>
     </row>
     <row r="209">
@@ -5205,10 +5205,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C209" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Data Flow reference</v>
       </c>
       <c r="D209" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
       </c>
       <c r="E209" t="str">
         <v>Completed</v>
@@ -5217,7 +5217,7 @@
         <v>2026-10-03</v>
       </c>
       <c r="G209" t="str">
-        <v/>
+        <v>CR-272</v>
       </c>
     </row>
     <row r="210">
@@ -5228,19 +5228,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C210" t="str">
-        <v>Locations guide</v>
+        <v>Phase 2 inventory</v>
       </c>
       <c r="D210" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
       </c>
       <c r="F210" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G210" t="str">
-        <v>CR-411…413</v>
+        <v/>
       </c>
     </row>
     <row r="211">
@@ -5251,19 +5251,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C211" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Locations guide</v>
       </c>
       <c r="D211" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
       </c>
       <c r="F211" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G211" t="str">
-        <v/>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="212">
@@ -5274,19 +5274,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C212" t="str">
-        <v>Demo / test environment</v>
+        <v>Deliverables list (this workbook)</v>
       </c>
       <c r="D212" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
       </c>
       <c r="F212" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G212" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="213">
@@ -5297,25 +5297,48 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C213" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D213" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E213" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F213" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G213" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C214" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D213" t="str">
+      <c r="D214" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E213" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F213" t="str">
+      <c r="E214" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F214" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G213" t="str">
+      <c r="G214" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G213"/>
+  <autoFilter ref="A1:G214"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G214"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G218</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G218"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -4604,22 +4604,22 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C183" t="str">
-        <v>Stock history in date order</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D183" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E183" t="str">
         <v>Completed</v>
       </c>
       <c r="F183" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-455</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="184">
@@ -4630,19 +4630,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C184" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D184" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E184" t="str">
         <v>Completed</v>
       </c>
       <c r="F184" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G184" t="str">
-        <v>CR-447</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="185">
@@ -4650,22 +4650,22 @@
         <v>184</v>
       </c>
       <c r="B185" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C185" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D185" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E185" t="str">
         <v>Completed</v>
       </c>
       <c r="F185" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G185" t="str">
-        <v>CR-448</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="186">
@@ -4673,22 +4673,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="str">
-        <v>Panel Craft</v>
+        <v>Customers</v>
       </c>
       <c r="C186" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D186" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E186" t="str">
         <v>Completed</v>
       </c>
       <c r="F186" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G186" t="str">
-        <v>CR-456</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="187">
@@ -4696,22 +4696,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C187" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D187" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E187" t="str">
         <v>Completed</v>
       </c>
       <c r="F187" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-449</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="188">
@@ -4719,13 +4719,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C188" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D188" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
@@ -4734,7 +4734,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-450</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="189">
@@ -4742,22 +4742,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C189" t="str">
-        <v>Location at every stage</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D189" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
       </c>
       <c r="F189" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-411…413</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="190">
@@ -4768,19 +4768,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C190" t="str">
-        <v>Panel location</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D190" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
       </c>
       <c r="F190" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-410</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="191">
@@ -4791,19 +4791,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C191" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D191" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
       </c>
       <c r="F191" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-419</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="192">
@@ -4814,19 +4814,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C192" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D192" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
       </c>
       <c r="F192" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-415</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="193">
@@ -4834,13 +4834,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C193" t="str">
-        <v>No long helper notes</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D193" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E193" t="str">
         <v>Completed</v>
@@ -4849,7 +4849,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-416</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="194">
@@ -4857,13 +4857,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Production</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C194" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>Panel location</v>
       </c>
       <c r="D194" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E194" t="str">
         <v>Completed</v>
@@ -4872,7 +4872,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G194" t="str">
-        <v>CR-417</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="195">
@@ -4880,13 +4880,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C195" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D195" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
@@ -4895,7 +4895,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-418</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="196">
@@ -4903,13 +4903,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C196" t="str">
-        <v>Notifications read / unread</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D196" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
@@ -4918,7 +4918,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-419…421</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="197">
@@ -4926,13 +4926,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C197" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D197" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
@@ -4941,7 +4941,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-422</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="198">
@@ -4949,22 +4949,22 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Panel Craft</v>
+        <v>Production</v>
       </c>
       <c r="C198" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D198" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
       </c>
       <c r="F198" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-404</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="199">
@@ -4972,22 +4972,22 @@
         <v>198</v>
       </c>
       <c r="B199" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C199" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D199" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E199" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F199" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="200">
@@ -4995,22 +4995,22 @@
         <v>199</v>
       </c>
       <c r="B200" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C200" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D200" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E200" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F200" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G200" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="201">
@@ -5018,22 +5018,22 @@
         <v>200</v>
       </c>
       <c r="B201" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C201" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D201" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E201" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F201" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G201" t="str">
-        <v>Panel Craft list #2</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="202">
@@ -5044,19 +5044,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C202" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D202" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E202" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F202" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G202" t="str">
-        <v>Panel Craft list #4</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="203">
@@ -5067,19 +5067,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C203" t="str">
-        <v>Godown print — issue / request</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D203" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E203" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F203" t="str">
         <v/>
       </c>
       <c r="G203" t="str">
-        <v>Panel Craft list #5</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="204">
@@ -5090,10 +5090,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C204" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D204" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E204" t="str">
         <v>Future</v>
@@ -5102,7 +5102,7 @@
         <v/>
       </c>
       <c r="G204" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="205">
@@ -5113,10 +5113,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C205" t="str">
-        <v>Bill / expense</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D205" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E205" t="str">
         <v>Future</v>
@@ -5125,7 +5125,7 @@
         <v/>
       </c>
       <c r="G205" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="206">
@@ -5133,22 +5133,22 @@
         <v>205</v>
       </c>
       <c r="B206" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C206" t="str">
-        <v>System reference and change-request register</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D206" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E206" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F206" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G206" t="str">
-        <v/>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="207">
@@ -5156,22 +5156,22 @@
         <v>206</v>
       </c>
       <c r="B207" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C207" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D207" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E207" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F207" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G207" t="str">
-        <v/>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="208">
@@ -5179,22 +5179,22 @@
         <v>207</v>
       </c>
       <c r="B208" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C208" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D208" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E208" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F208" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G208" t="str">
-        <v/>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="209">
@@ -5202,22 +5202,22 @@
         <v>208</v>
       </c>
       <c r="B209" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C209" t="str">
-        <v>Data Flow reference</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D209" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E209" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F209" t="str">
-        <v>2026-10-03</v>
+        <v/>
       </c>
       <c r="G209" t="str">
-        <v>CR-272</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="210">
@@ -5228,16 +5228,16 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C210" t="str">
-        <v>Phase 2 inventory</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D210" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
       </c>
       <c r="F210" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G210" t="str">
         <v/>
@@ -5251,19 +5251,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C211" t="str">
-        <v>Locations guide</v>
+        <v>Change log, user flow, user manual</v>
       </c>
       <c r="D211" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
       </c>
       <c r="F211" t="str">
-        <v>2026-10-24</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G211" t="str">
-        <v>CR-411…413</v>
+        <v/>
       </c>
     </row>
     <row r="212">
@@ -5274,16 +5274,16 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C212" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Seed and teardown scripts</v>
       </c>
       <c r="D212" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
       </c>
       <c r="F212" t="str">
-        <v>2026-10-22</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G212" t="str">
         <v/>
@@ -5297,19 +5297,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C213" t="str">
-        <v>Demo / test environment</v>
+        <v>Data Flow reference</v>
       </c>
       <c r="D213" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
       </c>
       <c r="F213" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-441</v>
+        <v>CR-272</v>
       </c>
     </row>
     <row r="214">
@@ -5320,25 +5320,117 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C214" t="str">
+        <v>Phase 2 inventory</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+      </c>
+      <c r="E214" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F214" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Locations guide</v>
+      </c>
+      <c r="D215" t="str">
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+      </c>
+      <c r="E215" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F215" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="G215" t="str">
+        <v>CR-411…413</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Deliverables list (this workbook)</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+      </c>
+      <c r="E216" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F216" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D217" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E217" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F217" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G217" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C218" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D214" t="str">
+      <c r="D218" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E214" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F214" t="str">
+      <c r="E218" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F218" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G214" t="str">
+      <c r="G218" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G214"/>
+  <autoFilter ref="A1:G218"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G214"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G218"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G225</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G225"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -2192,19 +2192,19 @@
         <v>Production</v>
       </c>
       <c r="C78" t="str">
-        <v>Record Production sheet (bulk, make-to-stock)</v>
+        <v>Bulk Record Production (make-to-stock)</v>
       </c>
       <c r="D78" t="str">
-        <v>One ruled sheet, one row per item: Size · Design · Batch (blank = automatic) · Box Brand · Qty · Remark; paste from Excel; one Save records every row into stock; retry-safe.</v>
+        <v>A form in the Adjust Stock shape: Production date, recorded by and a description over an Item Table — Size · Item · Batch (blank = automatic) · Qty · Box Brand · Location per line — one line to start, + Add line; paste a block from Excel; one Save records every line into stock; retry-safe.</v>
       </c>
       <c r="E78" t="str">
         <v>Completed</v>
       </c>
       <c r="F78" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G78" t="str">
-        <v>CR-244, 264</v>
+        <v>CR-244, 264, 469</v>
       </c>
     </row>
     <row r="79">
@@ -2215,19 +2215,19 @@
         <v>Production</v>
       </c>
       <c r="C79" t="str">
-        <v>Sheet edit mode</v>
+        <v>Sales Order ▸ Production tab per design</v>
       </c>
       <c r="D79" t="str">
-        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
+        <v>One row per design with its batches as chips and the requested / produced totals summed; totals footers on both tables.</v>
       </c>
       <c r="E79" t="str">
         <v>Completed</v>
       </c>
       <c r="F79" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G79" t="str">
-        <v>CR-111</v>
+        <v>CR-470</v>
       </c>
     </row>
     <row r="80">
@@ -2238,10 +2238,10 @@
         <v>Production</v>
       </c>
       <c r="C80" t="str">
-        <v>Excel import of the factory file</v>
+        <v>Sheet edit mode</v>
       </c>
       <c r="D80" t="str">
-        <v>Import production from the factory's spreadsheet.</v>
+        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
       </c>
       <c r="E80" t="str">
         <v>Completed</v>
@@ -2250,7 +2250,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G80" t="str">
-        <v/>
+        <v>CR-111</v>
       </c>
     </row>
     <row r="81">
@@ -2261,10 +2261,10 @@
         <v>Production</v>
       </c>
       <c r="C81" t="str">
-        <v>Batch numbering and rules</v>
+        <v>Excel import of the factory file</v>
       </c>
       <c r="D81" t="str">
-        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
+        <v>Import production from the factory's spreadsheet.</v>
       </c>
       <c r="E81" t="str">
         <v>Completed</v>
@@ -2284,10 +2284,10 @@
         <v>Production</v>
       </c>
       <c r="C82" t="str">
-        <v>Production detail page</v>
+        <v>Batch numbering and rules</v>
       </c>
       <c r="D82" t="str">
-        <v>Lines, batches logged, activity.</v>
+        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
       </c>
       <c r="E82" t="str">
         <v>Completed</v>
@@ -2307,19 +2307,19 @@
         <v>Production</v>
       </c>
       <c r="C83" t="str">
-        <v>Date-first production</v>
+        <v>Production detail page</v>
       </c>
       <c r="D83" t="str">
-        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
+        <v>Lines, batches logged, activity.</v>
       </c>
       <c r="E83" t="str">
         <v>Completed</v>
       </c>
       <c r="F83" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G83" t="str">
-        <v>CR-265, 267</v>
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -2330,19 +2330,19 @@
         <v>Production</v>
       </c>
       <c r="C84" t="str">
-        <v>Quality Control stage on the board</v>
+        <v>Date-first production</v>
       </c>
       <c r="D84" t="str">
-        <v>QC exists in the data model; putting it on the board is parked.</v>
+        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
       </c>
       <c r="E84" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F84" t="str">
-        <v/>
+        <v>2026-10-03</v>
       </c>
       <c r="G84" t="str">
-        <v>CR-051</v>
+        <v>CR-265, 267</v>
       </c>
     </row>
     <row r="85">
@@ -2353,10 +2353,10 @@
         <v>Production</v>
       </c>
       <c r="C85" t="str">
-        <v>Duplicate detection on Excel re-import</v>
+        <v>Quality Control stage on the board</v>
       </c>
       <c r="D85" t="str">
-        <v>Warn / skip when the same production file is imported twice.</v>
+        <v>QC exists in the data model; putting it on the board is parked.</v>
       </c>
       <c r="E85" t="str">
         <v>Future</v>
@@ -2365,7 +2365,7 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v/>
+        <v>CR-051</v>
       </c>
     </row>
     <row r="86">
@@ -2373,19 +2373,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>Palletization</v>
+        <v>Production</v>
       </c>
       <c r="C86" t="str">
-        <v>Palletization board and plan numbers</v>
+        <v>Duplicate detection on Excel re-import</v>
       </c>
       <c r="D86" t="str">
-        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
+        <v>Warn / skip when the same production file is imported twice.</v>
       </c>
       <c r="E86" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F86" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -2399,10 +2399,10 @@
         <v>Palletization</v>
       </c>
       <c r="C87" t="str">
-        <v>Columns, totals footer and selection bar</v>
+        <v>Palletization board and plan numbers</v>
       </c>
       <c r="D87" t="str">
-        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
+        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
       </c>
       <c r="E87" t="str">
         <v>Completed</v>
@@ -2411,7 +2411,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G87" t="str">
-        <v>CR-279</v>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -2422,10 +2422,10 @@
         <v>Palletization</v>
       </c>
       <c r="C88" t="str">
-        <v>Plan detail page</v>
+        <v>Columns, totals footer and selection bar</v>
       </c>
       <c r="D88" t="str">
-        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
+        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
       </c>
       <c r="E88" t="str">
         <v>Completed</v>
@@ -2434,7 +2434,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>CR-279</v>
       </c>
     </row>
     <row r="89">
@@ -2445,19 +2445,19 @@
         <v>Palletization</v>
       </c>
       <c r="C89" t="str">
-        <v>Prints on demand</v>
+        <v>Counts per batch: Ordered · Ready Pallets · Boxes / Pallet · Remaining</v>
       </c>
       <c r="D89" t="str">
-        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
+        <v>Every palletization page counts the row's own batch — a loaded batch of the same item no longer shows on its sibling. Columns Boxes · Ordered Boxes · Ready Pallets (N (boxes)) · Boxes / Pallet · Remaining with totals; the Complete Palletization dialog shows the same figures.</v>
       </c>
       <c r="E89" t="str">
         <v>Completed</v>
       </c>
       <c r="F89" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G89" t="str">
-        <v/>
+        <v>CR-472</v>
       </c>
     </row>
     <row r="90">
@@ -2468,10 +2468,10 @@
         <v>Palletization</v>
       </c>
       <c r="C90" t="str">
-        <v>Board rules</v>
+        <v>Plan detail page</v>
       </c>
       <c r="D90" t="str">
-        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
+        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
       </c>
       <c r="E90" t="str">
         <v>Completed</v>
@@ -2480,7 +2480,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G90" t="str">
-        <v>CR-129, 248</v>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -2491,10 +2491,10 @@
         <v>Palletization</v>
       </c>
       <c r="C91" t="str">
-        <v>Three ways onto the queue</v>
+        <v>Prints on demand</v>
       </c>
       <c r="D91" t="str">
-        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
+        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
       </c>
       <c r="E91" t="str">
         <v>Completed</v>
@@ -2503,7 +2503,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G91" t="str">
-        <v>CR-223/224</v>
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -2514,10 +2514,10 @@
         <v>Palletization</v>
       </c>
       <c r="C92" t="str">
-        <v>'+' menu: Start / Top Up Batch / Complete</v>
+        <v>Board rules</v>
       </c>
       <c r="D92" t="str">
-        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
+        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
       </c>
       <c r="E92" t="str">
         <v>Completed</v>
@@ -2526,7 +2526,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G92" t="str">
-        <v>CR-148…150, 281</v>
+        <v>CR-129, 248</v>
       </c>
     </row>
     <row r="93">
@@ -2537,10 +2537,10 @@
         <v>Palletization</v>
       </c>
       <c r="C93" t="str">
-        <v>Sheet edit mode and multi-select</v>
+        <v>Three ways onto the queue</v>
       </c>
       <c r="D93" t="str">
-        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
+        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
       </c>
       <c r="E93" t="str">
         <v>Completed</v>
@@ -2549,7 +2549,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G93" t="str">
-        <v>CR-153</v>
+        <v>CR-223/224</v>
       </c>
     </row>
     <row r="94">
@@ -2560,19 +2560,19 @@
         <v>Palletization</v>
       </c>
       <c r="C94" t="str">
-        <v>Date column, PAL code hidden</v>
+        <v>'+' menu: Start / Top Up Batch / Complete</v>
       </c>
       <c r="D94" t="str">
-        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
+        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
       </c>
       <c r="E94" t="str">
         <v>Completed</v>
       </c>
       <c r="F94" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G94" t="str">
-        <v>CR-266</v>
+        <v>CR-148…150, 281</v>
       </c>
     </row>
     <row r="95">
@@ -2583,19 +2583,19 @@
         <v>Palletization</v>
       </c>
       <c r="C95" t="str">
-        <v>Complete dialog shows progress</v>
+        <v>Sheet edit mode and multi-select</v>
       </c>
       <c r="D95" t="str">
-        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
+        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
       </c>
       <c r="E95" t="str">
         <v>Completed</v>
       </c>
       <c r="F95" t="str">
-        <v>2026-10-06</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G95" t="str">
-        <v>CR-280</v>
+        <v>CR-153</v>
       </c>
     </row>
     <row r="96">
@@ -2606,19 +2606,19 @@
         <v>Palletization</v>
       </c>
       <c r="C96" t="str">
-        <v>Plan edit keeps Box Brand and batches</v>
+        <v>Date column, PAL code hidden</v>
       </c>
       <c r="D96" t="str">
-        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
+        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
       </c>
       <c r="E96" t="str">
         <v>Completed</v>
       </c>
       <c r="F96" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G96" t="str">
-        <v>CR-340</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="97">
@@ -2629,19 +2629,19 @@
         <v>Palletization</v>
       </c>
       <c r="C97" t="str">
-        <v>Three pages, one stage each</v>
+        <v>Complete dialog shows progress</v>
       </c>
       <c r="D97" t="str">
-        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
+        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
       </c>
       <c r="E97" t="str">
         <v>Completed</v>
       </c>
       <c r="F97" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-06</v>
       </c>
       <c r="G97" t="str">
-        <v>CR-360, 364</v>
+        <v>CR-280</v>
       </c>
     </row>
     <row r="98">
@@ -2652,19 +2652,19 @@
         <v>Palletization</v>
       </c>
       <c r="C98" t="str">
-        <v>Release palletized boxes</v>
+        <v>Plan edit keeps Box Brand and batches</v>
       </c>
       <c r="D98" t="str">
-        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
+        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
       </c>
       <c r="E98" t="str">
         <v>Completed</v>
       </c>
       <c r="F98" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G98" t="str">
-        <v>CR-361</v>
+        <v>CR-340</v>
       </c>
     </row>
     <row r="99">
@@ -2675,19 +2675,19 @@
         <v>Palletization</v>
       </c>
       <c r="C99" t="str">
-        <v>Discard the current palletization task</v>
+        <v>Three pages, one stage each</v>
       </c>
       <c r="D99" t="str">
-        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
+        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
       </c>
       <c r="E99" t="str">
         <v>Completed</v>
       </c>
       <c r="F99" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G99" t="str">
-        <v>CR-369</v>
+        <v>CR-360, 364</v>
       </c>
     </row>
     <row r="100">
@@ -2698,19 +2698,19 @@
         <v>Palletization</v>
       </c>
       <c r="C100" t="str">
-        <v>Delete a plan returns its boxes</v>
+        <v>Release palletized boxes</v>
       </c>
       <c r="D100" t="str">
-        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
+        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
       </c>
       <c r="E100" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F100" t="str">
-        <v/>
+        <v>2026-10-21</v>
       </c>
       <c r="G100" t="str">
-        <v>CR-370</v>
+        <v>CR-361</v>
       </c>
     </row>
     <row r="101">
@@ -2721,19 +2721,19 @@
         <v>Palletization</v>
       </c>
       <c r="C101" t="str">
-        <v>Partial Start Palletization</v>
+        <v>Discard the current palletization task</v>
       </c>
       <c r="D101" t="str">
-        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
+        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
       </c>
       <c r="E101" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F101" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G101" t="str">
-        <v>Panel Craft list #9</v>
+        <v>CR-369</v>
       </c>
     </row>
     <row r="102">
@@ -2744,19 +2744,19 @@
         <v>Palletization</v>
       </c>
       <c r="C102" t="str">
-        <v>Ready pallets — type and pallet count</v>
+        <v>Delete a plan returns its boxes</v>
       </c>
       <c r="D102" t="str">
-        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
+        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
       </c>
       <c r="E102" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F102" t="str">
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>Panel Craft list #7</v>
+        <v>CR-370</v>
       </c>
     </row>
     <row r="103">
@@ -2767,10 +2767,10 @@
         <v>Palletization</v>
       </c>
       <c r="C103" t="str">
-        <v>Remove 'Ordered / Completed' where not needed</v>
+        <v>Partial Start Palletization</v>
       </c>
       <c r="D103" t="str">
-        <v>Screen to be confirmed.</v>
+        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
       </c>
       <c r="E103" t="str">
         <v>Future</v>
@@ -2779,7 +2779,7 @@
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>Panel Craft list #8</v>
+        <v>Panel Craft list #9</v>
       </c>
     </row>
     <row r="104">
@@ -2787,22 +2787,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C104" t="str">
-        <v>A loading = one container</v>
+        <v>Ready pallets — type and pallet count</v>
       </c>
       <c r="D104" t="str">
-        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
+        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
       </c>
       <c r="E104" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F104" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G104" t="str">
-        <v>CR-120…124</v>
+        <v>Panel Craft list #7</v>
       </c>
     </row>
     <row r="105">
@@ -2810,22 +2810,22 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C105" t="str">
-        <v>Loading and Dispatch page</v>
+        <v>Remove 'Ordered / Completed' where not needed</v>
       </c>
       <c r="D105" t="str">
-        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
+        <v>Screen to be confirmed.</v>
       </c>
       <c r="E105" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F105" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G105" t="str">
-        <v>CR-140, 141</v>
+        <v>Panel Craft list #8</v>
       </c>
     </row>
     <row r="106">
@@ -2836,10 +2836,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C106" t="str">
-        <v>Loading detail</v>
+        <v>A loading = one container</v>
       </c>
       <c r="D106" t="str">
-        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
+        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
       </c>
       <c r="E106" t="str">
         <v>Completed</v>
@@ -2848,7 +2848,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>CR-120…124</v>
       </c>
     </row>
     <row r="107">
@@ -2859,10 +2859,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C107" t="str">
-        <v>Vehicle and shipment details</v>
+        <v>Loading and Dispatch page</v>
       </c>
       <c r="D107" t="str">
-        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
+        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
       </c>
       <c r="E107" t="str">
         <v>Completed</v>
@@ -2871,7 +2871,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>CR-140, 141</v>
       </c>
     </row>
     <row r="108">
@@ -2882,10 +2882,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C108" t="str">
-        <v>Dispatch with gates and warnings</v>
+        <v>Loading detail</v>
       </c>
       <c r="D108" t="str">
-        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
+        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
       </c>
       <c r="E108" t="str">
         <v>Completed</v>
@@ -2905,10 +2905,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C109" t="str">
-        <v>Invoice and dispatch prints</v>
+        <v>Vehicle and shipment details</v>
       </c>
       <c r="D109" t="str">
-        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
+        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
       </c>
       <c r="E109" t="str">
         <v>Completed</v>
@@ -2928,10 +2928,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C110" t="str">
-        <v>Four ways to fill a container</v>
+        <v>Dispatch with gates and warnings</v>
       </c>
       <c r="D110" t="str">
-        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
+        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
       </c>
       <c r="E110" t="str">
         <v>Completed</v>
@@ -2940,7 +2940,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G110" t="str">
-        <v>CR-126…128, 201/202</v>
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -2951,10 +2951,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C111" t="str">
-        <v>Editing a loading</v>
+        <v>Invoice and dispatch prints</v>
       </c>
       <c r="D111" t="str">
-        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
+        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
       </c>
       <c r="E111" t="str">
         <v>Completed</v>
@@ -2974,19 +2974,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C112" t="str">
-        <v>Date column, LOAD code hidden</v>
+        <v>Four ways to fill a container</v>
       </c>
       <c r="D112" t="str">
-        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
+        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
       </c>
       <c r="E112" t="str">
         <v>Completed</v>
       </c>
       <c r="F112" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G112" t="str">
-        <v>CR-266</v>
+        <v>CR-126…128, 201/202</v>
       </c>
     </row>
     <row r="113">
@@ -2997,19 +2997,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C113" t="str">
-        <v>Several containers in one New Loading</v>
+        <v>Editing a loading</v>
       </c>
       <c r="D113" t="str">
-        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
+        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
       </c>
       <c r="E113" t="str">
         <v>Completed</v>
       </c>
       <c r="F113" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G113" t="str">
-        <v>CR-301</v>
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -3020,19 +3020,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C114" t="str">
-        <v>Loading Workspace — a tab per container</v>
+        <v>Date column, LOAD code hidden</v>
       </c>
       <c r="D114" t="str">
-        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
+        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
       </c>
       <c r="E114" t="str">
         <v>Completed</v>
       </c>
       <c r="F114" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G114" t="str">
-        <v>CR-326, 334, 335</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="115">
@@ -3043,19 +3043,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C115" t="str">
-        <v>Every customer listed, with search</v>
+        <v>Several containers in one New Loading</v>
       </c>
       <c r="D115" t="str">
-        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
+        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
       </c>
       <c r="E115" t="str">
         <v>Completed</v>
       </c>
       <c r="F115" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G115" t="str">
-        <v>CR-327</v>
+        <v>CR-301</v>
       </c>
     </row>
     <row r="116">
@@ -3066,10 +3066,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C116" t="str">
-        <v>'What to do first' reasons</v>
+        <v>Loading Workspace — a tab per container</v>
       </c>
       <c r="D116" t="str">
-        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
+        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
       </c>
       <c r="E116" t="str">
         <v>Completed</v>
@@ -3078,7 +3078,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G116" t="str">
-        <v>CR-328</v>
+        <v>CR-326, 334, 335</v>
       </c>
     </row>
     <row r="117">
@@ -3089,19 +3089,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C117" t="str">
-        <v>Pick the planned container at loading</v>
+        <v>Every customer listed, with search</v>
       </c>
       <c r="D117" t="str">
-        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
+        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
       </c>
       <c r="E117" t="str">
         <v>Completed</v>
       </c>
       <c r="F117" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G117" t="str">
-        <v>CR-338</v>
+        <v>CR-327</v>
       </c>
     </row>
     <row r="118">
@@ -3112,19 +3112,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C118" t="str">
-        <v>Two steps per container; C1 / C2 naming</v>
+        <v>'What to do first' reasons</v>
       </c>
       <c r="D118" t="str">
-        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
+        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
       </c>
       <c r="E118" t="str">
         <v>Completed</v>
       </c>
       <c r="F118" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G118" t="str">
-        <v>CR-350, 354</v>
+        <v>CR-328</v>
       </c>
     </row>
     <row r="119">
@@ -3135,19 +3135,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C119" t="str">
-        <v>Mix Batch at loading</v>
+        <v>Pick the planned container at loading</v>
       </c>
       <c r="D119" t="str">
-        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
+        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
       </c>
       <c r="E119" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>2026-10-13</v>
       </c>
       <c r="G119" t="str">
-        <v>CR-260 follow-up</v>
+        <v>CR-338</v>
       </c>
     </row>
     <row r="120">
@@ -3155,22 +3155,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C120" t="str">
-        <v>One stock rule everywhere</v>
+        <v>Two steps per container; C1 / C2 naming</v>
       </c>
       <c r="D120" t="str">
-        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
+        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
       </c>
       <c r="E120" t="str">
         <v>Completed</v>
       </c>
       <c r="F120" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G120" t="str">
-        <v/>
+        <v>CR-350, 354</v>
       </c>
     </row>
     <row r="121">
@@ -3178,22 +3178,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C121" t="str">
-        <v>Counters recomputed, never incremented</v>
+        <v>Mix Batch at loading</v>
       </c>
       <c r="D121" t="str">
-        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
+        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
       </c>
       <c r="E121" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F121" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G121" t="str">
-        <v/>
+        <v>CR-260 follow-up</v>
       </c>
     </row>
     <row r="122">
@@ -3204,10 +3204,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C122" t="str">
-        <v>Allocation and batch ledger</v>
+        <v>One stock rule everywhere</v>
       </c>
       <c r="D122" t="str">
-        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
+        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
       </c>
       <c r="E122" t="str">
         <v>Completed</v>
@@ -3227,10 +3227,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C123" t="str">
-        <v>Admin repair operations</v>
+        <v>Counters recomputed, never incremented</v>
       </c>
       <c r="D123" t="str">
-        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
+        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
       </c>
       <c r="E123" t="str">
         <v>Completed</v>
@@ -3250,19 +3250,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C124" t="str">
-        <v>Inventory adjustments</v>
+        <v>Allocation and batch ledger</v>
       </c>
       <c r="D124" t="str">
-        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
+        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
       </c>
       <c r="E124" t="str">
         <v>Completed</v>
       </c>
       <c r="F124" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G124" t="str">
-        <v>CR-308</v>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -3273,19 +3273,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C125" t="str">
-        <v>Stock per warehouse</v>
+        <v>Admin repair operations</v>
       </c>
       <c r="D125" t="str">
-        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
+        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
       </c>
       <c r="E125" t="str">
         <v>Completed</v>
       </c>
       <c r="F125" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G125" t="str">
-        <v>CR-329</v>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3296,19 +3296,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C126" t="str">
-        <v>Transfer Orders</v>
+        <v>Inventory adjustments</v>
       </c>
       <c r="D126" t="str">
-        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
+        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
       </c>
       <c r="E126" t="str">
         <v>Completed</v>
       </c>
       <c r="F126" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G126" t="str">
-        <v>CR-330</v>
+        <v>CR-308</v>
       </c>
     </row>
     <row r="127">
@@ -3319,10 +3319,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C127" t="str">
-        <v>Locations on items</v>
+        <v>Stock per warehouse</v>
       </c>
       <c r="D127" t="str">
-        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
+        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
       </c>
       <c r="E127" t="str">
         <v>Completed</v>
@@ -3331,7 +3331,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G127" t="str">
-        <v>CR-332</v>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="128">
@@ -3342,19 +3342,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C128" t="str">
-        <v>Stock keyed by the item</v>
+        <v>Transfer Orders</v>
       </c>
       <c r="D128" t="str">
-        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
+        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
       </c>
       <c r="E128" t="str">
         <v>Completed</v>
       </c>
       <c r="F128" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G128" t="str">
-        <v>CR-341</v>
+        <v>CR-330</v>
       </c>
     </row>
     <row r="129">
@@ -3362,22 +3362,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C129" t="str">
-        <v>Sales reports</v>
+        <v>Locations on items</v>
       </c>
       <c r="D129" t="str">
-        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
+        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
       </c>
       <c r="E129" t="str">
         <v>Completed</v>
       </c>
       <c r="F129" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G129" t="str">
-        <v/>
+        <v>CR-332</v>
       </c>
     </row>
     <row r="130">
@@ -3385,22 +3385,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C130" t="str">
-        <v>Inventory reports</v>
+        <v>Stock keyed by the item</v>
       </c>
       <c r="D130" t="str">
-        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
+        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
       </c>
       <c r="E130" t="str">
         <v>Completed</v>
       </c>
       <c r="F130" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G130" t="str">
-        <v>CR-104</v>
+        <v>CR-341</v>
       </c>
     </row>
     <row r="131">
@@ -3411,10 +3411,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C131" t="str">
-        <v>Dispatch reports</v>
+        <v>Sales reports</v>
       </c>
       <c r="D131" t="str">
-        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
+        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
       </c>
       <c r="E131" t="str">
         <v>Completed</v>
@@ -3423,7 +3423,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G131" t="str">
-        <v>CR-104</v>
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -3434,10 +3434,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C132" t="str">
-        <v>Audit log and activity</v>
+        <v>Inventory reports</v>
       </c>
       <c r="D132" t="str">
-        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
+        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
       </c>
       <c r="E132" t="str">
         <v>Completed</v>
@@ -3446,7 +3446,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G132" t="str">
-        <v/>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="133">
@@ -3457,10 +3457,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C133" t="str">
-        <v>Dashboard</v>
+        <v>Dispatch reports</v>
       </c>
       <c r="D133" t="str">
-        <v>Headline numbers.</v>
+        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
       </c>
       <c r="E133" t="str">
         <v>Completed</v>
@@ -3469,7 +3469,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G133" t="str">
-        <v/>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="134">
@@ -3480,19 +3480,19 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C134" t="str">
-        <v>Warehouse Stock report</v>
+        <v>Audit log and activity</v>
       </c>
       <c r="D134" t="str">
-        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
+        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
       </c>
       <c r="E134" t="str">
         <v>Completed</v>
       </c>
       <c r="F134" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G134" t="str">
-        <v>CR-331</v>
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -3500,22 +3500,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C135" t="str">
-        <v>Panel Master</v>
+        <v>Dashboard</v>
       </c>
       <c r="D135" t="str">
-        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
+        <v>Headline numbers.</v>
       </c>
       <c r="E135" t="str">
         <v>Completed</v>
       </c>
       <c r="F135" t="str">
-        <v>2026-10-08</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G135" t="str">
-        <v>CR-283…285, 291, 319</v>
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -3523,22 +3523,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C136" t="str">
-        <v>Remarks on a panel</v>
+        <v>Warehouse Stock report</v>
       </c>
       <c r="D136" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
       </c>
       <c r="E136" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F136" t="str">
-        <v/>
+        <v>2026-10-12</v>
       </c>
       <c r="G136" t="str">
-        <v>CR-425</v>
+        <v>CR-331</v>
       </c>
     </row>
     <row r="137">
@@ -3549,19 +3549,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C137" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Panel Master</v>
       </c>
       <c r="D137" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
       </c>
       <c r="E137" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F137" t="str">
-        <v/>
+        <v>2026-10-08</v>
       </c>
       <c r="G137" t="str">
-        <v>CR-426</v>
+        <v>CR-283…285, 291, 319</v>
       </c>
     </row>
     <row r="138">
@@ -3569,13 +3569,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C138" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D138" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E138" t="str">
         <v>In progress</v>
@@ -3584,7 +3584,7 @@
         <v/>
       </c>
       <c r="G138" t="str">
-        <v>CR-427</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="139">
@@ -3592,22 +3592,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C139" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D139" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E139" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F139" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G139" t="str">
-        <v>CR-428</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="140">
@@ -3615,22 +3615,22 @@
         <v>139</v>
       </c>
       <c r="B140" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C140" t="str">
-        <v>One Masters page</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D140" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E140" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F140" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G140" t="str">
-        <v>CR-436</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="141">
@@ -3641,10 +3641,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C141" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D141" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E141" t="str">
         <v>Completed</v>
@@ -3653,7 +3653,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G141" t="str">
-        <v>CR-439</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="142">
@@ -3664,10 +3664,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C142" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>One Masters page</v>
       </c>
       <c r="D142" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E142" t="str">
         <v>Completed</v>
@@ -3676,7 +3676,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G142" t="str">
-        <v>CR-440</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="143">
@@ -3684,13 +3684,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>Items</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C143" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D143" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E143" t="str">
         <v>Completed</v>
@@ -3699,7 +3699,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G143" t="str">
-        <v>CR-437</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="144">
@@ -3710,19 +3710,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C144" t="str">
-        <v>Names save as Title Case</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D144" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E144" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F144" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G144" t="str">
-        <v>CR-429</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="145">
@@ -3730,22 +3730,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Items</v>
       </c>
       <c r="C145" t="str">
-        <v>Brand off the Item form</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D145" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E145" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F145" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G145" t="str">
-        <v>CR-430</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="146">
@@ -3753,22 +3753,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C146" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D146" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E146" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F146" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G146" t="str">
-        <v>CR-306</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="147">
@@ -3776,22 +3776,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C147" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D147" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E147" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F147" t="str">
-        <v>2026-10-15</v>
+        <v/>
       </c>
       <c r="G147" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="148">
@@ -3802,19 +3802,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C148" t="str">
-        <v>MDF master</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D148" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E148" t="str">
         <v>Completed</v>
       </c>
       <c r="F148" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G148" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="149">
@@ -3825,19 +3825,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C149" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D149" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E149" t="str">
         <v>Completed</v>
       </c>
       <c r="F149" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G149" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="150">
@@ -3848,19 +3848,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C150" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>MDF master</v>
       </c>
       <c r="D150" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E150" t="str">
         <v>Completed</v>
       </c>
       <c r="F150" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G150" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="151">
@@ -3871,19 +3871,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C151" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D151" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E151" t="str">
         <v>Completed</v>
       </c>
       <c r="F151" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G151" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="152">
@@ -3894,10 +3894,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C152" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D152" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
@@ -3906,7 +3906,7 @@
         <v>2026-10-07</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="153">
@@ -3917,19 +3917,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C153" t="str">
-        <v>Production checkpoints</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D153" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
       </c>
       <c r="F153" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="154">
@@ -3940,19 +3940,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C154" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D154" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
       </c>
       <c r="F154" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="155">
@@ -3963,19 +3963,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C155" t="str">
-        <v>Sample Orders</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D155" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E155" t="str">
         <v>Completed</v>
       </c>
       <c r="F155" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G155" t="str">
-        <v>CR-315…317</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="156">
@@ -3986,19 +3986,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C156" t="str">
-        <v>One Orders register</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D156" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E156" t="str">
         <v>Completed</v>
       </c>
       <c r="F156" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G156" t="str">
-        <v>CR-345</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="157">
@@ -4009,19 +4009,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C157" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D157" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E157" t="str">
         <v>Completed</v>
       </c>
       <c r="F157" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G157" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="158">
@@ -4032,10 +4032,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C158" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>One Orders register</v>
       </c>
       <c r="D158" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E158" t="str">
         <v>Completed</v>
@@ -4044,7 +4044,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G158" t="str">
-        <v>CR-349</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="159">
@@ -4055,19 +4055,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C159" t="str">
-        <v>Load Copy print</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D159" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E159" t="str">
         <v>Completed</v>
       </c>
       <c r="F159" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G159" t="str">
-        <v>CR-351</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="160">
@@ -4078,19 +4078,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C160" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D160" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E160" t="str">
         <v>Completed</v>
       </c>
       <c r="F160" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G160" t="str">
-        <v>CR-433</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="161">
@@ -4101,19 +4101,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C161" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D161" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
       </c>
       <c r="F161" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-311</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="162">
@@ -4124,19 +4124,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C162" t="str">
-        <v>Small UX items</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D162" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E162" t="str">
         <v>Completed</v>
       </c>
       <c r="F162" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="163">
@@ -4147,19 +4147,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C163" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D163" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E163" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F163" t="str">
-        <v/>
+        <v>2026-10-07</v>
       </c>
       <c r="G163" t="str">
-        <v>CR-365</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="164">
@@ -4170,19 +4170,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C164" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Small UX items</v>
       </c>
       <c r="D164" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E164" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F164" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G164" t="str">
-        <v>CR-366</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="165">
@@ -4193,10 +4193,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C165" t="str">
-        <v>One Status column</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D165" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E165" t="str">
         <v>In progress</v>
@@ -4205,7 +4205,7 @@
         <v/>
       </c>
       <c r="G165" t="str">
-        <v>CR-367</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="166">
@@ -4216,10 +4216,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C166" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D166" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E166" t="str">
         <v>In progress</v>
@@ -4228,7 +4228,7 @@
         <v/>
       </c>
       <c r="G166" t="str">
-        <v>CR-368</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="167">
@@ -4239,10 +4239,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C167" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>One Status column</v>
       </c>
       <c r="D167" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E167" t="str">
         <v>In progress</v>
@@ -4251,7 +4251,7 @@
         <v/>
       </c>
       <c r="G167" t="str">
-        <v>CR-399</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="168">
@@ -4262,10 +4262,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>One four-state order status</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D168" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E168" t="str">
         <v>In progress</v>
@@ -4274,7 +4274,7 @@
         <v/>
       </c>
       <c r="G168" t="str">
-        <v>CR-400</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="169">
@@ -4285,10 +4285,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D169" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E169" t="str">
         <v>In progress</v>
@@ -4297,7 +4297,7 @@
         <v/>
       </c>
       <c r="G169" t="str">
-        <v>CR-401</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="170">
@@ -4308,10 +4308,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D170" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E170" t="str">
         <v>In progress</v>
@@ -4320,7 +4320,7 @@
         <v/>
       </c>
       <c r="G170" t="str">
-        <v>CR-402</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="171">
@@ -4331,10 +4331,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D171" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E171" t="str">
         <v>In progress</v>
@@ -4343,7 +4343,7 @@
         <v/>
       </c>
       <c r="G171" t="str">
-        <v>CR-403</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="172">
@@ -4354,10 +4354,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>Load part of a panel</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D172" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E172" t="str">
         <v>In progress</v>
@@ -4366,7 +4366,7 @@
         <v/>
       </c>
       <c r="G172" t="str">
-        <v>CR-405</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="173">
@@ -4377,10 +4377,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>MDF row on every panel</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D173" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E173" t="str">
         <v>In progress</v>
@@ -4389,7 +4389,7 @@
         <v/>
       </c>
       <c r="G173" t="str">
-        <v>CR-406</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="174">
@@ -4400,10 +4400,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Load whole panel in one click</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D174" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E174" t="str">
         <v>In progress</v>
@@ -4412,7 +4412,7 @@
         <v/>
       </c>
       <c r="G174" t="str">
-        <v>CR-407</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="175">
@@ -4420,22 +4420,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C175" t="str">
-        <v>Settings search everywhere</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D175" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E175" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F175" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G175" t="str">
-        <v>CR-408</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="176">
@@ -4443,22 +4443,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C176" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D176" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E176" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F176" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G176" t="str">
-        <v>CR-409</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="177">
@@ -4466,13 +4466,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C177" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D177" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E177" t="str">
         <v>Completed</v>
@@ -4481,7 +4481,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G177" t="str">
-        <v>CR-438</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="178">
@@ -4489,22 +4489,22 @@
         <v>177</v>
       </c>
       <c r="B178" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C178" t="str">
-        <v>Stock adjustment as a line form</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D178" t="str">
-        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E178" t="str">
         <v>Completed</v>
       </c>
       <c r="F178" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G178" t="str">
-        <v>CR-446</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="179">
@@ -4512,22 +4512,22 @@
         <v>178</v>
       </c>
       <c r="B179" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C179" t="str">
-        <v>Adjust Stock in the Zoho Books shape</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D179" t="str">
-        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E179" t="str">
         <v>Completed</v>
       </c>
       <c r="F179" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G179" t="str">
-        <v>CR-457</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="180">
@@ -4538,19 +4538,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C180" t="str">
-        <v>Location Transfer from the Adjust Stock screen</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D180" t="str">
-        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E180" t="str">
         <v>Completed</v>
       </c>
       <c r="F180" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G180" t="str">
-        <v>CR-458</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="181">
@@ -4561,10 +4561,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C181" t="str">
-        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D181" t="str">
-        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E181" t="str">
         <v>Completed</v>
@@ -4573,7 +4573,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G181" t="str">
-        <v>CR-459</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="182">
@@ -4584,10 +4584,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C182" t="str">
-        <v>Cut Piece detail page inside Panel Craft</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D182" t="str">
-        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E182" t="str">
         <v>Completed</v>
@@ -4596,7 +4596,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-460/461</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="183">
@@ -4604,22 +4604,22 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C183" t="str">
-        <v>Pager with First / Last arrows</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D183" t="str">
-        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E183" t="str">
         <v>Completed</v>
       </c>
       <c r="F183" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-467</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="184">
@@ -4627,22 +4627,22 @@
         <v>183</v>
       </c>
       <c r="B184" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C184" t="str">
-        <v>Red close × on every window</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D184" t="str">
-        <v>The × that closes any window or drawer is red on every screen.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E184" t="str">
         <v>Completed</v>
       </c>
       <c r="F184" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G184" t="str">
-        <v>CR-465</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="185">
@@ -4653,10 +4653,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C185" t="str">
-        <v>Advanced search date range fits the window</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D185" t="str">
-        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E185" t="str">
         <v>Completed</v>
@@ -4665,7 +4665,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G185" t="str">
-        <v>CR-464</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="186">
@@ -4673,13 +4673,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="str">
-        <v>Customers</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C186" t="str">
-        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D186" t="str">
-        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E186" t="str">
         <v>Completed</v>
@@ -4688,7 +4688,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G186" t="str">
-        <v>CR-463/466</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="187">
@@ -4696,22 +4696,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C187" t="str">
-        <v>Stock history in date order</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D187" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E187" t="str">
         <v>Completed</v>
       </c>
       <c r="F187" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-455</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="188">
@@ -4719,22 +4719,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Customers</v>
       </c>
       <c r="C188" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D188" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
       </c>
       <c r="F188" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-447</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="189">
@@ -4742,22 +4742,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C189" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D189" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
       </c>
       <c r="F189" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-448</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="190">
@@ -4765,22 +4765,22 @@
         <v>189</v>
       </c>
       <c r="B190" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C190" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D190" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
       </c>
       <c r="F190" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-456</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="191">
@@ -4791,10 +4791,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C191" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D191" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
@@ -4803,7 +4803,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-449</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="192">
@@ -4814,19 +4814,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C192" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D192" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
       </c>
       <c r="F192" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-450</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="193">
@@ -4834,22 +4834,22 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C193" t="str">
-        <v>Location at every stage</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D193" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E193" t="str">
         <v>Completed</v>
       </c>
       <c r="F193" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-411…413</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="194">
@@ -4860,19 +4860,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C194" t="str">
-        <v>Panel location</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D194" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E194" t="str">
         <v>Completed</v>
       </c>
       <c r="F194" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G194" t="str">
-        <v>CR-410</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="195">
@@ -4880,13 +4880,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C195" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D195" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
@@ -4895,7 +4895,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-419</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="196">
@@ -4906,10 +4906,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C196" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Panel location</v>
       </c>
       <c r="D196" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
@@ -4918,7 +4918,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-415</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="197">
@@ -4926,13 +4926,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C197" t="str">
-        <v>No long helper notes</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D197" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
@@ -4941,7 +4941,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-416</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="198">
@@ -4949,13 +4949,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Production</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C198" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D198" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
@@ -4964,7 +4964,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-417</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="199">
@@ -4975,10 +4975,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C199" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D199" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E199" t="str">
         <v>Completed</v>
@@ -4987,7 +4987,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-418</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="200">
@@ -4995,13 +4995,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Production</v>
       </c>
       <c r="C200" t="str">
-        <v>Notifications read / unread</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D200" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
@@ -5010,7 +5010,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G200" t="str">
-        <v>CR-419…421</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="201">
@@ -5018,13 +5018,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C201" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D201" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E201" t="str">
         <v>Completed</v>
@@ -5033,7 +5033,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G201" t="str">
-        <v>CR-422</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="202">
@@ -5041,22 +5041,22 @@
         <v>201</v>
       </c>
       <c r="B202" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C202" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D202" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E202" t="str">
         <v>Completed</v>
       </c>
       <c r="F202" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G202" t="str">
-        <v>CR-404</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="203">
@@ -5064,22 +5064,22 @@
         <v>202</v>
       </c>
       <c r="B203" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C203" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D203" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E203" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F203" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G203" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="204">
@@ -5090,19 +5090,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C204" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D204" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E204" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F204" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G204" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="205">
@@ -5113,19 +5113,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C205" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D205" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E205" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F205" t="str">
         <v/>
       </c>
       <c r="G205" t="str">
-        <v>Panel Craft list #2</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="206">
@@ -5136,10 +5136,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C206" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D206" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E206" t="str">
         <v>Future</v>
@@ -5148,7 +5148,7 @@
         <v/>
       </c>
       <c r="G206" t="str">
-        <v>Panel Craft list #4</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="207">
@@ -5159,10 +5159,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C207" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D207" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E207" t="str">
         <v>Future</v>
@@ -5171,7 +5171,7 @@
         <v/>
       </c>
       <c r="G207" t="str">
-        <v>Panel Craft list #5</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="208">
@@ -5182,10 +5182,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C208" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D208" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E208" t="str">
         <v>Future</v>
@@ -5194,7 +5194,7 @@
         <v/>
       </c>
       <c r="G208" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="209">
@@ -5205,10 +5205,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C209" t="str">
-        <v>Bill / expense</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D209" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E209" t="str">
         <v>Future</v>
@@ -5217,7 +5217,7 @@
         <v/>
       </c>
       <c r="G209" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="210">
@@ -5225,22 +5225,22 @@
         <v>209</v>
       </c>
       <c r="B210" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C210" t="str">
-        <v>System reference and change-request register</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D210" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E210" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F210" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G210" t="str">
-        <v/>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="211">
@@ -5248,22 +5248,22 @@
         <v>210</v>
       </c>
       <c r="B211" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C211" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D211" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E211" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F211" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G211" t="str">
-        <v/>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="212">
@@ -5271,22 +5271,22 @@
         <v>211</v>
       </c>
       <c r="B212" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C212" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Item code for the catalog</v>
       </c>
       <c r="D212" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
       </c>
       <c r="F212" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G212" t="str">
-        <v/>
+        <v>CR-473</v>
       </c>
     </row>
     <row r="213">
@@ -5294,22 +5294,22 @@
         <v>212</v>
       </c>
       <c r="B213" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C213" t="str">
-        <v>Data Flow reference</v>
+        <v>Panel Order PDF — one page per panel</v>
       </c>
       <c r="D213" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
       </c>
       <c r="F213" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-272</v>
+        <v>CR-474</v>
       </c>
     </row>
     <row r="214">
@@ -5317,22 +5317,22 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C214" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Sales Order without a Location field</v>
       </c>
       <c r="D214" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
       </c>
       <c r="E214" t="str">
         <v>Completed</v>
       </c>
       <c r="F214" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G214" t="str">
-        <v/>
+        <v>CR-468</v>
       </c>
     </row>
     <row r="215">
@@ -5340,22 +5340,22 @@
         <v>214</v>
       </c>
       <c r="B215" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C215" t="str">
-        <v>Locations guide</v>
+        <v>Pallet form without Box Weight</v>
       </c>
       <c r="D215" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
       </c>
       <c r="E215" t="str">
         <v>Completed</v>
       </c>
       <c r="F215" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G215" t="str">
-        <v>CR-411…413</v>
+        <v>CR-471</v>
       </c>
     </row>
     <row r="216">
@@ -5363,22 +5363,22 @@
         <v>215</v>
       </c>
       <c r="B216" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C216" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Boffo / Bonza company separation</v>
       </c>
       <c r="D216" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
       </c>
       <c r="E216" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F216" t="str">
-        <v>2026-10-22</v>
+        <v/>
       </c>
       <c r="G216" t="str">
-        <v/>
+        <v>ON-HOLD #1</v>
       </c>
     </row>
     <row r="217">
@@ -5389,19 +5389,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C217" t="str">
-        <v>Demo / test environment</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D217" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E217" t="str">
         <v>Completed</v>
       </c>
       <c r="F217" t="str">
-        <v>2026-10-25</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G217" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="218">
@@ -5412,25 +5412,186 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C218" t="str">
+        <v>Change log, user flow, user manual</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+      </c>
+      <c r="E218" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Seed and teardown scripts</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+      </c>
+      <c r="E219" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Data Flow reference</v>
+      </c>
+      <c r="D220" t="str">
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+      </c>
+      <c r="E220" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F220" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G220" t="str">
+        <v>CR-272</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Phase 2 inventory</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+      </c>
+      <c r="E221" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F221" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Locations guide</v>
+      </c>
+      <c r="D222" t="str">
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+      </c>
+      <c r="E222" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F222" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="G222" t="str">
+        <v>CR-411…413</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Deliverables list (this workbook)</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+      </c>
+      <c r="E223" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F223" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D224" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E224" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F224" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G224" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C225" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D218" t="str">
+      <c r="D225" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E218" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F218" t="str">
+      <c r="E225" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F225" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G218" t="str">
+      <c r="G225" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G218"/>
+  <autoFilter ref="A1:G225"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G218"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G225"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G235</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G235"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -947,22 +947,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C24" t="str">
-        <v>Items (Design Master)</v>
+        <v>PO number first on every stage screen</v>
       </c>
       <c r="D24" t="str">
-        <v>One record per sellable tile: name, SKU, size, finish, category, glaze, grade, brand, images (gallery + lightbox), per-box weight with per-piece / per-m² helpers, batch-tracked flag, Active / Inactive. Item detail shows stock, production and orders.</v>
+        <v>Palletization, Loading, Dispatch, Production and their pop-ups show the customer's PO number; the system SO number is a hidden column one tick away. Printed documents keep the SO number.</v>
       </c>
       <c r="E24" t="str">
         <v>Completed</v>
       </c>
       <c r="F24" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>CR-482</v>
       </c>
     </row>
     <row r="25">
@@ -973,19 +973,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C25" t="str">
-        <v>Design Master to the new spec</v>
+        <v>Items (Design Master)</v>
       </c>
       <c r="D25" t="str">
-        <v>Item form in five sections (Main Information · Calculations · Design Data · Working Data · Marketing Data) with the image on the form; Pcs Per Packing typed per item and coverage from the item's own numbers (a Size edit no longer rewrites them); Design Owner and Custom Design Buyer as customers (default owner in Settings); the buyer's brands offered as Customer Brand; Base Design picked from existing items; new lookups Surface Application, Punch Type (with image), Series, Catalogue.</v>
+        <v>One record per sellable tile: name, SKU, size, finish, category, glaze, grade, brand, images (gallery + lightbox), per-box weight with per-piece / per-m² helpers, batch-tracked flag, Active / Inactive. Item detail shows stock, production and orders.</v>
       </c>
       <c r="E25" t="str">
         <v>Completed</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-10-23</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G25" t="str">
-        <v>CR-391…396</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -996,19 +996,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C26" t="str">
-        <v>Opening stock with lock</v>
+        <v>Design Master to the new spec</v>
       </c>
       <c r="D26" t="str">
-        <v>Entered once per item (per batch for batch-tracked items); locks after first save; Admin can re-open with a reason written to the audit log.</v>
+        <v>Item form in five sections (Main Information · Calculations · Design Data · Working Data · Marketing Data) with the image on the form; Pcs Per Packing typed per item and coverage from the item's own numbers (a Size edit no longer rewrites them); Design Owner and Custom Design Buyer as customers (default owner in Settings); the buyer's brands offered as Customer Brand; Base Design picked from existing items; new lookups Surface Application, Punch Type (with image), Series, Catalogue.</v>
       </c>
       <c r="E26" t="str">
         <v>Completed</v>
       </c>
       <c r="F26" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-23</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>CR-391…396</v>
       </c>
     </row>
     <row r="27">
@@ -1019,10 +1019,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C27" t="str">
-        <v>Size Master with packing defaults</v>
+        <v>Opening stock with lock</v>
       </c>
       <c r="D27" t="str">
-        <v>Dimensions, pieces per box, coverage m² / ft², box weight. Pallet formats snapshot the size; items take the dimensions and start their own pieces per box and box weight from it. Editing a size fans the defaults out (typed item values are kept).</v>
+        <v>Entered once per item (per batch for batch-tracked items); locks after first save; Admin can re-open with a reason written to the audit log.</v>
       </c>
       <c r="E27" t="str">
         <v>Completed</v>
@@ -1031,7 +1031,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G27" t="str">
-        <v>CR-391</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1042,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C28" t="str">
-        <v>Pallet Master</v>
+        <v>Size Master with packing defaults</v>
       </c>
       <c r="D28" t="str">
-        <v>Pallet formats: boxes per pallet, empty and loaded pallet weight, which size they fit. Pick lists offer the formats matching the item's size. Boxes-only since Phase 2 (container capacity moved to Container Master).</v>
+        <v>Dimensions, pieces per box, coverage m² / ft², box weight. Pallet formats snapshot the size; items take the dimensions and start their own pieces per box and box weight from it. Editing a size fans the defaults out (typed item values are kept).</v>
       </c>
       <c r="E28" t="str">
         <v>Completed</v>
@@ -1054,7 +1054,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G28" t="str">
-        <v>CR-261</v>
+        <v>CR-391</v>
       </c>
     </row>
     <row r="29">
@@ -1065,10 +1065,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C29" t="str">
-        <v>Stock Details</v>
+        <v>Pallet Master</v>
       </c>
       <c r="D29" t="str">
-        <v>Batch-wise on-hand per item.</v>
+        <v>Pallet formats: boxes per pallet, empty and loaded pallet weight, which size they fit. Pick lists offer the formats matching the item's size. Boxes-only since Phase 2 (container capacity moved to Container Master).</v>
       </c>
       <c r="E29" t="str">
         <v>Completed</v>
@@ -1077,7 +1077,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>CR-261</v>
       </c>
     </row>
     <row r="30">
@@ -1088,10 +1088,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C30" t="str">
-        <v>Lookups</v>
+        <v>Stock Details</v>
       </c>
       <c r="D30" t="str">
-        <v>Brand (with logo on forms), Grade, Finish, Category, Glaze, Payment terms, Currency with exchange rate, Vehicle (kept in sync from typed numbers), Container sizes, Organization, document number series.</v>
+        <v>Batch-wise on-hand per item.</v>
       </c>
       <c r="E30" t="str">
         <v>Completed</v>
@@ -1111,19 +1111,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C31" t="str">
-        <v>Container Master</v>
+        <v>Lookups</v>
       </c>
       <c r="D31" t="str">
-        <v>New master: what one container of a size holds — pallet formats as lines (format × how many), totals follow; several containers per size; auto-name shows the pallet maths, e.g. 800x1600 - GVT - 2 · [(48*10) + (10*6)] = 540 boxes. Grid, form page, detail with Clone / Delete, activity.</v>
+        <v>Brand (with logo on forms), Grade, Finish, Category, Glaze, Payment terms, Currency with exchange rate, Vehicle (kept in sync from typed numbers), Container sizes, Organization, document number series.</v>
       </c>
       <c r="E31" t="str">
         <v>Completed</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G31" t="str">
-        <v>CR-261, 269, 273, 292</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1134,19 +1134,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C32" t="str">
-        <v>Capacity comes from the Container Master</v>
+        <v>Container Master</v>
       </c>
       <c r="D32" t="str">
-        <v>Fill % on loading and palletization and the planner's box fitting use the size's container; a size with no container shows no fill % and says so.</v>
+        <v>New master: what one container of a size holds — pallet formats as lines (format × how many), totals follow; several containers per size; auto-name shows the pallet maths, e.g. 800x1600 - GVT - 2 · [(48*10) + (10*6)] = 540 boxes. Grid, form page, detail with Clone / Delete, activity.</v>
       </c>
       <c r="E32" t="str">
         <v>Completed</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G32" t="str">
-        <v>CR-261</v>
+        <v>CR-261, 269, 273, 292</v>
       </c>
     </row>
     <row r="33">
@@ -1157,19 +1157,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C33" t="str">
-        <v>Warehouse master</v>
+        <v>Capacity comes from the Container Master</v>
       </c>
       <c r="D33" t="str">
-        <v>Settings ▸ Warehouses: name, Primary ★, purposes (Production · Palletization · Loading Bay · Raw Material · Sample Cut Panels), note. Primary and any warehouse with history cannot be deleted.</v>
+        <v>Fill % on loading and palletization and the planner's box fitting use the size's container; a size with no container shows no fill % and says so.</v>
       </c>
       <c r="E33" t="str">
         <v>Completed</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G33" t="str">
-        <v>CR-329</v>
+        <v>CR-261</v>
       </c>
     </row>
     <row r="34">
@@ -1180,19 +1180,19 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C34" t="str">
-        <v>Add a new container from where it is needed</v>
+        <v>Warehouse master</v>
       </c>
       <c r="D34" t="str">
-        <v>Create a Container Master record without leaving the loading / planning screen. Scope to be confirmed.</v>
+        <v>Settings ▸ Warehouses: name, Primary ★, purposes (Production · Palletization · Loading Bay · Raw Material · Sample Cut Panels), note. Primary and any warehouse with history cannot be deleted.</v>
       </c>
       <c r="E34" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>2026-10-12</v>
       </c>
       <c r="G34" t="str">
-        <v>Panel Craft list #10</v>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="35">
@@ -1203,10 +1203,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C35" t="str">
-        <v>Container master naming</v>
+        <v>Add a new container from where it is needed</v>
       </c>
       <c r="D35" t="str">
-        <v>Naming / login rule for container records. Requirement to be clarified.</v>
+        <v>Create a Container Master record without leaving the loading / planning screen. Scope to be confirmed.</v>
       </c>
       <c r="E35" t="str">
         <v>Future</v>
@@ -1215,7 +1215,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Panel Craft list #11</v>
+        <v>Panel Craft list #10</v>
       </c>
     </row>
     <row r="36">
@@ -1226,10 +1226,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C36" t="str">
-        <v>Pallet size as length × width</v>
+        <v>Container master naming</v>
       </c>
       <c r="D36" t="str">
-        <v>New Pallet form takes length and width instead of one size field.</v>
+        <v>Naming / login rule for container records. Requirement to be clarified.</v>
       </c>
       <c r="E36" t="str">
         <v>Future</v>
@@ -1238,7 +1238,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>CR-101</v>
+        <v>Panel Craft list #11</v>
       </c>
     </row>
     <row r="37">
@@ -1249,10 +1249,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C37" t="str">
-        <v>Readable SKU</v>
+        <v>Pallet size as length × width</v>
       </c>
       <c r="D37" t="str">
-        <v>Acronym-based SKU built from each master's short code (decisions agreed, not built).</v>
+        <v>New Pallet form takes length and width instead of one size field.</v>
       </c>
       <c r="E37" t="str">
         <v>Future</v>
@@ -1261,7 +1261,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>CR-015</v>
+        <v>CR-101</v>
       </c>
     </row>
     <row r="38">
@@ -1269,22 +1269,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Customers</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C38" t="str">
-        <v>Customer master (full page)</v>
+        <v>Readable SKU</v>
       </c>
       <c r="D38" t="str">
-        <v>Code, name, contacts, billing and shipping addresses side by side, country, currency, payment terms, default Box Brand, sales person, brand.</v>
+        <v>Acronym-based SKU built from each master's short code (decisions agreed, not built).</v>
       </c>
       <c r="E38" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F38" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>CR-015</v>
       </c>
     </row>
     <row r="39">
@@ -1295,19 +1295,19 @@
         <v>Customers</v>
       </c>
       <c r="C39" t="str">
-        <v>Customer Brands</v>
+        <v>Customer master (full page)</v>
       </c>
       <c r="D39" t="str">
-        <v>Several brand names per customer on the Customer detail (add / delete); the Item form offers them as the buyer's Customer Brand.</v>
+        <v>Code, name, contacts, billing and shipping addresses side by side, country, currency, payment terms, default Box Brand, sales person, brand.</v>
       </c>
       <c r="E39" t="str">
         <v>Completed</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-10-23</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G39" t="str">
-        <v>CR-393</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1318,19 +1318,19 @@
         <v>Customers</v>
       </c>
       <c r="C40" t="str">
-        <v>Customer detail</v>
+        <v>Customer Brands</v>
       </c>
       <c r="D40" t="str">
-        <v>Quotes, sales orders and dispatches for that customer in one place; Showcase Panels and Customer Samples sections.</v>
+        <v>Several brand names per customer on the Customer detail (add / delete); the Item form offers them as the buyer's Customer Brand.</v>
       </c>
       <c r="E40" t="str">
         <v>Completed</v>
       </c>
       <c r="F40" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-23</v>
       </c>
       <c r="G40" t="str">
-        <v/>
+        <v>CR-393</v>
       </c>
     </row>
     <row r="41">
@@ -1341,10 +1341,10 @@
         <v>Customers</v>
       </c>
       <c r="C41" t="str">
-        <v>Transactions inherit customer fields</v>
+        <v>Customer detail</v>
       </c>
       <c r="D41" t="str">
-        <v>Every quote and order fills currency, terms, addresses, brand and box brand from the customer on pick — nothing retyped.</v>
+        <v>Quotes, sales orders and dispatches for that customer in one place; Showcase Panels and Customer Samples sections.</v>
       </c>
       <c r="E41" t="str">
         <v>Completed</v>
@@ -1364,19 +1364,19 @@
         <v>Customers</v>
       </c>
       <c r="C42" t="str">
-        <v>Sign in with Zoho</v>
+        <v>Transactions inherit customer fields</v>
       </c>
       <c r="D42" t="str">
-        <v>Login page leads with a Zoho button; password form stays as fallback; only existing active app users get in; roles stay Admin-controlled.</v>
+        <v>Every quote and order fills currency, terms, addresses, brand and box brand from the customer on pick — nothing retyped.</v>
       </c>
       <c r="E42" t="str">
         <v>Completed</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G42" t="str">
-        <v>CR-324</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -1387,19 +1387,19 @@
         <v>Customers</v>
       </c>
       <c r="C43" t="str">
-        <v>Zoho CRM Accounts as the customer source</v>
+        <v>Sign in with Zoho</v>
       </c>
       <c r="D43" t="str">
-        <v>Changes arrive via webhook / scheduled pull; Import all once; Create in / Push to Zoho CRM from the customer; From Zoho CRM on the Customers page; Map / Re-pull / Unmap by hand. Contact persons from CRM Contacts; GSTIN, PAN, GST treatment, Place of Supply, Credit Limit, Payment Term picked up automatically.</v>
+        <v>Login page leads with a Zoho button; password form stays as fallback; only existing active app users get in; roles stay Admin-controlled.</v>
       </c>
       <c r="E43" t="str">
         <v>Completed</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G43" t="str">
-        <v>CR-359</v>
+        <v>CR-324</v>
       </c>
     </row>
     <row r="44">
@@ -1410,10 +1410,10 @@
         <v>Customers</v>
       </c>
       <c r="C44" t="str">
-        <v>Zoho Books customer sync (built, switched off)</v>
+        <v>Zoho CRM Accounts as the customer source</v>
       </c>
       <c r="D44" t="str">
-        <v>Two-way customer sync with Zoho Books (event-driven pull, Import all, Push) and the Books tax / credit / notes fields on the customer. Hidden since the switch to CRM at the customer's request; data kept.</v>
+        <v>Changes arrive via webhook / scheduled pull; Import all once; Create in / Push to Zoho CRM from the customer; From Zoho CRM on the Customers page; Map / Re-pull / Unmap by hand. Contact persons from CRM Contacts; GSTIN, PAN, GST treatment, Place of Supply, Credit Limit, Payment Term picked up automatically.</v>
       </c>
       <c r="E44" t="str">
         <v>Completed</v>
@@ -1422,7 +1422,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G44" t="str">
-        <v>CR-325, 356, 358</v>
+        <v>CR-359</v>
       </c>
     </row>
     <row r="45">
@@ -1433,10 +1433,10 @@
         <v>Customers</v>
       </c>
       <c r="C45" t="str">
-        <v>Zoho link status per customer</v>
+        <v>Zoho Books customer sync (built, switched off)</v>
       </c>
       <c r="D45" t="str">
-        <v>Customers grid column Zoho: CRM &amp; Books / CRM only / Books only; customer page spells it out with both ids; advanced filter takes the states; token handling fixed so the status fills for every synced customer.</v>
+        <v>Two-way customer sync with Zoho Books (event-driven pull, Import all, Push) and the Books tax / credit / notes fields on the customer. Hidden since the switch to CRM at the customer's request; data kept.</v>
       </c>
       <c r="E45" t="str">
         <v>Completed</v>
@@ -1445,7 +1445,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G45" t="str">
-        <v>CR-362, 363</v>
+        <v>CR-325, 356, 358</v>
       </c>
     </row>
     <row r="46">
@@ -1456,19 +1456,19 @@
         <v>Customers</v>
       </c>
       <c r="C46" t="str">
-        <v>Sync never creates a twin; duplicate names are an error</v>
+        <v>Zoho link status per customer</v>
       </c>
       <c r="D46" t="str">
-        <v>The existing-customer lookup reads every customer; a CRM account whose name already belongs to another linked customer is reported as a duplicate and not created; CRM comes first.</v>
+        <v>Customers grid column Zoho: CRM &amp; Books / CRM only / Books only; customer page spells it out with both ids; advanced filter takes the states; token handling fixed so the status fills for every synced customer.</v>
       </c>
       <c r="E46" t="str">
         <v>Completed</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G46" t="str">
-        <v>CR-372</v>
+        <v>CR-362, 363</v>
       </c>
     </row>
     <row r="47">
@@ -1479,10 +1479,10 @@
         <v>Customers</v>
       </c>
       <c r="C47" t="str">
-        <v>Duplicate customers card</v>
+        <v>Sync never creates a twin; duplicate names are an error</v>
       </c>
       <c r="D47" t="str">
-        <v>Settings ▸ Zoho CRM ▸ Duplicate customers: Find duplicates → Merge N duplicates (quotes, orders, panel and sample orders move to the surviving customer; reused codes renewed). Import all refuses to run while duplicates exist.</v>
+        <v>The existing-customer lookup reads every customer; a CRM account whose name already belongs to another linked customer is reported as a duplicate and not created; CRM comes first.</v>
       </c>
       <c r="E47" t="str">
         <v>Completed</v>
@@ -1491,7 +1491,7 @@
         <v>2026-10-22</v>
       </c>
       <c r="G47" t="str">
-        <v>CR-373</v>
+        <v>CR-372</v>
       </c>
     </row>
     <row r="48">
@@ -1502,19 +1502,19 @@
         <v>Customers</v>
       </c>
       <c r="C48" t="str">
-        <v>Zoho item reference</v>
+        <v>Duplicate customers card</v>
       </c>
       <c r="D48" t="str">
-        <v>Link items to the Zoho item master. Blocked — reference layout never supplied.</v>
+        <v>Settings ▸ Zoho CRM ▸ Duplicate customers: Find duplicates → Merge N duplicates (quotes, orders, panel and sample orders move to the surviving customer; reused codes renewed). Import all refuses to run while duplicates exist.</v>
       </c>
       <c r="E48" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>2026-10-22</v>
       </c>
       <c r="G48" t="str">
-        <v>CR-013.2</v>
+        <v>CR-373</v>
       </c>
     </row>
     <row r="49">
@@ -1522,22 +1522,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Quotes &amp; Approvals</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C49" t="str">
-        <v>Quote form (create / edit / clone)</v>
+        <v>List pages load in one round trip</v>
       </c>
       <c r="D49" t="str">
-        <v>Customer, currency (INR default, any currency with the day's rate), payment terms, box brand, lines item · size · boxes · rate; totals in document currency and INR.</v>
+        <v>Every list page joins the Customer table (2,800+ rows after the CRM import); it was fetched 300 rows per request, one after another, at about a second each. The server now returns a whole table in one response, so the sales order, quote, production, palletization, loading and customer lists stop waiting about ten seconds for it.</v>
       </c>
       <c r="E49" t="str">
         <v>Completed</v>
       </c>
       <c r="F49" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>CR-478</v>
       </c>
     </row>
     <row r="50">
@@ -1545,22 +1545,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Quotes &amp; Approvals</v>
+        <v>Customers</v>
       </c>
       <c r="C50" t="str">
-        <v>Grouped by design</v>
+        <v>Import all reaches every CRM account</v>
       </c>
       <c r="D50" t="str">
-        <v>On screen, in print and in the PDF, with per-design subtotals.</v>
+        <v>Zoho CRM only serves page numbers up to record 2,000, so older accounts never arrived; the import now walks Zoho's page tokens (200 accounts per list call) and a re-run works only on the changed or unlinked accounts instead of re-listing everything ten by ten.</v>
       </c>
       <c r="E50" t="str">
         <v>Completed</v>
       </c>
       <c r="F50" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>CR-477</v>
       </c>
     </row>
     <row r="51">
@@ -1568,22 +1568,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Quotes &amp; Approvals</v>
+        <v>Customers</v>
       </c>
       <c r="C51" t="str">
-        <v>PDF and public share link</v>
+        <v>Zoho item reference</v>
       </c>
       <c r="D51" t="str">
-        <v>Customer-facing PDF and an unguessable share link.</v>
+        <v>Link items to the Zoho item master. Blocked — reference layout never supplied.</v>
       </c>
       <c r="E51" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F51" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>CR-013.2</v>
       </c>
     </row>
     <row r="52">
@@ -1594,10 +1594,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C52" t="str">
-        <v>Container planning on the quote</v>
+        <v>Quote form (create / edit / clone)</v>
       </c>
       <c r="D52" t="str">
-        <v>Plan quoted boxes into containers in Box Fitting or Weight Fitting mode; move boxes between containers; fractional fill for mixed containers; optimiser respects pallet slots, area, weight and box caps.</v>
+        <v>Customer, currency (INR default, any currency with the day's rate), payment terms, box brand, lines item · size · boxes · rate; totals in document currency and INR.</v>
       </c>
       <c r="E52" t="str">
         <v>Completed</v>
@@ -1617,10 +1617,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C53" t="str">
-        <v>Approvals page</v>
+        <v>Grouped by design</v>
       </c>
       <c r="D53" t="str">
-        <v>Approve or reject with a reason; sales person notified; an approver's own quotes are born Approved. Lifecycle Draft → Pending approval → Approved → Sent → Accepted → Converted.</v>
+        <v>On screen, in print and in the PDF, with per-design subtotals.</v>
       </c>
       <c r="E53" t="str">
         <v>Completed</v>
@@ -1640,10 +1640,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C54" t="str">
-        <v>Quote aging report</v>
+        <v>PDF and public share link</v>
       </c>
       <c r="D54" t="str">
-        <v>Shows where quotes are stuck.</v>
+        <v>Customer-facing PDF and an unguessable share link.</v>
       </c>
       <c r="E54" t="str">
         <v>Completed</v>
@@ -1663,19 +1663,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C55" t="str">
-        <v>Suitable Containers panel</v>
+        <v>Container planning on the quote</v>
       </c>
       <c r="D55" t="str">
-        <v>Per size on the quote: the container it fits, boxes quoted, containers needed and how full the last one is (on screen).</v>
+        <v>Plan quoted boxes into containers in Box Fitting or Weight Fitting mode; move boxes between containers; fractional fill for mixed containers; optimiser respects pallet slots, area, weight and box caps.</v>
       </c>
       <c r="E55" t="str">
         <v>Completed</v>
       </c>
       <c r="F55" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G55" t="str">
-        <v>CR-262</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -1686,19 +1686,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C56" t="str">
-        <v>Planner picks the container per item row</v>
+        <v>Approvals page</v>
       </c>
       <c r="D56" t="str">
-        <v>A Container column on every planner row lists the containers of that size built from the chosen pallet; default the largest; saved with the plan; a loading made from the plan starts on it.</v>
+        <v>Approve or reject with a reason; sales person notified; an approver's own quotes are born Approved. Lifecycle Draft → Pending approval → Approved → Sent → Accepted → Converted.</v>
       </c>
       <c r="E56" t="str">
         <v>Completed</v>
       </c>
       <c r="F56" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G56" t="str">
-        <v>CR-274, 300</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -1709,19 +1709,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C57" t="str">
-        <v>Customer search modal</v>
+        <v>Quote aging report</v>
       </c>
       <c r="D57" t="str">
-        <v>Magnifier beside the Customer field on Quote, Sales Order and New Palletization opens a searchable customer table; dropdown shows code · country.</v>
+        <v>Shows where quotes are stuck.</v>
       </c>
       <c r="E57" t="str">
         <v>Completed</v>
       </c>
       <c r="F57" t="str">
-        <v>2026-10-06</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G57" t="str">
-        <v>CR-276</v>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -1732,19 +1732,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C58" t="str">
-        <v>Suitable Containers on print / PDF / share link</v>
+        <v>Suitable Containers panel</v>
       </c>
       <c r="D58" t="str">
-        <v>Carry the on-screen Suitable Containers panel onto the printed quote, PDF and share link.</v>
+        <v>Per size on the quote: the container it fits, boxes quoted, containers needed and how full the last one is (on screen).</v>
       </c>
       <c r="E58" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F58" t="str">
-        <v/>
+        <v>2026-10-03</v>
       </c>
       <c r="G58" t="str">
-        <v>CR-262 follow-up</v>
+        <v>CR-262</v>
       </c>
     </row>
     <row r="59">
@@ -1755,19 +1755,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C59" t="str">
-        <v>Weight fitting from the container's max weight</v>
+        <v>Planner picks the container per item row</v>
       </c>
       <c r="D59" t="str">
-        <v>Planner uses the container's own weight limit instead of a typed tonnage.</v>
+        <v>A Container column on every planner row lists the containers of that size built from the chosen pallet; default the largest; saved with the plan; a loading made from the plan starts on it.</v>
       </c>
       <c r="E59" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F59" t="str">
-        <v/>
+        <v>2026-10-07</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>CR-274, 300</v>
       </c>
     </row>
     <row r="60">
@@ -1778,19 +1778,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C60" t="str">
-        <v>Qty total on screen and on the printed quote</v>
+        <v>Customer search modal</v>
       </c>
       <c r="D60" t="str">
-        <v>Box total shown on the quote and in print / PDF.</v>
+        <v>Magnifier beside the Customer field on Quote, Sales Order and New Palletization opens a searchable customer table; dropdown shows code · country.</v>
       </c>
       <c r="E60" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F60" t="str">
-        <v/>
+        <v>2026-10-06</v>
       </c>
       <c r="G60" t="str">
-        <v>CR-079</v>
+        <v>CR-276</v>
       </c>
     </row>
     <row r="61">
@@ -1801,10 +1801,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C61" t="str">
-        <v>Collapse long remarks / terms</v>
+        <v>Suitable Containers on print / PDF / share link</v>
       </c>
       <c r="D61" t="str">
-        <v>Long remarks and terms fold behind 'view more' so the page does not stretch.</v>
+        <v>Carry the on-screen Suitable Containers panel onto the printed quote, PDF and share link.</v>
       </c>
       <c r="E61" t="str">
         <v>Future</v>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>CR-088</v>
+        <v>CR-262 follow-up</v>
       </c>
     </row>
     <row r="62">
@@ -1821,19 +1821,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Sales Orders</v>
+        <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C62" t="str">
-        <v>Convert to Sales Order</v>
+        <v>Weight fitting from the container's max weight</v>
       </c>
       <c r="D62" t="str">
-        <v>From an Accepted quote, full or partial (quote becomes Partially converted and can be converted again); the quote's container plan is copied and the order owns its editable copy.</v>
+        <v>Planner uses the container's own weight limit instead of a typed tonnage.</v>
       </c>
       <c r="E62" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F62" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -1844,22 +1844,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Sales Orders</v>
+        <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C63" t="str">
-        <v>Sales Order form (page)</v>
+        <v>Qty total on screen and on the printed quote</v>
       </c>
       <c r="D63" t="str">
-        <v>Same layout family as the quote; PO number; editable after work has started (a line with pallets or loads keeps its item and cannot drop below what was done).</v>
+        <v>Box total shown on the quote and in print / PDF.</v>
       </c>
       <c r="E63" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F63" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G63" t="str">
-        <v/>
+        <v>CR-079</v>
       </c>
     </row>
     <row r="64">
@@ -1867,22 +1867,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>Sales Orders</v>
+        <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C64" t="str">
-        <v>Allocate Stock</v>
+        <v>Collapse long remarks / terms</v>
       </c>
       <c r="D64" t="str">
-        <v>Hand free boxes of chosen batches to an order line (one flat table item → batch rows, with search). Allocation is a claim, not a movement.</v>
+        <v>Long remarks and terms fold behind 'view more' so the page does not stretch.</v>
       </c>
       <c r="E64" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F64" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G64" t="str">
-        <v>CR-194…200</v>
+        <v>CR-088</v>
       </c>
     </row>
     <row r="65">
@@ -1893,10 +1893,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C65" t="str">
-        <v>Status = order lifecycle; Palletization / Loading progress separate</v>
+        <v>Convert to Sales Order</v>
       </c>
       <c r="D65" t="str">
-        <v>Draft → Pending approval → Confirmed → In progress → Partially completed → Completed, rolled up from dispatched vs ordered. Palletization and Loading progress are their own columns / fields. Admin override with reason.</v>
+        <v>From an Accepted quote, full or partial (quote becomes Partially converted and can be converted again); the quote's container plan is copied and the order owns its editable copy.</v>
       </c>
       <c r="E65" t="str">
         <v>Completed</v>
@@ -1905,7 +1905,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G65" t="str">
-        <v>CR-230…233</v>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -1916,10 +1916,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C66" t="str">
-        <v>Order detail tabs and actions</v>
+        <v>Sales Order form (page)</v>
       </c>
       <c r="D66" t="str">
-        <v>Items (ordered · allocated · palletized · loaded · dispatched per line), Palletization, Dispatch, Activity; Send to Palletization, New Loading, Allocate Stock, Containerise, Clone.</v>
+        <v>Same layout family as the quote; PO number; editable after work has started (a line with pallets or loads keeps its item and cannot drop below what was done).</v>
       </c>
       <c r="E66" t="str">
         <v>Completed</v>
@@ -1939,10 +1939,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C67" t="str">
-        <v>Orders grid, By-order view, Kanban pipeline</v>
+        <v>Allocate Stock</v>
       </c>
       <c r="D67" t="str">
-        <v>Three views over the same data.</v>
+        <v>Hand free boxes of chosen batches to an order line (one flat table item → batch rows, with search). Allocation is a claim, not a movement.</v>
       </c>
       <c r="E67" t="str">
         <v>Completed</v>
@@ -1951,7 +1951,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>CR-194…200</v>
       </c>
     </row>
     <row r="68">
@@ -1962,19 +1962,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C68" t="str">
-        <v>Remaining, totals and Deallocate Stock</v>
+        <v>Status = order lifecycle; Palletization / Loading progress separate</v>
       </c>
       <c r="D68" t="str">
-        <v>Items table shows Remaining = Ordered − Allocated and a totals row; ✕ per allocated line returns boxes to free stock unless already palletized; partial deallocate ('5 of 520'); Allocate / Deallocate buttons always visible with the reason when greyed.</v>
+        <v>Draft → Pending approval → Confirmed → In progress → Partially completed → Completed, rolled up from dispatched vs ordered. Palletization and Loading progress are their own columns / fields. Admin override with reason.</v>
       </c>
       <c r="E68" t="str">
         <v>Completed</v>
       </c>
       <c r="F68" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G68" t="str">
-        <v>CR-263, 297</v>
+        <v>CR-230…233</v>
       </c>
     </row>
     <row r="69">
@@ -1985,19 +1985,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C69" t="str">
-        <v>Item STOCK card itemises on-hand</v>
+        <v>Order detail tabs and actions</v>
       </c>
       <c r="D69" t="str">
-        <v>Awaiting palletization row between In production and In loading, each with per-order drill-down, so Available adds up on screen.</v>
+        <v>Items (ordered · allocated · palletized · loaded · dispatched per line), Palletization, Dispatch, Activity; Send to Palletization, New Loading, Allocate Stock, Containerise, Clone.</v>
       </c>
       <c r="E69" t="str">
         <v>Completed</v>
       </c>
       <c r="F69" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G69" t="str">
-        <v>CR-298</v>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -2008,19 +2008,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C70" t="str">
-        <v>A worked order cannot be deleted</v>
+        <v>Orders grid, By-order view, Kanban pipeline</v>
       </c>
       <c r="D70" t="str">
-        <v>Once any line is allocated, palletized, loaded, dispatched or on a plan, Delete is greyed and refused ('Cancel it instead').</v>
+        <v>Three views over the same data.</v>
       </c>
       <c r="E70" t="str">
         <v>Completed</v>
       </c>
       <c r="F70" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G70" t="str">
-        <v>CR-271</v>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -2031,19 +2031,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C71" t="str">
-        <v>Customer PO first, SO number small</v>
+        <v>Remaining, totals and Deallocate Stock</v>
       </c>
       <c r="D71" t="str">
-        <v>Sales Order page titled by the customer's PO with SO/FY/NNN small beneath; Orders grid first column PO Number; drawer and By-Order cards follow.</v>
+        <v>Items table shows Remaining = Ordered − Allocated and a totals row; ✕ per allocated line returns boxes to free stock unless already palletized; partial deallocate ('5 of 520'); Allocate / Deallocate buttons always visible with the reason when greyed.</v>
       </c>
       <c r="E71" t="str">
         <v>Completed</v>
       </c>
       <c r="F71" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G71" t="str">
-        <v>CR-353</v>
+        <v>CR-263, 297</v>
       </c>
     </row>
     <row r="72">
@@ -2054,19 +2054,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C72" t="str">
-        <v>Cancel Order clears the palletization board</v>
+        <v>Item STOCK card itemises on-hand</v>
       </c>
       <c r="D72" t="str">
-        <v>Cancelling a sales order (reason required) removes its boxes from open containers, every palletization line and every allocation; a dispatched container blocks the cancel.</v>
+        <v>Awaiting palletization row between In production and In loading, each with per-order drill-down, so Available adds up on screen.</v>
       </c>
       <c r="E72" t="str">
         <v>Completed</v>
       </c>
       <c r="F72" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G72" t="str">
-        <v>CR-371</v>
+        <v>CR-298</v>
       </c>
     </row>
     <row r="73">
@@ -2077,19 +2077,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C73" t="str">
-        <v>'Mark in progress' → 'Mark as sent'</v>
+        <v>A worked order cannot be deleted</v>
       </c>
       <c r="D73" t="str">
-        <v>Rename the status action to what it means: the sales person acknowledged the customer.</v>
+        <v>Once any line is allocated, palletized, loaded, dispatched or on a plan, Delete is greyed and refused ('Cancel it instead').</v>
       </c>
       <c r="E73" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F73" t="str">
-        <v/>
+        <v>2026-10-03</v>
       </c>
       <c r="G73" t="str">
-        <v>CR-041</v>
+        <v>CR-271</v>
       </c>
     </row>
     <row r="74">
@@ -2100,19 +2100,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C74" t="str">
-        <v>'Send to Palletization' in the More menu</v>
+        <v>Customer PO first, SO number small</v>
       </c>
       <c r="D74" t="str">
-        <v>Move the action into More and name it 'Palletization'.</v>
+        <v>Sales Order page titled by the customer's PO with SO/FY/NNN small beneath; Orders grid first column PO Number; drawer and By-Order cards follow.</v>
       </c>
       <c r="E74" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G74" t="str">
-        <v>CR-042</v>
+        <v>CR-353</v>
       </c>
     </row>
     <row r="75">
@@ -2120,22 +2120,22 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>Production</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C75" t="str">
-        <v>Production page — Sheet / Kanban / Grid</v>
+        <v>Cancel Order clears the palletization board</v>
       </c>
       <c r="D75" t="str">
-        <v>Three views of the same rows (Sheet default); one row per logged batch; Group by Item / Customer / Order / Size; status filter with All.</v>
+        <v>Cancelling a sales order (reason required) removes its boxes from open containers, every palletization line and every allocation; a dispatched container blocks the cancel.</v>
       </c>
       <c r="E75" t="str">
         <v>Completed</v>
       </c>
       <c r="F75" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>CR-371</v>
       </c>
     </row>
     <row r="76">
@@ -2143,22 +2143,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>Production</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C76" t="str">
-        <v>To Produce view</v>
+        <v>'Mark in progress' → 'Mark as sent'</v>
       </c>
       <c r="D76" t="str">
-        <v>Per item: open demand, free stock, in production and what still needs producing, with the Box Brand wanted; tick rows to start a job.</v>
+        <v>Rename the status action to what it means: the sales person acknowledged the customer.</v>
       </c>
       <c r="E76" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F76" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G76" t="str">
-        <v/>
+        <v>CR-041</v>
       </c>
     </row>
     <row r="77">
@@ -2166,22 +2166,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>Production</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C77" t="str">
-        <v>Start / Log / Complete Production</v>
+        <v>'Send to Palletization' in the More menu</v>
       </c>
       <c r="D77" t="str">
-        <v>Start creates the job (Item · Quantity); Log adds batch rows from the row's + menu (first log → In Production, full coverage → Completed automatically); Complete closes the job.</v>
+        <v>Move the action into More and name it 'Palletization'.</v>
       </c>
       <c r="E77" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F77" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G77" t="str">
-        <v>CR-234…237</v>
+        <v>CR-042</v>
       </c>
     </row>
     <row r="78">
@@ -2192,19 +2192,19 @@
         <v>Production</v>
       </c>
       <c r="C78" t="str">
-        <v>Bulk Record Production (make-to-stock)</v>
+        <v>Production page — Sheet / Kanban / Grid</v>
       </c>
       <c r="D78" t="str">
-        <v>A form in the Adjust Stock shape: Production date, recorded by and a description over an Item Table — Size · Item · Batch (blank = automatic) · Qty · Box Brand · Location per line — one line to start, + Add line; paste a block from Excel; one Save records every line into stock; retry-safe.</v>
+        <v>Three views of the same rows (Sheet default); one row per logged batch; Group by Item / Customer / Order / Size; status filter with All.</v>
       </c>
       <c r="E78" t="str">
         <v>Completed</v>
       </c>
       <c r="F78" t="str">
-        <v>2026-10-27</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G78" t="str">
-        <v>CR-244, 264, 469</v>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -2215,19 +2215,19 @@
         <v>Production</v>
       </c>
       <c r="C79" t="str">
-        <v>Sales Order ▸ Production tab per design</v>
+        <v>To Produce view</v>
       </c>
       <c r="D79" t="str">
-        <v>One row per design with its batches as chips and the requested / produced totals summed; totals footers on both tables.</v>
+        <v>Per item: open demand, free stock, in production and what still needs producing, with the Box Brand wanted; tick rows to start a job.</v>
       </c>
       <c r="E79" t="str">
         <v>Completed</v>
       </c>
       <c r="F79" t="str">
-        <v>2026-10-27</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G79" t="str">
-        <v>CR-470</v>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2238,10 +2238,10 @@
         <v>Production</v>
       </c>
       <c r="C80" t="str">
-        <v>Sheet edit mode</v>
+        <v>Start / Log / Complete Production</v>
       </c>
       <c r="D80" t="str">
-        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
+        <v>Start creates the job (Item · Quantity); Log adds batch rows from the row's + menu (first log → In Production, full coverage → Completed automatically); Complete closes the job.</v>
       </c>
       <c r="E80" t="str">
         <v>Completed</v>
@@ -2250,7 +2250,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G80" t="str">
-        <v>CR-111</v>
+        <v>CR-234…237</v>
       </c>
     </row>
     <row r="81">
@@ -2261,19 +2261,19 @@
         <v>Production</v>
       </c>
       <c r="C81" t="str">
-        <v>Excel import of the factory file</v>
+        <v>Bulk Record Production (make-to-stock)</v>
       </c>
       <c r="D81" t="str">
-        <v>Import production from the factory's spreadsheet.</v>
+        <v>A form in the Adjust Stock shape: Production date, recorded by and a description over an Item Table — Size · Item · Batch (blank = automatic) · Qty · Box Brand · Location per line — one line to start, + Add line; paste a block from Excel; one Save records every line into stock; retry-safe.</v>
       </c>
       <c r="E81" t="str">
         <v>Completed</v>
       </c>
       <c r="F81" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G81" t="str">
-        <v/>
+        <v>CR-244, 264, 469</v>
       </c>
     </row>
     <row r="82">
@@ -2284,19 +2284,19 @@
         <v>Production</v>
       </c>
       <c r="C82" t="str">
-        <v>Batch numbering and rules</v>
+        <v>Sales Order ▸ Production tab per design</v>
       </c>
       <c r="D82" t="str">
-        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
+        <v>One row per design with its batches as chips and the requested / produced totals summed; totals footers on both tables.</v>
       </c>
       <c r="E82" t="str">
         <v>Completed</v>
       </c>
       <c r="F82" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G82" t="str">
-        <v/>
+        <v>CR-470</v>
       </c>
     </row>
     <row r="83">
@@ -2307,19 +2307,19 @@
         <v>Production</v>
       </c>
       <c r="C83" t="str">
-        <v>Production detail page</v>
+        <v>Production tab per batch with Production date; stock actions on the tab</v>
       </c>
       <c r="D83" t="str">
-        <v>Lines, batches logged, activity.</v>
+        <v>Each batch on its own line with the day it was produced (not the allocation day), its boxes and who allocated it; Allocate Stock / Deallocate Stock sit above this table instead of on the Items card.</v>
       </c>
       <c r="E83" t="str">
         <v>Completed</v>
       </c>
       <c r="F83" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G83" t="str">
-        <v/>
+        <v>CR-479</v>
       </c>
     </row>
     <row r="84">
@@ -2330,19 +2330,19 @@
         <v>Production</v>
       </c>
       <c r="C84" t="str">
-        <v>Date-first production</v>
+        <v>Sheet edit mode</v>
       </c>
       <c r="D84" t="str">
-        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
+        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
       </c>
       <c r="E84" t="str">
         <v>Completed</v>
       </c>
       <c r="F84" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G84" t="str">
-        <v>CR-265, 267</v>
+        <v>CR-111</v>
       </c>
     </row>
     <row r="85">
@@ -2353,19 +2353,19 @@
         <v>Production</v>
       </c>
       <c r="C85" t="str">
-        <v>Quality Control stage on the board</v>
+        <v>Excel import of the factory file</v>
       </c>
       <c r="D85" t="str">
-        <v>QC exists in the data model; putting it on the board is parked.</v>
+        <v>Import production from the factory's spreadsheet.</v>
       </c>
       <c r="E85" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G85" t="str">
-        <v>CR-051</v>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -2376,16 +2376,16 @@
         <v>Production</v>
       </c>
       <c r="C86" t="str">
-        <v>Duplicate detection on Excel re-import</v>
+        <v>Batch numbering and rules</v>
       </c>
       <c r="D86" t="str">
-        <v>Warn / skip when the same production file is imported twice.</v>
+        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
       </c>
       <c r="E86" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -2396,13 +2396,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>Palletization</v>
+        <v>Production</v>
       </c>
       <c r="C87" t="str">
-        <v>Palletization board and plan numbers</v>
+        <v>Production detail page</v>
       </c>
       <c r="D87" t="str">
-        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
+        <v>Lines, batches logged, activity.</v>
       </c>
       <c r="E87" t="str">
         <v>Completed</v>
@@ -2419,22 +2419,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>Palletization</v>
+        <v>Production</v>
       </c>
       <c r="C88" t="str">
-        <v>Columns, totals footer and selection bar</v>
+        <v>Date-first production</v>
       </c>
       <c r="D88" t="str">
-        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
+        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
       </c>
       <c r="E88" t="str">
         <v>Completed</v>
       </c>
       <c r="F88" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G88" t="str">
-        <v>CR-279</v>
+        <v>CR-265, 267</v>
       </c>
     </row>
     <row r="89">
@@ -2442,22 +2442,22 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>Palletization</v>
+        <v>Production</v>
       </c>
       <c r="C89" t="str">
-        <v>Counts per batch: Ordered · Ready Pallets · Boxes / Pallet · Remaining</v>
+        <v>Quality Control stage on the board</v>
       </c>
       <c r="D89" t="str">
-        <v>Every palletization page counts the row's own batch — a loaded batch of the same item no longer shows on its sibling. Columns Boxes · Ordered Boxes · Ready Pallets (N (boxes)) · Boxes / Pallet · Remaining with totals; the Complete Palletization dialog shows the same figures.</v>
+        <v>QC exists in the data model; putting it on the board is parked.</v>
       </c>
       <c r="E89" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F89" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G89" t="str">
-        <v>CR-472</v>
+        <v>CR-051</v>
       </c>
     </row>
     <row r="90">
@@ -2465,19 +2465,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>Palletization</v>
+        <v>Production</v>
       </c>
       <c r="C90" t="str">
-        <v>Plan detail page</v>
+        <v>Duplicate detection on Excel re-import</v>
       </c>
       <c r="D90" t="str">
-        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
+        <v>Warn / skip when the same production file is imported twice.</v>
       </c>
       <c r="E90" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F90" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -2491,10 +2491,10 @@
         <v>Palletization</v>
       </c>
       <c r="C91" t="str">
-        <v>Prints on demand</v>
+        <v>Palletization board and plan numbers</v>
       </c>
       <c r="D91" t="str">
-        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
+        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
       </c>
       <c r="E91" t="str">
         <v>Completed</v>
@@ -2514,10 +2514,10 @@
         <v>Palletization</v>
       </c>
       <c r="C92" t="str">
-        <v>Board rules</v>
+        <v>Columns, totals footer and selection bar</v>
       </c>
       <c r="D92" t="str">
-        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
+        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
       </c>
       <c r="E92" t="str">
         <v>Completed</v>
@@ -2526,7 +2526,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G92" t="str">
-        <v>CR-129, 248</v>
+        <v>CR-279</v>
       </c>
     </row>
     <row r="93">
@@ -2537,19 +2537,19 @@
         <v>Palletization</v>
       </c>
       <c r="C93" t="str">
-        <v>Three ways onto the queue</v>
+        <v>Counts per batch: Ordered · Ready Pallets · Boxes / Pallet · Remaining</v>
       </c>
       <c r="D93" t="str">
-        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
+        <v>Every palletization page counts the row's own batch — a loaded batch of the same item no longer shows on its sibling. Columns Boxes · Ordered Boxes · Ready Pallets (N (boxes)) · Boxes / Pallet · Remaining with totals; the Complete Palletization dialog shows the same figures.</v>
       </c>
       <c r="E93" t="str">
         <v>Completed</v>
       </c>
       <c r="F93" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G93" t="str">
-        <v>CR-223/224</v>
+        <v>CR-472</v>
       </c>
     </row>
     <row r="94">
@@ -2560,19 +2560,19 @@
         <v>Palletization</v>
       </c>
       <c r="C94" t="str">
-        <v>'+' menu: Start / Top Up Batch / Complete</v>
+        <v>Whole pallets: Possible / Prepared Pallets, pallets recorded</v>
       </c>
       <c r="D94" t="str">
-        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
+        <v>No fractions — 23 boxes on an 18-box pallet is 1 pallet · 18 boxes, the 5 wait for a mixed-batch pallet. Ready for Palletization shows Possible Pallets; In Palletization shows Pending Boxes, Possible Pallets, Prepared Pallets and the boxes on them; Ready for Loading shows Pallets and Boxes. Boxes / Pallet and Remaining removed; Complete Palletization asks for pallets.</v>
       </c>
       <c r="E94" t="str">
         <v>Completed</v>
       </c>
       <c r="F94" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G94" t="str">
-        <v>CR-148…150, 281</v>
+        <v>CR-481</v>
       </c>
     </row>
     <row r="95">
@@ -2583,10 +2583,10 @@
         <v>Palletization</v>
       </c>
       <c r="C95" t="str">
-        <v>Sheet edit mode and multi-select</v>
+        <v>Plan detail page</v>
       </c>
       <c r="D95" t="str">
-        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
+        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
       </c>
       <c r="E95" t="str">
         <v>Completed</v>
@@ -2595,7 +2595,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G95" t="str">
-        <v>CR-153</v>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -2606,19 +2606,19 @@
         <v>Palletization</v>
       </c>
       <c r="C96" t="str">
-        <v>Date column, PAL code hidden</v>
+        <v>Prints on demand</v>
       </c>
       <c r="D96" t="str">
-        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
+        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
       </c>
       <c r="E96" t="str">
         <v>Completed</v>
       </c>
       <c r="F96" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G96" t="str">
-        <v>CR-266</v>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -2629,19 +2629,19 @@
         <v>Palletization</v>
       </c>
       <c r="C97" t="str">
-        <v>Complete dialog shows progress</v>
+        <v>Board rules</v>
       </c>
       <c r="D97" t="str">
-        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
+        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
       </c>
       <c r="E97" t="str">
         <v>Completed</v>
       </c>
       <c r="F97" t="str">
-        <v>2026-10-06</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G97" t="str">
-        <v>CR-280</v>
+        <v>CR-129, 248</v>
       </c>
     </row>
     <row r="98">
@@ -2652,19 +2652,19 @@
         <v>Palletization</v>
       </c>
       <c r="C98" t="str">
-        <v>Plan edit keeps Box Brand and batches</v>
+        <v>Three ways onto the queue</v>
       </c>
       <c r="D98" t="str">
-        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
+        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
       </c>
       <c r="E98" t="str">
         <v>Completed</v>
       </c>
       <c r="F98" t="str">
-        <v>2026-10-13</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G98" t="str">
-        <v>CR-340</v>
+        <v>CR-223/224</v>
       </c>
     </row>
     <row r="99">
@@ -2675,19 +2675,19 @@
         <v>Palletization</v>
       </c>
       <c r="C99" t="str">
-        <v>Three pages, one stage each</v>
+        <v>'+' menu: Start / Top Up Batch / Complete</v>
       </c>
       <c r="D99" t="str">
-        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
+        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
       </c>
       <c r="E99" t="str">
         <v>Completed</v>
       </c>
       <c r="F99" t="str">
-        <v>2026-10-21</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G99" t="str">
-        <v>CR-360, 364</v>
+        <v>CR-148…150, 281</v>
       </c>
     </row>
     <row r="100">
@@ -2698,19 +2698,19 @@
         <v>Palletization</v>
       </c>
       <c r="C100" t="str">
-        <v>Release palletized boxes</v>
+        <v>Sheet edit mode and multi-select</v>
       </c>
       <c r="D100" t="str">
-        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
+        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
       </c>
       <c r="E100" t="str">
         <v>Completed</v>
       </c>
       <c r="F100" t="str">
-        <v>2026-10-21</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G100" t="str">
-        <v>CR-361</v>
+        <v>CR-153</v>
       </c>
     </row>
     <row r="101">
@@ -2721,19 +2721,19 @@
         <v>Palletization</v>
       </c>
       <c r="C101" t="str">
-        <v>Discard the current palletization task</v>
+        <v>Date column, PAL code hidden</v>
       </c>
       <c r="D101" t="str">
-        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
+        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
       </c>
       <c r="E101" t="str">
         <v>Completed</v>
       </c>
       <c r="F101" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G101" t="str">
-        <v>CR-369</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="102">
@@ -2744,19 +2744,19 @@
         <v>Palletization</v>
       </c>
       <c r="C102" t="str">
-        <v>Delete a plan returns its boxes</v>
+        <v>Complete dialog shows progress</v>
       </c>
       <c r="D102" t="str">
-        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
+        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
       </c>
       <c r="E102" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F102" t="str">
-        <v/>
+        <v>2026-10-06</v>
       </c>
       <c r="G102" t="str">
-        <v>CR-370</v>
+        <v>CR-280</v>
       </c>
     </row>
     <row r="103">
@@ -2767,19 +2767,19 @@
         <v>Palletization</v>
       </c>
       <c r="C103" t="str">
-        <v>Partial Start Palletization</v>
+        <v>Plan edit keeps Box Brand and batches</v>
       </c>
       <c r="D103" t="str">
-        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
+        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
       </c>
       <c r="E103" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F103" t="str">
-        <v/>
+        <v>2026-10-13</v>
       </c>
       <c r="G103" t="str">
-        <v>Panel Craft list #9</v>
+        <v>CR-340</v>
       </c>
     </row>
     <row r="104">
@@ -2790,19 +2790,19 @@
         <v>Palletization</v>
       </c>
       <c r="C104" t="str">
-        <v>Ready pallets — type and pallet count</v>
+        <v>Three pages, one stage each</v>
       </c>
       <c r="D104" t="str">
-        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
+        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
       </c>
       <c r="E104" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F104" t="str">
-        <v/>
+        <v>2026-10-21</v>
       </c>
       <c r="G104" t="str">
-        <v>Panel Craft list #7</v>
+        <v>CR-360, 364</v>
       </c>
     </row>
     <row r="105">
@@ -2813,19 +2813,19 @@
         <v>Palletization</v>
       </c>
       <c r="C105" t="str">
-        <v>Remove 'Ordered / Completed' where not needed</v>
+        <v>Release palletized boxes</v>
       </c>
       <c r="D105" t="str">
-        <v>Screen to be confirmed.</v>
+        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
       </c>
       <c r="E105" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F105" t="str">
-        <v/>
+        <v>2026-10-21</v>
       </c>
       <c r="G105" t="str">
-        <v>Panel Craft list #8</v>
+        <v>CR-361</v>
       </c>
     </row>
     <row r="106">
@@ -2833,22 +2833,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C106" t="str">
-        <v>A loading = one container</v>
+        <v>Discard the current palletization task</v>
       </c>
       <c r="D106" t="str">
-        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
+        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
       </c>
       <c r="E106" t="str">
         <v>Completed</v>
       </c>
       <c r="F106" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G106" t="str">
-        <v>CR-120…124</v>
+        <v>CR-369</v>
       </c>
     </row>
     <row r="107">
@@ -2856,22 +2856,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C107" t="str">
-        <v>Loading and Dispatch page</v>
+        <v>Delete a plan returns its boxes</v>
       </c>
       <c r="D107" t="str">
-        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
+        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
       </c>
       <c r="E107" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F107" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G107" t="str">
-        <v>CR-140, 141</v>
+        <v>CR-370</v>
       </c>
     </row>
     <row r="108">
@@ -2879,22 +2879,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C108" t="str">
-        <v>Loading detail</v>
+        <v>Partial Start Palletization</v>
       </c>
       <c r="D108" t="str">
-        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
+        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
       </c>
       <c r="E108" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F108" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>Panel Craft list #9</v>
       </c>
     </row>
     <row r="109">
@@ -2902,22 +2902,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C109" t="str">
-        <v>Vehicle and shipment details</v>
+        <v>Ready pallets — type and pallet count</v>
       </c>
       <c r="D109" t="str">
-        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
+        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
       </c>
       <c r="E109" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F109" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>Panel Craft list #7</v>
       </c>
     </row>
     <row r="110">
@@ -2925,22 +2925,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C110" t="str">
-        <v>Dispatch with gates and warnings</v>
+        <v>Remove 'Ordered / Completed' where not needed</v>
       </c>
       <c r="D110" t="str">
-        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
+        <v>Screen to be confirmed.</v>
       </c>
       <c r="E110" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F110" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>Panel Craft list #8</v>
       </c>
     </row>
     <row r="111">
@@ -2951,10 +2951,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C111" t="str">
-        <v>Invoice and dispatch prints</v>
+        <v>A loading = one container</v>
       </c>
       <c r="D111" t="str">
-        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
+        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
       </c>
       <c r="E111" t="str">
         <v>Completed</v>
@@ -2963,7 +2963,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>CR-120…124</v>
       </c>
     </row>
     <row r="112">
@@ -2974,10 +2974,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C112" t="str">
-        <v>Four ways to fill a container</v>
+        <v>Loading and Dispatch page</v>
       </c>
       <c r="D112" t="str">
-        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
+        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
       </c>
       <c r="E112" t="str">
         <v>Completed</v>
@@ -2986,7 +2986,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G112" t="str">
-        <v>CR-126…128, 201/202</v>
+        <v>CR-140, 141</v>
       </c>
     </row>
     <row r="113">
@@ -2997,10 +2997,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C113" t="str">
-        <v>Editing a loading</v>
+        <v>Loading detail</v>
       </c>
       <c r="D113" t="str">
-        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
+        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
       </c>
       <c r="E113" t="str">
         <v>Completed</v>
@@ -3020,19 +3020,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C114" t="str">
-        <v>Date column, LOAD code hidden</v>
+        <v>Vehicle and shipment details</v>
       </c>
       <c r="D114" t="str">
-        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
+        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
       </c>
       <c r="E114" t="str">
         <v>Completed</v>
       </c>
       <c r="F114" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G114" t="str">
-        <v>CR-266</v>
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -3043,19 +3043,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C115" t="str">
-        <v>Several containers in one New Loading</v>
+        <v>Dispatch with gates and warnings</v>
       </c>
       <c r="D115" t="str">
-        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
+        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
       </c>
       <c r="E115" t="str">
         <v>Completed</v>
       </c>
       <c r="F115" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G115" t="str">
-        <v>CR-301</v>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -3066,19 +3066,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C116" t="str">
-        <v>Loading Workspace — a tab per container</v>
+        <v>Invoice and dispatch prints</v>
       </c>
       <c r="D116" t="str">
-        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
+        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
       </c>
       <c r="E116" t="str">
         <v>Completed</v>
       </c>
       <c r="F116" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G116" t="str">
-        <v>CR-326, 334, 335</v>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -3089,19 +3089,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C117" t="str">
-        <v>Every customer listed, with search</v>
+        <v>Four ways to fill a container</v>
       </c>
       <c r="D117" t="str">
-        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
+        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
       </c>
       <c r="E117" t="str">
         <v>Completed</v>
       </c>
       <c r="F117" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G117" t="str">
-        <v>CR-327</v>
+        <v>CR-126…128, 201/202</v>
       </c>
     </row>
     <row r="118">
@@ -3112,19 +3112,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C118" t="str">
-        <v>'What to do first' reasons</v>
+        <v>Editing a loading</v>
       </c>
       <c r="D118" t="str">
-        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
+        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
       </c>
       <c r="E118" t="str">
         <v>Completed</v>
       </c>
       <c r="F118" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G118" t="str">
-        <v>CR-328</v>
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -3135,19 +3135,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C119" t="str">
-        <v>Pick the planned container at loading</v>
+        <v>Date column, LOAD code hidden</v>
       </c>
       <c r="D119" t="str">
-        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
+        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
       </c>
       <c r="E119" t="str">
         <v>Completed</v>
       </c>
       <c r="F119" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G119" t="str">
-        <v>CR-338</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="120">
@@ -3158,19 +3158,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C120" t="str">
-        <v>Two steps per container; C1 / C2 naming</v>
+        <v>Several containers in one New Loading</v>
       </c>
       <c r="D120" t="str">
-        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
+        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
       </c>
       <c r="E120" t="str">
         <v>Completed</v>
       </c>
       <c r="F120" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G120" t="str">
-        <v>CR-350, 354</v>
+        <v>CR-301</v>
       </c>
     </row>
     <row r="121">
@@ -3181,19 +3181,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C121" t="str">
-        <v>Mix Batch at loading</v>
+        <v>Loading Workspace — a tab per container</v>
       </c>
       <c r="D121" t="str">
-        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
+        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
       </c>
       <c r="E121" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F121" t="str">
-        <v/>
+        <v>2026-10-12</v>
       </c>
       <c r="G121" t="str">
-        <v>CR-260 follow-up</v>
+        <v>CR-326, 334, 335</v>
       </c>
     </row>
     <row r="122">
@@ -3201,22 +3201,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C122" t="str">
-        <v>One stock rule everywhere</v>
+        <v>Every customer listed, with search</v>
       </c>
       <c r="D122" t="str">
-        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
+        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
       </c>
       <c r="E122" t="str">
         <v>Completed</v>
       </c>
       <c r="F122" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G122" t="str">
-        <v/>
+        <v>CR-327</v>
       </c>
     </row>
     <row r="123">
@@ -3224,22 +3224,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C123" t="str">
-        <v>Counters recomputed, never incremented</v>
+        <v>'What to do first' reasons</v>
       </c>
       <c r="D123" t="str">
-        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
+        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
       </c>
       <c r="E123" t="str">
         <v>Completed</v>
       </c>
       <c r="F123" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G123" t="str">
-        <v/>
+        <v>CR-328</v>
       </c>
     </row>
     <row r="124">
@@ -3247,22 +3247,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C124" t="str">
-        <v>Allocation and batch ledger</v>
+        <v>Pick the planned container at loading</v>
       </c>
       <c r="D124" t="str">
-        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
+        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
       </c>
       <c r="E124" t="str">
         <v>Completed</v>
       </c>
       <c r="F124" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G124" t="str">
-        <v/>
+        <v>CR-338</v>
       </c>
     </row>
     <row r="125">
@@ -3270,22 +3270,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C125" t="str">
-        <v>Admin repair operations</v>
+        <v>Two steps per container; C1 / C2 naming</v>
       </c>
       <c r="D125" t="str">
-        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
+        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
       </c>
       <c r="E125" t="str">
         <v>Completed</v>
       </c>
       <c r="F125" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G125" t="str">
-        <v/>
+        <v>CR-350, 354</v>
       </c>
     </row>
     <row r="126">
@@ -3293,22 +3293,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C126" t="str">
-        <v>Inventory adjustments</v>
+        <v>Mix Batch at loading</v>
       </c>
       <c r="D126" t="str">
-        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
+        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
       </c>
       <c r="E126" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F126" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G126" t="str">
-        <v>CR-308</v>
+        <v>CR-260 follow-up</v>
       </c>
     </row>
     <row r="127">
@@ -3316,22 +3316,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C127" t="str">
-        <v>Stock per warehouse</v>
+        <v>Five stage pages: Palletization Completed, Loading, Dispatch</v>
       </c>
       <c r="D127" t="str">
-        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
+        <v>Palletization Completed stays its own page; Loading lists the items being loaded; the new Dispatch page lists the containers ready to dispatch and the dispatched ones, with their prints.</v>
       </c>
       <c r="E127" t="str">
         <v>Completed</v>
       </c>
       <c r="F127" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G127" t="str">
-        <v>CR-329</v>
+        <v>CR-480</v>
       </c>
     </row>
     <row r="128">
@@ -3342,19 +3342,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C128" t="str">
-        <v>Transfer Orders</v>
+        <v>One stock rule everywhere</v>
       </c>
       <c r="D128" t="str">
-        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
+        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
       </c>
       <c r="E128" t="str">
         <v>Completed</v>
       </c>
       <c r="F128" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G128" t="str">
-        <v>CR-330</v>
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -3365,19 +3365,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C129" t="str">
-        <v>Locations on items</v>
+        <v>Counters recomputed, never incremented</v>
       </c>
       <c r="D129" t="str">
-        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
+        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
       </c>
       <c r="E129" t="str">
         <v>Completed</v>
       </c>
       <c r="F129" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G129" t="str">
-        <v>CR-332</v>
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -3388,19 +3388,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C130" t="str">
-        <v>Stock keyed by the item</v>
+        <v>Allocation and batch ledger</v>
       </c>
       <c r="D130" t="str">
-        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
+        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
       </c>
       <c r="E130" t="str">
         <v>Completed</v>
       </c>
       <c r="F130" t="str">
-        <v>2026-10-13</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G130" t="str">
-        <v>CR-341</v>
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -3408,13 +3408,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C131" t="str">
-        <v>Sales reports</v>
+        <v>Admin repair operations</v>
       </c>
       <c r="D131" t="str">
-        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
+        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
       </c>
       <c r="E131" t="str">
         <v>Completed</v>
@@ -3431,22 +3431,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C132" t="str">
-        <v>Inventory reports</v>
+        <v>Inventory adjustments</v>
       </c>
       <c r="D132" t="str">
-        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
+        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
       </c>
       <c r="E132" t="str">
         <v>Completed</v>
       </c>
       <c r="F132" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G132" t="str">
-        <v>CR-104</v>
+        <v>CR-308</v>
       </c>
     </row>
     <row r="133">
@@ -3454,22 +3454,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C133" t="str">
-        <v>Dispatch reports</v>
+        <v>Stock per warehouse</v>
       </c>
       <c r="D133" t="str">
-        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
+        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
       </c>
       <c r="E133" t="str">
         <v>Completed</v>
       </c>
       <c r="F133" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G133" t="str">
-        <v>CR-104</v>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="134">
@@ -3477,22 +3477,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C134" t="str">
-        <v>Audit log and activity</v>
+        <v>Transfer Orders</v>
       </c>
       <c r="D134" t="str">
-        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
+        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
       </c>
       <c r="E134" t="str">
         <v>Completed</v>
       </c>
       <c r="F134" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G134" t="str">
-        <v/>
+        <v>CR-330</v>
       </c>
     </row>
     <row r="135">
@@ -3500,22 +3500,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C135" t="str">
-        <v>Dashboard</v>
+        <v>Locations on items</v>
       </c>
       <c r="D135" t="str">
-        <v>Headline numbers.</v>
+        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
       </c>
       <c r="E135" t="str">
         <v>Completed</v>
       </c>
       <c r="F135" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G135" t="str">
-        <v/>
+        <v>CR-332</v>
       </c>
     </row>
     <row r="136">
@@ -3523,22 +3523,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C136" t="str">
-        <v>Warehouse Stock report</v>
+        <v>Stock keyed by the item</v>
       </c>
       <c r="D136" t="str">
-        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
+        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
       </c>
       <c r="E136" t="str">
         <v>Completed</v>
       </c>
       <c r="F136" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G136" t="str">
-        <v>CR-331</v>
+        <v>CR-341</v>
       </c>
     </row>
     <row r="137">
@@ -3546,22 +3546,22 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C137" t="str">
-        <v>Panel Master</v>
+        <v>Sales reports</v>
       </c>
       <c r="D137" t="str">
-        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
+        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
       </c>
       <c r="E137" t="str">
         <v>Completed</v>
       </c>
       <c r="F137" t="str">
-        <v>2026-10-08</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G137" t="str">
-        <v>CR-283…285, 291, 319</v>
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -3569,22 +3569,22 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C138" t="str">
-        <v>Remarks on a panel</v>
+        <v>Inventory reports</v>
       </c>
       <c r="D138" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
       </c>
       <c r="E138" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F138" t="str">
-        <v/>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G138" t="str">
-        <v>CR-425</v>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="139">
@@ -3592,22 +3592,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C139" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Dispatch reports</v>
       </c>
       <c r="D139" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
       </c>
       <c r="E139" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F139" t="str">
-        <v/>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G139" t="str">
-        <v>CR-426</v>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="140">
@@ -3615,22 +3615,22 @@
         <v>139</v>
       </c>
       <c r="B140" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C140" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Audit log and activity</v>
       </c>
       <c r="D140" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
       </c>
       <c r="E140" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F140" t="str">
-        <v/>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G140" t="str">
-        <v>CR-427</v>
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -3638,22 +3638,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C141" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Dashboard</v>
       </c>
       <c r="D141" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>Headline numbers.</v>
       </c>
       <c r="E141" t="str">
         <v>Completed</v>
       </c>
       <c r="F141" t="str">
-        <v>2026-10-24</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G141" t="str">
-        <v>CR-428</v>
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -3661,22 +3661,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C142" t="str">
-        <v>One Masters page</v>
+        <v>Warehouse Stock report</v>
       </c>
       <c r="D142" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
       </c>
       <c r="E142" t="str">
         <v>Completed</v>
       </c>
       <c r="F142" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G142" t="str">
-        <v>CR-436</v>
+        <v>CR-331</v>
       </c>
     </row>
     <row r="143">
@@ -3684,22 +3684,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C143" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>Panel Master</v>
       </c>
       <c r="D143" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
       </c>
       <c r="E143" t="str">
         <v>Completed</v>
       </c>
       <c r="F143" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G143" t="str">
-        <v>CR-439</v>
+        <v>CR-283…285, 291, 319</v>
       </c>
     </row>
     <row r="144">
@@ -3707,22 +3707,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C144" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>Panel form opens with a blank size</v>
       </c>
       <c r="D144" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>New Panel no longer prefills 1200x2100; the size is typed.</v>
       </c>
       <c r="E144" t="str">
         <v>Completed</v>
       </c>
       <c r="F144" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G144" t="str">
-        <v>CR-440</v>
+        <v>CR-484</v>
       </c>
     </row>
     <row r="145">
@@ -3730,22 +3730,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>Items</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C145" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Sample order Actions tab</v>
       </c>
       <c r="D145" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>A sample order has the panel order's tabs (Details · Readiness · Actions · Dispatch · Activity). Loads are recorded on the Actions tab — quantity per row, + Load… on one row, Dispatch, Load Copy per trip — the header Record Load button is gone.</v>
       </c>
       <c r="E145" t="str">
         <v>Completed</v>
       </c>
       <c r="F145" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G145" t="str">
-        <v>CR-437</v>
+        <v>CR-485</v>
       </c>
     </row>
     <row r="146">
@@ -3753,22 +3753,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C146" t="str">
-        <v>Names save as Title Case</v>
+        <v>Sample order pick slip</v>
       </c>
       <c r="D146" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>More ▸ Print order PDF on a sample order: every item with its photo, name and item code, full tile / cut piece size, Requested · Supplied · Remaining, the remark typed on the line and an empty Broken / Adjustment box to fill in by hand; the Stock Adjustments reminder and Taken out by / Checked by lines.</v>
       </c>
       <c r="E146" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F146" t="str">
-        <v/>
+        <v>2026-10-28</v>
       </c>
       <c r="G146" t="str">
-        <v>CR-429</v>
+        <v>CR-486</v>
       </c>
     </row>
     <row r="147">
@@ -3776,13 +3776,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C147" t="str">
-        <v>Brand off the Item form</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D147" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E147" t="str">
         <v>In progress</v>
@@ -3791,7 +3791,7 @@
         <v/>
       </c>
       <c r="G147" t="str">
-        <v>CR-430</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="148">
@@ -3802,19 +3802,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C148" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D148" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E148" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F148" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G148" t="str">
-        <v>CR-306</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="149">
@@ -3822,22 +3822,22 @@
         <v>148</v>
       </c>
       <c r="B149" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C149" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D149" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E149" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F149" t="str">
-        <v>2026-10-15</v>
+        <v/>
       </c>
       <c r="G149" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="150">
@@ -3845,22 +3845,22 @@
         <v>149</v>
       </c>
       <c r="B150" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C150" t="str">
-        <v>MDF master</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D150" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E150" t="str">
         <v>Completed</v>
       </c>
       <c r="F150" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G150" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="151">
@@ -3868,22 +3868,22 @@
         <v>150</v>
       </c>
       <c r="B151" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C151" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>One Masters page</v>
       </c>
       <c r="D151" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E151" t="str">
         <v>Completed</v>
       </c>
       <c r="F151" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G151" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="152">
@@ -3891,22 +3891,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C152" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D152" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
       </c>
       <c r="F152" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="153">
@@ -3914,22 +3914,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C153" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D153" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
       </c>
       <c r="F153" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="154">
@@ -3937,22 +3937,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="str">
-        <v>Panel Craft</v>
+        <v>Items</v>
       </c>
       <c r="C154" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D154" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
       </c>
       <c r="F154" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="155">
@@ -3960,22 +3960,22 @@
         <v>154</v>
       </c>
       <c r="B155" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C155" t="str">
-        <v>Production checkpoints</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D155" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E155" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F155" t="str">
-        <v>2026-10-09</v>
+        <v/>
       </c>
       <c r="G155" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="156">
@@ -3983,22 +3983,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C156" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D156" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E156" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F156" t="str">
-        <v>2026-10-09</v>
+        <v/>
       </c>
       <c r="G156" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="157">
@@ -4009,19 +4009,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C157" t="str">
-        <v>Sample Orders</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D157" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E157" t="str">
         <v>Completed</v>
       </c>
       <c r="F157" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G157" t="str">
-        <v>CR-315…317</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="158">
@@ -4032,10 +4032,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C158" t="str">
-        <v>One Orders register</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D158" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E158" t="str">
         <v>Completed</v>
@@ -4044,7 +4044,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G158" t="str">
-        <v>CR-345</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="159">
@@ -4055,10 +4055,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C159" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>MDF master</v>
       </c>
       <c r="D159" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E159" t="str">
         <v>Completed</v>
@@ -4067,7 +4067,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G159" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="160">
@@ -4078,19 +4078,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C160" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D160" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E160" t="str">
         <v>Completed</v>
       </c>
       <c r="F160" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G160" t="str">
-        <v>CR-349</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="161">
@@ -4101,19 +4101,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C161" t="str">
-        <v>Load Copy print</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D161" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
       </c>
       <c r="F161" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-351</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="162">
@@ -4124,19 +4124,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C162" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D162" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E162" t="str">
         <v>Completed</v>
       </c>
       <c r="F162" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-433</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="163">
@@ -4147,10 +4147,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C163" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D163" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E163" t="str">
         <v>Completed</v>
@@ -4159,7 +4159,7 @@
         <v>2026-10-07</v>
       </c>
       <c r="G163" t="str">
-        <v>CR-311</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="164">
@@ -4170,19 +4170,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C164" t="str">
-        <v>Small UX items</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D164" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E164" t="str">
         <v>Completed</v>
       </c>
       <c r="F164" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G164" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="165">
@@ -4193,19 +4193,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C165" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D165" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E165" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F165" t="str">
-        <v/>
+        <v>2026-10-09</v>
       </c>
       <c r="G165" t="str">
-        <v>CR-365</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="166">
@@ -4216,19 +4216,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C166" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D166" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E166" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F166" t="str">
-        <v/>
+        <v>2026-10-08</v>
       </c>
       <c r="G166" t="str">
-        <v>CR-366</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="167">
@@ -4239,19 +4239,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C167" t="str">
-        <v>One Status column</v>
+        <v>One Orders register</v>
       </c>
       <c r="D167" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E167" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F167" t="str">
-        <v/>
+        <v>2026-10-15</v>
       </c>
       <c r="G167" t="str">
-        <v>CR-367</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="168">
@@ -4262,19 +4262,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D168" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E168" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F168" t="str">
-        <v/>
+        <v>2026-10-15</v>
       </c>
       <c r="G168" t="str">
-        <v>CR-368</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="169">
@@ -4285,19 +4285,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D169" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E169" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F169" t="str">
-        <v/>
+        <v>2026-10-15</v>
       </c>
       <c r="G169" t="str">
-        <v>CR-399</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="170">
@@ -4308,19 +4308,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>One four-state order status</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D170" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E170" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F170" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G170" t="str">
-        <v>CR-400</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="171">
@@ -4331,19 +4331,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D171" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E171" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F171" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G171" t="str">
-        <v>CR-401</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="172">
@@ -4354,19 +4354,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D172" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E172" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F172" t="str">
-        <v/>
+        <v>2026-10-07</v>
       </c>
       <c r="G172" t="str">
-        <v>CR-402</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="173">
@@ -4377,19 +4377,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Small UX items</v>
       </c>
       <c r="D173" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E173" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F173" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G173" t="str">
-        <v>CR-403</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="174">
@@ -4400,10 +4400,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Load part of a panel</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D174" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E174" t="str">
         <v>In progress</v>
@@ -4412,7 +4412,7 @@
         <v/>
       </c>
       <c r="G174" t="str">
-        <v>CR-405</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="175">
@@ -4423,10 +4423,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C175" t="str">
-        <v>MDF row on every panel</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D175" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E175" t="str">
         <v>In progress</v>
@@ -4435,7 +4435,7 @@
         <v/>
       </c>
       <c r="G175" t="str">
-        <v>CR-406</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="176">
@@ -4446,10 +4446,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C176" t="str">
-        <v>Load whole panel in one click</v>
+        <v>One Status column</v>
       </c>
       <c r="D176" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E176" t="str">
         <v>In progress</v>
@@ -4458,7 +4458,7 @@
         <v/>
       </c>
       <c r="G176" t="str">
-        <v>CR-407</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="177">
@@ -4466,22 +4466,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C177" t="str">
-        <v>Settings search everywhere</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D177" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E177" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F177" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G177" t="str">
-        <v>CR-408</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="178">
@@ -4489,22 +4489,22 @@
         <v>177</v>
       </c>
       <c r="B178" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C178" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D178" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E178" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F178" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G178" t="str">
-        <v>CR-409</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="179">
@@ -4512,22 +4512,22 @@
         <v>178</v>
       </c>
       <c r="B179" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C179" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D179" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E179" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F179" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G179" t="str">
-        <v>CR-438</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="180">
@@ -4535,22 +4535,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C180" t="str">
-        <v>Stock adjustment as a line form</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D180" t="str">
-        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E180" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F180" t="str">
-        <v>2026-10-25</v>
+        <v/>
       </c>
       <c r="G180" t="str">
-        <v>CR-446</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="181">
@@ -4558,22 +4558,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C181" t="str">
-        <v>Adjust Stock in the Zoho Books shape</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D181" t="str">
-        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E181" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F181" t="str">
-        <v>2026-10-26</v>
+        <v/>
       </c>
       <c r="G181" t="str">
-        <v>CR-457</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="182">
@@ -4581,22 +4581,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C182" t="str">
-        <v>Location Transfer from the Adjust Stock screen</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D182" t="str">
-        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E182" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F182" t="str">
-        <v>2026-10-26</v>
+        <v/>
       </c>
       <c r="G182" t="str">
-        <v>CR-458</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="183">
@@ -4604,22 +4604,22 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C183" t="str">
-        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D183" t="str">
-        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E183" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F183" t="str">
-        <v>2026-10-26</v>
+        <v/>
       </c>
       <c r="G183" t="str">
-        <v>CR-459</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="184">
@@ -4627,22 +4627,22 @@
         <v>183</v>
       </c>
       <c r="B184" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Cut Piece detail page inside Panel Craft</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D184" t="str">
-        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E184" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F184" t="str">
-        <v>2026-10-26</v>
+        <v/>
       </c>
       <c r="G184" t="str">
-        <v>CR-460/461</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="185">
@@ -4650,22 +4650,22 @@
         <v>184</v>
       </c>
       <c r="B185" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Pager with First / Last arrows</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D185" t="str">
-        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E185" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F185" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G185" t="str">
-        <v>CR-467</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="186">
@@ -4676,19 +4676,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C186" t="str">
-        <v>Red close × on every window</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D186" t="str">
-        <v>The × that closes any window or drawer is red on every screen.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E186" t="str">
         <v>Completed</v>
       </c>
       <c r="F186" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G186" t="str">
-        <v>CR-465</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="187">
@@ -4696,22 +4696,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C187" t="str">
-        <v>Advanced search date range fits the window</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D187" t="str">
-        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E187" t="str">
         <v>Completed</v>
       </c>
       <c r="F187" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-464</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="188">
@@ -4719,22 +4719,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Customers</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C188" t="str">
-        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D188" t="str">
-        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
       </c>
       <c r="F188" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-463/466</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="189">
@@ -4745,19 +4745,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C189" t="str">
-        <v>Stock history in date order</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D189" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
       </c>
       <c r="F189" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-455</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="190">
@@ -4765,22 +4765,22 @@
         <v>189</v>
       </c>
       <c r="B190" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C190" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D190" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
       </c>
       <c r="F190" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-447</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="191">
@@ -4788,22 +4788,22 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C191" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D191" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
       </c>
       <c r="F191" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-448</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="192">
@@ -4811,13 +4811,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C192" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D192" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
@@ -4826,7 +4826,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-456</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="193">
@@ -4834,22 +4834,22 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C193" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D193" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E193" t="str">
         <v>Completed</v>
       </c>
       <c r="F193" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-449</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="194">
@@ -4857,22 +4857,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C194" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D194" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E194" t="str">
         <v>Completed</v>
       </c>
       <c r="F194" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G194" t="str">
-        <v>CR-450</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="195">
@@ -4880,22 +4880,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C195" t="str">
-        <v>Location at every stage</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D195" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
       </c>
       <c r="F195" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-411…413</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="196">
@@ -4903,22 +4903,22 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C196" t="str">
-        <v>Panel location</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D196" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
       </c>
       <c r="F196" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-410</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="197">
@@ -4926,22 +4926,22 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Panel Craft</v>
+        <v>Customers</v>
       </c>
       <c r="C197" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D197" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
       </c>
       <c r="F197" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-419</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="198">
@@ -4949,22 +4949,22 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C198" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D198" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
       </c>
       <c r="F198" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-415</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="199">
@@ -4975,19 +4975,19 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C199" t="str">
-        <v>No long helper notes</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D199" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E199" t="str">
         <v>Completed</v>
       </c>
       <c r="F199" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-416</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="200">
@@ -4995,22 +4995,22 @@
         <v>199</v>
       </c>
       <c r="B200" t="str">
-        <v>Production</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C200" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D200" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
       </c>
       <c r="F200" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G200" t="str">
-        <v>CR-417</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="201">
@@ -5018,22 +5018,22 @@
         <v>200</v>
       </c>
       <c r="B201" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C201" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D201" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E201" t="str">
         <v>Completed</v>
       </c>
       <c r="F201" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G201" t="str">
-        <v>CR-418</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="202">
@@ -5041,22 +5041,22 @@
         <v>201</v>
       </c>
       <c r="B202" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C202" t="str">
-        <v>Notifications read / unread</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D202" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E202" t="str">
         <v>Completed</v>
       </c>
       <c r="F202" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G202" t="str">
-        <v>CR-419…421</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="203">
@@ -5064,22 +5064,22 @@
         <v>202</v>
       </c>
       <c r="B203" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C203" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D203" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E203" t="str">
         <v>Completed</v>
       </c>
       <c r="F203" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G203" t="str">
-        <v>CR-422</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="204">
@@ -5087,22 +5087,22 @@
         <v>203</v>
       </c>
       <c r="B204" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C204" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D204" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E204" t="str">
         <v>Completed</v>
       </c>
       <c r="F204" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G204" t="str">
-        <v>CR-404</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="205">
@@ -5113,19 +5113,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C205" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Panel location</v>
       </c>
       <c r="D205" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E205" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F205" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G205" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="206">
@@ -5136,19 +5136,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C206" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D206" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E206" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F206" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G206" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="207">
@@ -5159,19 +5159,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C207" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D207" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E207" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F207" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G207" t="str">
-        <v>Panel Craft list #2</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="208">
@@ -5179,22 +5179,22 @@
         <v>207</v>
       </c>
       <c r="B208" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C208" t="str">
-        <v>Panel auto-sequence</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D208" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E208" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F208" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G208" t="str">
-        <v>Panel Craft list #4</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="209">
@@ -5202,22 +5202,22 @@
         <v>208</v>
       </c>
       <c r="B209" t="str">
-        <v>Panel Craft</v>
+        <v>Production</v>
       </c>
       <c r="C209" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D209" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E209" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F209" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G209" t="str">
-        <v>Panel Craft list #5</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="210">
@@ -5225,22 +5225,22 @@
         <v>209</v>
       </c>
       <c r="B210" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C210" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D210" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E210" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F210" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G210" t="str">
-        <v>Panel Craft list #6</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="211">
@@ -5248,22 +5248,22 @@
         <v>210</v>
       </c>
       <c r="B211" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C211" t="str">
-        <v>Bill / expense</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D211" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E211" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F211" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G211" t="str">
-        <v>Panel Craft list #12</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="212">
@@ -5271,22 +5271,22 @@
         <v>211</v>
       </c>
       <c r="B212" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C212" t="str">
-        <v>Item code for the catalog</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D212" t="str">
-        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
       </c>
       <c r="F212" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G212" t="str">
-        <v>CR-473</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="213">
@@ -5297,19 +5297,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C213" t="str">
-        <v>Panel Order PDF — one page per panel</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D213" t="str">
-        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
       </c>
       <c r="F213" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-23</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-474</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="214">
@@ -5317,22 +5317,22 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C214" t="str">
-        <v>Sales Order without a Location field</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D214" t="str">
-        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E214" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F214" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G214" t="str">
-        <v>CR-468</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="215">
@@ -5340,22 +5340,22 @@
         <v>214</v>
       </c>
       <c r="B215" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C215" t="str">
-        <v>Pallet form without Box Weight</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D215" t="str">
-        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E215" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F215" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G215" t="str">
-        <v>CR-471</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="216">
@@ -5366,10 +5366,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C216" t="str">
-        <v>Boffo / Bonza company separation</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D216" t="str">
-        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E216" t="str">
         <v>Future</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="G216" t="str">
-        <v>ON-HOLD #1</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="217">
@@ -5386,22 +5386,22 @@
         <v>216</v>
       </c>
       <c r="B217" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C217" t="str">
-        <v>System reference and change-request register</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D217" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E217" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F217" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G217" t="str">
-        <v/>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="218">
@@ -5409,22 +5409,22 @@
         <v>217</v>
       </c>
       <c r="B218" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C218" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D218" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E218" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F218" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G218" t="str">
-        <v/>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="219">
@@ -5432,22 +5432,22 @@
         <v>218</v>
       </c>
       <c r="B219" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C219" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D219" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E219" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F219" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G219" t="str">
-        <v/>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="220">
@@ -5455,22 +5455,22 @@
         <v>219</v>
       </c>
       <c r="B220" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C220" t="str">
-        <v>Data Flow reference</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D220" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E220" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F220" t="str">
-        <v>2026-10-03</v>
+        <v/>
       </c>
       <c r="G220" t="str">
-        <v>CR-272</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="221">
@@ -5478,22 +5478,22 @@
         <v>220</v>
       </c>
       <c r="B221" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C221" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Item code for the catalog</v>
       </c>
       <c r="D221" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
       </c>
       <c r="E221" t="str">
         <v>Completed</v>
       </c>
       <c r="F221" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G221" t="str">
-        <v/>
+        <v>CR-473</v>
       </c>
     </row>
     <row r="222">
@@ -5501,22 +5501,22 @@
         <v>221</v>
       </c>
       <c r="B222" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C222" t="str">
-        <v>Locations guide</v>
+        <v>Panel Order PDF — one page per panel</v>
       </c>
       <c r="D222" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
       </c>
       <c r="E222" t="str">
         <v>Completed</v>
       </c>
       <c r="F222" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G222" t="str">
-        <v>CR-411…413</v>
+        <v>CR-474</v>
       </c>
     </row>
     <row r="223">
@@ -5524,22 +5524,22 @@
         <v>222</v>
       </c>
       <c r="B223" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C223" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Sales Order without a Location field</v>
       </c>
       <c r="D223" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
       </c>
       <c r="E223" t="str">
         <v>Completed</v>
       </c>
       <c r="F223" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G223" t="str">
-        <v/>
+        <v>CR-468</v>
       </c>
     </row>
     <row r="224">
@@ -5547,22 +5547,22 @@
         <v>223</v>
       </c>
       <c r="B224" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C224" t="str">
-        <v>Demo / test environment</v>
+        <v>Box Brand mandatory</v>
       </c>
       <c r="D224" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
       </c>
       <c r="E224" t="str">
         <v>Completed</v>
       </c>
       <c r="F224" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G224" t="str">
-        <v>CR-441</v>
+        <v>CR-483</v>
       </c>
     </row>
     <row r="225">
@@ -5570,28 +5570,258 @@
         <v>224</v>
       </c>
       <c r="B225" t="str">
+        <v>Masters (Inventory)</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Pallet form without Box Weight</v>
+      </c>
+      <c r="D225" t="str">
+        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
+      </c>
+      <c r="E225" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F225" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="G225" t="str">
+        <v>CR-471</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Panel Craft</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Boffo / Bonza company separation</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
+      </c>
+      <c r="E226" t="str">
+        <v>Future</v>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v>ON-HOLD #1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="str">
         <v>Documentation &amp; process</v>
       </c>
-      <c r="C225" t="str">
+      <c r="C227" t="str">
+        <v>System reference and change-request register</v>
+      </c>
+      <c r="D227" t="str">
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+      </c>
+      <c r="E227" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Change log, user flow, user manual</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+      </c>
+      <c r="E228" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F228" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Seed and teardown scripts</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+      </c>
+      <c r="E229" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Data Flow reference</v>
+      </c>
+      <c r="D230" t="str">
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+      </c>
+      <c r="E230" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F230" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G230" t="str">
+        <v>CR-272</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Phase 2 inventory</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+      </c>
+      <c r="E231" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F231" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Locations guide</v>
+      </c>
+      <c r="D232" t="str">
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+      </c>
+      <c r="E232" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F232" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="G232" t="str">
+        <v>CR-411…413</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Deliverables list (this workbook)</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+      </c>
+      <c r="E233" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F233" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D234" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E234" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F234" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G234" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C235" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D225" t="str">
+      <c r="D235" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E225" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F225" t="str">
+      <c r="E235" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F235" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G225" t="str">
+      <c r="G235" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G225"/>
+  <autoFilter ref="A1:G235"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G225"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G235"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G236</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G236"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3779,19 +3779,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C147" t="str">
-        <v>Remarks on a panel</v>
+        <v>Allocate Stock on sample orders</v>
       </c>
       <c r="D147" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>A sample order books cut pieces the way a panel order does: Requirements card on its Actions tab (Need · In Stock · Allocated · Short) and the same Allocate Stock window; a cut-piece row loads only once booked, the load consumes the booking; panel and sample bookings share one pool so no piece is promised twice; Pending Cut Stock counts sample demand.</v>
       </c>
       <c r="E147" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F147" t="str">
-        <v/>
+        <v>2026-10-28</v>
       </c>
       <c r="G147" t="str">
-        <v>CR-425</v>
+        <v>CR-487</v>
       </c>
     </row>
     <row r="148">
@@ -3802,10 +3802,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C148" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D148" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E148" t="str">
         <v>In progress</v>
@@ -3814,7 +3814,7 @@
         <v/>
       </c>
       <c r="G148" t="str">
-        <v>CR-426</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="149">
@@ -3822,13 +3822,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C149" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D149" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E149" t="str">
         <v>In progress</v>
@@ -3837,7 +3837,7 @@
         <v/>
       </c>
       <c r="G149" t="str">
-        <v>CR-427</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="150">
@@ -3845,22 +3845,22 @@
         <v>149</v>
       </c>
       <c r="B150" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C150" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D150" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E150" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F150" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G150" t="str">
-        <v>CR-428</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="151">
@@ -3871,10 +3871,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C151" t="str">
-        <v>One Masters page</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D151" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E151" t="str">
         <v>Completed</v>
@@ -3883,7 +3883,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G151" t="str">
-        <v>CR-436</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="152">
@@ -3894,10 +3894,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C152" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>One Masters page</v>
       </c>
       <c r="D152" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
@@ -3906,7 +3906,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-439</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="153">
@@ -3917,10 +3917,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C153" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D153" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
@@ -3929,7 +3929,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-440</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="154">
@@ -3937,13 +3937,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="str">
-        <v>Items</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C154" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D154" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
@@ -3952,7 +3952,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-437</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="155">
@@ -3960,22 +3960,22 @@
         <v>154</v>
       </c>
       <c r="B155" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Items</v>
       </c>
       <c r="C155" t="str">
-        <v>Names save as Title Case</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D155" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E155" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F155" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G155" t="str">
-        <v>CR-429</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="156">
@@ -3983,13 +3983,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C156" t="str">
-        <v>Brand off the Item form</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D156" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E156" t="str">
         <v>In progress</v>
@@ -3998,7 +3998,7 @@
         <v/>
       </c>
       <c r="G156" t="str">
-        <v>CR-430</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="157">
@@ -4006,22 +4006,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C157" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D157" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E157" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F157" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G157" t="str">
-        <v>CR-306</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="158">
@@ -4032,19 +4032,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C158" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D158" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E158" t="str">
         <v>Completed</v>
       </c>
       <c r="F158" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G158" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="159">
@@ -4055,10 +4055,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C159" t="str">
-        <v>MDF master</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D159" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E159" t="str">
         <v>Completed</v>
@@ -4067,7 +4067,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G159" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="160">
@@ -4078,19 +4078,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C160" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>MDF master</v>
       </c>
       <c r="D160" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E160" t="str">
         <v>Completed</v>
       </c>
       <c r="F160" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G160" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="161">
@@ -4101,19 +4101,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C161" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D161" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
       </c>
       <c r="F161" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="162">
@@ -4124,19 +4124,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C162" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D162" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E162" t="str">
         <v>Completed</v>
       </c>
       <c r="F162" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="163">
@@ -4147,19 +4147,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C163" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D163" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E163" t="str">
         <v>Completed</v>
       </c>
       <c r="F163" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G163" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="164">
@@ -4170,19 +4170,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C164" t="str">
-        <v>Production checkpoints</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D164" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E164" t="str">
         <v>Completed</v>
       </c>
       <c r="F164" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G164" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="165">
@@ -4193,10 +4193,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C165" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D165" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E165" t="str">
         <v>Completed</v>
@@ -4205,7 +4205,7 @@
         <v>2026-10-09</v>
       </c>
       <c r="G165" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="166">
@@ -4216,19 +4216,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C166" t="str">
-        <v>Sample Orders</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D166" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E166" t="str">
         <v>Completed</v>
       </c>
       <c r="F166" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G166" t="str">
-        <v>CR-315…317</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="167">
@@ -4239,19 +4239,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C167" t="str">
-        <v>One Orders register</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D167" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E167" t="str">
         <v>Completed</v>
       </c>
       <c r="F167" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G167" t="str">
-        <v>CR-345</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="168">
@@ -4262,10 +4262,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>One Orders register</v>
       </c>
       <c r="D168" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E168" t="str">
         <v>Completed</v>
@@ -4274,7 +4274,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G168" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="169">
@@ -4285,10 +4285,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D169" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E169" t="str">
         <v>Completed</v>
@@ -4297,7 +4297,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G169" t="str">
-        <v>CR-349</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="170">
@@ -4308,19 +4308,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>Load Copy print</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D170" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E170" t="str">
         <v>Completed</v>
       </c>
       <c r="F170" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G170" t="str">
-        <v>CR-351</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="171">
@@ -4331,19 +4331,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D171" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E171" t="str">
         <v>Completed</v>
       </c>
       <c r="F171" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G171" t="str">
-        <v>CR-433</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="172">
@@ -4354,19 +4354,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D172" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E172" t="str">
         <v>Completed</v>
       </c>
       <c r="F172" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G172" t="str">
-        <v>CR-311</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="173">
@@ -4377,19 +4377,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>Small UX items</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D173" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E173" t="str">
         <v>Completed</v>
       </c>
       <c r="F173" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G173" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="174">
@@ -4400,19 +4400,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>Small UX items</v>
       </c>
       <c r="D174" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E174" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F174" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G174" t="str">
-        <v>CR-365</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="175">
@@ -4423,10 +4423,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C175" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D175" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E175" t="str">
         <v>In progress</v>
@@ -4435,7 +4435,7 @@
         <v/>
       </c>
       <c r="G175" t="str">
-        <v>CR-366</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="176">
@@ -4446,10 +4446,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C176" t="str">
-        <v>One Status column</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D176" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E176" t="str">
         <v>In progress</v>
@@ -4458,7 +4458,7 @@
         <v/>
       </c>
       <c r="G176" t="str">
-        <v>CR-367</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="177">
@@ -4469,10 +4469,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C177" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>One Status column</v>
       </c>
       <c r="D177" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E177" t="str">
         <v>In progress</v>
@@ -4481,7 +4481,7 @@
         <v/>
       </c>
       <c r="G177" t="str">
-        <v>CR-368</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="178">
@@ -4492,10 +4492,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C178" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D178" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E178" t="str">
         <v>In progress</v>
@@ -4504,7 +4504,7 @@
         <v/>
       </c>
       <c r="G178" t="str">
-        <v>CR-399</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="179">
@@ -4515,10 +4515,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C179" t="str">
-        <v>One four-state order status</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D179" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E179" t="str">
         <v>In progress</v>
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="G179" t="str">
-        <v>CR-400</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="180">
@@ -4538,10 +4538,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C180" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D180" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E180" t="str">
         <v>In progress</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="G180" t="str">
-        <v>CR-401</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="181">
@@ -4561,10 +4561,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C181" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D181" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E181" t="str">
         <v>In progress</v>
@@ -4573,7 +4573,7 @@
         <v/>
       </c>
       <c r="G181" t="str">
-        <v>CR-402</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="182">
@@ -4584,10 +4584,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C182" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D182" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E182" t="str">
         <v>In progress</v>
@@ -4596,7 +4596,7 @@
         <v/>
       </c>
       <c r="G182" t="str">
-        <v>CR-403</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="183">
@@ -4607,10 +4607,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C183" t="str">
-        <v>Load part of a panel</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D183" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E183" t="str">
         <v>In progress</v>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="G183" t="str">
-        <v>CR-405</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="184">
@@ -4630,10 +4630,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>MDF row on every panel</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D184" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E184" t="str">
         <v>In progress</v>
@@ -4642,7 +4642,7 @@
         <v/>
       </c>
       <c r="G184" t="str">
-        <v>CR-406</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="185">
@@ -4653,10 +4653,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Load whole panel in one click</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D185" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E185" t="str">
         <v>In progress</v>
@@ -4665,7 +4665,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>CR-407</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="186">
@@ -4673,22 +4673,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>Settings search everywhere</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D186" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E186" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F186" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G186" t="str">
-        <v>CR-408</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="187">
@@ -4696,13 +4696,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C187" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D187" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E187" t="str">
         <v>Completed</v>
@@ -4711,7 +4711,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G187" t="str">
-        <v>CR-409</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="188">
@@ -4722,10 +4722,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C188" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D188" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
@@ -4734,7 +4734,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-438</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="189">
@@ -4742,22 +4742,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C189" t="str">
-        <v>Stock adjustment as a line form</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D189" t="str">
-        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
       </c>
       <c r="F189" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-446</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="190">
@@ -4768,19 +4768,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C190" t="str">
-        <v>Adjust Stock in the Zoho Books shape</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D190" t="str">
-        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
       </c>
       <c r="F190" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-457</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="191">
@@ -4791,10 +4791,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C191" t="str">
-        <v>Location Transfer from the Adjust Stock screen</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D191" t="str">
-        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
@@ -4803,7 +4803,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-458</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="192">
@@ -4814,10 +4814,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C192" t="str">
-        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D192" t="str">
-        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
@@ -4826,7 +4826,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-459</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="193">
@@ -4837,10 +4837,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C193" t="str">
-        <v>Cut Piece detail page inside Panel Craft</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D193" t="str">
-        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E193" t="str">
         <v>Completed</v>
@@ -4849,7 +4849,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-460/461</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="194">
@@ -4857,22 +4857,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C194" t="str">
-        <v>Pager with First / Last arrows</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D194" t="str">
-        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E194" t="str">
         <v>Completed</v>
       </c>
       <c r="F194" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G194" t="str">
-        <v>CR-467</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="195">
@@ -4883,10 +4883,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C195" t="str">
-        <v>Red close × on every window</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D195" t="str">
-        <v>The × that closes any window or drawer is red on every screen.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
@@ -4895,7 +4895,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-465</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="196">
@@ -4906,10 +4906,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C196" t="str">
-        <v>Advanced search date range fits the window</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D196" t="str">
-        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
@@ -4918,7 +4918,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-464</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="197">
@@ -4926,13 +4926,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Customers</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C197" t="str">
-        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D197" t="str">
-        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
@@ -4941,7 +4941,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-463/466</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="198">
@@ -4949,22 +4949,22 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Customers</v>
       </c>
       <c r="C198" t="str">
-        <v>Stock history in date order</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D198" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
       </c>
       <c r="F198" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-455</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="199">
@@ -4972,22 +4972,22 @@
         <v>198</v>
       </c>
       <c r="B199" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C199" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D199" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E199" t="str">
         <v>Completed</v>
       </c>
       <c r="F199" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-447</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="200">
@@ -4995,13 +4995,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C200" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D200" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
@@ -5010,7 +5010,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G200" t="str">
-        <v>CR-448</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="201">
@@ -5021,19 +5021,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C201" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D201" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E201" t="str">
         <v>Completed</v>
       </c>
       <c r="F201" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G201" t="str">
-        <v>CR-456</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="202">
@@ -5044,19 +5044,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C202" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D202" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E202" t="str">
         <v>Completed</v>
       </c>
       <c r="F202" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G202" t="str">
-        <v>CR-449</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="203">
@@ -5067,10 +5067,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C203" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D203" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E203" t="str">
         <v>Completed</v>
@@ -5079,7 +5079,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G203" t="str">
-        <v>CR-450</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="204">
@@ -5087,22 +5087,22 @@
         <v>203</v>
       </c>
       <c r="B204" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C204" t="str">
-        <v>Location at every stage</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D204" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E204" t="str">
         <v>Completed</v>
       </c>
       <c r="F204" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G204" t="str">
-        <v>CR-411…413</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="205">
@@ -5110,13 +5110,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C205" t="str">
-        <v>Panel location</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D205" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E205" t="str">
         <v>Completed</v>
@@ -5125,7 +5125,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G205" t="str">
-        <v>CR-410</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="206">
@@ -5136,10 +5136,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C206" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel location</v>
       </c>
       <c r="D206" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
@@ -5148,7 +5148,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G206" t="str">
-        <v>CR-419</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="207">
@@ -5159,10 +5159,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C207" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D207" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
@@ -5171,7 +5171,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G207" t="str">
-        <v>CR-415</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="208">
@@ -5179,13 +5179,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C208" t="str">
-        <v>No long helper notes</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D208" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E208" t="str">
         <v>Completed</v>
@@ -5194,7 +5194,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G208" t="str">
-        <v>CR-416</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="209">
@@ -5202,13 +5202,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="str">
-        <v>Production</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C209" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D209" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E209" t="str">
         <v>Completed</v>
@@ -5217,7 +5217,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G209" t="str">
-        <v>CR-417</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="210">
@@ -5225,13 +5225,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Production</v>
       </c>
       <c r="C210" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D210" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
@@ -5240,7 +5240,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G210" t="str">
-        <v>CR-418</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="211">
@@ -5251,10 +5251,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C211" t="str">
-        <v>Notifications read / unread</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D211" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
@@ -5263,7 +5263,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G211" t="str">
-        <v>CR-419…421</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="212">
@@ -5271,13 +5271,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C212" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D212" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
@@ -5286,7 +5286,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G212" t="str">
-        <v>CR-422</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="213">
@@ -5294,22 +5294,22 @@
         <v>212</v>
       </c>
       <c r="B213" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C213" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D213" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
       </c>
       <c r="F213" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-404</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="214">
@@ -5320,19 +5320,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C214" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D214" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E214" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F214" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G214" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="215">
@@ -5343,19 +5343,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C215" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D215" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E215" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F215" t="str">
         <v/>
       </c>
       <c r="G215" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="216">
@@ -5366,10 +5366,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C216" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D216" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E216" t="str">
         <v>Future</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="G216" t="str">
-        <v>Panel Craft list #2</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="217">
@@ -5389,10 +5389,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C217" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D217" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E217" t="str">
         <v>Future</v>
@@ -5401,7 +5401,7 @@
         <v/>
       </c>
       <c r="G217" t="str">
-        <v>Panel Craft list #4</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="218">
@@ -5412,10 +5412,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C218" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D218" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E218" t="str">
         <v>Future</v>
@@ -5424,7 +5424,7 @@
         <v/>
       </c>
       <c r="G218" t="str">
-        <v>Panel Craft list #5</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="219">
@@ -5435,10 +5435,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C219" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D219" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E219" t="str">
         <v>Future</v>
@@ -5447,7 +5447,7 @@
         <v/>
       </c>
       <c r="G219" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="220">
@@ -5458,10 +5458,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C220" t="str">
-        <v>Bill / expense</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D220" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E220" t="str">
         <v>Future</v>
@@ -5470,7 +5470,7 @@
         <v/>
       </c>
       <c r="G220" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="221">
@@ -5478,22 +5478,22 @@
         <v>220</v>
       </c>
       <c r="B221" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C221" t="str">
-        <v>Item code for the catalog</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D221" t="str">
-        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E221" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F221" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G221" t="str">
-        <v>CR-473</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="222">
@@ -5501,13 +5501,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C222" t="str">
-        <v>Panel Order PDF — one page per panel</v>
+        <v>Item code for the catalog</v>
       </c>
       <c r="D222" t="str">
-        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
+        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
       </c>
       <c r="E222" t="str">
         <v>Completed</v>
@@ -5516,7 +5516,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G222" t="str">
-        <v>CR-474</v>
+        <v>CR-473</v>
       </c>
     </row>
     <row r="223">
@@ -5524,13 +5524,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C223" t="str">
-        <v>Sales Order without a Location field</v>
+        <v>Panel Order PDF — one page per panel</v>
       </c>
       <c r="D223" t="str">
-        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
+        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
       </c>
       <c r="E223" t="str">
         <v>Completed</v>
@@ -5539,7 +5539,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G223" t="str">
-        <v>CR-468</v>
+        <v>CR-474</v>
       </c>
     </row>
     <row r="224">
@@ -5550,19 +5550,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C224" t="str">
-        <v>Box Brand mandatory</v>
+        <v>Sales Order without a Location field</v>
       </c>
       <c r="D224" t="str">
-        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
+        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
       </c>
       <c r="E224" t="str">
         <v>Completed</v>
       </c>
       <c r="F224" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G224" t="str">
-        <v>CR-483</v>
+        <v>CR-468</v>
       </c>
     </row>
     <row r="225">
@@ -5570,22 +5570,22 @@
         <v>224</v>
       </c>
       <c r="B225" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C225" t="str">
-        <v>Pallet form without Box Weight</v>
+        <v>Box Brand mandatory</v>
       </c>
       <c r="D225" t="str">
-        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
+        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
       </c>
       <c r="E225" t="str">
         <v>Completed</v>
       </c>
       <c r="F225" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G225" t="str">
-        <v>CR-471</v>
+        <v>CR-483</v>
       </c>
     </row>
     <row r="226">
@@ -5593,22 +5593,22 @@
         <v>225</v>
       </c>
       <c r="B226" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C226" t="str">
-        <v>Boffo / Bonza company separation</v>
+        <v>Pallet form without Box Weight</v>
       </c>
       <c r="D226" t="str">
-        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
+        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
       </c>
       <c r="E226" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F226" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
       <c r="G226" t="str">
-        <v>ON-HOLD #1</v>
+        <v>CR-471</v>
       </c>
     </row>
     <row r="227">
@@ -5616,22 +5616,22 @@
         <v>226</v>
       </c>
       <c r="B227" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C227" t="str">
-        <v>System reference and change-request register</v>
+        <v>Boffo / Bonza company separation</v>
       </c>
       <c r="D227" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
       </c>
       <c r="E227" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F227" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G227" t="str">
-        <v/>
+        <v>ON-HOLD #1</v>
       </c>
     </row>
     <row r="228">
@@ -5642,10 +5642,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C228" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D228" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E228" t="str">
         <v>Completed</v>
@@ -5665,10 +5665,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C229" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Change log, user flow, user manual</v>
       </c>
       <c r="D229" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
       </c>
       <c r="E229" t="str">
         <v>Completed</v>
@@ -5688,19 +5688,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C230" t="str">
-        <v>Data Flow reference</v>
+        <v>Seed and teardown scripts</v>
       </c>
       <c r="D230" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
       </c>
       <c r="E230" t="str">
         <v>Completed</v>
       </c>
       <c r="F230" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G230" t="str">
-        <v>CR-272</v>
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -5711,10 +5711,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C231" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Data Flow reference</v>
       </c>
       <c r="D231" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
       </c>
       <c r="E231" t="str">
         <v>Completed</v>
@@ -5723,7 +5723,7 @@
         <v>2026-10-03</v>
       </c>
       <c r="G231" t="str">
-        <v/>
+        <v>CR-272</v>
       </c>
     </row>
     <row r="232">
@@ -5734,19 +5734,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C232" t="str">
-        <v>Locations guide</v>
+        <v>Phase 2 inventory</v>
       </c>
       <c r="D232" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
       </c>
       <c r="E232" t="str">
         <v>Completed</v>
       </c>
       <c r="F232" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G232" t="str">
-        <v>CR-411…413</v>
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -5757,19 +5757,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C233" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Locations guide</v>
       </c>
       <c r="D233" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
       </c>
       <c r="E233" t="str">
         <v>Completed</v>
       </c>
       <c r="F233" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G233" t="str">
-        <v/>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="234">
@@ -5780,19 +5780,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C234" t="str">
-        <v>Demo / test environment</v>
+        <v>Deliverables list (this workbook)</v>
       </c>
       <c r="D234" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
       </c>
       <c r="E234" t="str">
         <v>Completed</v>
       </c>
       <c r="F234" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G234" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="235">
@@ -5803,25 +5803,48 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C235" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D235" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E235" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F235" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G235" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C236" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D235" t="str">
+      <c r="D236" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E235" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F235" t="str">
+      <c r="E236" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F236" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G235" t="str">
+      <c r="G236" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G235"/>
+  <autoFilter ref="A1:G236"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G235"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G236"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G237</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G236"/>
+  <dimension ref="A1:G237"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3802,19 +3802,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C148" t="str">
-        <v>Remarks on a panel</v>
+        <v>Full-tile samples book boxes</v>
       </c>
       <c r="D148" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>A sample order's full-tile line books boxes from a production batch (pending pieces at the item's pieces per box) with Book… on the Requirements row; the load is refused until booked, takes the booked boxes out of stock as a Sample / Display adjustment, and a deleted load puts them back. Boxes booked to a sample are not free for a Sales Order.</v>
       </c>
       <c r="E148" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F148" t="str">
-        <v/>
+        <v>2026-10-28</v>
       </c>
       <c r="G148" t="str">
-        <v>CR-425</v>
+        <v>CR-488</v>
       </c>
     </row>
     <row r="149">
@@ -3825,10 +3825,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C149" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D149" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E149" t="str">
         <v>In progress</v>
@@ -3837,7 +3837,7 @@
         <v/>
       </c>
       <c r="G149" t="str">
-        <v>CR-426</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="150">
@@ -3845,13 +3845,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C150" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D150" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E150" t="str">
         <v>In progress</v>
@@ -3860,7 +3860,7 @@
         <v/>
       </c>
       <c r="G150" t="str">
-        <v>CR-427</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="151">
@@ -3868,22 +3868,22 @@
         <v>150</v>
       </c>
       <c r="B151" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C151" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D151" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E151" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F151" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G151" t="str">
-        <v>CR-428</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="152">
@@ -3894,10 +3894,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C152" t="str">
-        <v>One Masters page</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D152" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
@@ -3906,7 +3906,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-436</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="153">
@@ -3917,10 +3917,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C153" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>One Masters page</v>
       </c>
       <c r="D153" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
@@ -3929,7 +3929,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-439</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="154">
@@ -3940,10 +3940,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C154" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D154" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
@@ -3952,7 +3952,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-440</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="155">
@@ -3960,13 +3960,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="str">
-        <v>Items</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C155" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D155" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E155" t="str">
         <v>Completed</v>
@@ -3975,7 +3975,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G155" t="str">
-        <v>CR-437</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="156">
@@ -3983,22 +3983,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Items</v>
       </c>
       <c r="C156" t="str">
-        <v>Names save as Title Case</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D156" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E156" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F156" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G156" t="str">
-        <v>CR-429</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="157">
@@ -4006,13 +4006,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C157" t="str">
-        <v>Brand off the Item form</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D157" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E157" t="str">
         <v>In progress</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="G157" t="str">
-        <v>CR-430</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="158">
@@ -4029,22 +4029,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C158" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D158" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E158" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F158" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G158" t="str">
-        <v>CR-306</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="159">
@@ -4055,19 +4055,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C159" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D159" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E159" t="str">
         <v>Completed</v>
       </c>
       <c r="F159" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G159" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="160">
@@ -4078,10 +4078,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C160" t="str">
-        <v>MDF master</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D160" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E160" t="str">
         <v>Completed</v>
@@ -4090,7 +4090,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G160" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="161">
@@ -4101,19 +4101,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C161" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>MDF master</v>
       </c>
       <c r="D161" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
       </c>
       <c r="F161" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="162">
@@ -4124,19 +4124,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C162" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D162" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E162" t="str">
         <v>Completed</v>
       </c>
       <c r="F162" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="163">
@@ -4147,19 +4147,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C163" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D163" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E163" t="str">
         <v>Completed</v>
       </c>
       <c r="F163" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G163" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="164">
@@ -4170,19 +4170,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C164" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D164" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E164" t="str">
         <v>Completed</v>
       </c>
       <c r="F164" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G164" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="165">
@@ -4193,19 +4193,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C165" t="str">
-        <v>Production checkpoints</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D165" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E165" t="str">
         <v>Completed</v>
       </c>
       <c r="F165" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G165" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="166">
@@ -4216,10 +4216,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C166" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D166" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E166" t="str">
         <v>Completed</v>
@@ -4228,7 +4228,7 @@
         <v>2026-10-09</v>
       </c>
       <c r="G166" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="167">
@@ -4239,19 +4239,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C167" t="str">
-        <v>Sample Orders</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D167" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E167" t="str">
         <v>Completed</v>
       </c>
       <c r="F167" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G167" t="str">
-        <v>CR-315…317</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="168">
@@ -4262,19 +4262,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>One Orders register</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D168" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E168" t="str">
         <v>Completed</v>
       </c>
       <c r="F168" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G168" t="str">
-        <v>CR-345</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="169">
@@ -4285,10 +4285,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>One Orders register</v>
       </c>
       <c r="D169" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E169" t="str">
         <v>Completed</v>
@@ -4297,7 +4297,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G169" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="170">
@@ -4308,10 +4308,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D170" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E170" t="str">
         <v>Completed</v>
@@ -4320,7 +4320,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G170" t="str">
-        <v>CR-349</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="171">
@@ -4331,19 +4331,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Load Copy print</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D171" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E171" t="str">
         <v>Completed</v>
       </c>
       <c r="F171" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G171" t="str">
-        <v>CR-351</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="172">
@@ -4354,19 +4354,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D172" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E172" t="str">
         <v>Completed</v>
       </c>
       <c r="F172" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G172" t="str">
-        <v>CR-433</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="173">
@@ -4377,19 +4377,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D173" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E173" t="str">
         <v>Completed</v>
       </c>
       <c r="F173" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G173" t="str">
-        <v>CR-311</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="174">
@@ -4400,19 +4400,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Small UX items</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D174" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E174" t="str">
         <v>Completed</v>
       </c>
       <c r="F174" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G174" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="175">
@@ -4423,19 +4423,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C175" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>Small UX items</v>
       </c>
       <c r="D175" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E175" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F175" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G175" t="str">
-        <v>CR-365</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="176">
@@ -4446,10 +4446,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C176" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D176" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E176" t="str">
         <v>In progress</v>
@@ -4458,7 +4458,7 @@
         <v/>
       </c>
       <c r="G176" t="str">
-        <v>CR-366</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="177">
@@ -4469,10 +4469,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C177" t="str">
-        <v>One Status column</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D177" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E177" t="str">
         <v>In progress</v>
@@ -4481,7 +4481,7 @@
         <v/>
       </c>
       <c r="G177" t="str">
-        <v>CR-367</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="178">
@@ -4492,10 +4492,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C178" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>One Status column</v>
       </c>
       <c r="D178" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E178" t="str">
         <v>In progress</v>
@@ -4504,7 +4504,7 @@
         <v/>
       </c>
       <c r="G178" t="str">
-        <v>CR-368</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="179">
@@ -4515,10 +4515,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C179" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D179" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E179" t="str">
         <v>In progress</v>
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="G179" t="str">
-        <v>CR-399</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="180">
@@ -4538,10 +4538,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C180" t="str">
-        <v>One four-state order status</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D180" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E180" t="str">
         <v>In progress</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="G180" t="str">
-        <v>CR-400</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="181">
@@ -4561,10 +4561,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C181" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D181" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E181" t="str">
         <v>In progress</v>
@@ -4573,7 +4573,7 @@
         <v/>
       </c>
       <c r="G181" t="str">
-        <v>CR-401</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="182">
@@ -4584,10 +4584,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C182" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D182" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E182" t="str">
         <v>In progress</v>
@@ -4596,7 +4596,7 @@
         <v/>
       </c>
       <c r="G182" t="str">
-        <v>CR-402</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="183">
@@ -4607,10 +4607,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C183" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D183" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E183" t="str">
         <v>In progress</v>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="G183" t="str">
-        <v>CR-403</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="184">
@@ -4630,10 +4630,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Load part of a panel</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D184" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E184" t="str">
         <v>In progress</v>
@@ -4642,7 +4642,7 @@
         <v/>
       </c>
       <c r="G184" t="str">
-        <v>CR-405</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="185">
@@ -4653,10 +4653,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>MDF row on every panel</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D185" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E185" t="str">
         <v>In progress</v>
@@ -4665,7 +4665,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>CR-406</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="186">
@@ -4676,10 +4676,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>Load whole panel in one click</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D186" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E186" t="str">
         <v>In progress</v>
@@ -4688,7 +4688,7 @@
         <v/>
       </c>
       <c r="G186" t="str">
-        <v>CR-407</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="187">
@@ -4696,22 +4696,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C187" t="str">
-        <v>Settings search everywhere</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D187" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E187" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F187" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G187" t="str">
-        <v>CR-408</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="188">
@@ -4719,13 +4719,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C188" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D188" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E188" t="str">
         <v>Completed</v>
@@ -4734,7 +4734,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G188" t="str">
-        <v>CR-409</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="189">
@@ -4745,10 +4745,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C189" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D189" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E189" t="str">
         <v>Completed</v>
@@ -4757,7 +4757,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G189" t="str">
-        <v>CR-438</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="190">
@@ -4765,22 +4765,22 @@
         <v>189</v>
       </c>
       <c r="B190" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C190" t="str">
-        <v>Stock adjustment as a line form</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D190" t="str">
-        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E190" t="str">
         <v>Completed</v>
       </c>
       <c r="F190" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G190" t="str">
-        <v>CR-446</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="191">
@@ -4791,19 +4791,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C191" t="str">
-        <v>Adjust Stock in the Zoho Books shape</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D191" t="str">
-        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E191" t="str">
         <v>Completed</v>
       </c>
       <c r="F191" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G191" t="str">
-        <v>CR-457</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="192">
@@ -4814,10 +4814,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C192" t="str">
-        <v>Location Transfer from the Adjust Stock screen</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D192" t="str">
-        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E192" t="str">
         <v>Completed</v>
@@ -4826,7 +4826,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G192" t="str">
-        <v>CR-458</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="193">
@@ -4837,10 +4837,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C193" t="str">
-        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D193" t="str">
-        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E193" t="str">
         <v>Completed</v>
@@ -4849,7 +4849,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G193" t="str">
-        <v>CR-459</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="194">
@@ -4860,10 +4860,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C194" t="str">
-        <v>Cut Piece detail page inside Panel Craft</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D194" t="str">
-        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E194" t="str">
         <v>Completed</v>
@@ -4872,7 +4872,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G194" t="str">
-        <v>CR-460/461</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="195">
@@ -4880,22 +4880,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C195" t="str">
-        <v>Pager with First / Last arrows</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D195" t="str">
-        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
       </c>
       <c r="F195" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-467</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="196">
@@ -4906,10 +4906,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C196" t="str">
-        <v>Red close × on every window</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D196" t="str">
-        <v>The × that closes any window or drawer is red on every screen.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
@@ -4918,7 +4918,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-465</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="197">
@@ -4929,10 +4929,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C197" t="str">
-        <v>Advanced search date range fits the window</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D197" t="str">
-        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
@@ -4941,7 +4941,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-464</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="198">
@@ -4949,13 +4949,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Customers</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C198" t="str">
-        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D198" t="str">
-        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
@@ -4964,7 +4964,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-463/466</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="199">
@@ -4972,22 +4972,22 @@
         <v>198</v>
       </c>
       <c r="B199" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Customers</v>
       </c>
       <c r="C199" t="str">
-        <v>Stock history in date order</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D199" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E199" t="str">
         <v>Completed</v>
       </c>
       <c r="F199" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-455</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="200">
@@ -4995,22 +4995,22 @@
         <v>199</v>
       </c>
       <c r="B200" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C200" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D200" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
       </c>
       <c r="F200" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G200" t="str">
-        <v>CR-447</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="201">
@@ -5018,13 +5018,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C201" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D201" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E201" t="str">
         <v>Completed</v>
@@ -5033,7 +5033,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G201" t="str">
-        <v>CR-448</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="202">
@@ -5044,19 +5044,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C202" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D202" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E202" t="str">
         <v>Completed</v>
       </c>
       <c r="F202" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G202" t="str">
-        <v>CR-456</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="203">
@@ -5067,19 +5067,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C203" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D203" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E203" t="str">
         <v>Completed</v>
       </c>
       <c r="F203" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G203" t="str">
-        <v>CR-449</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="204">
@@ -5090,10 +5090,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C204" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D204" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E204" t="str">
         <v>Completed</v>
@@ -5102,7 +5102,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G204" t="str">
-        <v>CR-450</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="205">
@@ -5110,22 +5110,22 @@
         <v>204</v>
       </c>
       <c r="B205" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C205" t="str">
-        <v>Location at every stage</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D205" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E205" t="str">
         <v>Completed</v>
       </c>
       <c r="F205" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G205" t="str">
-        <v>CR-411…413</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="206">
@@ -5133,13 +5133,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C206" t="str">
-        <v>Panel location</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D206" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
@@ -5148,7 +5148,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G206" t="str">
-        <v>CR-410</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="207">
@@ -5159,10 +5159,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C207" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel location</v>
       </c>
       <c r="D207" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
@@ -5171,7 +5171,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G207" t="str">
-        <v>CR-419</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="208">
@@ -5182,10 +5182,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C208" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D208" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E208" t="str">
         <v>Completed</v>
@@ -5194,7 +5194,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G208" t="str">
-        <v>CR-415</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="209">
@@ -5202,13 +5202,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C209" t="str">
-        <v>No long helper notes</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D209" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E209" t="str">
         <v>Completed</v>
@@ -5217,7 +5217,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G209" t="str">
-        <v>CR-416</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="210">
@@ -5225,13 +5225,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="str">
-        <v>Production</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C210" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D210" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
@@ -5240,7 +5240,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G210" t="str">
-        <v>CR-417</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="211">
@@ -5248,13 +5248,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Production</v>
       </c>
       <c r="C211" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D211" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
@@ -5263,7 +5263,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G211" t="str">
-        <v>CR-418</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="212">
@@ -5274,10 +5274,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C212" t="str">
-        <v>Notifications read / unread</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D212" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
@@ -5286,7 +5286,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G212" t="str">
-        <v>CR-419…421</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="213">
@@ -5294,13 +5294,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C213" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D213" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
@@ -5309,7 +5309,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-422</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="214">
@@ -5317,22 +5317,22 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C214" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D214" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E214" t="str">
         <v>Completed</v>
       </c>
       <c r="F214" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G214" t="str">
-        <v>CR-404</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="215">
@@ -5343,19 +5343,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C215" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D215" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E215" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F215" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G215" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="216">
@@ -5366,19 +5366,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C216" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D216" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E216" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F216" t="str">
         <v/>
       </c>
       <c r="G216" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="217">
@@ -5389,10 +5389,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C217" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D217" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E217" t="str">
         <v>Future</v>
@@ -5401,7 +5401,7 @@
         <v/>
       </c>
       <c r="G217" t="str">
-        <v>Panel Craft list #2</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="218">
@@ -5412,10 +5412,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C218" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D218" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E218" t="str">
         <v>Future</v>
@@ -5424,7 +5424,7 @@
         <v/>
       </c>
       <c r="G218" t="str">
-        <v>Panel Craft list #4</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="219">
@@ -5435,10 +5435,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C219" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D219" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E219" t="str">
         <v>Future</v>
@@ -5447,7 +5447,7 @@
         <v/>
       </c>
       <c r="G219" t="str">
-        <v>Panel Craft list #5</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="220">
@@ -5458,10 +5458,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C220" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D220" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E220" t="str">
         <v>Future</v>
@@ -5470,7 +5470,7 @@
         <v/>
       </c>
       <c r="G220" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="221">
@@ -5481,10 +5481,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C221" t="str">
-        <v>Bill / expense</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D221" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E221" t="str">
         <v>Future</v>
@@ -5493,7 +5493,7 @@
         <v/>
       </c>
       <c r="G221" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="222">
@@ -5501,22 +5501,22 @@
         <v>221</v>
       </c>
       <c r="B222" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C222" t="str">
-        <v>Item code for the catalog</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D222" t="str">
-        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E222" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F222" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G222" t="str">
-        <v>CR-473</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="223">
@@ -5524,13 +5524,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C223" t="str">
-        <v>Panel Order PDF — one page per panel</v>
+        <v>Item code for the catalog</v>
       </c>
       <c r="D223" t="str">
-        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
+        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
       </c>
       <c r="E223" t="str">
         <v>Completed</v>
@@ -5539,7 +5539,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G223" t="str">
-        <v>CR-474</v>
+        <v>CR-473</v>
       </c>
     </row>
     <row r="224">
@@ -5547,13 +5547,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C224" t="str">
-        <v>Sales Order without a Location field</v>
+        <v>Panel Order PDF — one page per panel</v>
       </c>
       <c r="D224" t="str">
-        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
+        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
       </c>
       <c r="E224" t="str">
         <v>Completed</v>
@@ -5562,7 +5562,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G224" t="str">
-        <v>CR-468</v>
+        <v>CR-474</v>
       </c>
     </row>
     <row r="225">
@@ -5573,19 +5573,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C225" t="str">
-        <v>Box Brand mandatory</v>
+        <v>Sales Order without a Location field</v>
       </c>
       <c r="D225" t="str">
-        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
+        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
       </c>
       <c r="E225" t="str">
         <v>Completed</v>
       </c>
       <c r="F225" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G225" t="str">
-        <v>CR-483</v>
+        <v>CR-468</v>
       </c>
     </row>
     <row r="226">
@@ -5593,22 +5593,22 @@
         <v>225</v>
       </c>
       <c r="B226" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C226" t="str">
-        <v>Pallet form without Box Weight</v>
+        <v>Box Brand mandatory</v>
       </c>
       <c r="D226" t="str">
-        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
+        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
       </c>
       <c r="E226" t="str">
         <v>Completed</v>
       </c>
       <c r="F226" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G226" t="str">
-        <v>CR-471</v>
+        <v>CR-483</v>
       </c>
     </row>
     <row r="227">
@@ -5616,22 +5616,22 @@
         <v>226</v>
       </c>
       <c r="B227" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C227" t="str">
-        <v>Boffo / Bonza company separation</v>
+        <v>Pallet form without Box Weight</v>
       </c>
       <c r="D227" t="str">
-        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
+        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
       </c>
       <c r="E227" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F227" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
       <c r="G227" t="str">
-        <v>ON-HOLD #1</v>
+        <v>CR-471</v>
       </c>
     </row>
     <row r="228">
@@ -5639,22 +5639,22 @@
         <v>227</v>
       </c>
       <c r="B228" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C228" t="str">
-        <v>System reference and change-request register</v>
+        <v>Boffo / Bonza company separation</v>
       </c>
       <c r="D228" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
       </c>
       <c r="E228" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F228" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G228" t="str">
-        <v/>
+        <v>ON-HOLD #1</v>
       </c>
     </row>
     <row r="229">
@@ -5665,10 +5665,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C229" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D229" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E229" t="str">
         <v>Completed</v>
@@ -5688,10 +5688,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C230" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Change log, user flow, user manual</v>
       </c>
       <c r="D230" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
       </c>
       <c r="E230" t="str">
         <v>Completed</v>
@@ -5711,19 +5711,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C231" t="str">
-        <v>Data Flow reference</v>
+        <v>Seed and teardown scripts</v>
       </c>
       <c r="D231" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
       </c>
       <c r="E231" t="str">
         <v>Completed</v>
       </c>
       <c r="F231" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G231" t="str">
-        <v>CR-272</v>
+        <v/>
       </c>
     </row>
     <row r="232">
@@ -5734,10 +5734,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C232" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Data Flow reference</v>
       </c>
       <c r="D232" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
       </c>
       <c r="E232" t="str">
         <v>Completed</v>
@@ -5746,7 +5746,7 @@
         <v>2026-10-03</v>
       </c>
       <c r="G232" t="str">
-        <v/>
+        <v>CR-272</v>
       </c>
     </row>
     <row r="233">
@@ -5757,19 +5757,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C233" t="str">
-        <v>Locations guide</v>
+        <v>Phase 2 inventory</v>
       </c>
       <c r="D233" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
       </c>
       <c r="E233" t="str">
         <v>Completed</v>
       </c>
       <c r="F233" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G233" t="str">
-        <v>CR-411…413</v>
+        <v/>
       </c>
     </row>
     <row r="234">
@@ -5780,19 +5780,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C234" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Locations guide</v>
       </c>
       <c r="D234" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
       </c>
       <c r="E234" t="str">
         <v>Completed</v>
       </c>
       <c r="F234" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G234" t="str">
-        <v/>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="235">
@@ -5803,19 +5803,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C235" t="str">
-        <v>Demo / test environment</v>
+        <v>Deliverables list (this workbook)</v>
       </c>
       <c r="D235" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
       </c>
       <c r="E235" t="str">
         <v>Completed</v>
       </c>
       <c r="F235" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G235" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -5826,25 +5826,48 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C236" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D236" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E236" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F236" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G236" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C237" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D236" t="str">
+      <c r="D237" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E236" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F236" t="str">
+      <c r="E237" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F237" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G236" t="str">
+      <c r="G237" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G236"/>
+  <autoFilter ref="A1:G237"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G237"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -3805,7 +3805,7 @@
         <v>Full-tile samples book boxes</v>
       </c>
       <c r="D148" t="str">
-        <v>A sample order's full-tile line books boxes from a production batch (pending pieces at the item's pieces per box) with Book… on the Requirements row; the load is refused until booked, takes the booked boxes out of stock as a Sample / Display adjustment, and a deleted load puts them back. Boxes booked to a sample are not free for a Sales Order.</v>
+        <v>A sample order's full-tile line books boxes from a production batch (pending pieces at the item's pieces per box) from the same Allocate Stock window as its cut pieces; the load is refused until booked, takes the booked boxes out of stock as a Sample / Display adjustment, and a deleted load puts them back. Boxes booked to a sample are not free for a Sales Order.</v>
       </c>
       <c r="E148" t="str">
         <v>Completed</v>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -3802,10 +3802,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C148" t="str">
-        <v>Full-tile samples book boxes</v>
+        <v>Full-tile samples book the sample stock</v>
       </c>
       <c r="D148" t="str">
-        <v>A sample order's full-tile line books boxes from a production batch (pending pieces at the item's pieces per box) from the same Allocate Stock window as its cut pieces; the load is refused until booked, takes the booked boxes out of stock as a Sample / Display adjustment, and a deleted load puts them back. Boxes booked to a sample are not free for a Sales Order.</v>
+        <v>A sample order's full-tile line books the item's full-size piece on Cut Stock — the separately managed sample stock — in pieces, from the same Allocate Stock window as its cut pieces (no batch picker; export box stock is never touched); the load is refused until booked and takes the pieces out of Cut Stock. The sample order form lists panel items only.</v>
       </c>
       <c r="E148" t="str">
         <v>Completed</v>
@@ -3814,7 +3814,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G148" t="str">
-        <v>CR-488</v>
+        <v>CR-489 (replaces CR-488)</v>
       </c>
     </row>
     <row r="149">

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G244</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:G244"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -2583,19 +2583,19 @@
         <v>Palletization</v>
       </c>
       <c r="C95" t="str">
-        <v>Plan detail page</v>
+        <v>One toolbar with the filters on top; Sheet Mode</v>
       </c>
       <c r="D95" t="str">
-        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
+        <v>Search and the customer / country / item / size filters sit in the page toolbar; Today's Report, Group, columns and New Palletization Plan ▾ on the right. The ▾ menu opens Sheet Mode — record boxes or a batch top-up across many rows, then Save.</v>
       </c>
       <c r="E95" t="str">
         <v>Completed</v>
       </c>
       <c r="F95" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G95" t="str">
-        <v/>
+        <v>CR-491</v>
       </c>
     </row>
     <row r="96">
@@ -2606,19 +2606,19 @@
         <v>Palletization</v>
       </c>
       <c r="C96" t="str">
-        <v>Prints on demand</v>
+        <v>Partial completion keeps the rest In Palletization</v>
       </c>
       <c r="D96" t="str">
-        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
+        <v>Complete fewer pallets than possible: those pallets move to Palletization Completed, the loose boxes stay on In Palletization for a mixed-batch pallet. Nothing goes back to the queue.</v>
       </c>
       <c r="E96" t="str">
         <v>Completed</v>
       </c>
       <c r="F96" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G96" t="str">
-        <v/>
+        <v>CR-492</v>
       </c>
     </row>
     <row r="97">
@@ -2629,19 +2629,19 @@
         <v>Palletization</v>
       </c>
       <c r="C97" t="str">
-        <v>Board rules</v>
+        <v>Top Up from either page; mixed pallet completes as one</v>
       </c>
       <c r="D97" t="str">
-        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
+        <v>A pallet is topped up from another batch of the same item on Ready for Palletization or In Palletization (the dialog shows which); a batch already on a mixed pallet cannot donate again. A mixed pallet completes as one pallet.</v>
       </c>
       <c r="E97" t="str">
         <v>Completed</v>
       </c>
       <c r="F97" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G97" t="str">
-        <v>CR-129, 248</v>
+        <v>CR-493/494/497</v>
       </c>
     </row>
     <row r="98">
@@ -2652,19 +2652,19 @@
         <v>Palletization</v>
       </c>
       <c r="C98" t="str">
-        <v>Three ways onto the queue</v>
+        <v>Mix Batch icon</v>
       </c>
       <c r="D98" t="str">
-        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
+        <v>One amber icon with a hover hint marks a shared (mixed-batch) pallet on every screen — no text chips.</v>
       </c>
       <c r="E98" t="str">
         <v>Completed</v>
       </c>
       <c r="F98" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G98" t="str">
-        <v>CR-223/224</v>
+        <v>CR-498</v>
       </c>
     </row>
     <row r="99">
@@ -2675,19 +2675,19 @@
         <v>Palletization</v>
       </c>
       <c r="C99" t="str">
-        <v>'+' menu: Start / Top Up Batch / Complete</v>
+        <v>Columns that read as one story</v>
       </c>
       <c r="D99" t="str">
-        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
+        <v>On every palletization page the pallet type comes first, then the counts left to right: Ready for Palletization shows Boxes · Pallets · Loose; In Palletization shows Pending · Pallets · Loose · Prepared (pallets with boxes); hover a header for what each number means. No duplicate Boxes columns.</v>
       </c>
       <c r="E99" t="str">
         <v>Completed</v>
       </c>
       <c r="F99" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G99" t="str">
-        <v>CR-148…150, 281</v>
+        <v>CR-495/499</v>
       </c>
     </row>
     <row r="100">
@@ -2698,10 +2698,10 @@
         <v>Palletization</v>
       </c>
       <c r="C100" t="str">
-        <v>Sheet edit mode and multi-select</v>
+        <v>Plan detail page</v>
       </c>
       <c r="D100" t="str">
-        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
+        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
       </c>
       <c r="E100" t="str">
         <v>Completed</v>
@@ -2710,7 +2710,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G100" t="str">
-        <v>CR-153</v>
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -2721,19 +2721,19 @@
         <v>Palletization</v>
       </c>
       <c r="C101" t="str">
-        <v>Date column, PAL code hidden</v>
+        <v>Prints on demand</v>
       </c>
       <c r="D101" t="str">
-        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
+        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
       </c>
       <c r="E101" t="str">
         <v>Completed</v>
       </c>
       <c r="F101" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G101" t="str">
-        <v>CR-266</v>
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -2744,19 +2744,19 @@
         <v>Palletization</v>
       </c>
       <c r="C102" t="str">
-        <v>Complete dialog shows progress</v>
+        <v>Board rules</v>
       </c>
       <c r="D102" t="str">
-        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
+        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
       </c>
       <c r="E102" t="str">
         <v>Completed</v>
       </c>
       <c r="F102" t="str">
-        <v>2026-10-06</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G102" t="str">
-        <v>CR-280</v>
+        <v>CR-129, 248</v>
       </c>
     </row>
     <row r="103">
@@ -2767,19 +2767,19 @@
         <v>Palletization</v>
       </c>
       <c r="C103" t="str">
-        <v>Plan edit keeps Box Brand and batches</v>
+        <v>Three ways onto the queue</v>
       </c>
       <c r="D103" t="str">
-        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
+        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
       </c>
       <c r="E103" t="str">
         <v>Completed</v>
       </c>
       <c r="F103" t="str">
-        <v>2026-10-13</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G103" t="str">
-        <v>CR-340</v>
+        <v>CR-223/224</v>
       </c>
     </row>
     <row r="104">
@@ -2790,19 +2790,19 @@
         <v>Palletization</v>
       </c>
       <c r="C104" t="str">
-        <v>Three pages, one stage each</v>
+        <v>'+' menu: Start / Top Up Batch / Complete</v>
       </c>
       <c r="D104" t="str">
-        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
+        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
       </c>
       <c r="E104" t="str">
         <v>Completed</v>
       </c>
       <c r="F104" t="str">
-        <v>2026-10-21</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G104" t="str">
-        <v>CR-360, 364</v>
+        <v>CR-148…150, 281</v>
       </c>
     </row>
     <row r="105">
@@ -2813,19 +2813,19 @@
         <v>Palletization</v>
       </c>
       <c r="C105" t="str">
-        <v>Release palletized boxes</v>
+        <v>Sheet edit mode and multi-select</v>
       </c>
       <c r="D105" t="str">
-        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
+        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
       </c>
       <c r="E105" t="str">
         <v>Completed</v>
       </c>
       <c r="F105" t="str">
-        <v>2026-10-21</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G105" t="str">
-        <v>CR-361</v>
+        <v>CR-153</v>
       </c>
     </row>
     <row r="106">
@@ -2836,19 +2836,19 @@
         <v>Palletization</v>
       </c>
       <c r="C106" t="str">
-        <v>Discard the current palletization task</v>
+        <v>Date column, PAL code hidden</v>
       </c>
       <c r="D106" t="str">
-        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
+        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
       </c>
       <c r="E106" t="str">
         <v>Completed</v>
       </c>
       <c r="F106" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G106" t="str">
-        <v>CR-369</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="107">
@@ -2859,19 +2859,19 @@
         <v>Palletization</v>
       </c>
       <c r="C107" t="str">
-        <v>Delete a plan returns its boxes</v>
+        <v>Complete dialog shows progress</v>
       </c>
       <c r="D107" t="str">
-        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
+        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
       </c>
       <c r="E107" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F107" t="str">
-        <v/>
+        <v>2026-10-06</v>
       </c>
       <c r="G107" t="str">
-        <v>CR-370</v>
+        <v>CR-280</v>
       </c>
     </row>
     <row r="108">
@@ -2882,19 +2882,19 @@
         <v>Palletization</v>
       </c>
       <c r="C108" t="str">
-        <v>Partial Start Palletization</v>
+        <v>Plan edit keeps Box Brand and batches</v>
       </c>
       <c r="D108" t="str">
-        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
+        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
       </c>
       <c r="E108" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F108" t="str">
-        <v/>
+        <v>2026-10-13</v>
       </c>
       <c r="G108" t="str">
-        <v>Panel Craft list #9</v>
+        <v>CR-340</v>
       </c>
     </row>
     <row r="109">
@@ -2905,19 +2905,19 @@
         <v>Palletization</v>
       </c>
       <c r="C109" t="str">
-        <v>Ready pallets — type and pallet count</v>
+        <v>Three pages, one stage each</v>
       </c>
       <c r="D109" t="str">
-        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
+        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
       </c>
       <c r="E109" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F109" t="str">
-        <v/>
+        <v>2026-10-21</v>
       </c>
       <c r="G109" t="str">
-        <v>Panel Craft list #7</v>
+        <v>CR-360, 364</v>
       </c>
     </row>
     <row r="110">
@@ -2928,19 +2928,19 @@
         <v>Palletization</v>
       </c>
       <c r="C110" t="str">
-        <v>Remove 'Ordered / Completed' where not needed</v>
+        <v>Release palletized boxes</v>
       </c>
       <c r="D110" t="str">
-        <v>Screen to be confirmed.</v>
+        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
       </c>
       <c r="E110" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F110" t="str">
-        <v/>
+        <v>2026-10-21</v>
       </c>
       <c r="G110" t="str">
-        <v>Panel Craft list #8</v>
+        <v>CR-361</v>
       </c>
     </row>
     <row r="111">
@@ -2948,22 +2948,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C111" t="str">
-        <v>A loading = one container</v>
+        <v>Release returns boxes to Ready for Palletization</v>
       </c>
       <c r="D111" t="str">
-        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
+        <v>Release on Palletization Completed puts the boxes back on the queue row of the same item and batch (counts recompute); the order keeps its allocation. Discard, Delete and Cancel Order still return boxes to free stock.</v>
       </c>
       <c r="E111" t="str">
         <v>Completed</v>
       </c>
       <c r="F111" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G111" t="str">
-        <v>CR-120…124</v>
+        <v>CR-500</v>
       </c>
     </row>
     <row r="112">
@@ -2971,22 +2971,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C112" t="str">
-        <v>Loading and Dispatch page</v>
+        <v>Cancel Palletization</v>
       </c>
       <c r="D112" t="str">
-        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
+        <v>On In Palletization: boxes + reason send the pallet back to Ready for Palletization on the same item and batch row, still booked to the order. Discard (free stock) stays on Ready for Palletization only.</v>
       </c>
       <c r="E112" t="str">
         <v>Completed</v>
       </c>
       <c r="F112" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G112" t="str">
-        <v>CR-140, 141</v>
+        <v>CR-501</v>
       </c>
     </row>
     <row r="113">
@@ -2994,22 +2994,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C113" t="str">
-        <v>Loading detail</v>
+        <v>Discard the current palletization task</v>
       </c>
       <c r="D113" t="str">
-        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
+        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
       </c>
       <c r="E113" t="str">
         <v>Completed</v>
       </c>
       <c r="F113" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>CR-369</v>
       </c>
     </row>
     <row r="114">
@@ -3017,22 +3017,22 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C114" t="str">
-        <v>Vehicle and shipment details</v>
+        <v>Delete a plan returns its boxes</v>
       </c>
       <c r="D114" t="str">
-        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
+        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
       </c>
       <c r="E114" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F114" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>CR-370</v>
       </c>
     </row>
     <row r="115">
@@ -3040,22 +3040,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C115" t="str">
-        <v>Dispatch with gates and warnings</v>
+        <v>Partial Start Palletization</v>
       </c>
       <c r="D115" t="str">
-        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
+        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
       </c>
       <c r="E115" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F115" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>Panel Craft list #9</v>
       </c>
     </row>
     <row r="116">
@@ -3063,22 +3063,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C116" t="str">
-        <v>Invoice and dispatch prints</v>
+        <v>Ready pallets — type and pallet count</v>
       </c>
       <c r="D116" t="str">
-        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
+        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
       </c>
       <c r="E116" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F116" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>Panel Craft list #7</v>
       </c>
     </row>
     <row r="117">
@@ -3086,22 +3086,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C117" t="str">
-        <v>Four ways to fill a container</v>
+        <v>Remove 'Ordered / Completed' where not needed</v>
       </c>
       <c r="D117" t="str">
-        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
+        <v>Screen to be confirmed.</v>
       </c>
       <c r="E117" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F117" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G117" t="str">
-        <v>CR-126…128, 201/202</v>
+        <v>Panel Craft list #8</v>
       </c>
     </row>
     <row r="118">
@@ -3112,10 +3112,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C118" t="str">
-        <v>Editing a loading</v>
+        <v>A loading = one container</v>
       </c>
       <c r="D118" t="str">
-        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
+        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
       </c>
       <c r="E118" t="str">
         <v>Completed</v>
@@ -3124,7 +3124,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G118" t="str">
-        <v/>
+        <v>CR-120…124</v>
       </c>
     </row>
     <row r="119">
@@ -3135,19 +3135,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C119" t="str">
-        <v>Date column, LOAD code hidden</v>
+        <v>Loading and Dispatch page</v>
       </c>
       <c r="D119" t="str">
-        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
+        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
       </c>
       <c r="E119" t="str">
         <v>Completed</v>
       </c>
       <c r="F119" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G119" t="str">
-        <v>CR-266</v>
+        <v>CR-140, 141</v>
       </c>
     </row>
     <row r="120">
@@ -3158,19 +3158,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C120" t="str">
-        <v>Several containers in one New Loading</v>
+        <v>Loading detail</v>
       </c>
       <c r="D120" t="str">
-        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
+        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
       </c>
       <c r="E120" t="str">
         <v>Completed</v>
       </c>
       <c r="F120" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G120" t="str">
-        <v>CR-301</v>
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -3181,19 +3181,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C121" t="str">
-        <v>Loading Workspace — a tab per container</v>
+        <v>Vehicle and shipment details</v>
       </c>
       <c r="D121" t="str">
-        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
+        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
       </c>
       <c r="E121" t="str">
         <v>Completed</v>
       </c>
       <c r="F121" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G121" t="str">
-        <v>CR-326, 334, 335</v>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -3204,19 +3204,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C122" t="str">
-        <v>Every customer listed, with search</v>
+        <v>Dispatch with gates and warnings</v>
       </c>
       <c r="D122" t="str">
-        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
+        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
       </c>
       <c r="E122" t="str">
         <v>Completed</v>
       </c>
       <c r="F122" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G122" t="str">
-        <v>CR-327</v>
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -3227,19 +3227,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C123" t="str">
-        <v>'What to do first' reasons</v>
+        <v>Invoice and dispatch prints</v>
       </c>
       <c r="D123" t="str">
-        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
+        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
       </c>
       <c r="E123" t="str">
         <v>Completed</v>
       </c>
       <c r="F123" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G123" t="str">
-        <v>CR-328</v>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -3250,19 +3250,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C124" t="str">
-        <v>Pick the planned container at loading</v>
+        <v>Four ways to fill a container</v>
       </c>
       <c r="D124" t="str">
-        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
+        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
       </c>
       <c r="E124" t="str">
         <v>Completed</v>
       </c>
       <c r="F124" t="str">
-        <v>2026-10-13</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G124" t="str">
-        <v>CR-338</v>
+        <v>CR-126…128, 201/202</v>
       </c>
     </row>
     <row r="125">
@@ -3273,19 +3273,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C125" t="str">
-        <v>Two steps per container; C1 / C2 naming</v>
+        <v>Editing a loading</v>
       </c>
       <c r="D125" t="str">
-        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
+        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
       </c>
       <c r="E125" t="str">
         <v>Completed</v>
       </c>
       <c r="F125" t="str">
-        <v>2026-10-19</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G125" t="str">
-        <v>CR-350, 354</v>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3296,19 +3296,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C126" t="str">
-        <v>Mix Batch at loading</v>
+        <v>Date column, LOAD code hidden</v>
       </c>
       <c r="D126" t="str">
-        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
+        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
       </c>
       <c r="E126" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F126" t="str">
-        <v/>
+        <v>2026-10-03</v>
       </c>
       <c r="G126" t="str">
-        <v>CR-260 follow-up</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="127">
@@ -3319,19 +3319,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C127" t="str">
-        <v>Five stage pages: Palletization Completed, Loading, Dispatch</v>
+        <v>Several containers in one New Loading</v>
       </c>
       <c r="D127" t="str">
-        <v>Palletization Completed stays its own page; Loading lists the items being loaded; the new Dispatch page lists the containers ready to dispatch and the dispatched ones, with their prints.</v>
+        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
       </c>
       <c r="E127" t="str">
         <v>Completed</v>
       </c>
       <c r="F127" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G127" t="str">
-        <v>CR-480</v>
+        <v>CR-301</v>
       </c>
     </row>
     <row r="128">
@@ -3339,22 +3339,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C128" t="str">
-        <v>One stock rule everywhere</v>
+        <v>Loading Workspace — a tab per container</v>
       </c>
       <c r="D128" t="str">
-        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
+        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
       </c>
       <c r="E128" t="str">
         <v>Completed</v>
       </c>
       <c r="F128" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G128" t="str">
-        <v/>
+        <v>CR-326, 334, 335</v>
       </c>
     </row>
     <row r="129">
@@ -3362,22 +3362,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C129" t="str">
-        <v>Counters recomputed, never incremented</v>
+        <v>Every customer listed, with search</v>
       </c>
       <c r="D129" t="str">
-        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
+        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
       </c>
       <c r="E129" t="str">
         <v>Completed</v>
       </c>
       <c r="F129" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G129" t="str">
-        <v/>
+        <v>CR-327</v>
       </c>
     </row>
     <row r="130">
@@ -3385,22 +3385,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C130" t="str">
-        <v>Allocation and batch ledger</v>
+        <v>'What to do first' reasons</v>
       </c>
       <c r="D130" t="str">
-        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
+        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
       </c>
       <c r="E130" t="str">
         <v>Completed</v>
       </c>
       <c r="F130" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G130" t="str">
-        <v/>
+        <v>CR-328</v>
       </c>
     </row>
     <row r="131">
@@ -3408,22 +3408,22 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C131" t="str">
-        <v>Admin repair operations</v>
+        <v>Pick the planned container at loading</v>
       </c>
       <c r="D131" t="str">
-        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
+        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
       </c>
       <c r="E131" t="str">
         <v>Completed</v>
       </c>
       <c r="F131" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G131" t="str">
-        <v/>
+        <v>CR-338</v>
       </c>
     </row>
     <row r="132">
@@ -3431,22 +3431,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C132" t="str">
-        <v>Inventory adjustments</v>
+        <v>Two steps per container; C1 / C2 naming</v>
       </c>
       <c r="D132" t="str">
-        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
+        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
       </c>
       <c r="E132" t="str">
         <v>Completed</v>
       </c>
       <c r="F132" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G132" t="str">
-        <v>CR-308</v>
+        <v>CR-350, 354</v>
       </c>
     </row>
     <row r="133">
@@ -3454,22 +3454,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C133" t="str">
-        <v>Stock per warehouse</v>
+        <v>Mix Batch at loading</v>
       </c>
       <c r="D133" t="str">
-        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
+        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
       </c>
       <c r="E133" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F133" t="str">
-        <v>2026-10-12</v>
+        <v/>
       </c>
       <c r="G133" t="str">
-        <v>CR-329</v>
+        <v>CR-260 follow-up</v>
       </c>
     </row>
     <row r="134">
@@ -3477,22 +3477,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C134" t="str">
-        <v>Transfer Orders</v>
+        <v>Five stage pages: Palletization Completed, Loading, Dispatch</v>
       </c>
       <c r="D134" t="str">
-        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
+        <v>Palletization Completed stays its own page; Loading lists the items being loaded; the new Dispatch page lists the containers ready to dispatch and the dispatched ones, with their prints.</v>
       </c>
       <c r="E134" t="str">
         <v>Completed</v>
       </c>
       <c r="F134" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G134" t="str">
-        <v>CR-330</v>
+        <v>CR-480</v>
       </c>
     </row>
     <row r="135">
@@ -3503,19 +3503,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C135" t="str">
-        <v>Locations on items</v>
+        <v>One stock rule everywhere</v>
       </c>
       <c r="D135" t="str">
-        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
+        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
       </c>
       <c r="E135" t="str">
         <v>Completed</v>
       </c>
       <c r="F135" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G135" t="str">
-        <v>CR-332</v>
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -3526,19 +3526,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C136" t="str">
-        <v>Stock keyed by the item</v>
+        <v>Counters recomputed, never incremented</v>
       </c>
       <c r="D136" t="str">
-        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
+        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
       </c>
       <c r="E136" t="str">
         <v>Completed</v>
       </c>
       <c r="F136" t="str">
-        <v>2026-10-13</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G136" t="str">
-        <v>CR-341</v>
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -3546,13 +3546,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C137" t="str">
-        <v>Sales reports</v>
+        <v>Allocation and batch ledger</v>
       </c>
       <c r="D137" t="str">
-        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
+        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
       </c>
       <c r="E137" t="str">
         <v>Completed</v>
@@ -3569,13 +3569,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C138" t="str">
-        <v>Inventory reports</v>
+        <v>Admin repair operations</v>
       </c>
       <c r="D138" t="str">
-        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
+        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
       </c>
       <c r="E138" t="str">
         <v>Completed</v>
@@ -3584,7 +3584,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G138" t="str">
-        <v>CR-104</v>
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -3592,22 +3592,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C139" t="str">
-        <v>Dispatch reports</v>
+        <v>Inventory adjustments</v>
       </c>
       <c r="D139" t="str">
-        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
+        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
       </c>
       <c r="E139" t="str">
         <v>Completed</v>
       </c>
       <c r="F139" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G139" t="str">
-        <v>CR-104</v>
+        <v>CR-308</v>
       </c>
     </row>
     <row r="140">
@@ -3615,22 +3615,22 @@
         <v>139</v>
       </c>
       <c r="B140" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C140" t="str">
-        <v>Audit log and activity</v>
+        <v>Stock per warehouse</v>
       </c>
       <c r="D140" t="str">
-        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
+        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
       </c>
       <c r="E140" t="str">
         <v>Completed</v>
       </c>
       <c r="F140" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G140" t="str">
-        <v/>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="141">
@@ -3638,22 +3638,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C141" t="str">
-        <v>Dashboard</v>
+        <v>Transfer Orders</v>
       </c>
       <c r="D141" t="str">
-        <v>Headline numbers.</v>
+        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
       </c>
       <c r="E141" t="str">
         <v>Completed</v>
       </c>
       <c r="F141" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G141" t="str">
-        <v/>
+        <v>CR-330</v>
       </c>
     </row>
     <row r="142">
@@ -3661,13 +3661,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C142" t="str">
-        <v>Warehouse Stock report</v>
+        <v>Locations on items</v>
       </c>
       <c r="D142" t="str">
-        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
+        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
       </c>
       <c r="E142" t="str">
         <v>Completed</v>
@@ -3676,7 +3676,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G142" t="str">
-        <v>CR-331</v>
+        <v>CR-332</v>
       </c>
     </row>
     <row r="143">
@@ -3684,22 +3684,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C143" t="str">
-        <v>Panel Master</v>
+        <v>Stock keyed by the item</v>
       </c>
       <c r="D143" t="str">
-        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
+        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
       </c>
       <c r="E143" t="str">
         <v>Completed</v>
       </c>
       <c r="F143" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G143" t="str">
-        <v>CR-283…285, 291, 319</v>
+        <v>CR-341</v>
       </c>
     </row>
     <row r="144">
@@ -3707,22 +3707,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C144" t="str">
-        <v>Panel form opens with a blank size</v>
+        <v>Sales reports</v>
       </c>
       <c r="D144" t="str">
-        <v>New Panel no longer prefills 1200x2100; the size is typed.</v>
+        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
       </c>
       <c r="E144" t="str">
         <v>Completed</v>
       </c>
       <c r="F144" t="str">
-        <v>2026-10-28</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G144" t="str">
-        <v>CR-484</v>
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -3730,22 +3730,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C145" t="str">
-        <v>Sample order Actions tab</v>
+        <v>Inventory reports</v>
       </c>
       <c r="D145" t="str">
-        <v>A sample order has the panel order's tabs (Details · Readiness · Actions · Dispatch · Activity). Loads are recorded on the Actions tab — quantity per row, + Load… on one row, Dispatch, Load Copy per trip — the header Record Load button is gone.</v>
+        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
       </c>
       <c r="E145" t="str">
         <v>Completed</v>
       </c>
       <c r="F145" t="str">
-        <v>2026-10-28</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G145" t="str">
-        <v>CR-485</v>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="146">
@@ -3753,22 +3753,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C146" t="str">
-        <v>Sample order pick slip</v>
+        <v>Dispatch reports</v>
       </c>
       <c r="D146" t="str">
-        <v>More ▸ Print order PDF on a sample order: every item with its photo, name and item code, full tile / cut piece size, Requested · Supplied · Remaining, the remark typed on the line and an empty Broken / Adjustment box to fill in by hand; the Stock Adjustments reminder and Taken out by / Checked by lines.</v>
+        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
       </c>
       <c r="E146" t="str">
         <v>Completed</v>
       </c>
       <c r="F146" t="str">
-        <v>2026-10-28</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G146" t="str">
-        <v>CR-486</v>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="147">
@@ -3776,22 +3776,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C147" t="str">
-        <v>Allocate Stock on sample orders</v>
+        <v>Audit log and activity</v>
       </c>
       <c r="D147" t="str">
-        <v>A sample order books cut pieces the way a panel order does: Requirements card on its Actions tab (Need · In Stock · Allocated · Short) and the same Allocate Stock window; a cut-piece row loads only once booked, the load consumes the booking; panel and sample bookings share one pool so no piece is promised twice; Pending Cut Stock counts sample demand.</v>
+        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
       </c>
       <c r="E147" t="str">
         <v>Completed</v>
       </c>
       <c r="F147" t="str">
-        <v>2026-10-28</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G147" t="str">
-        <v>CR-487</v>
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -3799,22 +3799,22 @@
         <v>147</v>
       </c>
       <c r="B148" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C148" t="str">
-        <v>Full-tile samples book the sample stock</v>
+        <v>Dashboard</v>
       </c>
       <c r="D148" t="str">
-        <v>A sample order's full-tile line books the item's full-size piece on Cut Stock — the separately managed sample stock — in pieces, from the same Allocate Stock window as its cut pieces (no batch picker; export box stock is never touched); the load is refused until booked and takes the pieces out of Cut Stock. The sample order form lists panel items only.</v>
+        <v>Headline numbers.</v>
       </c>
       <c r="E148" t="str">
         <v>Completed</v>
       </c>
       <c r="F148" t="str">
-        <v>2026-10-28</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G148" t="str">
-        <v>CR-489 (replaces CR-488)</v>
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -3822,22 +3822,22 @@
         <v>148</v>
       </c>
       <c r="B149" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C149" t="str">
-        <v>Remarks on a panel</v>
+        <v>Warehouse Stock report</v>
       </c>
       <c r="D149" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
       </c>
       <c r="E149" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F149" t="str">
-        <v/>
+        <v>2026-10-12</v>
       </c>
       <c r="G149" t="str">
-        <v>CR-425</v>
+        <v>CR-331</v>
       </c>
     </row>
     <row r="150">
@@ -3848,19 +3848,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C150" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Panel Master</v>
       </c>
       <c r="D150" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
       </c>
       <c r="E150" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F150" t="str">
-        <v/>
+        <v>2026-10-08</v>
       </c>
       <c r="G150" t="str">
-        <v>CR-426</v>
+        <v>CR-283…285, 291, 319</v>
       </c>
     </row>
     <row r="151">
@@ -3868,22 +3868,22 @@
         <v>150</v>
       </c>
       <c r="B151" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C151" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Panel form opens with a blank size</v>
       </c>
       <c r="D151" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>New Panel no longer prefills 1200x2100; the size is typed.</v>
       </c>
       <c r="E151" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F151" t="str">
-        <v/>
+        <v>2026-10-28</v>
       </c>
       <c r="G151" t="str">
-        <v>CR-427</v>
+        <v>CR-484</v>
       </c>
     </row>
     <row r="152">
@@ -3891,22 +3891,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C152" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Sample order Actions tab</v>
       </c>
       <c r="D152" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>A sample order has the panel order's tabs (Details · Readiness · Actions · Dispatch · Activity). Loads are recorded on the Actions tab — quantity per row, + Load… on one row, Dispatch, Load Copy per trip — the header Record Load button is gone.</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
       </c>
       <c r="F152" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-428</v>
+        <v>CR-485</v>
       </c>
     </row>
     <row r="153">
@@ -3914,22 +3914,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C153" t="str">
-        <v>One Masters page</v>
+        <v>Sample order pick slip</v>
       </c>
       <c r="D153" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>More ▸ Print order PDF on a sample order: every item with its photo, name and item code, full tile / cut piece size, Requested · Supplied · Remaining, the remark typed on the line and an empty Broken / Adjustment box to fill in by hand; the Stock Adjustments reminder and Taken out by / Checked by lines.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
       </c>
       <c r="F153" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-436</v>
+        <v>CR-486</v>
       </c>
     </row>
     <row r="154">
@@ -3937,22 +3937,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C154" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>Allocate Stock on sample orders</v>
       </c>
       <c r="D154" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>A sample order books cut pieces the way a panel order does: Requirements card on its Actions tab (Need · In Stock · Allocated · Short) and the same Allocate Stock window; a cut-piece row loads only once booked, the load consumes the booking; panel and sample bookings share one pool so no piece is promised twice; Pending Cut Stock counts sample demand.</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
       </c>
       <c r="F154" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-439</v>
+        <v>CR-487</v>
       </c>
     </row>
     <row r="155">
@@ -3960,22 +3960,22 @@
         <v>154</v>
       </c>
       <c r="B155" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C155" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>Full-tile samples book the sample stock</v>
       </c>
       <c r="D155" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>A sample order's full-tile line books the item's full-size piece on Cut Stock — the separately managed sample stock — in pieces, from the same Allocate Stock window as its cut pieces (no batch picker; export box stock is never touched); the load is refused until booked and takes the pieces out of Cut Stock. The sample order form lists panel items only.</v>
       </c>
       <c r="E155" t="str">
         <v>Completed</v>
       </c>
       <c r="F155" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G155" t="str">
-        <v>CR-440</v>
+        <v>CR-489 (replaces CR-488)</v>
       </c>
     </row>
     <row r="156">
@@ -3983,22 +3983,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="str">
-        <v>Items</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C156" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D156" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E156" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F156" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G156" t="str">
-        <v>CR-437</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="157">
@@ -4006,13 +4006,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C157" t="str">
-        <v>Names save as Title Case</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D157" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E157" t="str">
         <v>In progress</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="G157" t="str">
-        <v>CR-429</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="158">
@@ -4032,10 +4032,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C158" t="str">
-        <v>Brand off the Item form</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D158" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E158" t="str">
         <v>In progress</v>
@@ -4044,7 +4044,7 @@
         <v/>
       </c>
       <c r="G158" t="str">
-        <v>CR-430</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="159">
@@ -4052,22 +4052,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C159" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D159" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E159" t="str">
         <v>Completed</v>
       </c>
       <c r="F159" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G159" t="str">
-        <v>CR-306</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="160">
@@ -4075,22 +4075,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C160" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>One Masters page</v>
       </c>
       <c r="D160" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E160" t="str">
         <v>Completed</v>
       </c>
       <c r="F160" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G160" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="161">
@@ -4098,22 +4098,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C161" t="str">
-        <v>MDF master</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D161" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
       </c>
       <c r="F161" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="162">
@@ -4121,22 +4121,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C162" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D162" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E162" t="str">
         <v>Completed</v>
       </c>
       <c r="F162" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="163">
@@ -4144,22 +4144,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="str">
-        <v>Panel Craft</v>
+        <v>Items</v>
       </c>
       <c r="C163" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D163" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E163" t="str">
         <v>Completed</v>
       </c>
       <c r="F163" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G163" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="164">
@@ -4167,22 +4167,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C164" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D164" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E164" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F164" t="str">
-        <v>2026-10-08</v>
+        <v/>
       </c>
       <c r="G164" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="165">
@@ -4190,22 +4190,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C165" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D165" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E165" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F165" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G165" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="166">
@@ -4216,19 +4216,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C166" t="str">
-        <v>Production checkpoints</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D166" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E166" t="str">
         <v>Completed</v>
       </c>
       <c r="F166" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G166" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="167">
@@ -4239,19 +4239,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C167" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D167" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E167" t="str">
         <v>Completed</v>
       </c>
       <c r="F167" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G167" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="168">
@@ -4262,19 +4262,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>Sample Orders</v>
+        <v>MDF master</v>
       </c>
       <c r="D168" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E168" t="str">
         <v>Completed</v>
       </c>
       <c r="F168" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G168" t="str">
-        <v>CR-315…317</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="169">
@@ -4285,19 +4285,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>One Orders register</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D169" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E169" t="str">
         <v>Completed</v>
       </c>
       <c r="F169" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G169" t="str">
-        <v>CR-345</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="170">
@@ -4308,19 +4308,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D170" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E170" t="str">
         <v>Completed</v>
       </c>
       <c r="F170" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G170" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="171">
@@ -4331,19 +4331,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D171" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E171" t="str">
         <v>Completed</v>
       </c>
       <c r="F171" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G171" t="str">
-        <v>CR-349</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="172">
@@ -4354,19 +4354,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>Load Copy print</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D172" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E172" t="str">
         <v>Completed</v>
       </c>
       <c r="F172" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G172" t="str">
-        <v>CR-351</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="173">
@@ -4377,19 +4377,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D173" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E173" t="str">
         <v>Completed</v>
       </c>
       <c r="F173" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G173" t="str">
-        <v>CR-433</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="174">
@@ -4400,19 +4400,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D174" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E174" t="str">
         <v>Completed</v>
       </c>
       <c r="F174" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G174" t="str">
-        <v>CR-311</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="175">
@@ -4423,19 +4423,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C175" t="str">
-        <v>Small UX items</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D175" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E175" t="str">
         <v>Completed</v>
       </c>
       <c r="F175" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G175" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="176">
@@ -4446,19 +4446,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C176" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>One Orders register</v>
       </c>
       <c r="D176" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E176" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F176" t="str">
-        <v/>
+        <v>2026-10-15</v>
       </c>
       <c r="G176" t="str">
-        <v>CR-365</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="177">
@@ -4469,19 +4469,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C177" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D177" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E177" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F177" t="str">
-        <v/>
+        <v>2026-10-15</v>
       </c>
       <c r="G177" t="str">
-        <v>CR-366</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="178">
@@ -4492,19 +4492,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C178" t="str">
-        <v>One Status column</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D178" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E178" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F178" t="str">
-        <v/>
+        <v>2026-10-15</v>
       </c>
       <c r="G178" t="str">
-        <v>CR-367</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="179">
@@ -4515,19 +4515,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C179" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D179" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E179" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F179" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G179" t="str">
-        <v>CR-368</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="180">
@@ -4538,19 +4538,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C180" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D180" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E180" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F180" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G180" t="str">
-        <v>CR-399</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="181">
@@ -4561,19 +4561,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C181" t="str">
-        <v>One four-state order status</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D181" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E181" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F181" t="str">
-        <v/>
+        <v>2026-10-07</v>
       </c>
       <c r="G181" t="str">
-        <v>CR-400</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="182">
@@ -4584,19 +4584,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C182" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>Small UX items</v>
       </c>
       <c r="D182" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E182" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F182" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-401</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="183">
@@ -4607,10 +4607,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C183" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D183" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E183" t="str">
         <v>In progress</v>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="G183" t="str">
-        <v>CR-402</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="184">
@@ -4630,10 +4630,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D184" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E184" t="str">
         <v>In progress</v>
@@ -4642,7 +4642,7 @@
         <v/>
       </c>
       <c r="G184" t="str">
-        <v>CR-403</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="185">
@@ -4653,10 +4653,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Load part of a panel</v>
+        <v>One Status column</v>
       </c>
       <c r="D185" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E185" t="str">
         <v>In progress</v>
@@ -4665,7 +4665,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>CR-405</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="186">
@@ -4676,10 +4676,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>MDF row on every panel</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D186" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E186" t="str">
         <v>In progress</v>
@@ -4688,7 +4688,7 @@
         <v/>
       </c>
       <c r="G186" t="str">
-        <v>CR-406</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="187">
@@ -4699,10 +4699,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C187" t="str">
-        <v>Load whole panel in one click</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D187" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E187" t="str">
         <v>In progress</v>
@@ -4711,7 +4711,7 @@
         <v/>
       </c>
       <c r="G187" t="str">
-        <v>CR-407</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="188">
@@ -4719,22 +4719,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C188" t="str">
-        <v>Settings search everywhere</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D188" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E188" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F188" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G188" t="str">
-        <v>CR-408</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="189">
@@ -4742,22 +4742,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C189" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D189" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E189" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F189" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G189" t="str">
-        <v>CR-409</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="190">
@@ -4765,22 +4765,22 @@
         <v>189</v>
       </c>
       <c r="B190" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C190" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D190" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E190" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F190" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G190" t="str">
-        <v>CR-438</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="191">
@@ -4788,22 +4788,22 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C191" t="str">
-        <v>Stock adjustment as a line form</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D191" t="str">
-        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E191" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F191" t="str">
-        <v>2026-10-25</v>
+        <v/>
       </c>
       <c r="G191" t="str">
-        <v>CR-446</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="192">
@@ -4811,22 +4811,22 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C192" t="str">
-        <v>Adjust Stock in the Zoho Books shape</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D192" t="str">
-        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E192" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F192" t="str">
-        <v>2026-10-26</v>
+        <v/>
       </c>
       <c r="G192" t="str">
-        <v>CR-457</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="193">
@@ -4834,22 +4834,22 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C193" t="str">
-        <v>Location Transfer from the Adjust Stock screen</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D193" t="str">
-        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E193" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F193" t="str">
-        <v>2026-10-26</v>
+        <v/>
       </c>
       <c r="G193" t="str">
-        <v>CR-458</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="194">
@@ -4857,22 +4857,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C194" t="str">
-        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D194" t="str">
-        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E194" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F194" t="str">
-        <v>2026-10-26</v>
+        <v/>
       </c>
       <c r="G194" t="str">
-        <v>CR-459</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="195">
@@ -4880,22 +4880,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C195" t="str">
-        <v>Cut Piece detail page inside Panel Craft</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D195" t="str">
-        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E195" t="str">
         <v>Completed</v>
       </c>
       <c r="F195" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G195" t="str">
-        <v>CR-460/461</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="196">
@@ -4903,22 +4903,22 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C196" t="str">
-        <v>Pager with First / Last arrows</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D196" t="str">
-        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
       </c>
       <c r="F196" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-467</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="197">
@@ -4926,22 +4926,22 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C197" t="str">
-        <v>Red close × on every window</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D197" t="str">
-        <v>The × that closes any window or drawer is red on every screen.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
       </c>
       <c r="F197" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-465</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="198">
@@ -4949,22 +4949,22 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C198" t="str">
-        <v>Advanced search date range fits the window</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D198" t="str">
-        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
       </c>
       <c r="F198" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-464</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="199">
@@ -4972,22 +4972,22 @@
         <v>198</v>
       </c>
       <c r="B199" t="str">
-        <v>Customers</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C199" t="str">
-        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D199" t="str">
-        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E199" t="str">
         <v>Completed</v>
       </c>
       <c r="F199" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-463/466</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="200">
@@ -4998,10 +4998,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C200" t="str">
-        <v>Stock history in date order</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D200" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
@@ -5010,7 +5010,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G200" t="str">
-        <v>CR-455</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="201">
@@ -5018,22 +5018,22 @@
         <v>200</v>
       </c>
       <c r="B201" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C201" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D201" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E201" t="str">
         <v>Completed</v>
       </c>
       <c r="F201" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G201" t="str">
-        <v>CR-447</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="202">
@@ -5041,22 +5041,22 @@
         <v>201</v>
       </c>
       <c r="B202" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C202" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D202" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E202" t="str">
         <v>Completed</v>
       </c>
       <c r="F202" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G202" t="str">
-        <v>CR-448</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="203">
@@ -5064,22 +5064,22 @@
         <v>202</v>
       </c>
       <c r="B203" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C203" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D203" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E203" t="str">
         <v>Completed</v>
       </c>
       <c r="F203" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G203" t="str">
-        <v>CR-456</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="204">
@@ -5087,22 +5087,22 @@
         <v>203</v>
       </c>
       <c r="B204" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C204" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D204" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E204" t="str">
         <v>Completed</v>
       </c>
       <c r="F204" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G204" t="str">
-        <v>CR-449</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="205">
@@ -5110,22 +5110,22 @@
         <v>204</v>
       </c>
       <c r="B205" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C205" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D205" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E205" t="str">
         <v>Completed</v>
       </c>
       <c r="F205" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G205" t="str">
-        <v>CR-450</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="206">
@@ -5133,22 +5133,22 @@
         <v>205</v>
       </c>
       <c r="B206" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Customers</v>
       </c>
       <c r="C206" t="str">
-        <v>Location at every stage</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D206" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
       </c>
       <c r="F206" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G206" t="str">
-        <v>CR-411…413</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="207">
@@ -5156,22 +5156,22 @@
         <v>206</v>
       </c>
       <c r="B207" t="str">
-        <v>Panel Craft</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C207" t="str">
-        <v>Panel location</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D207" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
       </c>
       <c r="F207" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G207" t="str">
-        <v>CR-410</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="208">
@@ -5179,22 +5179,22 @@
         <v>207</v>
       </c>
       <c r="B208" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C208" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D208" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E208" t="str">
         <v>Completed</v>
       </c>
       <c r="F208" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G208" t="str">
-        <v>CR-419</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="209">
@@ -5205,19 +5205,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C209" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D209" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E209" t="str">
         <v>Completed</v>
       </c>
       <c r="F209" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G209" t="str">
-        <v>CR-415</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="210">
@@ -5225,22 +5225,22 @@
         <v>209</v>
       </c>
       <c r="B210" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C210" t="str">
-        <v>No long helper notes</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D210" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
       </c>
       <c r="F210" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G210" t="str">
-        <v>CR-416</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="211">
@@ -5248,22 +5248,22 @@
         <v>210</v>
       </c>
       <c r="B211" t="str">
-        <v>Production</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C211" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D211" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
       </c>
       <c r="F211" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G211" t="str">
-        <v>CR-417</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="212">
@@ -5271,22 +5271,22 @@
         <v>211</v>
       </c>
       <c r="B212" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C212" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D212" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
       </c>
       <c r="F212" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G212" t="str">
-        <v>CR-418</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="213">
@@ -5294,13 +5294,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C213" t="str">
-        <v>Notifications read / unread</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D213" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
@@ -5309,7 +5309,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-419…421</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="214">
@@ -5317,13 +5317,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C214" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Panel location</v>
       </c>
       <c r="D214" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E214" t="str">
         <v>Completed</v>
@@ -5332,7 +5332,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G214" t="str">
-        <v>CR-422</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="215">
@@ -5343,19 +5343,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C215" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D215" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E215" t="str">
         <v>Completed</v>
       </c>
       <c r="F215" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G215" t="str">
-        <v>CR-404</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="216">
@@ -5366,19 +5366,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C216" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D216" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E216" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F216" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G216" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="217">
@@ -5386,22 +5386,22 @@
         <v>216</v>
       </c>
       <c r="B217" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C217" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D217" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E217" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F217" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G217" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="218">
@@ -5409,22 +5409,22 @@
         <v>217</v>
       </c>
       <c r="B218" t="str">
-        <v>Panel Craft</v>
+        <v>Production</v>
       </c>
       <c r="C218" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D218" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E218" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F218" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G218" t="str">
-        <v>Panel Craft list #2</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="219">
@@ -5432,22 +5432,22 @@
         <v>218</v>
       </c>
       <c r="B219" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C219" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D219" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E219" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F219" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G219" t="str">
-        <v>Panel Craft list #4</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="220">
@@ -5455,22 +5455,22 @@
         <v>219</v>
       </c>
       <c r="B220" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C220" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D220" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E220" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F220" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G220" t="str">
-        <v>Panel Craft list #5</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="221">
@@ -5478,22 +5478,22 @@
         <v>220</v>
       </c>
       <c r="B221" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C221" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D221" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E221" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F221" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G221" t="str">
-        <v>Panel Craft list #6</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="222">
@@ -5504,19 +5504,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C222" t="str">
-        <v>Bill / expense</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D222" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E222" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F222" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G222" t="str">
-        <v>Panel Craft list #12</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="223">
@@ -5524,22 +5524,22 @@
         <v>222</v>
       </c>
       <c r="B223" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C223" t="str">
-        <v>Item code for the catalog</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D223" t="str">
-        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E223" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F223" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G223" t="str">
-        <v>CR-473</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="224">
@@ -5550,19 +5550,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C224" t="str">
-        <v>Panel Order PDF — one page per panel</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D224" t="str">
-        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E224" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F224" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G224" t="str">
-        <v>CR-474</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="225">
@@ -5570,22 +5570,22 @@
         <v>224</v>
       </c>
       <c r="B225" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C225" t="str">
-        <v>Sales Order without a Location field</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D225" t="str">
-        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E225" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F225" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G225" t="str">
-        <v>CR-468</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="226">
@@ -5593,22 +5593,22 @@
         <v>225</v>
       </c>
       <c r="B226" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C226" t="str">
-        <v>Box Brand mandatory</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D226" t="str">
-        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E226" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F226" t="str">
-        <v>2026-10-28</v>
+        <v/>
       </c>
       <c r="G226" t="str">
-        <v>CR-483</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="227">
@@ -5616,22 +5616,22 @@
         <v>226</v>
       </c>
       <c r="B227" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C227" t="str">
-        <v>Pallet form without Box Weight</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D227" t="str">
-        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E227" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F227" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G227" t="str">
-        <v>CR-471</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="228">
@@ -5642,10 +5642,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C228" t="str">
-        <v>Boffo / Bonza company separation</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D228" t="str">
-        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E228" t="str">
         <v>Future</v>
@@ -5654,7 +5654,7 @@
         <v/>
       </c>
       <c r="G228" t="str">
-        <v>ON-HOLD #1</v>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="229">
@@ -5662,22 +5662,22 @@
         <v>228</v>
       </c>
       <c r="B229" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C229" t="str">
-        <v>System reference and change-request register</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D229" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E229" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F229" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G229" t="str">
-        <v/>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="230">
@@ -5685,22 +5685,22 @@
         <v>229</v>
       </c>
       <c r="B230" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C230" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>Item code for the catalog</v>
       </c>
       <c r="D230" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
       </c>
       <c r="E230" t="str">
         <v>Completed</v>
       </c>
       <c r="F230" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G230" t="str">
-        <v/>
+        <v>CR-473</v>
       </c>
     </row>
     <row r="231">
@@ -5708,22 +5708,22 @@
         <v>230</v>
       </c>
       <c r="B231" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C231" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Panel Order PDF — one page per panel</v>
       </c>
       <c r="D231" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
       </c>
       <c r="E231" t="str">
         <v>Completed</v>
       </c>
       <c r="F231" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G231" t="str">
-        <v/>
+        <v>CR-474</v>
       </c>
     </row>
     <row r="232">
@@ -5731,22 +5731,22 @@
         <v>231</v>
       </c>
       <c r="B232" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C232" t="str">
-        <v>Data Flow reference</v>
+        <v>Sales Order without a Location field</v>
       </c>
       <c r="D232" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
       </c>
       <c r="E232" t="str">
         <v>Completed</v>
       </c>
       <c r="F232" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G232" t="str">
-        <v>CR-272</v>
+        <v>CR-468</v>
       </c>
     </row>
     <row r="233">
@@ -5754,22 +5754,22 @@
         <v>232</v>
       </c>
       <c r="B233" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C233" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Box Brand mandatory</v>
       </c>
       <c r="D233" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
       </c>
       <c r="E233" t="str">
         <v>Completed</v>
       </c>
       <c r="F233" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G233" t="str">
-        <v/>
+        <v>CR-483</v>
       </c>
     </row>
     <row r="234">
@@ -5777,22 +5777,22 @@
         <v>233</v>
       </c>
       <c r="B234" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C234" t="str">
-        <v>Locations guide</v>
+        <v>Pallet form without Box Weight</v>
       </c>
       <c r="D234" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
       </c>
       <c r="E234" t="str">
         <v>Completed</v>
       </c>
       <c r="F234" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G234" t="str">
-        <v>CR-411…413</v>
+        <v>CR-471</v>
       </c>
     </row>
     <row r="235">
@@ -5800,22 +5800,22 @@
         <v>234</v>
       </c>
       <c r="B235" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C235" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Boffo / Bonza company separation</v>
       </c>
       <c r="D235" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
       </c>
       <c r="E235" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F235" t="str">
-        <v>2026-10-22</v>
+        <v/>
       </c>
       <c r="G235" t="str">
-        <v/>
+        <v>ON-HOLD #1</v>
       </c>
     </row>
     <row r="236">
@@ -5826,19 +5826,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C236" t="str">
-        <v>Demo / test environment</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D236" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E236" t="str">
         <v>Completed</v>
       </c>
       <c r="F236" t="str">
-        <v>2026-10-25</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G236" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="237">
@@ -5849,25 +5849,186 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C237" t="str">
+        <v>Change log, user flow, user manual</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+      </c>
+      <c r="E237" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F237" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Seed and teardown scripts</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+      </c>
+      <c r="E238" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Data Flow reference</v>
+      </c>
+      <c r="D239" t="str">
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+      </c>
+      <c r="E239" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F239" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G239" t="str">
+        <v>CR-272</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Phase 2 inventory</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+      </c>
+      <c r="E240" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F240" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Locations guide</v>
+      </c>
+      <c r="D241" t="str">
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+      </c>
+      <c r="E241" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F241" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="G241" t="str">
+        <v>CR-411…413</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Deliverables list (this workbook)</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+      </c>
+      <c r="E242" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F242" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D243" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E243" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F243" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G243" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C244" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D237" t="str">
+      <c r="D244" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E237" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F237" t="str">
+      <c r="E244" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F244" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G237" t="str">
+      <c r="G244" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G237"/>
+  <autoFilter ref="A1:G244"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G237"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G244"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G251</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G244"/>
+  <dimension ref="A1:G251"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -1341,19 +1341,19 @@
         <v>Customers</v>
       </c>
       <c r="C41" t="str">
-        <v>Customer detail</v>
+        <v>Customer box labels</v>
       </c>
       <c r="D41" t="str">
-        <v>Quotes, sales orders and dispatches for that customer in one place; Showcase Panels and Customer Samples sections.</v>
+        <v>Customer ▸ Labels: the customer's own EAN-13 barcode per item (add, edit or import their Excel list; wrong check digits and duplicates refused) and the stickers that print for them — barcode strip, batch strip and a compliance box label in their language, each with its size, texts and a live preview. Print Box Labels from a production record, a Sales Order or a Palletization plan: one PDF per sticker, one label per page, copies = boxes.</v>
       </c>
       <c r="E41" t="str">
         <v>Completed</v>
       </c>
       <c r="F41" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-30</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>CR-502</v>
       </c>
     </row>
     <row r="42">
@@ -1364,10 +1364,10 @@
         <v>Customers</v>
       </c>
       <c r="C42" t="str">
-        <v>Transactions inherit customer fields</v>
+        <v>Customer detail</v>
       </c>
       <c r="D42" t="str">
-        <v>Every quote and order fills currency, terms, addresses, brand and box brand from the customer on pick — nothing retyped.</v>
+        <v>Quotes, sales orders and dispatches for that customer in one place; Showcase Panels and Customer Samples sections.</v>
       </c>
       <c r="E42" t="str">
         <v>Completed</v>
@@ -1387,19 +1387,19 @@
         <v>Customers</v>
       </c>
       <c r="C43" t="str">
-        <v>Sign in with Zoho</v>
+        <v>Transactions inherit customer fields</v>
       </c>
       <c r="D43" t="str">
-        <v>Login page leads with a Zoho button; password form stays as fallback; only existing active app users get in; roles stay Admin-controlled.</v>
+        <v>Every quote and order fills currency, terms, addresses, brand and box brand from the customer on pick — nothing retyped.</v>
       </c>
       <c r="E43" t="str">
         <v>Completed</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G43" t="str">
-        <v>CR-324</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -1410,19 +1410,19 @@
         <v>Customers</v>
       </c>
       <c r="C44" t="str">
-        <v>Zoho CRM Accounts as the customer source</v>
+        <v>Sign in with Zoho</v>
       </c>
       <c r="D44" t="str">
-        <v>Changes arrive via webhook / scheduled pull; Import all once; Create in / Push to Zoho CRM from the customer; From Zoho CRM on the Customers page; Map / Re-pull / Unmap by hand. Contact persons from CRM Contacts; GSTIN, PAN, GST treatment, Place of Supply, Credit Limit, Payment Term picked up automatically.</v>
+        <v>Login page leads with a Zoho button; password form stays as fallback; only existing active app users get in; roles stay Admin-controlled.</v>
       </c>
       <c r="E44" t="str">
         <v>Completed</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G44" t="str">
-        <v>CR-359</v>
+        <v>CR-324</v>
       </c>
     </row>
     <row r="45">
@@ -1433,10 +1433,10 @@
         <v>Customers</v>
       </c>
       <c r="C45" t="str">
-        <v>Zoho Books customer sync (built, switched off)</v>
+        <v>Zoho CRM Accounts as the customer source</v>
       </c>
       <c r="D45" t="str">
-        <v>Two-way customer sync with Zoho Books (event-driven pull, Import all, Push) and the Books tax / credit / notes fields on the customer. Hidden since the switch to CRM at the customer's request; data kept.</v>
+        <v>Changes arrive via webhook / scheduled pull; Import all once; Create in / Push to Zoho CRM from the customer; From Zoho CRM on the Customers page; Map / Re-pull / Unmap by hand. Contact persons from CRM Contacts; GSTIN, PAN, GST treatment, Place of Supply, Credit Limit, Payment Term picked up automatically.</v>
       </c>
       <c r="E45" t="str">
         <v>Completed</v>
@@ -1445,7 +1445,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G45" t="str">
-        <v>CR-325, 356, 358</v>
+        <v>CR-359</v>
       </c>
     </row>
     <row r="46">
@@ -1456,10 +1456,10 @@
         <v>Customers</v>
       </c>
       <c r="C46" t="str">
-        <v>Zoho link status per customer</v>
+        <v>Zoho Books customer sync (built, switched off)</v>
       </c>
       <c r="D46" t="str">
-        <v>Customers grid column Zoho: CRM &amp; Books / CRM only / Books only; customer page spells it out with both ids; advanced filter takes the states; token handling fixed so the status fills for every synced customer.</v>
+        <v>Two-way customer sync with Zoho Books (event-driven pull, Import all, Push) and the Books tax / credit / notes fields on the customer. Hidden since the switch to CRM at the customer's request; data kept.</v>
       </c>
       <c r="E46" t="str">
         <v>Completed</v>
@@ -1468,7 +1468,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G46" t="str">
-        <v>CR-362, 363</v>
+        <v>CR-325, 356, 358</v>
       </c>
     </row>
     <row r="47">
@@ -1479,19 +1479,19 @@
         <v>Customers</v>
       </c>
       <c r="C47" t="str">
-        <v>Sync never creates a twin; duplicate names are an error</v>
+        <v>Zoho link status per customer</v>
       </c>
       <c r="D47" t="str">
-        <v>The existing-customer lookup reads every customer; a CRM account whose name already belongs to another linked customer is reported as a duplicate and not created; CRM comes first.</v>
+        <v>Customers grid column Zoho: CRM &amp; Books / CRM only / Books only; customer page spells it out with both ids; advanced filter takes the states; token handling fixed so the status fills for every synced customer.</v>
       </c>
       <c r="E47" t="str">
         <v>Completed</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G47" t="str">
-        <v>CR-372</v>
+        <v>CR-362, 363</v>
       </c>
     </row>
     <row r="48">
@@ -1502,10 +1502,10 @@
         <v>Customers</v>
       </c>
       <c r="C48" t="str">
-        <v>Duplicate customers card</v>
+        <v>Sync never creates a twin; duplicate names are an error</v>
       </c>
       <c r="D48" t="str">
-        <v>Settings ▸ Zoho CRM ▸ Duplicate customers: Find duplicates → Merge N duplicates (quotes, orders, panel and sample orders move to the surviving customer; reused codes renewed). Import all refuses to run while duplicates exist.</v>
+        <v>The existing-customer lookup reads every customer; a CRM account whose name already belongs to another linked customer is reported as a duplicate and not created; CRM comes first.</v>
       </c>
       <c r="E48" t="str">
         <v>Completed</v>
@@ -1514,7 +1514,7 @@
         <v>2026-10-22</v>
       </c>
       <c r="G48" t="str">
-        <v>CR-373</v>
+        <v>CR-372</v>
       </c>
     </row>
     <row r="49">
@@ -1522,22 +1522,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Customers</v>
       </c>
       <c r="C49" t="str">
-        <v>List pages load in one round trip</v>
+        <v>Duplicate customers card</v>
       </c>
       <c r="D49" t="str">
-        <v>Every list page joins the Customer table (2,800+ rows after the CRM import); it was fetched 300 rows per request, one after another, at about a second each. The server now returns a whole table in one response, so the sales order, quote, production, palletization, loading and customer lists stop waiting about ten seconds for it.</v>
+        <v>Settings ▸ Zoho CRM ▸ Duplicate customers: Find duplicates → Merge N duplicates (quotes, orders, panel and sample orders move to the surviving customer; reused codes renewed). Import all refuses to run while duplicates exist.</v>
       </c>
       <c r="E49" t="str">
         <v>Completed</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G49" t="str">
-        <v>CR-478</v>
+        <v>CR-373</v>
       </c>
     </row>
     <row r="50">
@@ -1545,22 +1545,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Customers</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C50" t="str">
-        <v>Import all reaches every CRM account</v>
+        <v>List pages load in one round trip</v>
       </c>
       <c r="D50" t="str">
-        <v>Zoho CRM only serves page numbers up to record 2,000, so older accounts never arrived; the import now walks Zoho's page tokens (200 accounts per list call) and a re-run works only on the changed or unlinked accounts instead of re-listing everything ten by ten.</v>
+        <v>Every list page joins the Customer table (2,800+ rows after the CRM import); it was fetched 300 rows per request, one after another, at about a second each. The server now returns a whole table in one response, so the sales order, quote, production, palletization, loading and customer lists stop waiting about ten seconds for it.</v>
       </c>
       <c r="E50" t="str">
         <v>Completed</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G50" t="str">
-        <v>CR-477</v>
+        <v>CR-478</v>
       </c>
     </row>
     <row r="51">
@@ -1571,19 +1571,19 @@
         <v>Customers</v>
       </c>
       <c r="C51" t="str">
-        <v>Zoho item reference</v>
+        <v>Import all reaches every CRM account</v>
       </c>
       <c r="D51" t="str">
-        <v>Link items to the Zoho item master. Blocked — reference layout never supplied.</v>
+        <v>Zoho CRM only serves page numbers up to record 2,000, so older accounts never arrived; the import now walks Zoho's page tokens (200 accounts per list call) and a re-run works only on the changed or unlinked accounts instead of re-listing everything ten by ten.</v>
       </c>
       <c r="E51" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
       <c r="G51" t="str">
-        <v>CR-013.2</v>
+        <v>CR-477</v>
       </c>
     </row>
     <row r="52">
@@ -1591,22 +1591,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Quotes &amp; Approvals</v>
+        <v>Customers</v>
       </c>
       <c r="C52" t="str">
-        <v>Quote form (create / edit / clone)</v>
+        <v>Zoho item reference</v>
       </c>
       <c r="D52" t="str">
-        <v>Customer, currency (INR default, any currency with the day's rate), payment terms, box brand, lines item · size · boxes · rate; totals in document currency and INR.</v>
+        <v>Link items to the Zoho item master. Blocked — reference layout never supplied.</v>
       </c>
       <c r="E52" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F52" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>CR-013.2</v>
       </c>
     </row>
     <row r="53">
@@ -1617,10 +1617,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C53" t="str">
-        <v>Grouped by design</v>
+        <v>Quote form (create / edit / clone)</v>
       </c>
       <c r="D53" t="str">
-        <v>On screen, in print and in the PDF, with per-design subtotals.</v>
+        <v>Customer, currency (INR default, any currency with the day's rate), payment terms, box brand, lines item · size · boxes · rate; totals in document currency and INR.</v>
       </c>
       <c r="E53" t="str">
         <v>Completed</v>
@@ -1640,10 +1640,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C54" t="str">
-        <v>PDF and public share link</v>
+        <v>Grouped by design</v>
       </c>
       <c r="D54" t="str">
-        <v>Customer-facing PDF and an unguessable share link.</v>
+        <v>On screen, in print and in the PDF, with per-design subtotals.</v>
       </c>
       <c r="E54" t="str">
         <v>Completed</v>
@@ -1663,10 +1663,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C55" t="str">
-        <v>Container planning on the quote</v>
+        <v>PDF and public share link</v>
       </c>
       <c r="D55" t="str">
-        <v>Plan quoted boxes into containers in Box Fitting or Weight Fitting mode; move boxes between containers; fractional fill for mixed containers; optimiser respects pallet slots, area, weight and box caps.</v>
+        <v>Customer-facing PDF and an unguessable share link.</v>
       </c>
       <c r="E55" t="str">
         <v>Completed</v>
@@ -1686,10 +1686,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C56" t="str">
-        <v>Approvals page</v>
+        <v>Container planning on the quote</v>
       </c>
       <c r="D56" t="str">
-        <v>Approve or reject with a reason; sales person notified; an approver's own quotes are born Approved. Lifecycle Draft → Pending approval → Approved → Sent → Accepted → Converted.</v>
+        <v>Plan quoted boxes into containers in Box Fitting or Weight Fitting mode; move boxes between containers; fractional fill for mixed containers; optimiser respects pallet slots, area, weight and box caps.</v>
       </c>
       <c r="E56" t="str">
         <v>Completed</v>
@@ -1709,10 +1709,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C57" t="str">
-        <v>Quote aging report</v>
+        <v>Approvals page</v>
       </c>
       <c r="D57" t="str">
-        <v>Shows where quotes are stuck.</v>
+        <v>Approve or reject with a reason; sales person notified; an approver's own quotes are born Approved. Lifecycle Draft → Pending approval → Approved → Sent → Accepted → Converted.</v>
       </c>
       <c r="E57" t="str">
         <v>Completed</v>
@@ -1732,19 +1732,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C58" t="str">
-        <v>Suitable Containers panel</v>
+        <v>Quote aging report</v>
       </c>
       <c r="D58" t="str">
-        <v>Per size on the quote: the container it fits, boxes quoted, containers needed and how full the last one is (on screen).</v>
+        <v>Shows where quotes are stuck.</v>
       </c>
       <c r="E58" t="str">
         <v>Completed</v>
       </c>
       <c r="F58" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G58" t="str">
-        <v>CR-262</v>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -1755,19 +1755,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C59" t="str">
-        <v>Planner picks the container per item row</v>
+        <v>Suitable Containers panel</v>
       </c>
       <c r="D59" t="str">
-        <v>A Container column on every planner row lists the containers of that size built from the chosen pallet; default the largest; saved with the plan; a loading made from the plan starts on it.</v>
+        <v>Per size on the quote: the container it fits, boxes quoted, containers needed and how full the last one is (on screen).</v>
       </c>
       <c r="E59" t="str">
         <v>Completed</v>
       </c>
       <c r="F59" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G59" t="str">
-        <v>CR-274, 300</v>
+        <v>CR-262</v>
       </c>
     </row>
     <row r="60">
@@ -1778,19 +1778,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C60" t="str">
-        <v>Customer search modal</v>
+        <v>Planner picks the container per item row</v>
       </c>
       <c r="D60" t="str">
-        <v>Magnifier beside the Customer field on Quote, Sales Order and New Palletization opens a searchable customer table; dropdown shows code · country.</v>
+        <v>A Container column on every planner row lists the containers of that size built from the chosen pallet; default the largest; saved with the plan; a loading made from the plan starts on it.</v>
       </c>
       <c r="E60" t="str">
         <v>Completed</v>
       </c>
       <c r="F60" t="str">
-        <v>2026-10-06</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G60" t="str">
-        <v>CR-276</v>
+        <v>CR-274, 300</v>
       </c>
     </row>
     <row r="61">
@@ -1801,19 +1801,19 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C61" t="str">
-        <v>Suitable Containers on print / PDF / share link</v>
+        <v>Customer search modal</v>
       </c>
       <c r="D61" t="str">
-        <v>Carry the on-screen Suitable Containers panel onto the printed quote, PDF and share link.</v>
+        <v>Magnifier beside the Customer field on Quote, Sales Order and New Palletization opens a searchable customer table; dropdown shows code · country.</v>
       </c>
       <c r="E61" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F61" t="str">
-        <v/>
+        <v>2026-10-06</v>
       </c>
       <c r="G61" t="str">
-        <v>CR-262 follow-up</v>
+        <v>CR-276</v>
       </c>
     </row>
     <row r="62">
@@ -1824,10 +1824,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C62" t="str">
-        <v>Weight fitting from the container's max weight</v>
+        <v>Suitable Containers on print / PDF / share link</v>
       </c>
       <c r="D62" t="str">
-        <v>Planner uses the container's own weight limit instead of a typed tonnage.</v>
+        <v>Carry the on-screen Suitable Containers panel onto the printed quote, PDF and share link.</v>
       </c>
       <c r="E62" t="str">
         <v>Future</v>
@@ -1836,7 +1836,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>CR-262 follow-up</v>
       </c>
     </row>
     <row r="63">
@@ -1847,10 +1847,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C63" t="str">
-        <v>Qty total on screen and on the printed quote</v>
+        <v>Weight fitting from the container's max weight</v>
       </c>
       <c r="D63" t="str">
-        <v>Box total shown on the quote and in print / PDF.</v>
+        <v>Planner uses the container's own weight limit instead of a typed tonnage.</v>
       </c>
       <c r="E63" t="str">
         <v>Future</v>
@@ -1859,7 +1859,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>CR-079</v>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -1870,10 +1870,10 @@
         <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C64" t="str">
-        <v>Collapse long remarks / terms</v>
+        <v>Qty total on screen and on the printed quote</v>
       </c>
       <c r="D64" t="str">
-        <v>Long remarks and terms fold behind 'view more' so the page does not stretch.</v>
+        <v>Box total shown on the quote and in print / PDF.</v>
       </c>
       <c r="E64" t="str">
         <v>Future</v>
@@ -1882,7 +1882,7 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>CR-088</v>
+        <v>CR-079</v>
       </c>
     </row>
     <row r="65">
@@ -1890,22 +1890,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Sales Orders</v>
+        <v>Quotes &amp; Approvals</v>
       </c>
       <c r="C65" t="str">
-        <v>Convert to Sales Order</v>
+        <v>Collapse long remarks / terms</v>
       </c>
       <c r="D65" t="str">
-        <v>From an Accepted quote, full or partial (quote becomes Partially converted and can be converted again); the quote's container plan is copied and the order owns its editable copy.</v>
+        <v>Long remarks and terms fold behind 'view more' so the page does not stretch.</v>
       </c>
       <c r="E65" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F65" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>CR-088</v>
       </c>
     </row>
     <row r="66">
@@ -1916,10 +1916,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C66" t="str">
-        <v>Sales Order form (page)</v>
+        <v>Convert to Sales Order</v>
       </c>
       <c r="D66" t="str">
-        <v>Same layout family as the quote; PO number; editable after work has started (a line with pallets or loads keeps its item and cannot drop below what was done).</v>
+        <v>From an Accepted quote, full or partial (quote becomes Partially converted and can be converted again); the quote's container plan is copied and the order owns its editable copy.</v>
       </c>
       <c r="E66" t="str">
         <v>Completed</v>
@@ -1939,10 +1939,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C67" t="str">
-        <v>Allocate Stock</v>
+        <v>Sales Order form (page)</v>
       </c>
       <c r="D67" t="str">
-        <v>Hand free boxes of chosen batches to an order line (one flat table item → batch rows, with search). Allocation is a claim, not a movement.</v>
+        <v>Same layout family as the quote; PO number; editable after work has started (a line with pallets or loads keeps its item and cannot drop below what was done).</v>
       </c>
       <c r="E67" t="str">
         <v>Completed</v>
@@ -1951,7 +1951,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G67" t="str">
-        <v>CR-194…200</v>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -1962,10 +1962,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C68" t="str">
-        <v>Status = order lifecycle; Palletization / Loading progress separate</v>
+        <v>Allocate Stock</v>
       </c>
       <c r="D68" t="str">
-        <v>Draft → Pending approval → Confirmed → In progress → Partially completed → Completed, rolled up from dispatched vs ordered. Palletization and Loading progress are their own columns / fields. Admin override with reason.</v>
+        <v>Hand free boxes of chosen batches to an order line (one flat table item → batch rows, with search). Allocation is a claim, not a movement.</v>
       </c>
       <c r="E68" t="str">
         <v>Completed</v>
@@ -1974,7 +1974,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G68" t="str">
-        <v>CR-230…233</v>
+        <v>CR-194…200</v>
       </c>
     </row>
     <row r="69">
@@ -1985,10 +1985,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C69" t="str">
-        <v>Order detail tabs and actions</v>
+        <v>Status = order lifecycle; Palletization / Loading progress separate</v>
       </c>
       <c r="D69" t="str">
-        <v>Items (ordered · allocated · palletized · loaded · dispatched per line), Palletization, Dispatch, Activity; Send to Palletization, New Loading, Allocate Stock, Containerise, Clone.</v>
+        <v>Draft → Pending approval → Confirmed → In progress → Partially completed → Completed, rolled up from dispatched vs ordered. Palletization and Loading progress are their own columns / fields. Admin override with reason.</v>
       </c>
       <c r="E69" t="str">
         <v>Completed</v>
@@ -1997,7 +1997,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G69" t="str">
-        <v/>
+        <v>CR-230…233</v>
       </c>
     </row>
     <row r="70">
@@ -2008,10 +2008,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C70" t="str">
-        <v>Orders grid, By-order view, Kanban pipeline</v>
+        <v>Order detail tabs and actions</v>
       </c>
       <c r="D70" t="str">
-        <v>Three views over the same data.</v>
+        <v>Items (ordered · allocated · palletized · loaded · dispatched per line), Palletization, Dispatch, Activity; Send to Palletization, New Loading, Allocate Stock, Containerise, Clone.</v>
       </c>
       <c r="E70" t="str">
         <v>Completed</v>
@@ -2031,19 +2031,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C71" t="str">
-        <v>Remaining, totals and Deallocate Stock</v>
+        <v>Orders grid, By-order view, Kanban pipeline</v>
       </c>
       <c r="D71" t="str">
-        <v>Items table shows Remaining = Ordered − Allocated and a totals row; ✕ per allocated line returns boxes to free stock unless already palletized; partial deallocate ('5 of 520'); Allocate / Deallocate buttons always visible with the reason when greyed.</v>
+        <v>Three views over the same data.</v>
       </c>
       <c r="E71" t="str">
         <v>Completed</v>
       </c>
       <c r="F71" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G71" t="str">
-        <v>CR-263, 297</v>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -2054,10 +2054,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C72" t="str">
-        <v>Item STOCK card itemises on-hand</v>
+        <v>Remaining, totals and Deallocate Stock</v>
       </c>
       <c r="D72" t="str">
-        <v>Awaiting palletization row between In production and In loading, each with per-order drill-down, so Available adds up on screen.</v>
+        <v>Items table shows Remaining = Ordered − Allocated and a totals row; ✕ per allocated line returns boxes to free stock unless already palletized; partial deallocate ('5 of 520'); Allocate / Deallocate buttons always visible with the reason when greyed.</v>
       </c>
       <c r="E72" t="str">
         <v>Completed</v>
@@ -2066,7 +2066,7 @@
         <v>2026-10-07</v>
       </c>
       <c r="G72" t="str">
-        <v>CR-298</v>
+        <v>CR-263, 297</v>
       </c>
     </row>
     <row r="73">
@@ -2077,19 +2077,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C73" t="str">
-        <v>A worked order cannot be deleted</v>
+        <v>Item STOCK card itemises on-hand</v>
       </c>
       <c r="D73" t="str">
-        <v>Once any line is allocated, palletized, loaded, dispatched or on a plan, Delete is greyed and refused ('Cancel it instead').</v>
+        <v>Awaiting palletization row between In production and In loading, each with per-order drill-down, so Available adds up on screen.</v>
       </c>
       <c r="E73" t="str">
         <v>Completed</v>
       </c>
       <c r="F73" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G73" t="str">
-        <v>CR-271</v>
+        <v>CR-298</v>
       </c>
     </row>
     <row r="74">
@@ -2100,19 +2100,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C74" t="str">
-        <v>Customer PO first, SO number small</v>
+        <v>A worked order cannot be deleted</v>
       </c>
       <c r="D74" t="str">
-        <v>Sales Order page titled by the customer's PO with SO/FY/NNN small beneath; Orders grid first column PO Number; drawer and By-Order cards follow.</v>
+        <v>Once any line is allocated, palletized, loaded, dispatched or on a plan, Delete is greyed and refused ('Cancel it instead').</v>
       </c>
       <c r="E74" t="str">
         <v>Completed</v>
       </c>
       <c r="F74" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G74" t="str">
-        <v>CR-353</v>
+        <v>CR-271</v>
       </c>
     </row>
     <row r="75">
@@ -2123,19 +2123,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C75" t="str">
-        <v>Cancel Order clears the palletization board</v>
+        <v>Customer PO first, SO number small</v>
       </c>
       <c r="D75" t="str">
-        <v>Cancelling a sales order (reason required) removes its boxes from open containers, every palletization line and every allocation; a dispatched container blocks the cancel.</v>
+        <v>Sales Order page titled by the customer's PO with SO/FY/NNN small beneath; Orders grid first column PO Number; drawer and By-Order cards follow.</v>
       </c>
       <c r="E75" t="str">
         <v>Completed</v>
       </c>
       <c r="F75" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G75" t="str">
-        <v>CR-371</v>
+        <v>CR-353</v>
       </c>
     </row>
     <row r="76">
@@ -2146,19 +2146,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C76" t="str">
-        <v>'Mark in progress' → 'Mark as sent'</v>
+        <v>Cancel Order clears the palletization board</v>
       </c>
       <c r="D76" t="str">
-        <v>Rename the status action to what it means: the sales person acknowledged the customer.</v>
+        <v>Cancelling a sales order (reason required) removes its boxes from open containers, every palletization line and every allocation; a dispatched container blocks the cancel.</v>
       </c>
       <c r="E76" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G76" t="str">
-        <v>CR-041</v>
+        <v>CR-371</v>
       </c>
     </row>
     <row r="77">
@@ -2169,10 +2169,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C77" t="str">
-        <v>'Send to Palletization' in the More menu</v>
+        <v>'Mark in progress' → 'Mark as sent'</v>
       </c>
       <c r="D77" t="str">
-        <v>Move the action into More and name it 'Palletization'.</v>
+        <v>Rename the status action to what it means: the sales person acknowledged the customer.</v>
       </c>
       <c r="E77" t="str">
         <v>Future</v>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>CR-042</v>
+        <v>CR-041</v>
       </c>
     </row>
     <row r="78">
@@ -2189,22 +2189,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>Production</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C78" t="str">
-        <v>Production page — Sheet / Kanban / Grid</v>
+        <v>'Send to Palletization' in the More menu</v>
       </c>
       <c r="D78" t="str">
-        <v>Three views of the same rows (Sheet default); one row per logged batch; Group by Item / Customer / Order / Size; status filter with All.</v>
+        <v>Move the action into More and name it 'Palletization'.</v>
       </c>
       <c r="E78" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F78" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G78" t="str">
-        <v/>
+        <v>CR-042</v>
       </c>
     </row>
     <row r="79">
@@ -2215,10 +2215,10 @@
         <v>Production</v>
       </c>
       <c r="C79" t="str">
-        <v>To Produce view</v>
+        <v>Production page — Sheet / Kanban / Grid</v>
       </c>
       <c r="D79" t="str">
-        <v>Per item: open demand, free stock, in production and what still needs producing, with the Box Brand wanted; tick rows to start a job.</v>
+        <v>Three views of the same rows (Sheet default); one row per logged batch; Group by Item / Customer / Order / Size; status filter with All.</v>
       </c>
       <c r="E79" t="str">
         <v>Completed</v>
@@ -2238,10 +2238,10 @@
         <v>Production</v>
       </c>
       <c r="C80" t="str">
-        <v>Start / Log / Complete Production</v>
+        <v>To Produce view</v>
       </c>
       <c r="D80" t="str">
-        <v>Start creates the job (Item · Quantity); Log adds batch rows from the row's + menu (first log → In Production, full coverage → Completed automatically); Complete closes the job.</v>
+        <v>Per item: open demand, free stock, in production and what still needs producing, with the Box Brand wanted; tick rows to start a job.</v>
       </c>
       <c r="E80" t="str">
         <v>Completed</v>
@@ -2250,7 +2250,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G80" t="str">
-        <v>CR-234…237</v>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -2261,19 +2261,19 @@
         <v>Production</v>
       </c>
       <c r="C81" t="str">
-        <v>Bulk Record Production (make-to-stock)</v>
+        <v>Start / Log / Complete Production</v>
       </c>
       <c r="D81" t="str">
-        <v>A form in the Adjust Stock shape: Production date, recorded by and a description over an Item Table — Size · Item · Batch (blank = automatic) · Qty · Box Brand · Location per line — one line to start, + Add line; paste a block from Excel; one Save records every line into stock; retry-safe.</v>
+        <v>Start creates the job (Item · Quantity); Log adds batch rows from the row's + menu (first log → In Production, full coverage → Completed automatically); Complete closes the job.</v>
       </c>
       <c r="E81" t="str">
         <v>Completed</v>
       </c>
       <c r="F81" t="str">
-        <v>2026-10-27</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G81" t="str">
-        <v>CR-244, 264, 469</v>
+        <v>CR-234…237</v>
       </c>
     </row>
     <row r="82">
@@ -2284,10 +2284,10 @@
         <v>Production</v>
       </c>
       <c r="C82" t="str">
-        <v>Sales Order ▸ Production tab per design</v>
+        <v>Bulk Record Production (make-to-stock)</v>
       </c>
       <c r="D82" t="str">
-        <v>One row per design with its batches as chips and the requested / produced totals summed; totals footers on both tables.</v>
+        <v>A form in the Adjust Stock shape: Production date, recorded by and a description over an Item Table — Size · Item · Batch (blank = automatic) · Qty · Box Brand · Location per line — one line to start, + Add line; paste a block from Excel; one Save records every line into stock; retry-safe.</v>
       </c>
       <c r="E82" t="str">
         <v>Completed</v>
@@ -2296,7 +2296,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G82" t="str">
-        <v>CR-470</v>
+        <v>CR-244, 264, 469</v>
       </c>
     </row>
     <row r="83">
@@ -2307,19 +2307,19 @@
         <v>Production</v>
       </c>
       <c r="C83" t="str">
-        <v>Production tab per batch with Production date; stock actions on the tab</v>
+        <v>Sales Order ▸ Production tab per design</v>
       </c>
       <c r="D83" t="str">
-        <v>Each batch on its own line with the day it was produced (not the allocation day), its boxes and who allocated it; Allocate Stock / Deallocate Stock sit above this table instead of on the Items card.</v>
+        <v>One row per design with its batches as chips and the requested / produced totals summed; totals footers on both tables.</v>
       </c>
       <c r="E83" t="str">
         <v>Completed</v>
       </c>
       <c r="F83" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G83" t="str">
-        <v>CR-479</v>
+        <v>CR-470</v>
       </c>
     </row>
     <row r="84">
@@ -2330,19 +2330,19 @@
         <v>Production</v>
       </c>
       <c r="C84" t="str">
-        <v>Sheet edit mode</v>
+        <v>Production tab per batch with Production date; stock actions on the tab</v>
       </c>
       <c r="D84" t="str">
-        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
+        <v>Each batch on its own line with the day it was produced (not the allocation day), its boxes and who allocated it; Allocate Stock / Deallocate Stock sit above this table instead of on the Items card.</v>
       </c>
       <c r="E84" t="str">
         <v>Completed</v>
       </c>
       <c r="F84" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G84" t="str">
-        <v>CR-111</v>
+        <v>CR-479</v>
       </c>
     </row>
     <row r="85">
@@ -2353,10 +2353,10 @@
         <v>Production</v>
       </c>
       <c r="C85" t="str">
-        <v>Excel import of the factory file</v>
+        <v>Sheet edit mode</v>
       </c>
       <c r="D85" t="str">
-        <v>Import production from the factory's spreadsheet.</v>
+        <v>Edit makes plan qty, Produced and Status editable across rows; nothing written until Save; invalid cells block Save.</v>
       </c>
       <c r="E85" t="str">
         <v>Completed</v>
@@ -2365,7 +2365,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G85" t="str">
-        <v/>
+        <v>CR-111</v>
       </c>
     </row>
     <row r="86">
@@ -2376,10 +2376,10 @@
         <v>Production</v>
       </c>
       <c r="C86" t="str">
-        <v>Batch numbering and rules</v>
+        <v>Excel import of the factory file</v>
       </c>
       <c r="D86" t="str">
-        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
+        <v>Import production from the factory's spreadsheet.</v>
       </c>
       <c r="E86" t="str">
         <v>Completed</v>
@@ -2399,10 +2399,10 @@
         <v>Production</v>
       </c>
       <c r="C87" t="str">
-        <v>Production detail page</v>
+        <v>Batch numbering and rules</v>
       </c>
       <c r="D87" t="str">
-        <v>Lines, batches logged, activity.</v>
+        <v>Batches auto-numbered B/YYYY-MM/NNN (restarts monthly per item) or typed; never repeats on one item; Box Brand on every batch row; over-production blocked.</v>
       </c>
       <c r="E87" t="str">
         <v>Completed</v>
@@ -2422,19 +2422,19 @@
         <v>Production</v>
       </c>
       <c r="C88" t="str">
-        <v>Date-first production</v>
+        <v>Production detail page</v>
       </c>
       <c r="D88" t="str">
-        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
+        <v>Lines, batches logged, activity.</v>
       </c>
       <c r="E88" t="str">
         <v>Completed</v>
       </c>
       <c r="F88" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G88" t="str">
-        <v>CR-265, 267</v>
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -2445,19 +2445,19 @@
         <v>Production</v>
       </c>
       <c r="C89" t="str">
-        <v>Quality Control stage on the board</v>
+        <v>Date-first production</v>
       </c>
       <c r="D89" t="str">
-        <v>QC exists in the data model; putting it on the board is parked.</v>
+        <v>Grid opens grouped by date with the Production ID hidden; page titled by its date with the PRD number small; Bulk Record Production is the default button.</v>
       </c>
       <c r="E89" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F89" t="str">
-        <v/>
+        <v>2026-10-03</v>
       </c>
       <c r="G89" t="str">
-        <v>CR-051</v>
+        <v>CR-265, 267</v>
       </c>
     </row>
     <row r="90">
@@ -2468,10 +2468,10 @@
         <v>Production</v>
       </c>
       <c r="C90" t="str">
-        <v>Duplicate detection on Excel re-import</v>
+        <v>Quality Control stage on the board</v>
       </c>
       <c r="D90" t="str">
-        <v>Warn / skip when the same production file is imported twice.</v>
+        <v>QC exists in the data model; putting it on the board is parked.</v>
       </c>
       <c r="E90" t="str">
         <v>Future</v>
@@ -2480,7 +2480,7 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v/>
+        <v>CR-051</v>
       </c>
     </row>
     <row r="91">
@@ -2488,19 +2488,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>Palletization</v>
+        <v>Production</v>
       </c>
       <c r="C91" t="str">
-        <v>Palletization board and plan numbers</v>
+        <v>Duplicate detection on Excel re-import</v>
       </c>
       <c r="D91" t="str">
-        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
+        <v>Warn / skip when the same production file is imported twice.</v>
       </c>
       <c r="E91" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F91" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -2514,10 +2514,10 @@
         <v>Palletization</v>
       </c>
       <c r="C92" t="str">
-        <v>Columns, totals footer and selection bar</v>
+        <v>Palletization board and plan numbers</v>
       </c>
       <c r="D92" t="str">
-        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
+        <v>Sheet and Kanban views, Group, Today's Report, New Palletization; plans numbered PAL/FY/NNN; a plan may span several orders of one customer; each line is one item × one batch.</v>
       </c>
       <c r="E92" t="str">
         <v>Completed</v>
@@ -2526,7 +2526,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G92" t="str">
-        <v>CR-279</v>
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -2537,19 +2537,19 @@
         <v>Palletization</v>
       </c>
       <c r="C93" t="str">
-        <v>Counts per batch: Ordered · Ready Pallets · Boxes / Pallet · Remaining</v>
+        <v>Columns, totals footer and selection bar</v>
       </c>
       <c r="D93" t="str">
-        <v>Every palletization page counts the row's own batch — a loaded batch of the same item no longer shows on its sibling. Columns Boxes · Ordered Boxes · Ready Pallets (N (boxes)) · Boxes / Pallet · Remaining with totals; the Complete Palletization dialog shows the same figures.</v>
+        <v>Customer · Item · Order · Batch · Boxes · Remaining · Age · Ready Pallets (N (boxes)) · Pallet type; totals footer; selection bar when rows are ticked.</v>
       </c>
       <c r="E93" t="str">
         <v>Completed</v>
       </c>
       <c r="F93" t="str">
-        <v>2026-10-27</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G93" t="str">
-        <v>CR-472</v>
+        <v>CR-279</v>
       </c>
     </row>
     <row r="94">
@@ -2560,19 +2560,19 @@
         <v>Palletization</v>
       </c>
       <c r="C94" t="str">
-        <v>Whole pallets: Possible / Prepared Pallets, pallets recorded</v>
+        <v>Counts per batch: Ordered · Ready Pallets · Boxes / Pallet · Remaining</v>
       </c>
       <c r="D94" t="str">
-        <v>No fractions — 23 boxes on an 18-box pallet is 1 pallet · 18 boxes, the 5 wait for a mixed-batch pallet. Ready for Palletization shows Possible Pallets; In Palletization shows Pending Boxes, Possible Pallets, Prepared Pallets and the boxes on them; Ready for Loading shows Pallets and Boxes. Boxes / Pallet and Remaining removed; Complete Palletization asks for pallets.</v>
+        <v>Every palletization page counts the row's own batch — a loaded batch of the same item no longer shows on its sibling. Columns Boxes · Ordered Boxes · Ready Pallets (N (boxes)) · Boxes / Pallet · Remaining with totals; the Complete Palletization dialog shows the same figures.</v>
       </c>
       <c r="E94" t="str">
         <v>Completed</v>
       </c>
       <c r="F94" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G94" t="str">
-        <v>CR-481</v>
+        <v>CR-472</v>
       </c>
     </row>
     <row r="95">
@@ -2583,19 +2583,19 @@
         <v>Palletization</v>
       </c>
       <c r="C95" t="str">
-        <v>One toolbar with the filters on top; Sheet Mode</v>
+        <v>Whole pallets: Possible / Prepared Pallets, pallets recorded</v>
       </c>
       <c r="D95" t="str">
-        <v>Search and the customer / country / item / size filters sit in the page toolbar; Today's Report, Group, columns and New Palletization Plan ▾ on the right. The ▾ menu opens Sheet Mode — record boxes or a batch top-up across many rows, then Save.</v>
+        <v>No fractions — 23 boxes on an 18-box pallet is 1 pallet · 18 boxes, the 5 wait for a mixed-batch pallet. Ready for Palletization shows Possible Pallets; In Palletization shows Pending Boxes, Possible Pallets, Prepared Pallets and the boxes on them; Ready for Loading shows Pallets and Boxes. Boxes / Pallet and Remaining removed; Complete Palletization asks for pallets.</v>
       </c>
       <c r="E95" t="str">
         <v>Completed</v>
       </c>
       <c r="F95" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G95" t="str">
-        <v>CR-491</v>
+        <v>CR-481</v>
       </c>
     </row>
     <row r="96">
@@ -2606,10 +2606,10 @@
         <v>Palletization</v>
       </c>
       <c r="C96" t="str">
-        <v>Partial completion keeps the rest In Palletization</v>
+        <v>One toolbar with the filters on top; Sheet Mode</v>
       </c>
       <c r="D96" t="str">
-        <v>Complete fewer pallets than possible: those pallets move to Palletization Completed, the loose boxes stay on In Palletization for a mixed-batch pallet. Nothing goes back to the queue.</v>
+        <v>Search and the customer / country / item / size filters sit in the page toolbar; Today's Report, Group, columns and New Palletization Plan ▾ on the right. The ▾ menu opens Sheet Mode — record boxes or a batch top-up across many rows, then Save.</v>
       </c>
       <c r="E96" t="str">
         <v>Completed</v>
@@ -2618,7 +2618,7 @@
         <v>2026-10-29</v>
       </c>
       <c r="G96" t="str">
-        <v>CR-492</v>
+        <v>CR-491</v>
       </c>
     </row>
     <row r="97">
@@ -2629,10 +2629,10 @@
         <v>Palletization</v>
       </c>
       <c r="C97" t="str">
-        <v>Top Up from either page; mixed pallet completes as one</v>
+        <v>Partial completion keeps the rest In Palletization</v>
       </c>
       <c r="D97" t="str">
-        <v>A pallet is topped up from another batch of the same item on Ready for Palletization or In Palletization (the dialog shows which); a batch already on a mixed pallet cannot donate again. A mixed pallet completes as one pallet.</v>
+        <v>Complete fewer pallets than possible: those pallets move to Palletization Completed, the loose boxes stay on In Palletization for a mixed-batch pallet. Nothing goes back to the queue.</v>
       </c>
       <c r="E97" t="str">
         <v>Completed</v>
@@ -2641,7 +2641,7 @@
         <v>2026-10-29</v>
       </c>
       <c r="G97" t="str">
-        <v>CR-493/494/497</v>
+        <v>CR-492</v>
       </c>
     </row>
     <row r="98">
@@ -2652,10 +2652,10 @@
         <v>Palletization</v>
       </c>
       <c r="C98" t="str">
-        <v>Mix Batch icon</v>
+        <v>Top Up from either page; mixed pallet completes as one</v>
       </c>
       <c r="D98" t="str">
-        <v>One amber icon with a hover hint marks a shared (mixed-batch) pallet on every screen — no text chips.</v>
+        <v>A pallet is topped up from another batch of the same item on Ready for Palletization or In Palletization (the dialog shows which); a batch already on a mixed pallet cannot donate again. A mixed pallet completes as one pallet.</v>
       </c>
       <c r="E98" t="str">
         <v>Completed</v>
@@ -2664,7 +2664,7 @@
         <v>2026-10-29</v>
       </c>
       <c r="G98" t="str">
-        <v>CR-498</v>
+        <v>CR-493/494/497</v>
       </c>
     </row>
     <row r="99">
@@ -2675,10 +2675,10 @@
         <v>Palletization</v>
       </c>
       <c r="C99" t="str">
-        <v>Columns that read as one story</v>
+        <v>Mix Batch icon</v>
       </c>
       <c r="D99" t="str">
-        <v>On every palletization page the pallet type comes first, then the counts left to right: Ready for Palletization shows Boxes · Pallets · Loose; In Palletization shows Pending · Pallets · Loose · Prepared (pallets with boxes); hover a header for what each number means. No duplicate Boxes columns.</v>
+        <v>One amber icon with a hover hint marks a shared (mixed-batch) pallet on every screen — no text chips.</v>
       </c>
       <c r="E99" t="str">
         <v>Completed</v>
@@ -2687,7 +2687,7 @@
         <v>2026-10-29</v>
       </c>
       <c r="G99" t="str">
-        <v>CR-495/499</v>
+        <v>CR-498</v>
       </c>
     </row>
     <row r="100">
@@ -2698,19 +2698,19 @@
         <v>Palletization</v>
       </c>
       <c r="C100" t="str">
-        <v>Plan detail page</v>
+        <v>Columns that read as one story</v>
       </c>
       <c r="D100" t="str">
-        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
+        <v>On every palletization page the pallet type comes first, then the counts left to right: Ready for Palletization shows Boxes · Pallets · Loose; In Palletization shows Pending · Pallets · Loose · Prepared (pallets with boxes); hover a header for what each number means. No duplicate Boxes columns.</v>
       </c>
       <c r="E100" t="str">
         <v>Completed</v>
       </c>
       <c r="F100" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G100" t="str">
-        <v/>
+        <v>CR-495/499</v>
       </c>
     </row>
     <row r="101">
@@ -2721,10 +2721,10 @@
         <v>Palletization</v>
       </c>
       <c r="C101" t="str">
-        <v>Prints on demand</v>
+        <v>Plan detail page</v>
       </c>
       <c r="D101" t="str">
-        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
+        <v>Lines with status, batches, pallets; Edit + More; activity.</v>
       </c>
       <c r="E101" t="str">
         <v>Completed</v>
@@ -2744,10 +2744,10 @@
         <v>Palletization</v>
       </c>
       <c r="C102" t="str">
-        <v>Board rules</v>
+        <v>Prints on demand</v>
       </c>
       <c r="D102" t="str">
-        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
+        <v>Pallet Packing Report; Pallet Slips (one per physical pallet, mixed pallet lists every batch); pallet QR labels; batch QR slips.</v>
       </c>
       <c r="E102" t="str">
         <v>Completed</v>
@@ -2756,7 +2756,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G102" t="str">
-        <v>CR-129, 248</v>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -2767,10 +2767,10 @@
         <v>Palletization</v>
       </c>
       <c r="C103" t="str">
-        <v>Three ways onto the queue</v>
+        <v>Board rules</v>
       </c>
       <c r="D103" t="str">
-        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
+        <v>Planned boxes never exceed the order; batches attributed oldest-first; a hand-edited plan is pinned; the palletized part of a batch can be loaded while the rest is in progress.</v>
       </c>
       <c r="E103" t="str">
         <v>Completed</v>
@@ -2779,7 +2779,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G103" t="str">
-        <v>CR-223/224</v>
+        <v>CR-129, 248</v>
       </c>
     </row>
     <row r="104">
@@ -2790,10 +2790,10 @@
         <v>Palletization</v>
       </c>
       <c r="C104" t="str">
-        <v>'+' menu: Start / Top Up Batch / Complete</v>
+        <v>Three ways onto the queue</v>
       </c>
       <c r="D104" t="str">
-        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
+        <v>Automatic from every production record; New Palletization (customer-first page); Send to Palletization from a sales order.</v>
       </c>
       <c r="E104" t="str">
         <v>Completed</v>
@@ -2802,7 +2802,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G104" t="str">
-        <v>CR-148…150, 281</v>
+        <v>CR-223/224</v>
       </c>
     </row>
     <row r="105">
@@ -2813,10 +2813,10 @@
         <v>Palletization</v>
       </c>
       <c r="C105" t="str">
-        <v>Sheet edit mode and multi-select</v>
+        <v>'+' menu: Start / Top Up Batch / Complete</v>
       </c>
       <c r="D105" t="str">
-        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
+        <v>Start confirms the pallet format; Top Up (Mix Batch) moves boxes of another batch onto the open pallet; Complete records finished boxes to Ready for Loading, partial is normal and the rest is re-queued.</v>
       </c>
       <c r="E105" t="str">
         <v>Completed</v>
@@ -2825,7 +2825,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G105" t="str">
-        <v>CR-153</v>
+        <v>CR-148…150, 281</v>
       </c>
     </row>
     <row r="106">
@@ -2836,19 +2836,19 @@
         <v>Palletization</v>
       </c>
       <c r="C106" t="str">
-        <v>Date column, PAL code hidden</v>
+        <v>Sheet edit mode and multi-select</v>
       </c>
       <c r="D106" t="str">
-        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
+        <v>Edit adds Palletise qty and Top Up From cells on every row (✓ / ✗ per row, Save all); multi-select rows → palletize together, print slips, or Load.</v>
       </c>
       <c r="E106" t="str">
         <v>Completed</v>
       </c>
       <c r="F106" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G106" t="str">
-        <v>CR-266</v>
+        <v>CR-153</v>
       </c>
     </row>
     <row r="107">
@@ -2859,19 +2859,19 @@
         <v>Palletization</v>
       </c>
       <c r="C107" t="str">
-        <v>Complete dialog shows progress</v>
+        <v>Date column, PAL code hidden</v>
       </c>
       <c r="D107" t="str">
-        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
+        <v>Grids show the date a line entered palletization; PAL code available in the column picker.</v>
       </c>
       <c r="E107" t="str">
         <v>Completed</v>
       </c>
       <c r="F107" t="str">
-        <v>2026-10-06</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G107" t="str">
-        <v>CR-280</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="108">
@@ -2882,19 +2882,19 @@
         <v>Palletization</v>
       </c>
       <c r="C108" t="str">
-        <v>Plan edit keeps Box Brand and batches</v>
+        <v>Complete dialog shows progress</v>
       </c>
       <c r="D108" t="str">
-        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
+        <v>Per item: ready pallets (boxes) already palletized and boxes still remaining.</v>
       </c>
       <c r="E108" t="str">
         <v>Completed</v>
       </c>
       <c r="F108" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-06</v>
       </c>
       <c r="G108" t="str">
-        <v>CR-340</v>
+        <v>CR-280</v>
       </c>
     </row>
     <row r="109">
@@ -2905,19 +2905,19 @@
         <v>Palletization</v>
       </c>
       <c r="C109" t="str">
-        <v>Three pages, one stage each</v>
+        <v>Plan edit keeps Box Brand and batches</v>
       </c>
       <c r="D109" t="str">
-        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
+        <v>Editing a plan carries carton brand and batch of each line; a Completed plan is refused.</v>
       </c>
       <c r="E109" t="str">
         <v>Completed</v>
       </c>
       <c r="F109" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G109" t="str">
-        <v>CR-360, 364</v>
+        <v>CR-340</v>
       </c>
     </row>
     <row r="110">
@@ -2928,10 +2928,10 @@
         <v>Palletization</v>
       </c>
       <c r="C110" t="str">
-        <v>Release palletized boxes</v>
+        <v>Three pages, one stage each</v>
       </c>
       <c r="D110" t="str">
-        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
+        <v>Ready for Palletization, In Palletization, Palletization Completed (waiting to load); no status filter — each page lists its own rows.</v>
       </c>
       <c r="E110" t="str">
         <v>Completed</v>
@@ -2940,7 +2940,7 @@
         <v>2026-10-21</v>
       </c>
       <c r="G110" t="str">
-        <v>CR-361</v>
+        <v>CR-360, 364</v>
       </c>
     </row>
     <row r="111">
@@ -2951,19 +2951,19 @@
         <v>Palletization</v>
       </c>
       <c r="C111" t="str">
-        <v>Release returns boxes to Ready for Palletization</v>
+        <v>Release palletized boxes</v>
       </c>
       <c r="D111" t="str">
-        <v>Release on Palletization Completed puts the boxes back on the queue row of the same item and batch (counts recompute); the order keeps its allocation. Discard, Delete and Cancel Order still return boxes to free stock.</v>
+        <v>From the + menu on Palletization Completed and Loading: boxes + reason. Loaded boxes return to Ready for Loading; palletized boxes return to free stock with the allocation; partial or whole; dispatched refused.</v>
       </c>
       <c r="E111" t="str">
         <v>Completed</v>
       </c>
       <c r="F111" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G111" t="str">
-        <v>CR-500</v>
+        <v>CR-361</v>
       </c>
     </row>
     <row r="112">
@@ -2974,10 +2974,10 @@
         <v>Palletization</v>
       </c>
       <c r="C112" t="str">
-        <v>Cancel Palletization</v>
+        <v>Release returns boxes to Ready for Palletization</v>
       </c>
       <c r="D112" t="str">
-        <v>On In Palletization: boxes + reason send the pallet back to Ready for Palletization on the same item and batch row, still booked to the order. Discard (free stock) stays on Ready for Palletization only.</v>
+        <v>Release on Palletization Completed puts the boxes back on the queue row of the same item and batch (counts recompute); the order keeps its allocation. Discard, Delete and Cancel Order still return boxes to free stock.</v>
       </c>
       <c r="E112" t="str">
         <v>Completed</v>
@@ -2986,7 +2986,7 @@
         <v>2026-10-29</v>
       </c>
       <c r="G112" t="str">
-        <v>CR-501</v>
+        <v>CR-500</v>
       </c>
     </row>
     <row r="113">
@@ -2997,19 +2997,19 @@
         <v>Palletization</v>
       </c>
       <c r="C113" t="str">
-        <v>Discard the current palletization task</v>
+        <v>Cancel Palletization</v>
       </c>
       <c r="D113" t="str">
-        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
+        <v>On In Palletization: boxes + reason send the pallet back to Ready for Palletization on the same item and batch row, still booked to the order. Discard (free stock) stays on Ready for Palletization only.</v>
       </c>
       <c r="E113" t="str">
         <v>Completed</v>
       </c>
       <c r="F113" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G113" t="str">
-        <v>CR-369</v>
+        <v>CR-501</v>
       </c>
     </row>
     <row r="114">
@@ -3020,19 +3020,19 @@
         <v>Palletization</v>
       </c>
       <c r="C114" t="str">
-        <v>Delete a plan returns its boxes</v>
+        <v>Discard the current palletization task</v>
       </c>
       <c r="D114" t="str">
-        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
+        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
       </c>
       <c r="E114" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F114" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G114" t="str">
-        <v>CR-370</v>
+        <v>CR-369</v>
       </c>
     </row>
     <row r="115">
@@ -3043,19 +3043,19 @@
         <v>Palletization</v>
       </c>
       <c r="C115" t="str">
-        <v>Partial Start Palletization</v>
+        <v>Delete a plan returns its boxes</v>
       </c>
       <c r="D115" t="str">
-        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
+        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
       </c>
       <c r="E115" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F115" t="str">
         <v/>
       </c>
       <c r="G115" t="str">
-        <v>Panel Craft list #9</v>
+        <v>CR-370</v>
       </c>
     </row>
     <row r="116">
@@ -3066,10 +3066,10 @@
         <v>Palletization</v>
       </c>
       <c r="C116" t="str">
-        <v>Ready pallets — type and pallet count</v>
+        <v>Partial Start Palletization</v>
       </c>
       <c r="D116" t="str">
-        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
+        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
       </c>
       <c r="E116" t="str">
         <v>Future</v>
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="G116" t="str">
-        <v>Panel Craft list #7</v>
+        <v>Panel Craft list #9</v>
       </c>
     </row>
     <row r="117">
@@ -3089,10 +3089,10 @@
         <v>Palletization</v>
       </c>
       <c r="C117" t="str">
-        <v>Remove 'Ordered / Completed' where not needed</v>
+        <v>Ready pallets — type and pallet count</v>
       </c>
       <c r="D117" t="str">
-        <v>Screen to be confirmed.</v>
+        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
       </c>
       <c r="E117" t="str">
         <v>Future</v>
@@ -3101,7 +3101,7 @@
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>Panel Craft list #8</v>
+        <v>Panel Craft list #7</v>
       </c>
     </row>
     <row r="118">
@@ -3109,22 +3109,22 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C118" t="str">
-        <v>A loading = one container</v>
+        <v>Remove 'Ordered / Completed' where not needed</v>
       </c>
       <c r="D118" t="str">
-        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
+        <v>Screen to be confirmed.</v>
       </c>
       <c r="E118" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F118" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G118" t="str">
-        <v>CR-120…124</v>
+        <v>Panel Craft list #8</v>
       </c>
     </row>
     <row r="119">
@@ -3135,10 +3135,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C119" t="str">
-        <v>Loading and Dispatch page</v>
+        <v>A loading = one container</v>
       </c>
       <c r="D119" t="str">
-        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
+        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
       </c>
       <c r="E119" t="str">
         <v>Completed</v>
@@ -3147,7 +3147,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G119" t="str">
-        <v>CR-140, 141</v>
+        <v>CR-120…124</v>
       </c>
     </row>
     <row r="120">
@@ -3158,10 +3158,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C120" t="str">
-        <v>Loading detail</v>
+        <v>Loading and Dispatch page</v>
       </c>
       <c r="D120" t="str">
-        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
+        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
       </c>
       <c r="E120" t="str">
         <v>Completed</v>
@@ -3170,7 +3170,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G120" t="str">
-        <v/>
+        <v>CR-140, 141</v>
       </c>
     </row>
     <row r="121">
@@ -3181,10 +3181,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C121" t="str">
-        <v>Vehicle and shipment details</v>
+        <v>Loading detail</v>
       </c>
       <c r="D121" t="str">
-        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
+        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
       </c>
       <c r="E121" t="str">
         <v>Completed</v>
@@ -3204,10 +3204,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C122" t="str">
-        <v>Dispatch with gates and warnings</v>
+        <v>Vehicle and shipment details</v>
       </c>
       <c r="D122" t="str">
-        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
+        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
       </c>
       <c r="E122" t="str">
         <v>Completed</v>
@@ -3227,10 +3227,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C123" t="str">
-        <v>Invoice and dispatch prints</v>
+        <v>Dispatch with gates and warnings</v>
       </c>
       <c r="D123" t="str">
-        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
+        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
       </c>
       <c r="E123" t="str">
         <v>Completed</v>
@@ -3250,10 +3250,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C124" t="str">
-        <v>Four ways to fill a container</v>
+        <v>Invoice and dispatch prints</v>
       </c>
       <c r="D124" t="str">
-        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
+        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
       </c>
       <c r="E124" t="str">
         <v>Completed</v>
@@ -3262,7 +3262,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G124" t="str">
-        <v>CR-126…128, 201/202</v>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -3273,10 +3273,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C125" t="str">
-        <v>Editing a loading</v>
+        <v>Four ways to fill a container</v>
       </c>
       <c r="D125" t="str">
-        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
+        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
       </c>
       <c r="E125" t="str">
         <v>Completed</v>
@@ -3285,7 +3285,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G125" t="str">
-        <v/>
+        <v>CR-126…128, 201/202</v>
       </c>
     </row>
     <row r="126">
@@ -3296,19 +3296,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C126" t="str">
-        <v>Date column, LOAD code hidden</v>
+        <v>Editing a loading</v>
       </c>
       <c r="D126" t="str">
-        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
+        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
       </c>
       <c r="E126" t="str">
         <v>Completed</v>
       </c>
       <c r="F126" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G126" t="str">
-        <v>CR-266</v>
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -3319,19 +3319,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C127" t="str">
-        <v>Several containers in one New Loading</v>
+        <v>Date column, LOAD code hidden</v>
       </c>
       <c r="D127" t="str">
-        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
+        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
       </c>
       <c r="E127" t="str">
         <v>Completed</v>
       </c>
       <c r="F127" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G127" t="str">
-        <v>CR-301</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="128">
@@ -3342,19 +3342,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C128" t="str">
-        <v>Loading Workspace — a tab per container</v>
+        <v>Several containers in one New Loading</v>
       </c>
       <c r="D128" t="str">
-        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
+        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
       </c>
       <c r="E128" t="str">
         <v>Completed</v>
       </c>
       <c r="F128" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G128" t="str">
-        <v>CR-326, 334, 335</v>
+        <v>CR-301</v>
       </c>
     </row>
     <row r="129">
@@ -3365,10 +3365,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C129" t="str">
-        <v>Every customer listed, with search</v>
+        <v>Loading Workspace — a tab per container</v>
       </c>
       <c r="D129" t="str">
-        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
+        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
       </c>
       <c r="E129" t="str">
         <v>Completed</v>
@@ -3377,7 +3377,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G129" t="str">
-        <v>CR-327</v>
+        <v>CR-326, 334, 335</v>
       </c>
     </row>
     <row r="130">
@@ -3388,10 +3388,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C130" t="str">
-        <v>'What to do first' reasons</v>
+        <v>Every customer listed, with search</v>
       </c>
       <c r="D130" t="str">
-        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
+        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
       </c>
       <c r="E130" t="str">
         <v>Completed</v>
@@ -3400,7 +3400,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G130" t="str">
-        <v>CR-328</v>
+        <v>CR-327</v>
       </c>
     </row>
     <row r="131">
@@ -3411,19 +3411,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C131" t="str">
-        <v>Pick the planned container at loading</v>
+        <v>'What to do first' reasons</v>
       </c>
       <c r="D131" t="str">
-        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
+        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
       </c>
       <c r="E131" t="str">
         <v>Completed</v>
       </c>
       <c r="F131" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G131" t="str">
-        <v>CR-338</v>
+        <v>CR-328</v>
       </c>
     </row>
     <row r="132">
@@ -3434,19 +3434,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C132" t="str">
-        <v>Two steps per container; C1 / C2 naming</v>
+        <v>Pick the planned container at loading</v>
       </c>
       <c r="D132" t="str">
-        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
+        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
       </c>
       <c r="E132" t="str">
         <v>Completed</v>
       </c>
       <c r="F132" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G132" t="str">
-        <v>CR-350, 354</v>
+        <v>CR-338</v>
       </c>
     </row>
     <row r="133">
@@ -3457,19 +3457,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C133" t="str">
-        <v>Mix Batch at loading</v>
+        <v>Two steps per container; C1 / C2 naming</v>
       </c>
       <c r="D133" t="str">
-        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
+        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
       </c>
       <c r="E133" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G133" t="str">
-        <v>CR-260 follow-up</v>
+        <v>CR-350, 354</v>
       </c>
     </row>
     <row r="134">
@@ -3480,19 +3480,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C134" t="str">
-        <v>Five stage pages: Palletization Completed, Loading, Dispatch</v>
+        <v>Mix Batch at loading</v>
       </c>
       <c r="D134" t="str">
-        <v>Palletization Completed stays its own page; Loading lists the items being loaded; the new Dispatch page lists the containers ready to dispatch and the dispatched ones, with their prints.</v>
+        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
       </c>
       <c r="E134" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F134" t="str">
-        <v>2026-10-28</v>
+        <v/>
       </c>
       <c r="G134" t="str">
-        <v>CR-480</v>
+        <v>CR-260 follow-up</v>
       </c>
     </row>
     <row r="135">
@@ -3500,22 +3500,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C135" t="str">
-        <v>One stock rule everywhere</v>
+        <v>Five stage pages: Palletization Completed, Loading, Dispatch</v>
       </c>
       <c r="D135" t="str">
-        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
+        <v>Palletization Completed stays its own page; Loading lists the items being loaded; the new Dispatch page lists the containers ready to dispatch and the dispatched ones, with their prints.</v>
       </c>
       <c r="E135" t="str">
         <v>Completed</v>
       </c>
       <c r="F135" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G135" t="str">
-        <v/>
+        <v>CR-480</v>
       </c>
     </row>
     <row r="136">
@@ -3526,10 +3526,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C136" t="str">
-        <v>Counters recomputed, never incremented</v>
+        <v>One stock rule everywhere</v>
       </c>
       <c r="D136" t="str">
-        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
+        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
       </c>
       <c r="E136" t="str">
         <v>Completed</v>
@@ -3549,10 +3549,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C137" t="str">
-        <v>Allocation and batch ledger</v>
+        <v>Counters recomputed, never incremented</v>
       </c>
       <c r="D137" t="str">
-        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
+        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
       </c>
       <c r="E137" t="str">
         <v>Completed</v>
@@ -3572,10 +3572,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C138" t="str">
-        <v>Admin repair operations</v>
+        <v>Allocation and batch ledger</v>
       </c>
       <c r="D138" t="str">
-        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
+        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
       </c>
       <c r="E138" t="str">
         <v>Completed</v>
@@ -3595,19 +3595,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C139" t="str">
-        <v>Inventory adjustments</v>
+        <v>Admin repair operations</v>
       </c>
       <c r="D139" t="str">
-        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
+        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
       </c>
       <c r="E139" t="str">
         <v>Completed</v>
       </c>
       <c r="F139" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G139" t="str">
-        <v>CR-308</v>
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -3618,19 +3618,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C140" t="str">
-        <v>Stock per warehouse</v>
+        <v>Inventory adjustments</v>
       </c>
       <c r="D140" t="str">
-        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
+        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
       </c>
       <c r="E140" t="str">
         <v>Completed</v>
       </c>
       <c r="F140" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G140" t="str">
-        <v>CR-329</v>
+        <v>CR-308</v>
       </c>
     </row>
     <row r="141">
@@ -3641,10 +3641,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C141" t="str">
-        <v>Transfer Orders</v>
+        <v>Stock per warehouse</v>
       </c>
       <c r="D141" t="str">
-        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
+        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
       </c>
       <c r="E141" t="str">
         <v>Completed</v>
@@ -3653,7 +3653,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G141" t="str">
-        <v>CR-330</v>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="142">
@@ -3664,10 +3664,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C142" t="str">
-        <v>Locations on items</v>
+        <v>Transfer Orders</v>
       </c>
       <c r="D142" t="str">
-        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
+        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
       </c>
       <c r="E142" t="str">
         <v>Completed</v>
@@ -3676,7 +3676,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G142" t="str">
-        <v>CR-332</v>
+        <v>CR-330</v>
       </c>
     </row>
     <row r="143">
@@ -3687,19 +3687,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C143" t="str">
-        <v>Stock keyed by the item</v>
+        <v>Locations on items</v>
       </c>
       <c r="D143" t="str">
-        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
+        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
       </c>
       <c r="E143" t="str">
         <v>Completed</v>
       </c>
       <c r="F143" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G143" t="str">
-        <v>CR-341</v>
+        <v>CR-332</v>
       </c>
     </row>
     <row r="144">
@@ -3707,22 +3707,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C144" t="str">
-        <v>Sales reports</v>
+        <v>Stock keyed by the item</v>
       </c>
       <c r="D144" t="str">
-        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
+        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
       </c>
       <c r="E144" t="str">
         <v>Completed</v>
       </c>
       <c r="F144" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G144" t="str">
-        <v/>
+        <v>CR-341</v>
       </c>
     </row>
     <row r="145">
@@ -3733,10 +3733,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C145" t="str">
-        <v>Inventory reports</v>
+        <v>Sales reports</v>
       </c>
       <c r="D145" t="str">
-        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
+        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
       </c>
       <c r="E145" t="str">
         <v>Completed</v>
@@ -3745,7 +3745,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G145" t="str">
-        <v>CR-104</v>
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -3756,10 +3756,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C146" t="str">
-        <v>Dispatch reports</v>
+        <v>Inventory reports</v>
       </c>
       <c r="D146" t="str">
-        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
+        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
       </c>
       <c r="E146" t="str">
         <v>Completed</v>
@@ -3779,10 +3779,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C147" t="str">
-        <v>Audit log and activity</v>
+        <v>Dispatch reports</v>
       </c>
       <c r="D147" t="str">
-        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
+        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
       </c>
       <c r="E147" t="str">
         <v>Completed</v>
@@ -3791,7 +3791,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G147" t="str">
-        <v/>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="148">
@@ -3802,10 +3802,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C148" t="str">
-        <v>Dashboard</v>
+        <v>Audit log and activity</v>
       </c>
       <c r="D148" t="str">
-        <v>Headline numbers.</v>
+        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
       </c>
       <c r="E148" t="str">
         <v>Completed</v>
@@ -3825,19 +3825,19 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C149" t="str">
-        <v>Warehouse Stock report</v>
+        <v>Dashboard</v>
       </c>
       <c r="D149" t="str">
-        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
+        <v>Headline numbers.</v>
       </c>
       <c r="E149" t="str">
         <v>Completed</v>
       </c>
       <c r="F149" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G149" t="str">
-        <v>CR-331</v>
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -3845,22 +3845,22 @@
         <v>149</v>
       </c>
       <c r="B150" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C150" t="str">
-        <v>Panel Master</v>
+        <v>Warehouse Stock report</v>
       </c>
       <c r="D150" t="str">
-        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
+        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
       </c>
       <c r="E150" t="str">
         <v>Completed</v>
       </c>
       <c r="F150" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G150" t="str">
-        <v>CR-283…285, 291, 319</v>
+        <v>CR-331</v>
       </c>
     </row>
     <row r="151">
@@ -3871,19 +3871,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C151" t="str">
-        <v>Panel form opens with a blank size</v>
+        <v>Panel Master</v>
       </c>
       <c r="D151" t="str">
-        <v>New Panel no longer prefills 1200x2100; the size is typed.</v>
+        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
       </c>
       <c r="E151" t="str">
         <v>Completed</v>
       </c>
       <c r="F151" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G151" t="str">
-        <v>CR-484</v>
+        <v>CR-283…285, 291, 319</v>
       </c>
     </row>
     <row r="152">
@@ -3894,10 +3894,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C152" t="str">
-        <v>Sample order Actions tab</v>
+        <v>Panel form opens with a blank size</v>
       </c>
       <c r="D152" t="str">
-        <v>A sample order has the panel order's tabs (Details · Readiness · Actions · Dispatch · Activity). Loads are recorded on the Actions tab — quantity per row, + Load… on one row, Dispatch, Load Copy per trip — the header Record Load button is gone.</v>
+        <v>New Panel no longer prefills 1200x2100; the size is typed.</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
@@ -3906,7 +3906,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-485</v>
+        <v>CR-484</v>
       </c>
     </row>
     <row r="153">
@@ -3917,10 +3917,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C153" t="str">
-        <v>Sample order pick slip</v>
+        <v>Sample order Actions tab</v>
       </c>
       <c r="D153" t="str">
-        <v>More ▸ Print order PDF on a sample order: every item with its photo, name and item code, full tile / cut piece size, Requested · Supplied · Remaining, the remark typed on the line and an empty Broken / Adjustment box to fill in by hand; the Stock Adjustments reminder and Taken out by / Checked by lines.</v>
+        <v>A sample order has the panel order's tabs (Details · Readiness · Actions · Dispatch · Activity). Loads are recorded on the Actions tab — quantity per row, + Load… on one row, Dispatch, Load Copy per trip — the header Record Load button is gone.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
@@ -3929,7 +3929,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-486</v>
+        <v>CR-485</v>
       </c>
     </row>
     <row r="154">
@@ -3940,10 +3940,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C154" t="str">
-        <v>Allocate Stock on sample orders</v>
+        <v>Sample order pick slip</v>
       </c>
       <c r="D154" t="str">
-        <v>A sample order books cut pieces the way a panel order does: Requirements card on its Actions tab (Need · In Stock · Allocated · Short) and the same Allocate Stock window; a cut-piece row loads only once booked, the load consumes the booking; panel and sample bookings share one pool so no piece is promised twice; Pending Cut Stock counts sample demand.</v>
+        <v>More ▸ Print order PDF on a sample order: every item with its photo, name and item code, full tile / cut piece size, Requested · Supplied · Remaining, the remark typed on the line and an empty Broken / Adjustment box to fill in by hand; the Stock Adjustments reminder and Taken out by / Checked by lines.</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
@@ -3952,7 +3952,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-487</v>
+        <v>CR-486</v>
       </c>
     </row>
     <row r="155">
@@ -3963,10 +3963,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C155" t="str">
-        <v>Full-tile samples book the sample stock</v>
+        <v>Allocate Stock on sample orders</v>
       </c>
       <c r="D155" t="str">
-        <v>A sample order's full-tile line books the item's full-size piece on Cut Stock — the separately managed sample stock — in pieces, from the same Allocate Stock window as its cut pieces (no batch picker; export box stock is never touched); the load is refused until booked and takes the pieces out of Cut Stock. The sample order form lists panel items only.</v>
+        <v>A sample order books cut pieces the way a panel order does: Requirements card on its Actions tab (Need · In Stock · Allocated · Short) and the same Allocate Stock window; a cut-piece row loads only once booked, the load consumes the booking; panel and sample bookings share one pool so no piece is promised twice; Pending Cut Stock counts sample demand.</v>
       </c>
       <c r="E155" t="str">
         <v>Completed</v>
@@ -3975,7 +3975,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G155" t="str">
-        <v>CR-489 (replaces CR-488)</v>
+        <v>CR-487</v>
       </c>
     </row>
     <row r="156">
@@ -3986,19 +3986,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C156" t="str">
-        <v>Remarks on a panel</v>
+        <v>Full-tile samples book the sample stock</v>
       </c>
       <c r="D156" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>A sample order's full-tile line books the item's full-size piece on Cut Stock — the separately managed sample stock — in pieces, from the same Allocate Stock window as its cut pieces (no batch picker; export box stock is never touched); the load is refused until booked and takes the pieces out of Cut Stock. The sample order form lists panel items only.</v>
       </c>
       <c r="E156" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F156" t="str">
-        <v/>
+        <v>2026-10-28</v>
       </c>
       <c r="G156" t="str">
-        <v>CR-425</v>
+        <v>CR-489 (replaces CR-488)</v>
       </c>
     </row>
     <row r="157">
@@ -4009,10 +4009,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C157" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D157" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E157" t="str">
         <v>In progress</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="G157" t="str">
-        <v>CR-426</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="158">
@@ -4029,13 +4029,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C158" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D158" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E158" t="str">
         <v>In progress</v>
@@ -4044,7 +4044,7 @@
         <v/>
       </c>
       <c r="G158" t="str">
-        <v>CR-427</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="159">
@@ -4052,22 +4052,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C159" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D159" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E159" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F159" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G159" t="str">
-        <v>CR-428</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="160">
@@ -4078,10 +4078,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C160" t="str">
-        <v>One Masters page</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D160" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E160" t="str">
         <v>Completed</v>
@@ -4090,7 +4090,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G160" t="str">
-        <v>CR-436</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="161">
@@ -4101,10 +4101,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C161" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>One Masters page</v>
       </c>
       <c r="D161" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
@@ -4113,7 +4113,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-439</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="162">
@@ -4124,10 +4124,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C162" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D162" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E162" t="str">
         <v>Completed</v>
@@ -4136,7 +4136,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-440</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="163">
@@ -4144,13 +4144,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="str">
-        <v>Items</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C163" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D163" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E163" t="str">
         <v>Completed</v>
@@ -4159,7 +4159,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G163" t="str">
-        <v>CR-437</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="164">
@@ -4167,22 +4167,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Items</v>
       </c>
       <c r="C164" t="str">
-        <v>Names save as Title Case</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D164" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E164" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F164" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G164" t="str">
-        <v>CR-429</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="165">
@@ -4190,13 +4190,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C165" t="str">
-        <v>Brand off the Item form</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D165" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E165" t="str">
         <v>In progress</v>
@@ -4205,7 +4205,7 @@
         <v/>
       </c>
       <c r="G165" t="str">
-        <v>CR-430</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="166">
@@ -4213,22 +4213,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C166" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D166" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E166" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F166" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G166" t="str">
-        <v>CR-306</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="167">
@@ -4239,19 +4239,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C167" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D167" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E167" t="str">
         <v>Completed</v>
       </c>
       <c r="F167" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G167" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="168">
@@ -4262,10 +4262,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>MDF master</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D168" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E168" t="str">
         <v>Completed</v>
@@ -4274,7 +4274,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G168" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="169">
@@ -4285,19 +4285,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>MDF master</v>
       </c>
       <c r="D169" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E169" t="str">
         <v>Completed</v>
       </c>
       <c r="F169" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G169" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="170">
@@ -4308,19 +4308,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D170" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E170" t="str">
         <v>Completed</v>
       </c>
       <c r="F170" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G170" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="171">
@@ -4331,19 +4331,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D171" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E171" t="str">
         <v>Completed</v>
       </c>
       <c r="F171" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G171" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="172">
@@ -4354,19 +4354,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D172" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E172" t="str">
         <v>Completed</v>
       </c>
       <c r="F172" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G172" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="173">
@@ -4377,19 +4377,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>Production checkpoints</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D173" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E173" t="str">
         <v>Completed</v>
       </c>
       <c r="F173" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G173" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="174">
@@ -4400,10 +4400,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D174" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E174" t="str">
         <v>Completed</v>
@@ -4412,7 +4412,7 @@
         <v>2026-10-09</v>
       </c>
       <c r="G174" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="175">
@@ -4423,19 +4423,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C175" t="str">
-        <v>Sample Orders</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D175" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E175" t="str">
         <v>Completed</v>
       </c>
       <c r="F175" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G175" t="str">
-        <v>CR-315…317</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="176">
@@ -4446,19 +4446,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C176" t="str">
-        <v>One Orders register</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D176" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E176" t="str">
         <v>Completed</v>
       </c>
       <c r="F176" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G176" t="str">
-        <v>CR-345</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="177">
@@ -4469,10 +4469,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C177" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>One Orders register</v>
       </c>
       <c r="D177" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E177" t="str">
         <v>Completed</v>
@@ -4481,7 +4481,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G177" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="178">
@@ -4492,10 +4492,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C178" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D178" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E178" t="str">
         <v>Completed</v>
@@ -4504,7 +4504,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G178" t="str">
-        <v>CR-349</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="179">
@@ -4515,19 +4515,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C179" t="str">
-        <v>Load Copy print</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D179" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E179" t="str">
         <v>Completed</v>
       </c>
       <c r="F179" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G179" t="str">
-        <v>CR-351</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="180">
@@ -4538,19 +4538,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C180" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D180" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E180" t="str">
         <v>Completed</v>
       </c>
       <c r="F180" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G180" t="str">
-        <v>CR-433</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="181">
@@ -4561,19 +4561,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C181" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D181" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E181" t="str">
         <v>Completed</v>
       </c>
       <c r="F181" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G181" t="str">
-        <v>CR-311</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="182">
@@ -4584,19 +4584,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C182" t="str">
-        <v>Small UX items</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D182" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E182" t="str">
         <v>Completed</v>
       </c>
       <c r="F182" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="183">
@@ -4607,19 +4607,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C183" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>Small UX items</v>
       </c>
       <c r="D183" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E183" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F183" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-365</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="184">
@@ -4630,10 +4630,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D184" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E184" t="str">
         <v>In progress</v>
@@ -4642,7 +4642,7 @@
         <v/>
       </c>
       <c r="G184" t="str">
-        <v>CR-366</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="185">
@@ -4653,10 +4653,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>One Status column</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D185" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E185" t="str">
         <v>In progress</v>
@@ -4665,7 +4665,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>CR-367</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="186">
@@ -4676,10 +4676,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>One Status column</v>
       </c>
       <c r="D186" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E186" t="str">
         <v>In progress</v>
@@ -4688,7 +4688,7 @@
         <v/>
       </c>
       <c r="G186" t="str">
-        <v>CR-368</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="187">
@@ -4699,10 +4699,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C187" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D187" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E187" t="str">
         <v>In progress</v>
@@ -4711,7 +4711,7 @@
         <v/>
       </c>
       <c r="G187" t="str">
-        <v>CR-399</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="188">
@@ -4722,10 +4722,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C188" t="str">
-        <v>One four-state order status</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D188" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E188" t="str">
         <v>In progress</v>
@@ -4734,7 +4734,7 @@
         <v/>
       </c>
       <c r="G188" t="str">
-        <v>CR-400</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="189">
@@ -4745,10 +4745,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C189" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D189" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E189" t="str">
         <v>In progress</v>
@@ -4757,7 +4757,7 @@
         <v/>
       </c>
       <c r="G189" t="str">
-        <v>CR-401</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="190">
@@ -4768,10 +4768,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C190" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D190" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E190" t="str">
         <v>In progress</v>
@@ -4780,7 +4780,7 @@
         <v/>
       </c>
       <c r="G190" t="str">
-        <v>CR-402</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="191">
@@ -4791,10 +4791,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C191" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D191" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E191" t="str">
         <v>In progress</v>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="G191" t="str">
-        <v>CR-403</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="192">
@@ -4814,10 +4814,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C192" t="str">
-        <v>Load part of a panel</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D192" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E192" t="str">
         <v>In progress</v>
@@ -4826,7 +4826,7 @@
         <v/>
       </c>
       <c r="G192" t="str">
-        <v>CR-405</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="193">
@@ -4837,10 +4837,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C193" t="str">
-        <v>MDF row on every panel</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D193" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E193" t="str">
         <v>In progress</v>
@@ -4849,7 +4849,7 @@
         <v/>
       </c>
       <c r="G193" t="str">
-        <v>CR-406</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="194">
@@ -4860,10 +4860,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C194" t="str">
-        <v>Load whole panel in one click</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D194" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E194" t="str">
         <v>In progress</v>
@@ -4872,7 +4872,7 @@
         <v/>
       </c>
       <c r="G194" t="str">
-        <v>CR-407</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="195">
@@ -4880,22 +4880,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C195" t="str">
-        <v>Settings search everywhere</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D195" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E195" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F195" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G195" t="str">
-        <v>CR-408</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="196">
@@ -4903,13 +4903,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C196" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D196" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E196" t="str">
         <v>Completed</v>
@@ -4918,7 +4918,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G196" t="str">
-        <v>CR-409</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="197">
@@ -4929,10 +4929,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C197" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D197" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
@@ -4941,7 +4941,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-438</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="198">
@@ -4949,22 +4949,22 @@
         <v>197</v>
       </c>
       <c r="B198" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C198" t="str">
-        <v>Stock adjustment as a line form</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D198" t="str">
-        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
       </c>
       <c r="F198" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-446</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="199">
@@ -4975,19 +4975,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C199" t="str">
-        <v>Adjust Stock in the Zoho Books shape</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D199" t="str">
-        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E199" t="str">
         <v>Completed</v>
       </c>
       <c r="F199" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-457</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="200">
@@ -4998,10 +4998,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C200" t="str">
-        <v>Location Transfer from the Adjust Stock screen</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D200" t="str">
-        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
@@ -5010,7 +5010,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G200" t="str">
-        <v>CR-458</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="201">
@@ -5021,10 +5021,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C201" t="str">
-        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D201" t="str">
-        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E201" t="str">
         <v>Completed</v>
@@ -5033,7 +5033,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G201" t="str">
-        <v>CR-459</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="202">
@@ -5044,10 +5044,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C202" t="str">
-        <v>Cut Piece detail page inside Panel Craft</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D202" t="str">
-        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E202" t="str">
         <v>Completed</v>
@@ -5056,7 +5056,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G202" t="str">
-        <v>CR-460/461</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="203">
@@ -5064,22 +5064,22 @@
         <v>202</v>
       </c>
       <c r="B203" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C203" t="str">
-        <v>Pager with First / Last arrows</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D203" t="str">
-        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E203" t="str">
         <v>Completed</v>
       </c>
       <c r="F203" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G203" t="str">
-        <v>CR-467</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="204">
@@ -5090,10 +5090,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C204" t="str">
-        <v>Red close × on every window</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D204" t="str">
-        <v>The × that closes any window or drawer is red on every screen.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E204" t="str">
         <v>Completed</v>
@@ -5102,7 +5102,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G204" t="str">
-        <v>CR-465</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="205">
@@ -5113,10 +5113,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C205" t="str">
-        <v>Advanced search date range fits the window</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D205" t="str">
-        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E205" t="str">
         <v>Completed</v>
@@ -5125,7 +5125,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G205" t="str">
-        <v>CR-464</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="206">
@@ -5133,13 +5133,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="str">
-        <v>Customers</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C206" t="str">
-        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D206" t="str">
-        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
@@ -5148,7 +5148,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G206" t="str">
-        <v>CR-463/466</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="207">
@@ -5156,22 +5156,22 @@
         <v>206</v>
       </c>
       <c r="B207" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Customers</v>
       </c>
       <c r="C207" t="str">
-        <v>Stock history in date order</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D207" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
       </c>
       <c r="F207" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G207" t="str">
-        <v>CR-455</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="208">
@@ -5179,22 +5179,22 @@
         <v>207</v>
       </c>
       <c r="B208" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C208" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D208" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E208" t="str">
         <v>Completed</v>
       </c>
       <c r="F208" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G208" t="str">
-        <v>CR-447</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="209">
@@ -5202,13 +5202,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C209" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D209" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E209" t="str">
         <v>Completed</v>
@@ -5217,7 +5217,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G209" t="str">
-        <v>CR-448</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="210">
@@ -5228,19 +5228,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C210" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D210" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
       </c>
       <c r="F210" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G210" t="str">
-        <v>CR-456</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="211">
@@ -5251,19 +5251,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C211" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D211" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
       </c>
       <c r="F211" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G211" t="str">
-        <v>CR-449</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="212">
@@ -5274,10 +5274,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C212" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D212" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
@@ -5286,7 +5286,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G212" t="str">
-        <v>CR-450</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="213">
@@ -5294,22 +5294,22 @@
         <v>212</v>
       </c>
       <c r="B213" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C213" t="str">
-        <v>Location at every stage</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D213" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
       </c>
       <c r="F213" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-411…413</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="214">
@@ -5317,13 +5317,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C214" t="str">
-        <v>Panel location</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D214" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E214" t="str">
         <v>Completed</v>
@@ -5332,7 +5332,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G214" t="str">
-        <v>CR-410</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="215">
@@ -5343,10 +5343,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C215" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel location</v>
       </c>
       <c r="D215" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E215" t="str">
         <v>Completed</v>
@@ -5355,7 +5355,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G215" t="str">
-        <v>CR-419</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="216">
@@ -5366,10 +5366,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C216" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D216" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E216" t="str">
         <v>Completed</v>
@@ -5378,7 +5378,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G216" t="str">
-        <v>CR-415</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="217">
@@ -5386,13 +5386,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C217" t="str">
-        <v>No long helper notes</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D217" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E217" t="str">
         <v>Completed</v>
@@ -5401,7 +5401,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G217" t="str">
-        <v>CR-416</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="218">
@@ -5409,13 +5409,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="str">
-        <v>Production</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C218" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D218" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E218" t="str">
         <v>Completed</v>
@@ -5424,7 +5424,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G218" t="str">
-        <v>CR-417</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="219">
@@ -5432,13 +5432,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Production</v>
       </c>
       <c r="C219" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D219" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E219" t="str">
         <v>Completed</v>
@@ -5447,7 +5447,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G219" t="str">
-        <v>CR-418</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="220">
@@ -5458,10 +5458,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C220" t="str">
-        <v>Notifications read / unread</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D220" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E220" t="str">
         <v>Completed</v>
@@ -5470,7 +5470,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G220" t="str">
-        <v>CR-419…421</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="221">
@@ -5478,13 +5478,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C221" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D221" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E221" t="str">
         <v>Completed</v>
@@ -5493,7 +5493,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G221" t="str">
-        <v>CR-422</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="222">
@@ -5501,22 +5501,22 @@
         <v>221</v>
       </c>
       <c r="B222" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C222" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D222" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E222" t="str">
         <v>Completed</v>
       </c>
       <c r="F222" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G222" t="str">
-        <v>CR-404</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="223">
@@ -5527,19 +5527,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C223" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D223" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E223" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F223" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G223" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="224">
@@ -5550,19 +5550,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C224" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D224" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E224" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F224" t="str">
         <v/>
       </c>
       <c r="G224" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="225">
@@ -5573,10 +5573,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C225" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D225" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E225" t="str">
         <v>Future</v>
@@ -5585,7 +5585,7 @@
         <v/>
       </c>
       <c r="G225" t="str">
-        <v>Panel Craft list #2</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="226">
@@ -5596,10 +5596,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C226" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D226" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E226" t="str">
         <v>Future</v>
@@ -5608,7 +5608,7 @@
         <v/>
       </c>
       <c r="G226" t="str">
-        <v>Panel Craft list #4</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="227">
@@ -5619,10 +5619,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C227" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D227" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E227" t="str">
         <v>Future</v>
@@ -5631,7 +5631,7 @@
         <v/>
       </c>
       <c r="G227" t="str">
-        <v>Panel Craft list #5</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="228">
@@ -5642,10 +5642,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C228" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D228" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E228" t="str">
         <v>Future</v>
@@ -5654,7 +5654,7 @@
         <v/>
       </c>
       <c r="G228" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="229">
@@ -5665,10 +5665,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C229" t="str">
-        <v>Bill / expense</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D229" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E229" t="str">
         <v>Future</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="G229" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="230">
@@ -5685,22 +5685,22 @@
         <v>229</v>
       </c>
       <c r="B230" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C230" t="str">
-        <v>Item code for the catalog</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D230" t="str">
-        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E230" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F230" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G230" t="str">
-        <v>CR-473</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="231">
@@ -5708,13 +5708,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C231" t="str">
-        <v>Panel Order PDF — one page per panel</v>
+        <v>Item code for the catalog</v>
       </c>
       <c r="D231" t="str">
-        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
+        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
       </c>
       <c r="E231" t="str">
         <v>Completed</v>
@@ -5723,7 +5723,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G231" t="str">
-        <v>CR-474</v>
+        <v>CR-473</v>
       </c>
     </row>
     <row r="232">
@@ -5731,22 +5731,22 @@
         <v>231</v>
       </c>
       <c r="B232" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C232" t="str">
-        <v>Sales Order without a Location field</v>
+        <v>Panel Craft pricing</v>
       </c>
       <c r="D232" t="str">
-        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
+        <v>Every panel is priced from three parts — Vinyl (vinyl size sqft × the panel's vinyl rate per sqft), MDF (board weight × the MDF rate per kg) and Cut pieces (each piece's sqft × the item's rate per sqft). Worked out when the order is saved and frozen on the order, each part editable; sample orders priced by piece size. Prices show on the panel order page and PDF, the sample order, the Orders list (Amount), the panel master's Pricing tab and every cut piece (sqft and price per piece).</v>
       </c>
       <c r="E232" t="str">
         <v>Completed</v>
       </c>
       <c r="F232" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G232" t="str">
-        <v>CR-468</v>
+        <v>CR-504</v>
       </c>
     </row>
     <row r="233">
@@ -5754,22 +5754,22 @@
         <v>232</v>
       </c>
       <c r="B233" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C233" t="str">
-        <v>Box Brand mandatory</v>
+        <v>Your own Panel Codes</v>
       </c>
       <c r="D233" t="str">
-        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
+        <v>Type the panel's code on New / Edit Panel (mandatory, saved in capitals, no duplicates) instead of an automatic PANEL-001 number; rename an old panel and every order, load and print shows the new code.</v>
       </c>
       <c r="E233" t="str">
         <v>Completed</v>
       </c>
       <c r="F233" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G233" t="str">
-        <v>CR-483</v>
+        <v>CR-506</v>
       </c>
     </row>
     <row r="234">
@@ -5777,22 +5777,22 @@
         <v>233</v>
       </c>
       <c r="B234" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C234" t="str">
-        <v>Pallet form without Box Weight</v>
+        <v>Bulk Update of rates</v>
       </c>
       <c r="D234" t="str">
-        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
+        <v>Filter the list, tick the rows, Bulk Update, pick the field, type the value — one save sets Rate / sqft on many Panel Items (new filter by size, finish, brand, category, rate, stock), Vinyl Rate on many panels, Rate/kg on MDF rows. The Item master's bulk edit works the same way, now with Rate / sqft.</v>
       </c>
       <c r="E234" t="str">
         <v>Completed</v>
       </c>
       <c r="F234" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G234" t="str">
-        <v>CR-471</v>
+        <v>CR-505</v>
       </c>
     </row>
     <row r="235">
@@ -5803,19 +5803,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C235" t="str">
-        <v>Boffo / Bonza company separation</v>
+        <v>Panel Order PDF — one page per panel</v>
       </c>
       <c r="D235" t="str">
-        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
+        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
       </c>
       <c r="E235" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F235" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
       <c r="G235" t="str">
-        <v>ON-HOLD #1</v>
+        <v>CR-474</v>
       </c>
     </row>
     <row r="236">
@@ -5823,22 +5823,22 @@
         <v>235</v>
       </c>
       <c r="B236" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C236" t="str">
-        <v>System reference and change-request register</v>
+        <v>Sales Order without a Location field</v>
       </c>
       <c r="D236" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
       </c>
       <c r="E236" t="str">
         <v>Completed</v>
       </c>
       <c r="F236" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G236" t="str">
-        <v/>
+        <v>CR-468</v>
       </c>
     </row>
     <row r="237">
@@ -5846,22 +5846,22 @@
         <v>236</v>
       </c>
       <c r="B237" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C237" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>Box Brand mandatory</v>
       </c>
       <c r="D237" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
       </c>
       <c r="E237" t="str">
         <v>Completed</v>
       </c>
       <c r="F237" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G237" t="str">
-        <v/>
+        <v>CR-483</v>
       </c>
     </row>
     <row r="238">
@@ -5869,22 +5869,22 @@
         <v>237</v>
       </c>
       <c r="B238" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C238" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>One line per item</v>
       </c>
       <c r="D238" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>Adding an item that is already on the quote or order shows a warning; on save the quantities merge into one line when the rate is the same (a different rate keeps two lines).</v>
       </c>
       <c r="E238" t="str">
         <v>Completed</v>
       </c>
       <c r="F238" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G238" t="str">
-        <v/>
+        <v>CR-507</v>
       </c>
     </row>
     <row r="239">
@@ -5892,22 +5892,22 @@
         <v>238</v>
       </c>
       <c r="B239" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C239" t="str">
-        <v>Data Flow reference</v>
+        <v>Box Brand per line</v>
       </c>
       <c r="D239" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Each Sales Order line has its own Box Brand (prefilled from the customer, the quote or the line above) instead of one for the whole order; shown per line on the order page and on the Production list, sheet and production page.</v>
       </c>
       <c r="E239" t="str">
         <v>Completed</v>
       </c>
       <c r="F239" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G239" t="str">
-        <v>CR-272</v>
+        <v>CR-508</v>
       </c>
     </row>
     <row r="240">
@@ -5915,22 +5915,22 @@
         <v>239</v>
       </c>
       <c r="B240" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C240" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Allocate Stock by Box Brand</v>
       </c>
       <c r="D240" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>Allocate Stock offers only batches packed in the line's Box Brand and says how many boxes in other brands were left out.</v>
       </c>
       <c r="E240" t="str">
         <v>Completed</v>
       </c>
       <c r="F240" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G240" t="str">
-        <v/>
+        <v>CR-509</v>
       </c>
     </row>
     <row r="241">
@@ -5938,22 +5938,22 @@
         <v>240</v>
       </c>
       <c r="B241" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C241" t="str">
-        <v>Locations guide</v>
+        <v>Pallet form without Box Weight</v>
       </c>
       <c r="D241" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
       </c>
       <c r="E241" t="str">
         <v>Completed</v>
       </c>
       <c r="F241" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G241" t="str">
-        <v>CR-411…413</v>
+        <v>CR-471</v>
       </c>
     </row>
     <row r="242">
@@ -5961,22 +5961,22 @@
         <v>241</v>
       </c>
       <c r="B242" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C242" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Boffo / Bonza company separation</v>
       </c>
       <c r="D242" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
       </c>
       <c r="E242" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F242" t="str">
-        <v>2026-10-22</v>
+        <v/>
       </c>
       <c r="G242" t="str">
-        <v/>
+        <v>ON-HOLD #1</v>
       </c>
     </row>
     <row r="243">
@@ -5987,19 +5987,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C243" t="str">
-        <v>Demo / test environment</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D243" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E243" t="str">
         <v>Completed</v>
       </c>
       <c r="F243" t="str">
-        <v>2026-10-25</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G243" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -6010,25 +6010,186 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C244" t="str">
+        <v>Change log, user flow, user manual</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+      </c>
+      <c r="E244" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Seed and teardown scripts</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+      </c>
+      <c r="E245" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F245" t="str">
+        <v>Phase 1 (by 01-Oct-2026)</v>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Data Flow reference</v>
+      </c>
+      <c r="D246" t="str">
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+      </c>
+      <c r="E246" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F246" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G246" t="str">
+        <v>CR-272</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Phase 2 inventory</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+      </c>
+      <c r="E247" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F247" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Locations guide</v>
+      </c>
+      <c r="D248" t="str">
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+      </c>
+      <c r="E248" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F248" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="G248" t="str">
+        <v>CR-411…413</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Deliverables list (this workbook)</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+      </c>
+      <c r="E249" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F249" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D250" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E250" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F250" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G250" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C251" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D244" t="str">
+      <c r="D251" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E244" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F244" t="str">
+      <c r="E251" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F251" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G244" t="str">
+      <c r="G251" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G244"/>
+  <autoFilter ref="A1:G251"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G244"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G251"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deliverables'!A1:G252</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G252"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3020,19 +3020,19 @@
         <v>Palletization</v>
       </c>
       <c r="C114" t="str">
-        <v>Discard the current palletization task</v>
+        <v>In Palletization columns</v>
       </c>
       <c r="D114" t="str">
-        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
+        <v>In Palletization shows Boxes (on the row), Boxes per Pallet, Pallets (whole pallets those boxes fill) and Prepared; the Pending and Loose columns are gone from that page.</v>
       </c>
       <c r="E114" t="str">
         <v>Completed</v>
       </c>
       <c r="F114" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G114" t="str">
-        <v>CR-369</v>
+        <v>CR-510</v>
       </c>
     </row>
     <row r="115">
@@ -3043,19 +3043,19 @@
         <v>Palletization</v>
       </c>
       <c r="C115" t="str">
-        <v>Delete a plan returns its boxes</v>
+        <v>Discard the current palletization task</v>
       </c>
       <c r="D115" t="str">
-        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
+        <v>+ menu on Ready for / In Palletization: boxes + reason; boxes return to free stock and the allocation is returned. Reason required for every role.</v>
       </c>
       <c r="E115" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F115" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G115" t="str">
-        <v>CR-370</v>
+        <v>CR-369</v>
       </c>
     </row>
     <row r="116">
@@ -3066,19 +3066,19 @@
         <v>Palletization</v>
       </c>
       <c r="C116" t="str">
-        <v>Partial Start Palletization</v>
+        <v>Delete a plan returns its boxes</v>
       </c>
       <c r="D116" t="str">
-        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
+        <v>Deleting a palletization returns every line to free stock first; refused while any box sits in a container.</v>
       </c>
       <c r="E116" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F116" t="str">
         <v/>
       </c>
       <c r="G116" t="str">
-        <v>Panel Craft list #9</v>
+        <v>CR-370</v>
       </c>
     </row>
     <row r="117">
@@ -3089,10 +3089,10 @@
         <v>Palletization</v>
       </c>
       <c r="C117" t="str">
-        <v>Ready pallets — type and pallet count</v>
+        <v>Partial Start Palletization</v>
       </c>
       <c r="D117" t="str">
-        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
+        <v>Start only part of a Ready row (today Start takes the whole line; partial is on Complete).</v>
       </c>
       <c r="E117" t="str">
         <v>Future</v>
@@ -3101,7 +3101,7 @@
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>Panel Craft list #7</v>
+        <v>Panel Craft list #9</v>
       </c>
     </row>
     <row r="118">
@@ -3112,10 +3112,10 @@
         <v>Palletization</v>
       </c>
       <c r="C118" t="str">
-        <v>Remove 'Ordered / Completed' where not needed</v>
+        <v>Ready pallets — type and pallet count</v>
       </c>
       <c r="D118" t="str">
-        <v>Screen to be confirmed.</v>
+        <v>Show pallet type and count per ready row / print. To be confirmed against what CR-279 already shows.</v>
       </c>
       <c r="E118" t="str">
         <v>Future</v>
@@ -3124,7 +3124,7 @@
         <v/>
       </c>
       <c r="G118" t="str">
-        <v>Panel Craft list #8</v>
+        <v>Panel Craft list #7</v>
       </c>
     </row>
     <row r="119">
@@ -3132,22 +3132,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>Loading &amp; Dispatch</v>
+        <v>Palletization</v>
       </c>
       <c r="C119" t="str">
-        <v>A loading = one container</v>
+        <v>Remove 'Ordered / Completed' where not needed</v>
       </c>
       <c r="D119" t="str">
-        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
+        <v>Screen to be confirmed.</v>
       </c>
       <c r="E119" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F119" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G119" t="str">
-        <v>CR-120…124</v>
+        <v>Panel Craft list #8</v>
       </c>
     </row>
     <row r="120">
@@ -3158,10 +3158,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C120" t="str">
-        <v>Loading and Dispatch page</v>
+        <v>A loading = one container</v>
       </c>
       <c r="D120" t="str">
-        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
+        <v>Numbered LOAD/FY/NNN; a multi-container plan groups its containers.</v>
       </c>
       <c r="E120" t="str">
         <v>Completed</v>
@@ -3170,7 +3170,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G120" t="str">
-        <v>CR-140, 141</v>
+        <v>CR-120…124</v>
       </c>
     </row>
     <row r="121">
@@ -3181,10 +3181,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C121" t="str">
-        <v>Loading detail</v>
+        <v>Loading and Dispatch page</v>
       </c>
       <c r="D121" t="str">
-        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
+        <v>Sheet with derived stages Ready for Loading → In Loading → Ready for Dispatch → Dispatched; Loadings grid (one row per container); Customer Sheet (every loaded line of one customer, export style).</v>
       </c>
       <c r="E121" t="str">
         <v>Completed</v>
@@ -3193,7 +3193,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G121" t="str">
-        <v/>
+        <v>CR-140, 141</v>
       </c>
     </row>
     <row r="122">
@@ -3204,10 +3204,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C122" t="str">
-        <v>Vehicle and shipment details</v>
+        <v>Loading detail</v>
       </c>
       <c r="D122" t="str">
-        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
+        <v>Loaded Items (Mix Batch pallets as a tree), Loading Sheet tab (export-style ruled sheet, editable in place), Container Planning tab, Activity.</v>
       </c>
       <c r="E122" t="str">
         <v>Completed</v>
@@ -3227,10 +3227,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C123" t="str">
-        <v>Dispatch with gates and warnings</v>
+        <v>Vehicle and shipment details</v>
       </c>
       <c r="D123" t="str">
-        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
+        <v>Vehicle number (auto-formatted), driver, mobile, transporter, LR number, destination, supervisor, container size / number, seals; Vehicle master updates itself.</v>
       </c>
       <c r="E123" t="str">
         <v>Completed</v>
@@ -3250,10 +3250,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C124" t="str">
-        <v>Invoice and dispatch prints</v>
+        <v>Dispatch with gates and warnings</v>
       </c>
       <c r="D124" t="str">
-        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
+        <v>Dispatch always on the menu, greyed with the reason when it cannot run; blank seals / LR / transporter warn; duplicate seal or container numbers warn; dispatch events show on the order and the plan.</v>
       </c>
       <c r="E124" t="str">
         <v>Completed</v>
@@ -3273,10 +3273,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C125" t="str">
-        <v>Four ways to fill a container</v>
+        <v>Invoice and dispatch prints</v>
       </c>
       <c r="D125" t="str">
-        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
+        <v>Invoice per container (PDF); Dispatch Entry and Dispatch Copy with design names and pallet numbers.</v>
       </c>
       <c r="E125" t="str">
         <v>Completed</v>
@@ -3285,7 +3285,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G125" t="str">
-        <v>CR-126…128, 201/202</v>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3296,10 +3296,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C126" t="str">
-        <v>Editing a loading</v>
+        <v>Four ways to fill a container</v>
       </c>
       <c r="D126" t="str">
-        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
+        <v>New Loading page (batch picker chooses pallets + loose boxes, Fill from plan); Load from the palletization board; New Loading from a sales order; Send to Loading from an order.</v>
       </c>
       <c r="E126" t="str">
         <v>Completed</v>
@@ -3308,7 +3308,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G126" t="str">
-        <v/>
+        <v>CR-126…128, 201/202</v>
       </c>
     </row>
     <row r="127">
@@ -3319,19 +3319,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C127" t="str">
-        <v>Date column, LOAD code hidden</v>
+        <v>Editing a loading</v>
       </c>
       <c r="D127" t="str">
-        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
+        <v>Reduce loaded quantities (rest returns to Ready for Loading), remove lines, add pallets, complete details; Sheet edit mode for loaded qty / move / unload.</v>
       </c>
       <c r="E127" t="str">
         <v>Completed</v>
       </c>
       <c r="F127" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G127" t="str">
-        <v>CR-266</v>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -3342,19 +3342,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C128" t="str">
-        <v>Several containers in one New Loading</v>
+        <v>Date column, LOAD code hidden</v>
       </c>
       <c r="D128" t="str">
-        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
+        <v>Sheet and Loadings grid show the loading date; LOAD code in the column picker.</v>
       </c>
       <c r="E128" t="str">
         <v>Completed</v>
       </c>
       <c r="F128" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G128" t="str">
-        <v>CR-301</v>
+        <v>CR-266</v>
       </c>
     </row>
     <row r="129">
@@ -3365,19 +3365,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C129" t="str">
-        <v>Loading Workspace — a tab per container</v>
+        <v>Several containers in one New Loading</v>
       </c>
       <c r="D129" t="str">
-        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
+        <v>One section per container, each with its own Container Master pick, item rows and vehicle; stock shared across sections; one Save creates the linked loadings.</v>
       </c>
       <c r="E129" t="str">
         <v>Completed</v>
       </c>
       <c r="F129" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G129" t="str">
-        <v>CR-326, 334, 335</v>
+        <v>CR-301</v>
       </c>
     </row>
     <row r="130">
@@ -3388,10 +3388,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C130" t="str">
-        <v>Every customer listed, with search</v>
+        <v>Loading Workspace — a tab per container</v>
       </c>
       <c r="D130" t="str">
-        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
+        <v>New Loading and Edit are one page: each container a tab with a plain sheet and its own vehicle &amp; seals rail; Dispatch and documents per tab; Tabs | Sheet toggle shows every container on one grid.</v>
       </c>
       <c r="E130" t="str">
         <v>Completed</v>
@@ -3400,7 +3400,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G130" t="str">
-        <v>CR-327</v>
+        <v>CR-326, 334, 335</v>
       </c>
     </row>
     <row r="131">
@@ -3411,10 +3411,10 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C131" t="str">
-        <v>'What to do first' reasons</v>
+        <v>Every customer listed, with search</v>
       </c>
       <c r="D131" t="str">
-        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
+        <v>Loading and Palletization list all active customers (stock-bearing first) with the search modal.</v>
       </c>
       <c r="E131" t="str">
         <v>Completed</v>
@@ -3423,7 +3423,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G131" t="str">
-        <v>CR-328</v>
+        <v>CR-327</v>
       </c>
     </row>
     <row r="132">
@@ -3434,19 +3434,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C132" t="str">
-        <v>Pick the planned container at loading</v>
+        <v>'What to do first' reasons</v>
       </c>
       <c r="D132" t="str">
-        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
+        <v>A customer or order that cannot be loaded / palletized shows why and the next step; Sales Order detail shows a Next: line.</v>
       </c>
       <c r="E132" t="str">
         <v>Completed</v>
       </c>
       <c r="F132" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G132" t="str">
-        <v>CR-338</v>
+        <v>CR-328</v>
       </c>
     </row>
     <row r="133">
@@ -3457,19 +3457,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C133" t="str">
-        <v>Two steps per container; C1 / C2 naming</v>
+        <v>Pick the planned container at loading</v>
       </c>
       <c r="D133" t="str">
-        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
+        <v>Each container tab's plan row is a picker over the order's planned containers (format, pallets, boxes, Planned / Sent / Claimed by); the claim is saved.</v>
       </c>
       <c r="E133" t="str">
         <v>Completed</v>
       </c>
       <c r="F133" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G133" t="str">
-        <v>CR-350, 354</v>
+        <v>CR-338</v>
       </c>
     </row>
     <row r="134">
@@ -3480,19 +3480,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C134" t="str">
-        <v>Mix Batch at loading</v>
+        <v>Two steps per container; C1 / C2 naming</v>
       </c>
       <c r="D134" t="str">
-        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
+        <v>Designs &amp; pallets first, then Container &amp; vehicle (container pick, number, vehicle, driver, seals) under the rows; party and customer PO lead the header, SO numbers small.</v>
       </c>
       <c r="E134" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F134" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G134" t="str">
-        <v>CR-260 follow-up</v>
+        <v>CR-350, 354</v>
       </c>
     </row>
     <row r="135">
@@ -3503,19 +3503,19 @@
         <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C135" t="str">
-        <v>Five stage pages: Palletization Completed, Loading, Dispatch</v>
+        <v>Mix Batch at loading</v>
       </c>
       <c r="D135" t="str">
-        <v>Palletization Completed stays its own page; Loading lists the items being loaded; the new Dispatch page lists the containers ready to dispatch and the dispatched ones, with their prints.</v>
+        <v>Top up a pallet with another batch at loading time, not only at palletization.</v>
       </c>
       <c r="E135" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F135" t="str">
-        <v>2026-10-28</v>
+        <v/>
       </c>
       <c r="G135" t="str">
-        <v>CR-480</v>
+        <v>CR-260 follow-up</v>
       </c>
     </row>
     <row r="136">
@@ -3523,22 +3523,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Loading &amp; Dispatch</v>
       </c>
       <c r="C136" t="str">
-        <v>One stock rule everywhere</v>
+        <v>Five stage pages: Palletization Completed, Loading, Dispatch</v>
       </c>
       <c r="D136" t="str">
-        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
+        <v>Palletization Completed stays its own page; Loading lists the items being loaded; the new Dispatch page lists the containers ready to dispatch and the dispatched ones, with their prints.</v>
       </c>
       <c r="E136" t="str">
         <v>Completed</v>
       </c>
       <c r="F136" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G136" t="str">
-        <v/>
+        <v>CR-480</v>
       </c>
     </row>
     <row r="137">
@@ -3549,10 +3549,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C137" t="str">
-        <v>Counters recomputed, never incremented</v>
+        <v>One stock rule everywhere</v>
       </c>
       <c r="D137" t="str">
-        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
+        <v>Opening + produced − loaded, oldest batch first — used by Stock Details, reports, pickers and the server alike.</v>
       </c>
       <c r="E137" t="str">
         <v>Completed</v>
@@ -3572,10 +3572,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C138" t="str">
-        <v>Allocation and batch ledger</v>
+        <v>Counters recomputed, never incremented</v>
       </c>
       <c r="D138" t="str">
-        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
+        <v>Order-line counters are recalculated from the records, so a failed save can never leave a wrong total.</v>
       </c>
       <c r="E138" t="str">
         <v>Completed</v>
@@ -3595,10 +3595,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C139" t="str">
-        <v>Admin repair operations</v>
+        <v>Allocation and batch ledger</v>
       </c>
       <c r="D139" t="str">
-        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
+        <v>Allocation = a claim on free stock, visible on the order line; the ledger shows where every batch went (produced → queued → palletized → loaded → dispatched).</v>
       </c>
       <c r="E139" t="str">
         <v>Completed</v>
@@ -3618,19 +3618,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C140" t="str">
-        <v>Inventory adjustments</v>
+        <v>Admin repair operations</v>
       </c>
       <c r="D140" t="str">
-        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
+        <v>Settings ▸ Data operations: recount order lines, resync size snapshots, backfill line pallets, renumber loadings, re-attribute blank batch lines.</v>
       </c>
       <c r="E140" t="str">
         <v>Completed</v>
       </c>
       <c r="F140" t="str">
-        <v>2026-10-07</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G140" t="str">
-        <v>CR-308</v>
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -3641,19 +3641,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C141" t="str">
-        <v>Stock per warehouse</v>
+        <v>Inventory adjustments</v>
       </c>
       <c r="D141" t="str">
-        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
+        <v>Inventory ▸ Stock Adjustments: every ± correction with reason (Adjustment Reason master); bulk New Adjustment sheet; never below on hand; warns when it eats reserved boxes; every stock reader includes adjustments.</v>
       </c>
       <c r="E141" t="str">
         <v>Completed</v>
       </c>
       <c r="F141" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G141" t="str">
-        <v>CR-329</v>
+        <v>CR-308</v>
       </c>
     </row>
     <row r="142">
@@ -3664,10 +3664,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C142" t="str">
-        <v>Transfer Orders</v>
+        <v>Stock per warehouse</v>
       </c>
       <c r="D142" t="str">
-        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
+        <v>Every stock entry records its warehouse (default primary); loads take from the warehouse holding the batch, Loading Bay first; global figures unchanged.</v>
       </c>
       <c r="E142" t="str">
         <v>Completed</v>
@@ -3676,7 +3676,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G142" t="str">
-        <v>CR-330</v>
+        <v>CR-329</v>
       </c>
     </row>
     <row r="143">
@@ -3687,10 +3687,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C143" t="str">
-        <v>Locations on items</v>
+        <v>Transfer Orders</v>
       </c>
       <c r="D143" t="str">
-        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
+        <v>Inventory ▸ Transfer Orders: dated TRF/FY/NNN moving boxes or cut pieces between warehouses with a reason; a line cannot exceed what the From warehouse holds.</v>
       </c>
       <c r="E143" t="str">
         <v>Completed</v>
@@ -3699,7 +3699,7 @@
         <v>2026-10-12</v>
       </c>
       <c r="G143" t="str">
-        <v>CR-332</v>
+        <v>CR-330</v>
       </c>
     </row>
     <row r="144">
@@ -3710,19 +3710,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C144" t="str">
-        <v>Stock keyed by the item</v>
+        <v>Locations on items</v>
       </c>
       <c r="D144" t="str">
-        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
+        <v>Item detail ▸ Locations tab (warehouse → batches, on hand · committed · available); Panel Item detail ▸ Locations card.</v>
       </c>
       <c r="E144" t="str">
         <v>Completed</v>
       </c>
       <c r="F144" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G144" t="str">
-        <v>CR-341</v>
+        <v>CR-332</v>
       </c>
     </row>
     <row r="145">
@@ -3730,22 +3730,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>Reports &amp; audit</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C145" t="str">
-        <v>Sales reports</v>
+        <v>Stock keyed by the item</v>
       </c>
       <c r="D145" t="str">
-        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
+        <v>Live stock, opening / adjustment / allocation sums and To Produce demand key on the item, not its shared design name; Item detail agrees with Allocate Stock.</v>
       </c>
       <c r="E145" t="str">
         <v>Completed</v>
       </c>
       <c r="F145" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v>2026-10-13</v>
       </c>
       <c r="G145" t="str">
-        <v/>
+        <v>CR-341</v>
       </c>
     </row>
     <row r="146">
@@ -3756,10 +3756,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C146" t="str">
-        <v>Inventory reports</v>
+        <v>Sales reports</v>
       </c>
       <c r="D146" t="str">
-        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
+        <v>By Item, By PO, Customer Sales, Salesperson Sales, Size-wise, Quote Aging — date range, filters, CSV, day / week / month buckets.</v>
       </c>
       <c r="E146" t="str">
         <v>Completed</v>
@@ -3768,7 +3768,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G146" t="str">
-        <v>CR-104</v>
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -3779,10 +3779,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C147" t="str">
-        <v>Dispatch reports</v>
+        <v>Inventory reports</v>
       </c>
       <c r="D147" t="str">
-        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
+        <v>Live Stock, Batch-wise Stock (over-consumed flagged), Production Batches (list or item × date matrix), Batch Movement (pivot), Ready Pallets.</v>
       </c>
       <c r="E147" t="str">
         <v>Completed</v>
@@ -3802,10 +3802,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C148" t="str">
-        <v>Audit log and activity</v>
+        <v>Dispatch reports</v>
       </c>
       <c r="D148" t="str">
-        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
+        <v>Palletization Status, Loading &amp; Dispatch (per container with vehicle, seals, transporter, LR, destination, fill %), Dispatch Register.</v>
       </c>
       <c r="E148" t="str">
         <v>Completed</v>
@@ -3814,7 +3814,7 @@
         <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G148" t="str">
-        <v/>
+        <v>CR-104</v>
       </c>
     </row>
     <row r="149">
@@ -3825,10 +3825,10 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C149" t="str">
-        <v>Dashboard</v>
+        <v>Audit log and activity</v>
       </c>
       <c r="D149" t="str">
-        <v>Headline numbers.</v>
+        <v>Every change logged with who and what; every status move recorded; admin overrides carry their reason; Audit Log page plus Activity tab and Status history on every record.</v>
       </c>
       <c r="E149" t="str">
         <v>Completed</v>
@@ -3848,19 +3848,19 @@
         <v>Reports &amp; audit</v>
       </c>
       <c r="C150" t="str">
-        <v>Warehouse Stock report</v>
+        <v>Dashboard</v>
       </c>
       <c r="D150" t="str">
-        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
+        <v>Headline numbers.</v>
       </c>
       <c r="E150" t="str">
         <v>Completed</v>
       </c>
       <c r="F150" t="str">
-        <v>2026-10-12</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G150" t="str">
-        <v>CR-331</v>
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -3868,22 +3868,22 @@
         <v>150</v>
       </c>
       <c r="B151" t="str">
-        <v>Panel Craft</v>
+        <v>Reports &amp; audit</v>
       </c>
       <c r="C151" t="str">
-        <v>Panel Master</v>
+        <v>Warehouse Stock report</v>
       </c>
       <c r="D151" t="str">
-        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
+        <v>Boxes or cut pieces, list or Item × Warehouse matrix, a tile per warehouse, filters, CSV.</v>
       </c>
       <c r="E151" t="str">
         <v>Completed</v>
       </c>
       <c r="F151" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-12</v>
       </c>
       <c r="G151" t="str">
-        <v>CR-283…285, 291, 319</v>
+        <v>CR-331</v>
       </c>
     </row>
     <row r="152">
@@ -3894,19 +3894,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C152" t="str">
-        <v>Panel form opens with a blank size</v>
+        <v>Panel Master</v>
       </c>
       <c r="D152" t="str">
-        <v>New Panel no longer prefills 1200x2100; the size is typed.</v>
+        <v>Showcase panel master with one image, PANEL-001 numbering by the server, full-page New / Edit form; grid opens as photo tiles with a toggle to the column grid; row / tile click opens the panel.</v>
       </c>
       <c r="E152" t="str">
         <v>Completed</v>
       </c>
       <c r="F152" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G152" t="str">
-        <v>CR-484</v>
+        <v>CR-283…285, 291, 319</v>
       </c>
     </row>
     <row r="153">
@@ -3917,10 +3917,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C153" t="str">
-        <v>Sample order Actions tab</v>
+        <v>Panel form opens with a blank size</v>
       </c>
       <c r="D153" t="str">
-        <v>A sample order has the panel order's tabs (Details · Readiness · Actions · Dispatch · Activity). Loads are recorded on the Actions tab — quantity per row, + Load… on one row, Dispatch, Load Copy per trip — the header Record Load button is gone.</v>
+        <v>New Panel no longer prefills 1200x2100; the size is typed.</v>
       </c>
       <c r="E153" t="str">
         <v>Completed</v>
@@ -3929,7 +3929,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G153" t="str">
-        <v>CR-485</v>
+        <v>CR-484</v>
       </c>
     </row>
     <row r="154">
@@ -3940,10 +3940,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C154" t="str">
-        <v>Sample order pick slip</v>
+        <v>Sample order Actions tab</v>
       </c>
       <c r="D154" t="str">
-        <v>More ▸ Print order PDF on a sample order: every item with its photo, name and item code, full tile / cut piece size, Requested · Supplied · Remaining, the remark typed on the line and an empty Broken / Adjustment box to fill in by hand; the Stock Adjustments reminder and Taken out by / Checked by lines.</v>
+        <v>A sample order has the panel order's tabs (Details · Readiness · Actions · Dispatch · Activity). Loads are recorded on the Actions tab — quantity per row, + Load… on one row, Dispatch, Load Copy per trip — the header Record Load button is gone.</v>
       </c>
       <c r="E154" t="str">
         <v>Completed</v>
@@ -3952,7 +3952,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G154" t="str">
-        <v>CR-486</v>
+        <v>CR-485</v>
       </c>
     </row>
     <row r="155">
@@ -3963,10 +3963,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C155" t="str">
-        <v>Allocate Stock on sample orders</v>
+        <v>Sample order pick slip</v>
       </c>
       <c r="D155" t="str">
-        <v>A sample order books cut pieces the way a panel order does: Requirements card on its Actions tab (Need · In Stock · Allocated · Short) and the same Allocate Stock window; a cut-piece row loads only once booked, the load consumes the booking; panel and sample bookings share one pool so no piece is promised twice; Pending Cut Stock counts sample demand.</v>
+        <v>More ▸ Print order PDF on a sample order: every item with its photo, name and item code, full tile / cut piece size, Requested · Supplied · Remaining, the remark typed on the line and an empty Broken / Adjustment box to fill in by hand; the Stock Adjustments reminder and Taken out by / Checked by lines.</v>
       </c>
       <c r="E155" t="str">
         <v>Completed</v>
@@ -3975,7 +3975,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G155" t="str">
-        <v>CR-487</v>
+        <v>CR-486</v>
       </c>
     </row>
     <row r="156">
@@ -3986,10 +3986,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C156" t="str">
-        <v>Full-tile samples book the sample stock</v>
+        <v>Allocate Stock on sample orders</v>
       </c>
       <c r="D156" t="str">
-        <v>A sample order's full-tile line books the item's full-size piece on Cut Stock — the separately managed sample stock — in pieces, from the same Allocate Stock window as its cut pieces (no batch picker; export box stock is never touched); the load is refused until booked and takes the pieces out of Cut Stock. The sample order form lists panel items only.</v>
+        <v>A sample order books cut pieces the way a panel order does: Requirements card on its Actions tab (Need · In Stock · Allocated · Short) and the same Allocate Stock window; a cut-piece row loads only once booked, the load consumes the booking; panel and sample bookings share one pool so no piece is promised twice; Pending Cut Stock counts sample demand.</v>
       </c>
       <c r="E156" t="str">
         <v>Completed</v>
@@ -3998,7 +3998,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="G156" t="str">
-        <v>CR-489 (replaces CR-488)</v>
+        <v>CR-487</v>
       </c>
     </row>
     <row r="157">
@@ -4009,19 +4009,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C157" t="str">
-        <v>Remarks on a panel</v>
+        <v>Full-tile samples book the sample stock</v>
       </c>
       <c r="D157" t="str">
-        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
+        <v>A sample order's full-tile line books the item's full-size piece on Cut Stock — the separately managed sample stock — in pieces, from the same Allocate Stock window as its cut pieces (no batch picker; export box stock is never touched); the load is refused until booked and takes the pieces out of Cut Stock. The sample order form lists panel items only.</v>
       </c>
       <c r="E157" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F157" t="str">
-        <v/>
+        <v>2026-10-28</v>
       </c>
       <c r="G157" t="str">
-        <v>CR-425</v>
+        <v>CR-489 (replaces CR-488)</v>
       </c>
     </row>
     <row r="158">
@@ -4032,10 +4032,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C158" t="str">
-        <v>Cut Piece Size master under Panel Items</v>
+        <v>Remarks on a panel</v>
       </c>
       <c r="D158" t="str">
-        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
+        <v>Free-text Remarks on New / Edit Panel for the old reference ID; shown on the panel page and searchable in the panel list.</v>
       </c>
       <c r="E158" t="str">
         <v>In progress</v>
@@ -4044,7 +4044,7 @@
         <v/>
       </c>
       <c r="G158" t="str">
-        <v>CR-426</v>
+        <v>CR-425</v>
       </c>
     </row>
     <row r="159">
@@ -4052,13 +4052,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C159" t="str">
-        <v>Box Weight in Bulk edit, frozen per order</v>
+        <v>Cut Piece Size master under Panel Items</v>
       </c>
       <c r="D159" t="str">
-        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
+        <v>The cut piece size list is maintained from the Panel Items page (Cut Piece Sizes button) instead of Settings ▸ Masters.</v>
       </c>
       <c r="E159" t="str">
         <v>In progress</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="G159" t="str">
-        <v>CR-427</v>
+        <v>CR-426</v>
       </c>
     </row>
     <row r="160">
@@ -4075,22 +4075,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C160" t="str">
-        <v>Settings groups: Item Master and Panel Master</v>
+        <v>Box Weight in Bulk edit, frozen per order</v>
       </c>
       <c r="D160" t="str">
-        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
+        <v>Search the Items list, select every match, set Box Weight once; each quote / sales-order line keeps the weight it was created with, so Container Planning on older orders does not move.</v>
       </c>
       <c r="E160" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F160" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G160" t="str">
-        <v>CR-428</v>
+        <v>CR-427</v>
       </c>
     </row>
     <row r="161">
@@ -4101,10 +4101,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C161" t="str">
-        <v>One Masters page</v>
+        <v>Settings groups: Item Master and Panel Master</v>
       </c>
       <c r="D161" t="str">
-        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
+        <v>Item reference lists under Item Master, panel ones (Cut Piece Size, MDF) under Panel Master; Adjustment Reason and Warehouses under Setup &amp; Configuration. Superseded by the Masters page (CR-436).</v>
       </c>
       <c r="E161" t="str">
         <v>Completed</v>
@@ -4113,7 +4113,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G161" t="str">
-        <v>CR-436</v>
+        <v>CR-428</v>
       </c>
     </row>
     <row r="162">
@@ -4124,10 +4124,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C162" t="str">
-        <v>Masters menu inside Settings with horizontal tabs</v>
+        <v>One Masters page</v>
       </c>
       <c r="D162" t="str">
-        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
+        <v>Single Masters entry in the sidebar with Export Master · Item Master · Panel Master sub-tabs; every master (Pallets, Containers, Sizes, Items, Panel Items, Panels, lookups, Currencies, Warehouses) opens in place; old menu entries and links redirect into it; roles with Items or Panel Craft view see it.</v>
       </c>
       <c r="E162" t="str">
         <v>Completed</v>
@@ -4136,7 +4136,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G162" t="str">
-        <v>CR-439</v>
+        <v>CR-436</v>
       </c>
     </row>
     <row r="163">
@@ -4147,10 +4147,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C163" t="str">
-        <v>Masters only under Settings, clearer tabs</v>
+        <v>Masters menu inside Settings with horizontal tabs</v>
       </c>
       <c r="D163" t="str">
-        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
+        <v>The Settings page's left menu has Masters ▸ Item / Panel / Export; the chosen group shows its title and its masters as horizontal tabs that open each list in place. The sidebar Masters entry opens the same page.</v>
       </c>
       <c r="E163" t="str">
         <v>Completed</v>
@@ -4159,7 +4159,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G163" t="str">
-        <v>CR-440</v>
+        <v>CR-439</v>
       </c>
     </row>
     <row r="164">
@@ -4167,13 +4167,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="str">
-        <v>Items</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C164" t="str">
-        <v>Base Design Name defaults to the Design Name</v>
+        <v>Masters only under Settings, clearer tabs</v>
       </c>
       <c r="D164" t="str">
-        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
+        <v>The sidebar no longer lists Masters; the menu is Settings ▸ Masters ▸ Item / Panel / Export and the selected master tab is a highlighted pill. Old links and search still open it.</v>
       </c>
       <c r="E164" t="str">
         <v>Completed</v>
@@ -4182,7 +4182,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G164" t="str">
-        <v>CR-437</v>
+        <v>CR-440</v>
       </c>
     </row>
     <row r="165">
@@ -4190,22 +4190,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Items</v>
       </c>
       <c r="C165" t="str">
-        <v>Names save as Title Case</v>
+        <v>Base Design Name defaults to the Design Name</v>
       </c>
       <c r="D165" t="str">
-        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
+        <v>Leave Base Design Name blank and the item is saved with its Design Name as the base; the field stays clearable while editing.</v>
       </c>
       <c r="E165" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F165" t="str">
-        <v/>
+        <v>2026-10-24</v>
       </c>
       <c r="G165" t="str">
-        <v>CR-429</v>
+        <v>CR-437</v>
       </c>
     </row>
     <row r="166">
@@ -4213,13 +4213,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C166" t="str">
-        <v>Brand off the Item form</v>
+        <v>Names save as Title Case</v>
       </c>
       <c r="D166" t="str">
-        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
+        <v>Item, customer, contact, driver, transporter, supervisor, user and master names are stored as "Dhiraj Shah Of ABC Exports LLP" however typed — on every form, import and Zoho sync; short acronyms and LLP / LTD / PVT keep their capitals.</v>
       </c>
       <c r="E166" t="str">
         <v>In progress</v>
@@ -4228,7 +4228,7 @@
         <v/>
       </c>
       <c r="G166" t="str">
-        <v>CR-430</v>
+        <v>CR-429</v>
       </c>
     </row>
     <row r="167">
@@ -4236,22 +4236,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C167" t="str">
-        <v>Panel Items with weighed cut pieces</v>
+        <v>Brand off the Item form</v>
       </c>
       <c r="D167" t="str">
-        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
+        <v>The Item form no longer asks for Brand; the Items grid, search, bulk edit and item page still show it.</v>
       </c>
       <c r="E167" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F167" t="str">
-        <v>2026-10-07</v>
+        <v/>
       </c>
       <c r="G167" t="str">
-        <v>CR-306</v>
+        <v>CR-430</v>
       </c>
     </row>
     <row r="168">
@@ -4262,19 +4262,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C168" t="str">
-        <v>Cut Piece stock as items + bulk sheets + ledger</v>
+        <v>Panel Items with weighed cut pieces</v>
       </c>
       <c r="D168" t="str">
-        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
+        <v>Designs picked from the Item master into Panel Craft, each with its cut pieces (add, weigh, remove); the Panel form offers only these.</v>
       </c>
       <c r="E168" t="str">
         <v>Completed</v>
       </c>
       <c r="F168" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G168" t="str">
-        <v>CR-282, 307, 308, 343</v>
+        <v>CR-306</v>
       </c>
     </row>
     <row r="169">
@@ -4285,10 +4285,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C169" t="str">
-        <v>MDF master</v>
+        <v>Cut Piece stock as items + bulk sheets + ledger</v>
       </c>
       <c r="D169" t="str">
-        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
+        <v>One row per cut piece (image, size, weight, on hand, stock weight); Add Stock and Adjust Stock are dated bulk sheets; every movement in a ledger shown as Stock History. Menu reads 'Cut Piece'.</v>
       </c>
       <c r="E169" t="str">
         <v>Completed</v>
@@ -4297,7 +4297,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G169" t="str">
-        <v>CR-309, 320, 344</v>
+        <v>CR-282, 307, 308, 343</v>
       </c>
     </row>
     <row r="170">
@@ -4308,19 +4308,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C170" t="str">
-        <v>Panel Order = header + lines</v>
+        <v>MDF master</v>
       </c>
       <c r="D170" t="str">
-        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
+        <v>Settings ▸ Masters ▸ MDF: Size · Thickness · Weight rows; the Panel master states its MDF size; the order line picks a thickness; weight = cut pieces + MDF, × qty.</v>
       </c>
       <c r="E170" t="str">
         <v>Completed</v>
       </c>
       <c r="F170" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G170" t="str">
-        <v>CR-302, 304, 310, 346, 289, 357</v>
+        <v>CR-309, 320, 344</v>
       </c>
     </row>
     <row r="171">
@@ -4331,19 +4331,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C171" t="str">
-        <v>Panel Order page is the only place status changes</v>
+        <v>Panel Order = header + lines</v>
       </c>
       <c r="D171" t="str">
-        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
+        <v>One customer order holds several panels (PNL/FY/NNN); SO-shape form (Pick from showcase with Design · Panel Size · Cut Piece Size · In-stock filters) and detail; loose cut-piece lines ('10 panels + 20 cut pieces'); blank cut piece size = full size.</v>
       </c>
       <c r="E171" t="str">
         <v>Completed</v>
       </c>
       <c r="F171" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-21</v>
       </c>
       <c r="G171" t="str">
-        <v>CR-287, 294</v>
+        <v>CR-302, 304, 310, 346, 289, 357</v>
       </c>
     </row>
     <row r="172">
@@ -4354,19 +4354,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C172" t="str">
-        <v>Request Panels / Samples from a Quote or Sales Order</v>
+        <v>Panel Order page is the only place status changes</v>
       </c>
       <c r="D172" t="str">
-        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
+        <v>Status chip, next-step buttons (Accept / Start Cutting / Ready / Dispatch), Edit, More ▸ Clone / Delete, Overview | Activity; every order is born 'New'.</v>
       </c>
       <c r="E172" t="str">
         <v>Completed</v>
       </c>
       <c r="F172" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G172" t="str">
-        <v>CR-286, 317</v>
+        <v>CR-287, 294</v>
       </c>
     </row>
     <row r="173">
@@ -4377,19 +4377,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C173" t="str">
-        <v>Requirements checklist with booking</v>
+        <v>Request Panels / Samples from a Quote or Sales Order</v>
       </c>
       <c r="D173" t="str">
-        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
+        <v>More ▸ Request Panels / Request Samples opens the new order with the customer locked and the sale's designs picked; the Quote / SO gains a Panel Orders tab.</v>
       </c>
       <c r="E173" t="str">
         <v>Completed</v>
       </c>
       <c r="F173" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G173" t="str">
-        <v>CR-288, 303, 305, 312</v>
+        <v>CR-286, 317</v>
       </c>
     </row>
     <row r="174">
@@ -4400,19 +4400,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C174" t="str">
-        <v>Production checkpoints</v>
+        <v>Requirements checklist with booking</v>
       </c>
       <c r="D174" t="str">
-        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
+        <v>Per design × cut size: Need, In Stock, Allocated · Short, the panels it serves; one Allocate Stock modal; Dispatch needs every piece booked; Ready books its own output. Replaces the godown print slip.</v>
       </c>
       <c r="E174" t="str">
         <v>Completed</v>
       </c>
       <c r="F174" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G174" t="str">
-        <v>CR-313, 323</v>
+        <v>CR-288, 303, 305, 312</v>
       </c>
     </row>
     <row r="175">
@@ -4423,10 +4423,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C175" t="str">
-        <v>Pending Cut Piece page</v>
+        <v>Production checkpoints</v>
       </c>
       <c r="D175" t="str">
-        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
+        <v>MDF · Vinyl Printing · Cut Pieces · Vinyl Pasted on MDF, marked independently with who / when; readiness on the page, sheet, cards and dashboard.</v>
       </c>
       <c r="E175" t="str">
         <v>Completed</v>
@@ -4435,7 +4435,7 @@
         <v>2026-10-09</v>
       </c>
       <c r="G175" t="str">
-        <v>CR-314, 322</v>
+        <v>CR-313, 323</v>
       </c>
     </row>
     <row r="176">
@@ -4446,19 +4446,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C176" t="str">
-        <v>Sample Orders</v>
+        <v>Pending Cut Piece page</v>
       </c>
       <c r="D176" t="str">
-        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
+        <v>Per cut piece: Required · On Hand · Booked · Free · Shortage · Orders (each order linked with its quantity).</v>
       </c>
       <c r="E176" t="str">
         <v>Completed</v>
       </c>
       <c r="F176" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="G176" t="str">
-        <v>CR-315…317</v>
+        <v>CR-314, 322</v>
       </c>
     </row>
     <row r="177">
@@ -4469,19 +4469,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C177" t="str">
-        <v>One Orders register</v>
+        <v>Sample Orders</v>
       </c>
       <c r="D177" t="str">
-        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
+        <v>Separate order type (SMP/FY/NNN) for customer samples — full tile or cut piece; per-line partial supply with a date; cut pieces come off cut stock; Customer page lists every sample line.</v>
       </c>
       <c r="E177" t="str">
         <v>Completed</v>
       </c>
       <c r="F177" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="G177" t="str">
-        <v>CR-345</v>
+        <v>CR-315…317</v>
       </c>
     </row>
     <row r="178">
@@ -4492,10 +4492,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C178" t="str">
-        <v>Loading entries and Panel Craft ▸ Loading page</v>
+        <v>One Orders register</v>
       </c>
       <c r="D178" t="str">
-        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
+        <v>Panel + Sample orders in one grid with a Type column and filter; New Order asks the type first.</v>
       </c>
       <c r="E178" t="str">
         <v>Completed</v>
@@ -4504,7 +4504,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G178" t="str">
-        <v>CR-347, 348</v>
+        <v>CR-345</v>
       </c>
     </row>
     <row r="179">
@@ -4515,10 +4515,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C179" t="str">
-        <v>Weight split and frozen at load</v>
+        <v>Loading entries and Panel Craft ▸ Loading page</v>
       </c>
       <c r="D179" t="str">
-        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
+        <v>Record Load per order (date, vehicle, driver, photos, qty per line × material — Panel / MDF / cut piece); several orders per trip; Dispatched is derived from the loads; Loading page lists everything pending with multi-select → one trip.</v>
       </c>
       <c r="E179" t="str">
         <v>Completed</v>
@@ -4527,7 +4527,7 @@
         <v>2026-10-15</v>
       </c>
       <c r="G179" t="str">
-        <v>CR-349</v>
+        <v>CR-347, 348</v>
       </c>
     </row>
     <row r="180">
@@ -4538,19 +4538,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C180" t="str">
-        <v>Load Copy print</v>
+        <v>Weight split and frozen at load</v>
       </c>
       <c r="D180" t="str">
-        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
+        <v>Pieces kg · MDF kg · Total kg; shipped kg stamped at load time; pending kg follow the master.</v>
       </c>
       <c r="E180" t="str">
         <v>Completed</v>
       </c>
       <c r="F180" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-15</v>
       </c>
       <c r="G180" t="str">
-        <v>CR-351</v>
+        <v>CR-349</v>
       </c>
     </row>
     <row r="181">
@@ -4561,19 +4561,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C181" t="str">
-        <v>Load Copy from the Actions tab</v>
+        <v>Load Copy print</v>
       </c>
       <c r="D181" t="str">
-        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
+        <v>Branded Load Copy PDF per trip (vehicle block, lines, kg, signatures) from the Loads table; vehicle details kept on the Vehicle master.</v>
       </c>
       <c r="E181" t="str">
         <v>Completed</v>
       </c>
       <c r="F181" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-19</v>
       </c>
       <c r="G181" t="str">
-        <v>CR-433</v>
+        <v>CR-351</v>
       </c>
     </row>
     <row r="182">
@@ -4584,19 +4584,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C182" t="str">
-        <v>Panel Craft dashboard</v>
+        <v>Load Copy from the Actions tab</v>
       </c>
       <c r="D182" t="str">
-        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
+        <v>The panel order Actions tab lists every vehicle trip under Load Copy, newest first; each copy shows only what left on that trip.</v>
       </c>
       <c r="E182" t="str">
         <v>Completed</v>
       </c>
       <c r="F182" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G182" t="str">
-        <v>CR-311</v>
+        <v>CR-433</v>
       </c>
     </row>
     <row r="183">
@@ -4607,19 +4607,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C183" t="str">
-        <v>Small UX items</v>
+        <v>Panel Craft dashboard</v>
       </c>
       <c r="D183" t="str">
-        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
+        <v>Open / in-cutting / ready / short counts, cut stock pcs + kg, pipeline strip, panels by status, orders per week, shortages, most-ordered panels, latest orders, Pending to Load.</v>
       </c>
       <c r="E183" t="str">
         <v>Completed</v>
       </c>
       <c r="F183" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-07</v>
       </c>
       <c r="G183" t="str">
-        <v>CR-293, 295, 318, 321, 352</v>
+        <v>CR-311</v>
       </c>
     </row>
     <row r="184">
@@ -4630,19 +4630,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C184" t="str">
-        <v>Actions tab on the Panel Order</v>
+        <v>Small UX items</v>
       </c>
       <c r="D184" t="str">
-        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
+        <v>Upload shows the BOFFO processing state; Stock column Available / Unavailable; Panels column opens a card list; filter × clears; (i) card per line; notes under the content they explain.</v>
       </c>
       <c r="E184" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F184" t="str">
-        <v/>
+        <v>2026-10-19</v>
       </c>
       <c r="G184" t="str">
-        <v>CR-365</v>
+        <v>CR-293, 295, 318, 321, 352</v>
       </c>
     </row>
     <row r="185">
@@ -4653,10 +4653,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C185" t="str">
-        <v>Vinyl Pasted waits for MDF + Vinyl</v>
+        <v>Actions tab on the Panel Order</v>
       </c>
       <c r="D185" t="str">
-        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
+        <v>Per line × material: Ordered · Loaded · Pending · Ready or what is missing · Load Now; Dispatch opens Record Load with those quantities.</v>
       </c>
       <c r="E185" t="str">
         <v>In progress</v>
@@ -4665,7 +4665,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>CR-366</v>
+        <v>CR-365</v>
       </c>
     </row>
     <row r="186">
@@ -4676,10 +4676,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C186" t="str">
-        <v>One Status column</v>
+        <v>Vinyl Pasted waits for MDF + Vinyl</v>
       </c>
       <c r="D186" t="str">
-        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
+        <v>The pasted checkpoint is greyed and refused until both MDF and Vinyl Printing are Ready.</v>
       </c>
       <c r="E186" t="str">
         <v>In progress</v>
@@ -4688,7 +4688,7 @@
         <v/>
       </c>
       <c r="G186" t="str">
-        <v>CR-367</v>
+        <v>CR-366</v>
       </c>
     </row>
     <row r="187">
@@ -4699,10 +4699,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C187" t="str">
-        <v>Cancel Order (panel and sample)</v>
+        <v>One Status column</v>
       </c>
       <c r="D187" t="str">
-        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
+        <v>Pending · Not Started · In Progress · Ready · Completed · Cancelled replaces the four checkpoint columns + Readiness on the grid, kanban, dashboard and detail chip; lifecycle stage shown as a Stage field.</v>
       </c>
       <c r="E187" t="str">
         <v>In progress</v>
@@ -4711,7 +4711,7 @@
         <v/>
       </c>
       <c r="G187" t="str">
-        <v>CR-368</v>
+        <v>CR-367</v>
       </c>
     </row>
     <row r="188">
@@ -4722,10 +4722,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C188" t="str">
-        <v>Panel Order page: customer heading</v>
+        <v>Cancel Order (panel and sample)</v>
       </c>
       <c r="D188" t="str">
-        <v>The customer's name is the page title; the PNL number sits small under it.</v>
+        <v>Reason required for everyone; blocked once a load exists; bookings return to free stock.</v>
       </c>
       <c r="E188" t="str">
         <v>In progress</v>
@@ -4734,7 +4734,7 @@
         <v/>
       </c>
       <c r="G188" t="str">
-        <v>CR-399</v>
+        <v>CR-368</v>
       </c>
     </row>
     <row r="189">
@@ -4745,10 +4745,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C189" t="str">
-        <v>One four-state order status</v>
+        <v>Panel Order page: customer heading</v>
       </c>
       <c r="D189" t="str">
-        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
+        <v>The customer's name is the page title; the PNL number sits small under it.</v>
       </c>
       <c r="E189" t="str">
         <v>In progress</v>
@@ -4757,7 +4757,7 @@
         <v/>
       </c>
       <c r="G189" t="str">
-        <v>CR-400</v>
+        <v>CR-399</v>
       </c>
     </row>
     <row r="190">
@@ -4768,10 +4768,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C190" t="str">
-        <v>Vinyl print waits for MDF</v>
+        <v>One four-state order status</v>
       </c>
       <c r="D190" t="str">
-        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
+        <v>New → Ready (every panel pasted) → Completed (pieces booked too) → Dispatched, derived automatically; no Accept / Start Cutting buttons.</v>
       </c>
       <c r="E190" t="str">
         <v>In progress</v>
@@ -4780,7 +4780,7 @@
         <v/>
       </c>
       <c r="G190" t="str">
-        <v>CR-401</v>
+        <v>CR-400</v>
       </c>
     </row>
     <row r="191">
@@ -4791,10 +4791,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C191" t="str">
-        <v>Marks on the Actions tab</v>
+        <v>Vinyl print waits for MDF</v>
       </c>
       <c r="D191" t="str">
-        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
+        <v>The Vinyl Printing mark opens only once that panel's MDF is Ready.</v>
       </c>
       <c r="E191" t="str">
         <v>In progress</v>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="G191" t="str">
-        <v>CR-402</v>
+        <v>CR-401</v>
       </c>
     </row>
     <row r="192">
@@ -4814,10 +4814,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C192" t="str">
-        <v>Load pieces, boards or both</v>
+        <v>Marks on the Actions tab</v>
       </c>
       <c r="D192" t="str">
-        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
+        <v>MDF · Vinyl · Pasted are set per panel on the Actions tab beside the loading rows.</v>
       </c>
       <c r="E192" t="str">
         <v>In progress</v>
@@ -4826,7 +4826,7 @@
         <v/>
       </c>
       <c r="G192" t="str">
-        <v>CR-403</v>
+        <v>CR-402</v>
       </c>
     </row>
     <row r="193">
@@ -4837,10 +4837,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C193" t="str">
-        <v>Load part of a panel</v>
+        <v>Load pieces, boards or both</v>
       </c>
       <c r="D193" t="str">
-        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
+        <v>Cut pieces load once booked; the MDF board once pasted; one row alone or everything ready together.</v>
       </c>
       <c r="E193" t="str">
         <v>In progress</v>
@@ -4849,7 +4849,7 @@
         <v/>
       </c>
       <c r="G193" t="str">
-        <v>CR-405</v>
+        <v>CR-403</v>
       </c>
     </row>
     <row r="194">
@@ -4860,10 +4860,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C194" t="str">
-        <v>MDF row on every panel</v>
+        <v>Load part of a panel</v>
       </c>
       <c r="D194" t="str">
-        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
+        <v>Each panel lists its cut pieces one kind per row; any count can leave on a trip, the rest later. Stock and booking move per piece kind.</v>
       </c>
       <c r="E194" t="str">
         <v>In progress</v>
@@ -4872,7 +4872,7 @@
         <v/>
       </c>
       <c r="G194" t="str">
-        <v>CR-406</v>
+        <v>CR-405</v>
       </c>
     </row>
     <row r="195">
@@ -4883,10 +4883,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C195" t="str">
-        <v>Load whole panel in one click</v>
+        <v>MDF row on every panel</v>
       </c>
       <c r="D195" t="str">
-        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
+        <v>Every panel line has an MDF board row, thickness picked or not; it loads once the vinyl is pasted.</v>
       </c>
       <c r="E195" t="str">
         <v>In progress</v>
@@ -4895,7 +4895,7 @@
         <v/>
       </c>
       <c r="G195" t="str">
-        <v>CR-407</v>
+        <v>CR-406</v>
       </c>
     </row>
     <row r="196">
@@ -4903,22 +4903,22 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C196" t="str">
-        <v>Settings search everywhere</v>
+        <v>Load whole panel in one click</v>
       </c>
       <c r="D196" t="str">
-        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
+        <v>A panel's + menu loads all its ready pieces and its pasted board on one vehicle; Allocate Stock sits on the Actions tab.</v>
       </c>
       <c r="E196" t="str">
-        <v>Completed</v>
+        <v>In progress</v>
       </c>
       <c r="F196" t="str">
-        <v>2026-10-24</v>
+        <v/>
       </c>
       <c r="G196" t="str">
-        <v>CR-408</v>
+        <v>CR-407</v>
       </c>
     </row>
     <row r="197">
@@ -4926,13 +4926,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C197" t="str">
-        <v>Locations inside a warehouse</v>
+        <v>Settings search everywhere</v>
       </c>
       <c r="D197" t="str">
-        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
+        <v>The header search (⌘K) finds settings pages and preferences for admins; the Settings search matches every typed word plus synonyms (godown, truck, login) and the Preferences rows.</v>
       </c>
       <c r="E197" t="str">
         <v>Completed</v>
@@ -4941,7 +4941,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G197" t="str">
-        <v>CR-409</v>
+        <v>CR-408</v>
       </c>
     </row>
     <row r="198">
@@ -4952,10 +4952,10 @@
         <v>Masters (Inventory)</v>
       </c>
       <c r="C198" t="str">
-        <v>Location per item / per row when recording</v>
+        <v>Locations inside a warehouse</v>
       </c>
       <c r="D198" t="str">
-        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
+        <v>A warehouse holds locations like A1 … F12 (generate the whole grid in one go). Stock is recorded at a location and stays there until a Transfer Order moves it; every label reads Warehouse ▸ Location; old stock shows as Unassigned until moved.</v>
       </c>
       <c r="E198" t="str">
         <v>Completed</v>
@@ -4964,7 +4964,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G198" t="str">
-        <v>CR-438</v>
+        <v>CR-409</v>
       </c>
     </row>
     <row r="199">
@@ -4972,22 +4972,22 @@
         <v>198</v>
       </c>
       <c r="B199" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C199" t="str">
-        <v>Stock adjustment as a line form</v>
+        <v>Location per item / per row when recording</v>
       </c>
       <c r="D199" t="str">
-        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
+        <v>Log Production asks the Location per item, Production Completion per line; the bulk Record Production, cut-stock Add / Adjust and Stock Adjustments sheets have a per-row Location column (blank = the bar's default; paste by label or bay code); the Excel import takes a Location column.</v>
       </c>
       <c r="E199" t="str">
         <v>Completed</v>
       </c>
       <c r="F199" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G199" t="str">
-        <v>CR-446</v>
+        <v>CR-438</v>
       </c>
     </row>
     <row r="200">
@@ -4998,19 +4998,19 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C200" t="str">
-        <v>Adjust Stock in the Zoho Books shape</v>
+        <v>Stock adjustment as a line form</v>
       </c>
       <c r="D200" t="str">
-        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
+        <v>Adjust Stock (Panel Craft) and New Stock Adjustment (Inventory) open with one line and '+ Add line' like Zoho Books; each line shows the current stock at its location and carries its own Location, Add / Remove, Qty, Date, Reason and Remark; Add Stock and Transfers keep the bulk sheet.</v>
       </c>
       <c r="E200" t="str">
         <v>Completed</v>
       </c>
       <c r="F200" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G200" t="str">
-        <v>CR-457</v>
+        <v>CR-446</v>
       </c>
     </row>
     <row r="201">
@@ -5021,10 +5021,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C201" t="str">
-        <v>Location Transfer from the Adjust Stock screen</v>
+        <v>Adjust Stock in the Zoho Books shape</v>
       </c>
       <c r="D201" t="str">
-        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
+        <v>Both Adjust Stock pages open with a header (Mode of adjustment, Date, Reason, Description) over an Item Table showing Available, New on hand and one signed Qty adjusted field per line; date and reason are entered once per adjustment.</v>
       </c>
       <c r="E201" t="str">
         <v>Completed</v>
@@ -5033,7 +5033,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G201" t="str">
-        <v>CR-458</v>
+        <v>CR-457</v>
       </c>
     </row>
     <row r="202">
@@ -5044,10 +5044,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C202" t="str">
-        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
+        <v>Location Transfer from the Adjust Stock screen</v>
       </c>
       <c r="D202" t="str">
-        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
+        <v>Mode switch Quantity Adjustment / Location Transfer: pick From and To, list items and the quantity to move, save one Transfer Order (TRF number); total stock unchanged. Boxes and cut pieces.</v>
       </c>
       <c r="E202" t="str">
         <v>Completed</v>
@@ -5056,7 +5056,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G202" t="str">
-        <v>CR-459</v>
+        <v>CR-458</v>
       </c>
     </row>
     <row r="203">
@@ -5067,10 +5067,10 @@
         <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C203" t="str">
-        <v>Cut Piece detail page inside Panel Craft</v>
+        <v>Cut-piece Adjust Stock without a Cut Piece Size column</v>
       </c>
       <c r="D203" t="str">
-        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
+        <v>On the Panel Craft Adjust Stock screen the Item list names the stock row itself (the item alone for its full size, 'Item · 600x600' for a special cut); pick the row and enter the quantity.</v>
       </c>
       <c r="E203" t="str">
         <v>Completed</v>
@@ -5079,7 +5079,7 @@
         <v>2026-10-26</v>
       </c>
       <c r="G203" t="str">
-        <v>CR-460/461</v>
+        <v>CR-459</v>
       </c>
     </row>
     <row r="204">
@@ -5087,22 +5087,22 @@
         <v>203</v>
       </c>
       <c r="B204" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C204" t="str">
-        <v>Pager with First / Last arrows</v>
+        <v>Cut Piece detail page inside Panel Craft</v>
       </c>
       <c r="D204" t="str">
-        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
+        <v>Clicking a row on Panel Craft ▸ Stock opens that cut piece's own page (on hand, booked, free, weight, locations, panels using it, orders booking it, stock history) with the Stock menu still selected; Add / Adjust / Transfer open prefilled with the piece. The grid has no Image column.</v>
       </c>
       <c r="E204" t="str">
         <v>Completed</v>
       </c>
       <c r="F204" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G204" t="str">
-        <v>CR-467</v>
+        <v>CR-460/461</v>
       </c>
     </row>
     <row r="205">
@@ -5113,10 +5113,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C205" t="str">
-        <v>Red close × on every window</v>
+        <v>Pager with First / Last arrows</v>
       </c>
       <c r="D205" t="str">
-        <v>The × that closes any window or drawer is red on every screen.</v>
+        <v>Every list footer has « ‹ › » buttons — first, previous, next, last page — beside the page numbers; the range still shows the total.</v>
       </c>
       <c r="E205" t="str">
         <v>Completed</v>
@@ -5125,7 +5125,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G205" t="str">
-        <v>CR-465</v>
+        <v>CR-467</v>
       </c>
     </row>
     <row r="206">
@@ -5136,10 +5136,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C206" t="str">
-        <v>Advanced search date range fits the window</v>
+        <v>Red close × on every window</v>
       </c>
       <c r="D206" t="str">
-        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
+        <v>The × that closes any window or drawer is red on every screen.</v>
       </c>
       <c r="E206" t="str">
         <v>Completed</v>
@@ -5148,7 +5148,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G206" t="str">
-        <v>CR-464</v>
+        <v>CR-465</v>
       </c>
     </row>
     <row r="207">
@@ -5156,13 +5156,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="str">
-        <v>Customers</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C207" t="str">
-        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
+        <v>Advanced search date range fits the window</v>
       </c>
       <c r="D207" t="str">
-        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
+        <v>Created Between (and every other date range) sits inside the search window on all grids.</v>
       </c>
       <c r="E207" t="str">
         <v>Completed</v>
@@ -5171,7 +5171,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G207" t="str">
-        <v>CR-463/466</v>
+        <v>CR-464</v>
       </c>
     </row>
     <row r="208">
@@ -5179,22 +5179,22 @@
         <v>207</v>
       </c>
       <c r="B208" t="str">
-        <v>Stock &amp; batch ledger</v>
+        <v>Customers</v>
       </c>
       <c r="C208" t="str">
-        <v>Stock history in date order</v>
+        <v>New customer menu: From Zoho CRM / Refresh from Zoho CRM</v>
       </c>
       <c r="D208" t="str">
-        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
+        <v>New customer stays one click; the arrow beside it offers From Zoho CRM (prefill from a CRM account) and, for admins, Refresh from Zoho CRM. The Active / Inactive pills above the grid are gone — use Working Status in Search Customers.</v>
       </c>
       <c r="E208" t="str">
         <v>Completed</v>
       </c>
       <c r="F208" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G208" t="str">
-        <v>CR-455</v>
+        <v>CR-463/466</v>
       </c>
     </row>
     <row r="209">
@@ -5202,22 +5202,22 @@
         <v>208</v>
       </c>
       <c r="B209" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Stock &amp; batch ledger</v>
       </c>
       <c r="C209" t="str">
-        <v>Title Case for the remaining name fields</v>
+        <v>Stock history in date order</v>
       </c>
       <c r="D209" t="str">
-        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
+        <v>The Panel Item Stock History and the Item master Production tab list entries by the date shown, newest first, then by when they were saved.</v>
       </c>
       <c r="E209" t="str">
         <v>Completed</v>
       </c>
       <c r="F209" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G209" t="str">
-        <v>CR-447</v>
+        <v>CR-455</v>
       </c>
     </row>
     <row r="210">
@@ -5225,13 +5225,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="str">
-        <v>Panel Craft</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C210" t="str">
-        <v>Stock list: items with their cut pieces beneath</v>
+        <v>Title Case for the remaining name fields</v>
       </c>
       <c r="D210" t="str">
-        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
+        <v>Collection Name on the Item form, a container's vessel name, extra-address attention names and role names save as Title Case like every other name.</v>
       </c>
       <c r="E210" t="str">
         <v>Completed</v>
@@ -5240,7 +5240,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G210" t="str">
-        <v>CR-448</v>
+        <v>CR-447</v>
       </c>
     </row>
     <row r="211">
@@ -5251,19 +5251,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C211" t="str">
-        <v>Stock list: cut-piece rows only for special sizes</v>
+        <v>Stock list: items with their cut pieces beneath</v>
       </c>
       <c r="D211" t="str">
-        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
+        <v>Panel Craft ▸ Stock (was 'Cut Piece'): one row per item with totals, its cut pieces listed beneath; fold an item, search by item, size or cut size.</v>
       </c>
       <c r="E211" t="str">
         <v>Completed</v>
       </c>
       <c r="F211" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G211" t="str">
-        <v>CR-456</v>
+        <v>CR-448</v>
       </c>
     </row>
     <row r="212">
@@ -5274,19 +5274,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C212" t="str">
-        <v>Panel Item page: read-only weight, Actions tab</v>
+        <v>Stock list: cut-piece rows only for special sizes</v>
       </c>
       <c r="D212" t="str">
-        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
+        <v>An item whose stock is only its full size is one plain row; the chevron and cut-piece rows appear only for items that also have another cut size.</v>
       </c>
       <c r="E212" t="str">
         <v>Completed</v>
       </c>
       <c r="F212" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G212" t="str">
-        <v>CR-449</v>
+        <v>CR-456</v>
       </c>
     </row>
     <row r="213">
@@ -5297,10 +5297,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C213" t="str">
-        <v>Panel Order page: Details informative, Requirements on Actions</v>
+        <v>Panel Item page: read-only weight, Actions tab</v>
       </c>
       <c r="D213" t="str">
-        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
+        <v>The item's Details tab shows cut pieces read-only; adding a cut piece, removing one and the Add Stock / Adjust / Transfer buttons sit on an Actions tab; the weight per piece is the formula value, never typed.</v>
       </c>
       <c r="E213" t="str">
         <v>Completed</v>
@@ -5309,7 +5309,7 @@
         <v>2026-10-25</v>
       </c>
       <c r="G213" t="str">
-        <v>CR-450</v>
+        <v>CR-449</v>
       </c>
     </row>
     <row r="214">
@@ -5317,22 +5317,22 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C214" t="str">
-        <v>Location at every stage</v>
+        <v>Panel Order page: Details informative, Requirements on Actions</v>
       </c>
       <c r="D214" t="str">
-        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
+        <v>The Requirements card (need, in stock, allocated, short, Available tick, Allocate Stock) lives on the Actions tab; Details shows the order's fields and items only.</v>
       </c>
       <c r="E214" t="str">
         <v>Completed</v>
       </c>
       <c r="F214" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="G214" t="str">
-        <v>CR-411…413</v>
+        <v>CR-450</v>
       </c>
     </row>
     <row r="215">
@@ -5340,13 +5340,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C215" t="str">
-        <v>Panel location</v>
+        <v>Location at every stage</v>
       </c>
       <c r="D215" t="str">
-        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
+        <v>Every production screen records a location (default = the bay of the warehouse marked Production); a pallet carries its location from palletization until it is loaded — asked once in the Palletize dialog (Palletization bay on Start, Loading Bay on Complete), changed with Set Location on the boards, shown as a Location column, on the item's Locations tab and as a Pallets view on Stock Locations; panel orders take a location on the form.</v>
       </c>
       <c r="E215" t="str">
         <v>Completed</v>
@@ -5355,7 +5355,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G215" t="str">
-        <v>CR-410</v>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="216">
@@ -5366,10 +5366,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C216" t="str">
-        <v>Actions tab: panels on top, cut pieces below</v>
+        <v>Panel location</v>
       </c>
       <c r="D216" t="str">
-        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
+        <v>Set where a panel order's panels sit (More ▸ Set Location); shown on the order, as a grid column and in the Stock Locations report's Panels view.</v>
       </c>
       <c r="E216" t="str">
         <v>Completed</v>
@@ -5378,7 +5378,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G216" t="str">
-        <v>CR-419</v>
+        <v>CR-410</v>
       </c>
     </row>
     <row r="217">
@@ -5389,10 +5389,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C217" t="str">
-        <v>Actions tab reads at a glance</v>
+        <v>Actions tab: panels on top, cut pieces below</v>
       </c>
       <c r="D217" t="str">
-        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
+        <v>One row per panel with its marks, its MDF board and a status; click a panel to see its cut pieces underneath with their own Load boxes. Pending counts amber, loaded ones say Loaded; no empty spanning cells.</v>
       </c>
       <c r="E217" t="str">
         <v>Completed</v>
@@ -5401,7 +5401,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G217" t="str">
-        <v>CR-415</v>
+        <v>CR-419</v>
       </c>
     </row>
     <row r="218">
@@ -5409,13 +5409,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C218" t="str">
-        <v>No long helper notes</v>
+        <v>Actions tab reads at a glance</v>
       </c>
       <c r="D218" t="str">
-        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
+        <v>Material cell = cut size (150x150) or MDF — the design sits behind the Line ⓘ; Status on one line; Vinyl / Pasted dropdowns visibly greyed until their gate is met, with the reason on hover.</v>
       </c>
       <c r="E218" t="str">
         <v>Completed</v>
@@ -5424,7 +5424,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G218" t="str">
-        <v>CR-416</v>
+        <v>CR-415</v>
       </c>
     </row>
     <row r="219">
@@ -5432,13 +5432,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="str">
-        <v>Production</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C219" t="str">
-        <v>Production toolbar: Table + Sheet</v>
+        <v>No long helper notes</v>
       </c>
       <c r="D219" t="str">
-        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
+        <v>Thirteen how-to paragraphs removed from under tables and cards; what blocks a row is said in its Status cell and tooltips. Standing rule: no multi-sentence instructions in the app.</v>
       </c>
       <c r="E219" t="str">
         <v>Completed</v>
@@ -5447,7 +5447,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G219" t="str">
-        <v>CR-417</v>
+        <v>CR-416</v>
       </c>
     </row>
     <row r="220">
@@ -5455,13 +5455,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="str">
-        <v>Foundation &amp; workspace</v>
+        <v>Production</v>
       </c>
       <c r="C220" t="str">
-        <v>Kanban hidden app-wide</v>
+        <v>Production toolbar: Table + Sheet</v>
       </c>
       <c r="D220" t="str">
-        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
+        <v>Two views only; Kanban, To Produce and Import hidden. Filter, search, Group, Fields, Edit, Start New Production and Bulk Record Production stay.</v>
       </c>
       <c r="E220" t="str">
         <v>Completed</v>
@@ -5470,7 +5470,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G220" t="str">
-        <v>CR-418</v>
+        <v>CR-417</v>
       </c>
     </row>
     <row r="221">
@@ -5481,10 +5481,10 @@
         <v>Foundation &amp; workspace</v>
       </c>
       <c r="C221" t="str">
-        <v>Notifications read / unread</v>
+        <v>Kanban hidden app-wide</v>
       </c>
       <c r="D221" t="str">
-        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
+        <v>Packing, Panel Orders, Sales Orders and Production show the Sheet only; the Default view setting is hidden with it.</v>
       </c>
       <c r="E221" t="str">
         <v>Completed</v>
@@ -5493,7 +5493,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G221" t="str">
-        <v>CR-419…421</v>
+        <v>CR-418</v>
       </c>
     </row>
     <row r="222">
@@ -5501,13 +5501,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="str">
-        <v>Sales Orders</v>
+        <v>Foundation &amp; workspace</v>
       </c>
       <c r="C222" t="str">
-        <v>Sales Order page without Panel Orders tab</v>
+        <v>Notifications read / unread</v>
       </c>
       <c r="D222" t="str">
-        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
+        <v>Bell rows stay bold until Mark all read; the marker survives new tabs. Sidebar logo centred; Settings sub-pages open with a small Back link above the title.</v>
       </c>
       <c r="E222" t="str">
         <v>Completed</v>
@@ -5516,7 +5516,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="G222" t="str">
-        <v>CR-422</v>
+        <v>CR-419…421</v>
       </c>
     </row>
     <row r="223">
@@ -5524,22 +5524,22 @@
         <v>222</v>
       </c>
       <c r="B223" t="str">
-        <v>Panel Craft</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C223" t="str">
-        <v>Readiness tab on every Panel / Sample order</v>
+        <v>Sales Order page without Panel Orders tab</v>
       </c>
       <c r="D223" t="str">
-        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
+        <v>Production, Palletization and Container Planning tabs only; Request Panels stays in the More menu.</v>
       </c>
       <c r="E223" t="str">
         <v>Completed</v>
       </c>
       <c r="F223" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G223" t="str">
-        <v>CR-404</v>
+        <v>CR-422</v>
       </c>
     </row>
     <row r="224">
@@ -5550,19 +5550,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C224" t="str">
-        <v>'Full size — 800x1600' placeholder on the form</v>
+        <v>Readiness tab on every Panel / Sample order</v>
       </c>
       <c r="D224" t="str">
-        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
+        <v>Per-order dashboard: ring of panels ready to load, next stage headline, Panels · Pieces · Ready · Pending tiles, one ring per stage (MDF · Vinyl · Pasted · Cut pieces · Weighed · Loaded) and a stage-cell table per panel — all read from the marks, booking, weight and loads already recorded. Sample orders show the one stage Supplied.</v>
       </c>
       <c r="E224" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F224" t="str">
-        <v/>
+        <v>2026-10-23</v>
       </c>
       <c r="G224" t="str">
-        <v>CR-289 follow-up</v>
+        <v>CR-404</v>
       </c>
     </row>
     <row r="225">
@@ -5573,19 +5573,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C225" t="str">
-        <v>Status change from within the Panel Orders form</v>
+        <v>'Full size — 800x1600' placeholder on the form</v>
       </c>
       <c r="D225" t="str">
-        <v>Change the stage while editing the order, not only on the order page.</v>
+        <v>The form half of the full-size default: keep lines without a cut piece size and show the design's size as the placeholder.</v>
       </c>
       <c r="E225" t="str">
-        <v>Future</v>
+        <v>In progress</v>
       </c>
       <c r="F225" t="str">
         <v/>
       </c>
       <c r="G225" t="str">
-        <v>Panel Craft list #3</v>
+        <v>CR-289 follow-up</v>
       </c>
     </row>
     <row r="226">
@@ -5596,10 +5596,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C226" t="str">
-        <v>Panel request from Quote / SO — refinements</v>
+        <v>Status change from within the Panel Orders form</v>
       </c>
       <c r="D226" t="str">
-        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
+        <v>Change the stage while editing the order, not only on the order page.</v>
       </c>
       <c r="E226" t="str">
         <v>Future</v>
@@ -5608,7 +5608,7 @@
         <v/>
       </c>
       <c r="G226" t="str">
-        <v>Panel Craft list #2</v>
+        <v>Panel Craft list #3</v>
       </c>
     </row>
     <row r="227">
@@ -5619,10 +5619,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C227" t="str">
-        <v>Panel auto-sequence</v>
+        <v>Panel request from Quote / SO — refinements</v>
       </c>
       <c r="D227" t="str">
-        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
+        <v>Follow-ups to the New Request flow. Scope to be confirmed.</v>
       </c>
       <c r="E227" t="str">
         <v>Future</v>
@@ -5631,7 +5631,7 @@
         <v/>
       </c>
       <c r="G227" t="str">
-        <v>Panel Craft list #4</v>
+        <v>Panel Craft list #2</v>
       </c>
     </row>
     <row r="228">
@@ -5642,10 +5642,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C228" t="str">
-        <v>Godown print — issue / request</v>
+        <v>Panel auto-sequence</v>
       </c>
       <c r="D228" t="str">
-        <v>A printed issue / request slip for the godown.</v>
+        <v>PANEL-NNN is already automatic; what 'sequence' should add is to be clarified.</v>
       </c>
       <c r="E228" t="str">
         <v>Future</v>
@@ -5654,7 +5654,7 @@
         <v/>
       </c>
       <c r="G228" t="str">
-        <v>Panel Craft list #5</v>
+        <v>Panel Craft list #4</v>
       </c>
     </row>
     <row r="229">
@@ -5665,10 +5665,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C229" t="str">
-        <v>Missing items to fulfil an order</v>
+        <v>Godown print — issue / request</v>
       </c>
       <c r="D229" t="str">
-        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
+        <v>A printed issue / request slip for the godown.</v>
       </c>
       <c r="E229" t="str">
         <v>Future</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="G229" t="str">
-        <v>Panel Craft list #6</v>
+        <v>Panel Craft list #5</v>
       </c>
     </row>
     <row r="230">
@@ -5688,10 +5688,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C230" t="str">
-        <v>Bill / expense</v>
+        <v>Missing items to fulfil an order</v>
       </c>
       <c r="D230" t="str">
-        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
+        <v>A view of what is missing per order (Pending Cut Piece + requirements exist; the extra needed is to be clarified).</v>
       </c>
       <c r="E230" t="str">
         <v>Future</v>
@@ -5700,7 +5700,7 @@
         <v/>
       </c>
       <c r="G230" t="str">
-        <v>Panel Craft list #12</v>
+        <v>Panel Craft list #6</v>
       </c>
     </row>
     <row r="231">
@@ -5708,22 +5708,22 @@
         <v>230</v>
       </c>
       <c r="B231" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C231" t="str">
-        <v>Item code for the catalog</v>
+        <v>Bill / expense</v>
       </c>
       <c r="D231" t="str">
-        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
+        <v>Record expenses or bills against panel work. New area, scope to be defined.</v>
       </c>
       <c r="E231" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F231" t="str">
-        <v>2026-10-27</v>
+        <v/>
       </c>
       <c r="G231" t="str">
-        <v>CR-473</v>
+        <v>Panel Craft list #12</v>
       </c>
     </row>
     <row r="232">
@@ -5731,22 +5731,22 @@
         <v>231</v>
       </c>
       <c r="B232" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C232" t="str">
-        <v>Panel Craft pricing</v>
+        <v>Item code for the catalog</v>
       </c>
       <c r="D232" t="str">
-        <v>Every panel is priced from three parts — Vinyl (vinyl size sqft × the panel's vinyl rate per sqft), MDF (board weight × the MDF rate per kg) and Cut pieces (each piece's sqft × the item's rate per sqft). Worked out when the order is saved and frozen on the order, each part editable; sample orders priced by piece size. Prices show on the panel order page and PDF, the sample order, the Orders list (Amount), the panel master's Pricing tab and every cut piece (sqft and price per piece).</v>
+        <v>Every item gets a short unique code such as LSN-800x1600-7K4 (initials of the design · size · three random characters that never repeat), assigned by the system. Shown on the item page, the Items grid, item pickers, the ⌘K search, Panel Craft ▸ Stock and panel pages; existing items are coded in one admin step.</v>
       </c>
       <c r="E232" t="str">
         <v>Completed</v>
       </c>
       <c r="F232" t="str">
-        <v>2026-10-31</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G232" t="str">
-        <v>CR-504</v>
+        <v>CR-473</v>
       </c>
     </row>
     <row r="233">
@@ -5757,10 +5757,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C233" t="str">
-        <v>Your own Panel Codes</v>
+        <v>Panel Craft pricing</v>
       </c>
       <c r="D233" t="str">
-        <v>Type the panel's code on New / Edit Panel (mandatory, saved in capitals, no duplicates) instead of an automatic PANEL-001 number; rename an old panel and every order, load and print shows the new code.</v>
+        <v>Every panel is priced from three parts — Vinyl (vinyl size sqft × the panel's vinyl rate per sqft), MDF (board weight × the MDF rate per kg) and Cut pieces (each piece's sqft × the item's rate per sqft). Worked out when the order is saved and frozen on the order, each part editable; sample orders priced by piece size. Prices show on the panel order page and PDF, the sample order, the Orders list (Amount), the panel master's Pricing tab and every cut piece (sqft and price per piece).</v>
       </c>
       <c r="E233" t="str">
         <v>Completed</v>
@@ -5769,7 +5769,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="G233" t="str">
-        <v>CR-506</v>
+        <v>CR-504</v>
       </c>
     </row>
     <row r="234">
@@ -5780,10 +5780,10 @@
         <v>Panel Craft</v>
       </c>
       <c r="C234" t="str">
-        <v>Bulk Update of rates</v>
+        <v>Your own Panel Codes</v>
       </c>
       <c r="D234" t="str">
-        <v>Filter the list, tick the rows, Bulk Update, pick the field, type the value — one save sets Rate / sqft on many Panel Items (new filter by size, finish, brand, category, rate, stock), Vinyl Rate on many panels, Rate/kg on MDF rows. The Item master's bulk edit works the same way, now with Rate / sqft.</v>
+        <v>Type the panel's code on New / Edit Panel (mandatory, saved in capitals, no duplicates) instead of an automatic PANEL-001 number; rename an old panel and every order, load and print shows the new code.</v>
       </c>
       <c r="E234" t="str">
         <v>Completed</v>
@@ -5792,7 +5792,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="G234" t="str">
-        <v>CR-505</v>
+        <v>CR-506</v>
       </c>
     </row>
     <row r="235">
@@ -5803,19 +5803,19 @@
         <v>Panel Craft</v>
       </c>
       <c r="C235" t="str">
-        <v>Panel Order PDF — one page per panel</v>
+        <v>Bulk Update of rates</v>
       </c>
       <c r="D235" t="str">
-        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
+        <v>Filter the list, tick the rows, Bulk Update, pick the field, type the value — one save sets Rate / sqft on many Panel Items (new filter by size, finish, brand, category, rate, stock), Vinyl Rate on many panels, Rate/kg on MDF rows. The Item master's bulk edit works the same way, now with Rate / sqft.</v>
       </c>
       <c r="E235" t="str">
         <v>Completed</v>
       </c>
       <c r="F235" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G235" t="str">
-        <v>CR-474</v>
+        <v>CR-505</v>
       </c>
     </row>
     <row r="236">
@@ -5823,13 +5823,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="str">
-        <v>Sales Orders</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C236" t="str">
-        <v>Sales Order without a Location field</v>
+        <v>Panel Order PDF — one page per panel</v>
       </c>
       <c r="D236" t="str">
-        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
+        <v>More ▸ Print order PDF on a panel order: a cover page with the order details and lines, then one page per panel with the showcase photo as large as the page allows, the panel's sizes and its cut pieces with totals for the ordered quantity.</v>
       </c>
       <c r="E236" t="str">
         <v>Completed</v>
@@ -5838,7 +5838,7 @@
         <v>2026-10-27</v>
       </c>
       <c r="G236" t="str">
-        <v>CR-468</v>
+        <v>CR-474</v>
       </c>
     </row>
     <row r="237">
@@ -5849,19 +5849,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C237" t="str">
-        <v>Box Brand mandatory</v>
+        <v>Sales Order without a Location field</v>
       </c>
       <c r="D237" t="str">
-        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
+        <v>The order form no longer asks for a Location; location is recorded where stock is written (production, cut stock, pallets).</v>
       </c>
       <c r="E237" t="str">
         <v>Completed</v>
       </c>
       <c r="F237" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-27</v>
       </c>
       <c r="G237" t="str">
-        <v>CR-483</v>
+        <v>CR-468</v>
       </c>
     </row>
     <row r="238">
@@ -5872,19 +5872,19 @@
         <v>Sales Orders</v>
       </c>
       <c r="C238" t="str">
-        <v>One line per item</v>
+        <v>Box Brand mandatory</v>
       </c>
       <c r="D238" t="str">
-        <v>Adding an item that is already on the quote or order shows a warning; on save the quantities merge into one line when the rate is the same (a different rate keeps two lines).</v>
+        <v>A Sales Order cannot be saved without a box brand; the customer's default still prefills it.</v>
       </c>
       <c r="E238" t="str">
         <v>Completed</v>
       </c>
       <c r="F238" t="str">
-        <v>2026-10-31</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G238" t="str">
-        <v>CR-507</v>
+        <v>CR-483</v>
       </c>
     </row>
     <row r="239">
@@ -5895,10 +5895,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C239" t="str">
-        <v>Box Brand per line</v>
+        <v>One line per item</v>
       </c>
       <c r="D239" t="str">
-        <v>Each Sales Order line has its own Box Brand (prefilled from the customer, the quote or the line above) instead of one for the whole order; shown per line on the order page and on the Production list, sheet and production page.</v>
+        <v>Adding an item that is already on the quote or order shows a warning; on save the quantities merge into one line when the rate is the same (a different rate keeps two lines).</v>
       </c>
       <c r="E239" t="str">
         <v>Completed</v>
@@ -5907,7 +5907,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="G239" t="str">
-        <v>CR-508</v>
+        <v>CR-507</v>
       </c>
     </row>
     <row r="240">
@@ -5918,10 +5918,10 @@
         <v>Sales Orders</v>
       </c>
       <c r="C240" t="str">
-        <v>Allocate Stock by Box Brand</v>
+        <v>Box Brand per line</v>
       </c>
       <c r="D240" t="str">
-        <v>Allocate Stock offers only batches packed in the line's Box Brand and says how many boxes in other brands were left out.</v>
+        <v>Each Sales Order line has its own Box Brand (prefilled from the customer, the quote or the line above) instead of one for the whole order; shown per line on the order page and on the Production list, sheet and production page.</v>
       </c>
       <c r="E240" t="str">
         <v>Completed</v>
@@ -5930,7 +5930,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="G240" t="str">
-        <v>CR-509</v>
+        <v>CR-508</v>
       </c>
     </row>
     <row r="241">
@@ -5938,22 +5938,22 @@
         <v>240</v>
       </c>
       <c r="B241" t="str">
-        <v>Masters (Inventory)</v>
+        <v>Sales Orders</v>
       </c>
       <c r="C241" t="str">
-        <v>Pallet form without Box Weight</v>
+        <v>Allocate Stock by Box Brand</v>
       </c>
       <c r="D241" t="str">
-        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
+        <v>Allocate Stock offers only batches packed in the line's Box Brand and says how many boxes in other brands were left out.</v>
       </c>
       <c r="E241" t="str">
         <v>Completed</v>
       </c>
       <c r="F241" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-31</v>
       </c>
       <c r="G241" t="str">
-        <v>CR-471</v>
+        <v>CR-509</v>
       </c>
     </row>
     <row r="242">
@@ -5961,22 +5961,22 @@
         <v>241</v>
       </c>
       <c r="B242" t="str">
-        <v>Panel Craft</v>
+        <v>Masters (Inventory)</v>
       </c>
       <c r="C242" t="str">
-        <v>Boffo / Bonza company separation</v>
+        <v>Pallet form without Box Weight</v>
       </c>
       <c r="D242" t="str">
-        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
+        <v>New / Edit Pallet no longer asks for the box weight; the Size's weight is used.</v>
       </c>
       <c r="E242" t="str">
-        <v>Future</v>
+        <v>Completed</v>
       </c>
       <c r="F242" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
       <c r="G242" t="str">
-        <v>ON-HOLD #1</v>
+        <v>CR-471</v>
       </c>
     </row>
     <row r="243">
@@ -5984,22 +5984,22 @@
         <v>242</v>
       </c>
       <c r="B243" t="str">
-        <v>Documentation &amp; process</v>
+        <v>Panel Craft</v>
       </c>
       <c r="C243" t="str">
-        <v>System reference and change-request register</v>
+        <v>Boffo / Bonza company separation</v>
       </c>
       <c r="D243" t="str">
-        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
+        <v>Two companies in one system — login-time company selection; the Export module mainly for Bonza. On hold at the user's request (docs/ON-HOLD.md #1).</v>
       </c>
       <c r="E243" t="str">
-        <v>Completed</v>
+        <v>Future</v>
       </c>
       <c r="F243" t="str">
-        <v>Phase 1 (by 01-Oct-2026)</v>
+        <v/>
       </c>
       <c r="G243" t="str">
-        <v/>
+        <v>ON-HOLD #1</v>
       </c>
     </row>
     <row r="244">
@@ -6010,10 +6010,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C244" t="str">
-        <v>Change log, user flow, user manual</v>
+        <v>System reference and change-request register</v>
       </c>
       <c r="D244" t="str">
-        <v>Dated change log, user flow guide, user manual, formula reference.</v>
+        <v>The system as built, kept true with every change; every request numbered with Change · Where · Why · Apply to · Like · Done when, status, date and proof.</v>
       </c>
       <c r="E244" t="str">
         <v>Completed</v>
@@ -6033,10 +6033,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C245" t="str">
-        <v>Seed and teardown scripts</v>
+        <v>Change log, user flow, user manual</v>
       </c>
       <c r="D245" t="str">
-        <v>Create a full customer-to-dispatch test flow and remove it.</v>
+        <v>Dated change log, user flow guide, user manual, formula reference.</v>
       </c>
       <c r="E245" t="str">
         <v>Completed</v>
@@ -6056,19 +6056,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C246" t="str">
-        <v>Data Flow reference</v>
+        <v>Seed and teardown scripts</v>
       </c>
       <c r="D246" t="str">
-        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
+        <v>Create a full customer-to-dispatch test flow and remove it.</v>
       </c>
       <c r="E246" t="str">
         <v>Completed</v>
       </c>
       <c r="F246" t="str">
-        <v>2026-10-03</v>
+        <v>Phase 1 (by 01-Oct-2026)</v>
       </c>
       <c r="G246" t="str">
-        <v>CR-272</v>
+        <v/>
       </c>
     </row>
     <row r="247">
@@ -6079,10 +6079,10 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C247" t="str">
-        <v>Phase 2 inventory</v>
+        <v>Data Flow reference</v>
       </c>
       <c r="D247" t="str">
-        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
+        <v>For every record type, every screen and server action that can create, change, delete or re-status it, and the one place each rule lives.</v>
       </c>
       <c r="E247" t="str">
         <v>Completed</v>
@@ -6091,7 +6091,7 @@
         <v>2026-10-03</v>
       </c>
       <c r="G247" t="str">
-        <v/>
+        <v>CR-272</v>
       </c>
     </row>
     <row r="248">
@@ -6102,19 +6102,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C248" t="str">
-        <v>Locations guide</v>
+        <v>Phase 2 inventory</v>
       </c>
       <c r="D248" t="str">
-        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
+        <v>Running plain-language inventory of Phase 2, updated as each request ships.</v>
       </c>
       <c r="E248" t="str">
         <v>Completed</v>
       </c>
       <c r="F248" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-03</v>
       </c>
       <c r="G248" t="str">
-        <v>CR-411…413</v>
+        <v/>
       </c>
     </row>
     <row r="249">
@@ -6125,19 +6125,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C249" t="str">
-        <v>Deliverables list (this workbook)</v>
+        <v>Locations guide</v>
       </c>
       <c r="D249" t="str">
-        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
+        <v>User-manual chapter: what to set up before using locations (warehouses, primary, bays, purposes), every screen where a location is picked or shown for boxes, pallets and panels, and the two rules for the floor.</v>
       </c>
       <c r="E249" t="str">
         <v>Completed</v>
       </c>
       <c r="F249" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-24</v>
       </c>
       <c r="G249" t="str">
-        <v/>
+        <v>CR-411…413</v>
       </c>
     </row>
     <row r="250">
@@ -6148,19 +6148,19 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C250" t="str">
-        <v>Demo / test environment</v>
+        <v>Deliverables list (this workbook)</v>
       </c>
       <c r="D250" t="str">
-        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+        <v>Feature-wise list of Completed / In progress / Future deliverables, maintained in Excel from here on.</v>
       </c>
       <c r="E250" t="str">
         <v>Completed</v>
       </c>
       <c r="F250" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-22</v>
       </c>
       <c r="G250" t="str">
-        <v>CR-441</v>
+        <v/>
       </c>
     </row>
     <row r="251">
@@ -6171,25 +6171,48 @@
         <v>Documentation &amp; process</v>
       </c>
       <c r="C251" t="str">
+        <v>Demo / test environment</v>
+      </c>
+      <c r="D251" t="str">
+        <v>A second, fully separate copy of the system (own database with the same 60 tables, own server functions, public web address) filled with dummy data for demos and testing; live data is never touched. Runbook: docs/DEMO-ENVIRONMENT.md.</v>
+      </c>
+      <c r="E251" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F251" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="G251" t="str">
+        <v>CR-441</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Documentation &amp; process</v>
+      </c>
+      <c r="C252" t="str">
         <v>Demo carries no BOFFO branding</v>
       </c>
-      <c r="D251" t="str">
+      <c r="D252" t="str">
         <v>The demo shows a neutral "Demo" company everywhere (sidebar, tab title, PDFs, sign-in), no BOFFO logo, and a plain pulsing "Processing…" / "Uploading…" text while it works instead of the BOFFO wordmark; the live system is unchanged.</v>
       </c>
-      <c r="E251" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="F251" t="str">
+      <c r="E252" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F252" t="str">
         <v>2026-10-26</v>
       </c>
-      <c r="G251" t="str">
+      <c r="G252" t="str">
         <v>CR-454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G251"/>
+  <autoFilter ref="A1:G252"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G251"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G252"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/BOFFO-DELIVERABLES.xlsx
+++ b/docs/BOFFO-DELIVERABLES.xlsx
@@ -3023,7 +3023,7 @@
         <v>In Palletization columns</v>
       </c>
       <c r="D114" t="str">
-        <v>In Palletization shows Boxes (on the row), Boxes per Pallet, Pallets (whole pallets those boxes fill) and Prepared; the Pending and Loose columns are gone from that page.</v>
+        <v>In Palletization shows Boxes (on the row), Boxes per Pallet, Pallets (whole pallets those boxes fill) and Ready Boxes (already palletized); the Pending and Loose columns are gone from that page.</v>
       </c>
       <c r="E114" t="str">
         <v>Completed</v>
